--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU296"/>
+  <dimension ref="A1:AU298"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G21">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G72">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G86">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G153">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G158">
@@ -26179,27 +26179,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G159">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-09-06 12:15:00</t>
+          <t>2026-09-06 12:00:00</t>
         </is>
       </c>
     </row>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G161">
@@ -26668,27 +26668,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G162">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-09-06 12:30:00</t>
+          <t>2026-09-06 12:15:00</t>
         </is>
       </c>
     </row>
@@ -26836,22 +26836,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,22 +27162,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,22 +27325,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G168">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G170">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G173">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G174">
@@ -28787,27 +28787,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G175">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-09-06 12:45:00</t>
+          <t>2026-09-06 12:30:00</t>
         </is>
       </c>
     </row>
@@ -28955,22 +28955,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G176">
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G177">
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-09-06 13:00:00</t>
+          <t>2026-09-06 12:45:00</t>
         </is>
       </c>
     </row>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G182">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G218">
@@ -35959,12 +35959,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G219">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-09-06 13:10:00</t>
+          <t>2026-09-06 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-09-06 13:15:00</t>
+          <t>2026-09-06 13:10:00</t>
         </is>
       </c>
     </row>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G222">
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:00</t>
+          <t>2026-09-06 13:15:00</t>
         </is>
       </c>
     </row>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G229">
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-09-06 14:00:00</t>
+          <t>2026-09-06 13:30:00</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G231">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G237">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G242">
@@ -39871,27 +39871,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-06 14:15:00</t>
+          <t>2026-09-06 14:00:00</t>
         </is>
       </c>
     </row>
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G245">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G246">
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-09-06 14:30:00</t>
+          <t>2026-09-06 14:15:00</t>
         </is>
       </c>
     </row>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G248">
@@ -40849,27 +40849,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G249">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-09-06 14:45:00</t>
+          <t>2026-09-06 14:30:00</t>
         </is>
       </c>
     </row>
@@ -41017,22 +41017,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G250">
@@ -41175,27 +41175,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O251">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P251">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-09-06 15:00:00</t>
+          <t>2026-09-06 14:45:00</t>
         </is>
       </c>
     </row>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="O252">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P252">
-        <v>2.87</v>
+        <v>5.05</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41506,22 +41506,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41669,22 +41669,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G254">
@@ -41827,27 +41827,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-09-06 15:15:00</t>
+          <t>2026-09-06 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41990,12 +41990,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G256">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-09-06 15:15:00</t>
+          <t>2026-09-06 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G257">
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-06 15:30:00</t>
+          <t>2026-09-06 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42479,27 +42479,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O259">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P259">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-09-06 15:30:00</t>
+          <t>2026-09-06 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42647,22 +42647,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O260">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P260">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O261">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P261">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43136,22 +43136,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-09-06 15:45:00</t>
+          <t>2026-09-06 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43457,12 +43457,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-09-06 15:45:00</t>
+          <t>2026-09-06 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-06 16:00:00</t>
+          <t>2026-09-06 15:45:00</t>
         </is>
       </c>
     </row>
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-06 16:00:00</t>
+          <t>2026-09-06 15:45:00</t>
         </is>
       </c>
     </row>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G268">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O271">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P271">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G279">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G280">
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-06 16:30:00</t>
+          <t>2026-09-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46228,27 +46228,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-06 17:00:00</t>
+          <t>2026-09-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46391,27 +46391,27 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-06 17:00:00</t>
+          <t>2026-09-06 16:30:00</t>
         </is>
       </c>
     </row>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G286">
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-06 18:15:00</t>
+          <t>2026-09-06 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-06 18:30:00</t>
+          <t>2026-09-06 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-06 18:30:00</t>
+          <t>2026-09-06 18:15:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-09-06 19:00:00</t>
+          <t>2026-09-06 18:30:00</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G291">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-09-06 19:30:00</t>
+          <t>2026-09-06 18:30:00</t>
         </is>
       </c>
     </row>
@@ -47858,12 +47858,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G292">
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-09-06 19:30:00</t>
+          <t>2026-09-06 19:00:00</t>
         </is>
       </c>
     </row>
@@ -48021,12 +48021,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00:00</t>
+          <t>2026-09-06 19:30:00</t>
         </is>
       </c>
     </row>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-09-06 21:00:00</t>
+          <t>2026-09-06 19:30:00</t>
         </is>
       </c>
     </row>
@@ -48347,27 +48347,27 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-09-06 21:00:00</t>
+          <t>2026-09-06 20:00:00</t>
         </is>
       </c>
     </row>
@@ -48510,156 +48510,482 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>0</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>0</v>
+      </c>
+      <c r="L296">
+        <v>0</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N296">
+        <v>0</v>
+      </c>
+      <c r="O296">
+        <v>0</v>
+      </c>
+      <c r="P296">
+        <v>0</v>
+      </c>
+      <c r="Q296">
+        <v>0</v>
+      </c>
+      <c r="R296">
+        <v>0</v>
+      </c>
+      <c r="S296">
+        <v>0</v>
+      </c>
+      <c r="T296">
+        <v>0</v>
+      </c>
+      <c r="U296">
+        <v>0</v>
+      </c>
+      <c r="V296">
+        <v>0</v>
+      </c>
+      <c r="W296">
+        <v>0</v>
+      </c>
+      <c r="X296">
+        <v>0</v>
+      </c>
+      <c r="Y296">
+        <v>0</v>
+      </c>
+      <c r="Z296">
+        <v>0</v>
+      </c>
+      <c r="AA296">
+        <v>0</v>
+      </c>
+      <c r="AB296">
+        <v>0</v>
+      </c>
+      <c r="AC296">
+        <v>0</v>
+      </c>
+      <c r="AD296">
+        <v>0</v>
+      </c>
+      <c r="AE296">
+        <v>0</v>
+      </c>
+      <c r="AF296">
+        <v>0</v>
+      </c>
+      <c r="AG296">
+        <v>0</v>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ296">
+        <v>0</v>
+      </c>
+      <c r="AK296">
+        <v>0</v>
+      </c>
+      <c r="AL296">
+        <v>0</v>
+      </c>
+      <c r="AM296">
+        <v>-1</v>
+      </c>
+      <c r="AN296">
+        <v>-1</v>
+      </c>
+      <c r="AO296">
+        <v>-1</v>
+      </c>
+      <c r="AP296">
+        <v>-1</v>
+      </c>
+      <c r="AQ296">
+        <v>0</v>
+      </c>
+      <c r="AR296">
+        <v>0</v>
+      </c>
+      <c r="AS296">
+        <v>0</v>
+      </c>
+      <c r="AT296">
+        <v>0</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>2026-09-06 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Aresimi</t>
+        </is>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>0</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>0</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N297">
+        <v>0</v>
+      </c>
+      <c r="O297">
+        <v>0</v>
+      </c>
+      <c r="P297">
+        <v>0</v>
+      </c>
+      <c r="Q297">
+        <v>0</v>
+      </c>
+      <c r="R297">
+        <v>0</v>
+      </c>
+      <c r="S297">
+        <v>0</v>
+      </c>
+      <c r="T297">
+        <v>0</v>
+      </c>
+      <c r="U297">
+        <v>0</v>
+      </c>
+      <c r="V297">
+        <v>0</v>
+      </c>
+      <c r="W297">
+        <v>0</v>
+      </c>
+      <c r="X297">
+        <v>0</v>
+      </c>
+      <c r="Y297">
+        <v>0</v>
+      </c>
+      <c r="Z297">
+        <v>0</v>
+      </c>
+      <c r="AA297">
+        <v>0</v>
+      </c>
+      <c r="AB297">
+        <v>0</v>
+      </c>
+      <c r="AC297">
+        <v>0</v>
+      </c>
+      <c r="AD297">
+        <v>0</v>
+      </c>
+      <c r="AE297">
+        <v>0</v>
+      </c>
+      <c r="AF297">
+        <v>0</v>
+      </c>
+      <c r="AG297">
+        <v>0</v>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ297">
+        <v>0</v>
+      </c>
+      <c r="AK297">
+        <v>0</v>
+      </c>
+      <c r="AL297">
+        <v>0</v>
+      </c>
+      <c r="AM297">
+        <v>-1</v>
+      </c>
+      <c r="AN297">
+        <v>-1</v>
+      </c>
+      <c r="AO297">
+        <v>-1</v>
+      </c>
+      <c r="AP297">
+        <v>-1</v>
+      </c>
+      <c r="AQ297">
+        <v>0</v>
+      </c>
+      <c r="AR297">
+        <v>0</v>
+      </c>
+      <c r="AS297">
+        <v>0</v>
+      </c>
+      <c r="AT297">
+        <v>0</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>2026-09-06 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="E298" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
+      <c r="F298" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="G296">
-        <v>0</v>
-      </c>
-      <c r="H296">
-        <v>0</v>
-      </c>
-      <c r="I296">
-        <v>0</v>
-      </c>
-      <c r="J296">
-        <v>0</v>
-      </c>
-      <c r="K296">
-        <v>0</v>
-      </c>
-      <c r="L296">
-        <v>0</v>
-      </c>
-      <c r="M296" t="inlineStr">
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>0</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+      <c r="M298" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N296">
-        <v>0</v>
-      </c>
-      <c r="O296">
-        <v>0</v>
-      </c>
-      <c r="P296">
-        <v>0</v>
-      </c>
-      <c r="Q296">
-        <v>0</v>
-      </c>
-      <c r="R296">
-        <v>0</v>
-      </c>
-      <c r="S296">
-        <v>0</v>
-      </c>
-      <c r="T296">
-        <v>0</v>
-      </c>
-      <c r="U296">
-        <v>0</v>
-      </c>
-      <c r="V296">
-        <v>0</v>
-      </c>
-      <c r="W296">
-        <v>0</v>
-      </c>
-      <c r="X296">
-        <v>0</v>
-      </c>
-      <c r="Y296">
-        <v>0</v>
-      </c>
-      <c r="Z296">
-        <v>0</v>
-      </c>
-      <c r="AA296">
-        <v>0</v>
-      </c>
-      <c r="AB296">
-        <v>0</v>
-      </c>
-      <c r="AC296">
-        <v>0</v>
-      </c>
-      <c r="AD296">
-        <v>0</v>
-      </c>
-      <c r="AE296">
-        <v>0</v>
-      </c>
-      <c r="AF296">
-        <v>0</v>
-      </c>
-      <c r="AG296">
-        <v>0</v>
-      </c>
-      <c r="AH296" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI296" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ296">
-        <v>0</v>
-      </c>
-      <c r="AK296">
-        <v>0</v>
-      </c>
-      <c r="AL296">
-        <v>0</v>
-      </c>
-      <c r="AM296">
-        <v>-1</v>
-      </c>
-      <c r="AN296">
-        <v>-1</v>
-      </c>
-      <c r="AO296">
-        <v>-1</v>
-      </c>
-      <c r="AP296">
-        <v>-1</v>
-      </c>
-      <c r="AQ296">
-        <v>0</v>
-      </c>
-      <c r="AR296">
-        <v>0</v>
-      </c>
-      <c r="AS296">
-        <v>0</v>
-      </c>
-      <c r="AT296">
-        <v>0</v>
-      </c>
-      <c r="AU296" t="inlineStr">
+      <c r="N298">
+        <v>0</v>
+      </c>
+      <c r="O298">
+        <v>0</v>
+      </c>
+      <c r="P298">
+        <v>0</v>
+      </c>
+      <c r="Q298">
+        <v>0</v>
+      </c>
+      <c r="R298">
+        <v>0</v>
+      </c>
+      <c r="S298">
+        <v>0</v>
+      </c>
+      <c r="T298">
+        <v>0</v>
+      </c>
+      <c r="U298">
+        <v>0</v>
+      </c>
+      <c r="V298">
+        <v>0</v>
+      </c>
+      <c r="W298">
+        <v>0</v>
+      </c>
+      <c r="X298">
+        <v>0</v>
+      </c>
+      <c r="Y298">
+        <v>0</v>
+      </c>
+      <c r="Z298">
+        <v>0</v>
+      </c>
+      <c r="AA298">
+        <v>0</v>
+      </c>
+      <c r="AB298">
+        <v>0</v>
+      </c>
+      <c r="AC298">
+        <v>0</v>
+      </c>
+      <c r="AD298">
+        <v>0</v>
+      </c>
+      <c r="AE298">
+        <v>0</v>
+      </c>
+      <c r="AF298">
+        <v>0</v>
+      </c>
+      <c r="AG298">
+        <v>0</v>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ298">
+        <v>0</v>
+      </c>
+      <c r="AK298">
+        <v>0</v>
+      </c>
+      <c r="AL298">
+        <v>0</v>
+      </c>
+      <c r="AM298">
+        <v>-1</v>
+      </c>
+      <c r="AN298">
+        <v>-1</v>
+      </c>
+      <c r="AO298">
+        <v>-1</v>
+      </c>
+      <c r="AP298">
+        <v>-1</v>
+      </c>
+      <c r="AQ298">
+        <v>0</v>
+      </c>
+      <c r="AR298">
+        <v>0</v>
+      </c>
+      <c r="AS298">
+        <v>0</v>
+      </c>
+      <c r="AT298">
+        <v>0</v>
+      </c>
+      <c r="AU298" t="inlineStr">
         <is>
           <t>2026-09-06 22:00:00</t>
         </is>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G30">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G84">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G214">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G282">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G21">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G30">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G35">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G56">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G222">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G9">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G35">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G144">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G183">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G186">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G194">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G200">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G211">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G215">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G222">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G270">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G281">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G10">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G144">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G215">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G282">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G51">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G278">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G279">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G34">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G53">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G129">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G151">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="G194">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G217">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G233">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G34">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G226">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G188">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G146">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G151">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G226">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G295">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G202">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N209">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G285">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G286">

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU314"/>
+  <dimension ref="A1:AU316"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G58">
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-06 08:30:00</t>
+          <t>2026-09-06 08:00:00</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G66">
@@ -11183,27 +11183,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-06 08:35:00</t>
+          <t>2026-09-06 08:30:00</t>
         </is>
       </c>
     </row>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G68">
@@ -11509,27 +11509,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-09-06 09:00:00</t>
+          <t>2026-09-06 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G80">
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-06 09:15:00</t>
+          <t>2026-09-06 09:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-09-06 09:30:00</t>
+          <t>2026-09-06 09:15:00</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G85">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-06 09:45:00</t>
+          <t>2026-09-06 09:30:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G87">
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-09-06 10:00:00</t>
+          <t>2026-09-06 09:45:00</t>
         </is>
       </c>
     </row>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G111">
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-06 10:15:00</t>
+          <t>2026-09-06 10:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-06 10:30:00</t>
+          <t>2026-09-06 10:15:00</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G116">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-06 10:40:00</t>
+          <t>2026-09-06 10:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-06 10:45:00</t>
+          <t>2026-09-06 10:40:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-06 11:00:00</t>
+          <t>2026-09-06 10:45:00</t>
         </is>
       </c>
     </row>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G136">
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-09-06 11:15:00</t>
+          <t>2026-09-06 11:00:00</t>
         </is>
       </c>
     </row>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G138">
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G139">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-09-06 11:30:00</t>
+          <t>2026-09-06 11:15:00</t>
         </is>
       </c>
     </row>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,22 +23576,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G147">
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-09-06 11:45:00</t>
+          <t>2026-09-06 11:30:00</t>
         </is>
       </c>
     </row>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G153">
@@ -25364,12 +25364,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Al Musannah</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G154">
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>2026-09-06 11:55:00</t>
+          <t>2026-09-06 11:45:00</t>
         </is>
       </c>
     </row>
@@ -25527,12 +25527,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Al Musannah</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G155">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-09-06 12:00:00</t>
+          <t>2026-09-06 11:55:00</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G156">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,22 +27488,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G167">
@@ -27646,27 +27646,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G168">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-09-06 12:15:00</t>
+          <t>2026-09-06 12:00:00</t>
         </is>
       </c>
     </row>
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G170">
@@ -28135,27 +28135,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-09-06 12:30:00</t>
+          <t>2026-09-06 12:15:00</t>
         </is>
       </c>
     </row>
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G173">
@@ -28629,22 +28629,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G183">
@@ -30254,27 +30254,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G184">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-09-06 12:45:00</t>
+          <t>2026-09-06 12:30:00</t>
         </is>
       </c>
     </row>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G185">
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G186">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-09-06 13:00:00</t>
+          <t>2026-09-06 12:45:00</t>
         </is>
       </c>
     </row>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G209">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G210">
@@ -34535,7 +34535,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G230">
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-09-06 13:10:00</t>
+          <t>2026-09-06 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-09-06 13:15:00</t>
+          <t>2026-09-06 13:10:00</t>
         </is>
       </c>
     </row>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G234">
@@ -38567,12 +38567,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:00</t>
+          <t>2026-09-06 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G238">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G242">
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-06 14:00:00</t>
+          <t>2026-09-06 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G244">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G252">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G257">
@@ -42316,27 +42316,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-06 14:15:00</t>
+          <t>2026-09-06 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42484,22 +42484,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G260">
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-06 14:30:00</t>
+          <t>2026-09-06 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G264">
@@ -43457,27 +43457,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-09-06 14:45:00</t>
+          <t>2026-09-06 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43625,22 +43625,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O267">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P267">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-06 15:00:00</t>
+          <t>2026-09-06 14:45:00</t>
         </is>
       </c>
     </row>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="O268">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P268">
-        <v>2.87</v>
+        <v>5.05</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44114,22 +44114,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,22 +44440,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G272">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G273">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-06 15:15:00</t>
+          <t>2026-09-06 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-06 15:15:00</t>
+          <t>2026-09-06 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G275">
@@ -45250,12 +45250,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G276">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-09-06 15:30:00</t>
+          <t>2026-09-06 15:15:00</t>
         </is>
       </c>
     </row>
@@ -45413,27 +45413,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O277">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P277">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-09-06 15:30:00</t>
+          <t>2026-09-06 15:15:00</t>
         </is>
       </c>
     </row>
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O278">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P278">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O279">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P279">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45907,22 +45907,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46070,22 +46070,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-06 15:45:00</t>
+          <t>2026-09-06 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G283">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-06 15:45:00</t>
+          <t>2026-09-06 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46554,27 +46554,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-09-06 16:00:00</t>
+          <t>2026-09-06 15:45:00</t>
         </is>
       </c>
     </row>
@@ -46717,27 +46717,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-06 16:00:00</t>
+          <t>2026-09-06 15:45:00</t>
         </is>
       </c>
     </row>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,22 +47211,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G288">
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O289">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P289">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47537,22 +47537,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O290">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P290">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G295">
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G296">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G298">
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-06 16:30:00</t>
+          <t>2026-09-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,27 +49162,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G300">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-09-06 17:00:00</t>
+          <t>2026-09-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O301">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P301">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-06 17:00:00</t>
+          <t>2026-09-06 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G304">
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-09-06 18:15:00</t>
+          <t>2026-09-06 17:00:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-09-06 18:30:00</t>
+          <t>2026-09-06 17:00:00</t>
         </is>
       </c>
     </row>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G307">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-09-06 18:30:00</t>
+          <t>2026-09-06 18:15:00</t>
         </is>
       </c>
     </row>
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G308">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-09-06 19:00:00</t>
+          <t>2026-09-06 18:30:00</t>
         </is>
       </c>
     </row>
@@ -50629,12 +50629,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G309">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-09-06 19:30:00</t>
+          <t>2026-09-06 18:30:00</t>
         </is>
       </c>
     </row>
@@ -50792,12 +50792,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G310">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-09-06 19:30:00</t>
+          <t>2026-09-06 19:00:00</t>
         </is>
       </c>
     </row>
@@ -50955,12 +50955,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G311">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00:00</t>
+          <t>2026-09-06 19:30:00</t>
         </is>
       </c>
     </row>
@@ -51118,12 +51118,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-09-06 21:00:00</t>
+          <t>2026-09-06 19:30:00</t>
         </is>
       </c>
     </row>
@@ -51281,27 +51281,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G313">
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-09-06 21:00:00</t>
+          <t>2026-09-06 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51444,156 +51444,482 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G314">
+        <v>0</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>0</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N314">
+        <v>0</v>
+      </c>
+      <c r="O314">
+        <v>0</v>
+      </c>
+      <c r="P314">
+        <v>0</v>
+      </c>
+      <c r="Q314">
+        <v>0</v>
+      </c>
+      <c r="R314">
+        <v>0</v>
+      </c>
+      <c r="S314">
+        <v>0</v>
+      </c>
+      <c r="T314">
+        <v>0</v>
+      </c>
+      <c r="U314">
+        <v>0</v>
+      </c>
+      <c r="V314">
+        <v>0</v>
+      </c>
+      <c r="W314">
+        <v>0</v>
+      </c>
+      <c r="X314">
+        <v>0</v>
+      </c>
+      <c r="Y314">
+        <v>0</v>
+      </c>
+      <c r="Z314">
+        <v>0</v>
+      </c>
+      <c r="AA314">
+        <v>0</v>
+      </c>
+      <c r="AB314">
+        <v>0</v>
+      </c>
+      <c r="AC314">
+        <v>0</v>
+      </c>
+      <c r="AD314">
+        <v>0</v>
+      </c>
+      <c r="AE314">
+        <v>0</v>
+      </c>
+      <c r="AF314">
+        <v>0</v>
+      </c>
+      <c r="AG314">
+        <v>0</v>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ314">
+        <v>0</v>
+      </c>
+      <c r="AK314">
+        <v>0</v>
+      </c>
+      <c r="AL314">
+        <v>0</v>
+      </c>
+      <c r="AM314">
+        <v>-1</v>
+      </c>
+      <c r="AN314">
+        <v>-1</v>
+      </c>
+      <c r="AO314">
+        <v>-1</v>
+      </c>
+      <c r="AP314">
+        <v>-1</v>
+      </c>
+      <c r="AQ314">
+        <v>0</v>
+      </c>
+      <c r="AR314">
+        <v>0</v>
+      </c>
+      <c r="AS314">
+        <v>0</v>
+      </c>
+      <c r="AT314">
+        <v>0</v>
+      </c>
+      <c r="AU314" t="inlineStr">
+        <is>
+          <t>2026-09-06 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Aresimi</t>
+        </is>
+      </c>
+      <c r="G315">
+        <v>0</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
+      <c r="L315">
+        <v>0</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N315">
+        <v>0</v>
+      </c>
+      <c r="O315">
+        <v>0</v>
+      </c>
+      <c r="P315">
+        <v>0</v>
+      </c>
+      <c r="Q315">
+        <v>0</v>
+      </c>
+      <c r="R315">
+        <v>0</v>
+      </c>
+      <c r="S315">
+        <v>0</v>
+      </c>
+      <c r="T315">
+        <v>0</v>
+      </c>
+      <c r="U315">
+        <v>0</v>
+      </c>
+      <c r="V315">
+        <v>0</v>
+      </c>
+      <c r="W315">
+        <v>0</v>
+      </c>
+      <c r="X315">
+        <v>0</v>
+      </c>
+      <c r="Y315">
+        <v>0</v>
+      </c>
+      <c r="Z315">
+        <v>0</v>
+      </c>
+      <c r="AA315">
+        <v>0</v>
+      </c>
+      <c r="AB315">
+        <v>0</v>
+      </c>
+      <c r="AC315">
+        <v>0</v>
+      </c>
+      <c r="AD315">
+        <v>0</v>
+      </c>
+      <c r="AE315">
+        <v>0</v>
+      </c>
+      <c r="AF315">
+        <v>0</v>
+      </c>
+      <c r="AG315">
+        <v>0</v>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ315">
+        <v>0</v>
+      </c>
+      <c r="AK315">
+        <v>0</v>
+      </c>
+      <c r="AL315">
+        <v>0</v>
+      </c>
+      <c r="AM315">
+        <v>-1</v>
+      </c>
+      <c r="AN315">
+        <v>-1</v>
+      </c>
+      <c r="AO315">
+        <v>-1</v>
+      </c>
+      <c r="AP315">
+        <v>-1</v>
+      </c>
+      <c r="AQ315">
+        <v>0</v>
+      </c>
+      <c r="AR315">
+        <v>0</v>
+      </c>
+      <c r="AS315">
+        <v>0</v>
+      </c>
+      <c r="AT315">
+        <v>0</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>2026-09-06 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
+      <c r="D316" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
+      <c r="E316" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="G314">
-        <v>0</v>
-      </c>
-      <c r="H314">
-        <v>0</v>
-      </c>
-      <c r="I314">
-        <v>0</v>
-      </c>
-      <c r="J314">
-        <v>0</v>
-      </c>
-      <c r="K314">
-        <v>0</v>
-      </c>
-      <c r="L314">
-        <v>0</v>
-      </c>
-      <c r="M314" t="inlineStr">
+      <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>0</v>
+      </c>
+      <c r="M316" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N314">
-        <v>0</v>
-      </c>
-      <c r="O314">
-        <v>0</v>
-      </c>
-      <c r="P314">
-        <v>0</v>
-      </c>
-      <c r="Q314">
-        <v>0</v>
-      </c>
-      <c r="R314">
-        <v>0</v>
-      </c>
-      <c r="S314">
-        <v>0</v>
-      </c>
-      <c r="T314">
-        <v>0</v>
-      </c>
-      <c r="U314">
-        <v>0</v>
-      </c>
-      <c r="V314">
-        <v>0</v>
-      </c>
-      <c r="W314">
-        <v>0</v>
-      </c>
-      <c r="X314">
-        <v>0</v>
-      </c>
-      <c r="Y314">
-        <v>0</v>
-      </c>
-      <c r="Z314">
-        <v>0</v>
-      </c>
-      <c r="AA314">
-        <v>0</v>
-      </c>
-      <c r="AB314">
-        <v>0</v>
-      </c>
-      <c r="AC314">
-        <v>0</v>
-      </c>
-      <c r="AD314">
-        <v>0</v>
-      </c>
-      <c r="AE314">
-        <v>0</v>
-      </c>
-      <c r="AF314">
-        <v>0</v>
-      </c>
-      <c r="AG314">
-        <v>0</v>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ314">
-        <v>0</v>
-      </c>
-      <c r="AK314">
-        <v>0</v>
-      </c>
-      <c r="AL314">
-        <v>0</v>
-      </c>
-      <c r="AM314">
-        <v>-1</v>
-      </c>
-      <c r="AN314">
-        <v>-1</v>
-      </c>
-      <c r="AO314">
-        <v>-1</v>
-      </c>
-      <c r="AP314">
-        <v>-1</v>
-      </c>
-      <c r="AQ314">
-        <v>0</v>
-      </c>
-      <c r="AR314">
-        <v>0</v>
-      </c>
-      <c r="AS314">
-        <v>0</v>
-      </c>
-      <c r="AT314">
-        <v>0</v>
-      </c>
-      <c r="AU314" t="inlineStr">
+      <c r="N316">
+        <v>0</v>
+      </c>
+      <c r="O316">
+        <v>0</v>
+      </c>
+      <c r="P316">
+        <v>0</v>
+      </c>
+      <c r="Q316">
+        <v>0</v>
+      </c>
+      <c r="R316">
+        <v>0</v>
+      </c>
+      <c r="S316">
+        <v>0</v>
+      </c>
+      <c r="T316">
+        <v>0</v>
+      </c>
+      <c r="U316">
+        <v>0</v>
+      </c>
+      <c r="V316">
+        <v>0</v>
+      </c>
+      <c r="W316">
+        <v>0</v>
+      </c>
+      <c r="X316">
+        <v>0</v>
+      </c>
+      <c r="Y316">
+        <v>0</v>
+      </c>
+      <c r="Z316">
+        <v>0</v>
+      </c>
+      <c r="AA316">
+        <v>0</v>
+      </c>
+      <c r="AB316">
+        <v>0</v>
+      </c>
+      <c r="AC316">
+        <v>0</v>
+      </c>
+      <c r="AD316">
+        <v>0</v>
+      </c>
+      <c r="AE316">
+        <v>0</v>
+      </c>
+      <c r="AF316">
+        <v>0</v>
+      </c>
+      <c r="AG316">
+        <v>0</v>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ316">
+        <v>0</v>
+      </c>
+      <c r="AK316">
+        <v>0</v>
+      </c>
+      <c r="AL316">
+        <v>0</v>
+      </c>
+      <c r="AM316">
+        <v>-1</v>
+      </c>
+      <c r="AN316">
+        <v>-1</v>
+      </c>
+      <c r="AO316">
+        <v>-1</v>
+      </c>
+      <c r="AP316">
+        <v>-1</v>
+      </c>
+      <c r="AQ316">
+        <v>0</v>
+      </c>
+      <c r="AR316">
+        <v>0</v>
+      </c>
+      <c r="AS316">
+        <v>0</v>
+      </c>
+      <c r="AT316">
+        <v>0</v>
+      </c>
+      <c r="AU316" t="inlineStr">
         <is>
           <t>2026-09-06 22:00:00</t>
         </is>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G40">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37808,55 +37808,55 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W230">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL230">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16642,31 +16642,31 @@
         <v>0</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE100">
         <v>0</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G101">
@@ -16781,55 +16781,55 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G130">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21997,16 +21997,16 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -22021,31 +22021,31 @@
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE133">
         <v>0</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T141">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U141">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z141">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE141">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK141">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T173">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U173">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V173">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W173">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X173">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z173">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC173">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AD173">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK173">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G183">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T216">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X216">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V221">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W221">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X221">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z221">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC221">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD221">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK221">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R236">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S236">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T236">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U236">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V236">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X236">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y236">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z236">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC236">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD236">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE236">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF236">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG236">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK236">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -40090,55 +40090,55 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40742,55 +40742,55 @@
         <v>0</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -41059,64 +41059,64 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA250">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB250">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43830,64 +43830,64 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q267">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R267">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T267">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U267">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V267">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W267">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X267">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y267">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z267">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA267">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB267">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC267">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD267">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE267">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF267">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG267">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK267">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF272">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG272">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL277">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
         <v>3.35</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="R5">
+        <v>2.07</v>
+      </c>
+      <c r="S5">
+        <v>1.37</v>
+      </c>
+      <c r="T5">
+        <v>2.74</v>
+      </c>
+      <c r="U5">
+        <v>2.7</v>
+      </c>
+      <c r="V5">
+        <v>1.38</v>
+      </c>
+      <c r="W5">
+        <v>1.06</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.25</v>
+      </c>
+      <c r="Z5">
+        <v>3.28</v>
+      </c>
+      <c r="AA5">
+        <v>1.85</v>
+      </c>
+      <c r="AB5">
+        <v>1.9</v>
+      </c>
+      <c r="AC5">
+        <v>3.04</v>
+      </c>
+      <c r="AD5">
+        <v>1.29</v>
+      </c>
+      <c r="AE5">
+        <v>1.08</v>
+      </c>
+      <c r="AF5">
+        <v>1.69</v>
+      </c>
+      <c r="AG5">
         <v>2.03</v>
-      </c>
-      <c r="S5">
-        <v>1.41</v>
-      </c>
-      <c r="T5">
-        <v>2.59</v>
-      </c>
-      <c r="U5">
-        <v>2.88</v>
-      </c>
-      <c r="V5">
-        <v>1.34</v>
-      </c>
-      <c r="W5">
-        <v>1.04</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>1.3</v>
-      </c>
-      <c r="Z5">
-        <v>2.97</v>
-      </c>
-      <c r="AA5">
-        <v>2.07</v>
-      </c>
-      <c r="AB5">
-        <v>1.72</v>
-      </c>
-      <c r="AC5">
-        <v>3.34</v>
-      </c>
-      <c r="AD5">
-        <v>1.24</v>
-      </c>
-      <c r="AE5">
-        <v>1.05</v>
-      </c>
-      <c r="AF5">
-        <v>1.83</v>
-      </c>
-      <c r="AG5">
-        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O6">
         <v>3.35</v>
       </c>
       <c r="P6">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="Q6">
-        <v>3.94</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
+        <v>2.03</v>
+      </c>
+      <c r="S6">
+        <v>1.41</v>
+      </c>
+      <c r="T6">
+        <v>2.59</v>
+      </c>
+      <c r="U6">
+        <v>2.88</v>
+      </c>
+      <c r="V6">
+        <v>1.34</v>
+      </c>
+      <c r="W6">
+        <v>1.04</v>
+      </c>
+      <c r="X6">
+        <v>1.02</v>
+      </c>
+      <c r="Y6">
+        <v>1.3</v>
+      </c>
+      <c r="Z6">
+        <v>2.97</v>
+      </c>
+      <c r="AA6">
         <v>2.07</v>
       </c>
-      <c r="S6">
-        <v>1.37</v>
-      </c>
-      <c r="T6">
-        <v>2.74</v>
-      </c>
-      <c r="U6">
-        <v>2.7</v>
-      </c>
-      <c r="V6">
-        <v>1.38</v>
-      </c>
-      <c r="W6">
-        <v>1.06</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.25</v>
-      </c>
-      <c r="Z6">
-        <v>3.28</v>
-      </c>
-      <c r="AA6">
-        <v>1.85</v>
-      </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G10">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="Q21">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="R21">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="S21">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>2.62</v>
+        <v>3.68</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AB21">
+        <v>1.93</v>
+      </c>
+      <c r="AC21">
+        <v>2.88</v>
+      </c>
+      <c r="AD21">
+        <v>1.32</v>
+      </c>
+      <c r="AE21">
+        <v>1.08</v>
+      </c>
+      <c r="AF21">
         <v>1.61</v>
       </c>
-      <c r="AC21">
-        <v>3.96</v>
-      </c>
-      <c r="AD21">
-        <v>1.17</v>
-      </c>
-      <c r="AE21">
-        <v>1.02</v>
-      </c>
-      <c r="AF21">
-        <v>1.91</v>
-      </c>
       <c r="AG21">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="Q22">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R22">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="T22">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
+        <v>1.02</v>
+      </c>
+      <c r="X22">
         <v>1.05</v>
       </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>3.68</v>
+        <v>2.62</v>
       </c>
       <c r="AA22">
+        <v>2.25</v>
+      </c>
+      <c r="AB22">
+        <v>1.61</v>
+      </c>
+      <c r="AC22">
+        <v>3.96</v>
+      </c>
+      <c r="AD22">
+        <v>1.17</v>
+      </c>
+      <c r="AE22">
+        <v>1.02</v>
+      </c>
+      <c r="AF22">
+        <v>1.91</v>
+      </c>
+      <c r="AG22">
         <v>1.78</v>
       </c>
-      <c r="AB22">
-        <v>1.93</v>
-      </c>
-      <c r="AC22">
-        <v>2.88</v>
-      </c>
-      <c r="AD22">
-        <v>1.32</v>
-      </c>
-      <c r="AE22">
-        <v>1.08</v>
-      </c>
-      <c r="AF22">
-        <v>1.61</v>
-      </c>
-      <c r="AG22">
-        <v>2.16</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G31">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P62">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q62">
-        <v>2.4</v>
+        <v>3.37</v>
       </c>
       <c r="R62">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T62">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="V62">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>5.45</v>
+        <v>5.1</v>
       </c>
       <c r="AA62">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AB62">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="AC62">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AD62">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AE62">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG62">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK62">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="O63">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="P63">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="Q63">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="R63">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="S63">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="U63">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="V63">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z63">
-        <v>5.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA63">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AB63">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="AC63">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="AD63">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF63">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>2.66</v>
+        <v>2.21</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="O64">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="R64">
+        <v>2.35</v>
+      </c>
+      <c r="S64">
+        <v>1.22</v>
+      </c>
+      <c r="T64">
+        <v>3.66</v>
+      </c>
+      <c r="U64">
         <v>2.14</v>
       </c>
-      <c r="S64">
-        <v>1.35</v>
-      </c>
-      <c r="T64">
-        <v>2.94</v>
-      </c>
-      <c r="U64">
-        <v>2.56</v>
-      </c>
       <c r="V64">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="W64">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>3.62</v>
+        <v>5.45</v>
       </c>
       <c r="AA64">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AB64">
-        <v>2.03</v>
+        <v>2.54</v>
       </c>
       <c r="AC64">
-        <v>2.92</v>
+        <v>2.14</v>
       </c>
       <c r="AD64">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE64">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF64">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AG64">
-        <v>2.21</v>
+        <v>2.69</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="O79">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
-        <v>5.9</v>
+        <v>3.35</v>
       </c>
       <c r="Q79">
-        <v>1.91</v>
+        <v>2.67</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="S79">
+        <v>1.41</v>
+      </c>
+      <c r="T79">
+        <v>2.56</v>
+      </c>
+      <c r="U79">
+        <v>2.92</v>
+      </c>
+      <c r="V79">
         <v>1.32</v>
       </c>
-      <c r="T79">
-        <v>2.92</v>
-      </c>
-      <c r="U79">
-        <v>2.72</v>
-      </c>
-      <c r="V79">
-        <v>1.42</v>
-      </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z79">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="AA79">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB79">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AC79">
-        <v>2.81</v>
+        <v>3.42</v>
       </c>
       <c r="AD79">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE79">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF79">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AG79">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>2.88</v>
+        <v>1.64</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,80 +13349,80 @@
         </is>
       </c>
       <c r="N80">
+        <v>1.39</v>
+      </c>
+      <c r="O80">
+        <v>4.3</v>
+      </c>
+      <c r="P80">
+        <v>5.9</v>
+      </c>
+      <c r="Q80">
+        <v>1.91</v>
+      </c>
+      <c r="R80">
+        <v>2.3</v>
+      </c>
+      <c r="S80">
+        <v>1.32</v>
+      </c>
+      <c r="T80">
+        <v>2.92</v>
+      </c>
+      <c r="U80">
+        <v>2.72</v>
+      </c>
+      <c r="V80">
+        <v>1.42</v>
+      </c>
+      <c r="W80">
+        <v>1.07</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.21</v>
+      </c>
+      <c r="Z80">
+        <v>3.58</v>
+      </c>
+      <c r="AA80">
+        <v>1.8</v>
+      </c>
+      <c r="AB80">
         <v>1.94</v>
       </c>
-      <c r="O80">
-        <v>3.3</v>
-      </c>
-      <c r="P80">
-        <v>3.35</v>
-      </c>
-      <c r="Q80">
-        <v>2.67</v>
-      </c>
-      <c r="R80">
-        <v>1.98</v>
-      </c>
-      <c r="S80">
-        <v>1.41</v>
-      </c>
-      <c r="T80">
-        <v>2.56</v>
-      </c>
-      <c r="U80">
-        <v>2.92</v>
-      </c>
-      <c r="V80">
-        <v>1.32</v>
-      </c>
-      <c r="W80">
-        <v>1.03</v>
-      </c>
-      <c r="X80">
-        <v>1.02</v>
-      </c>
-      <c r="Y80">
-        <v>1.29</v>
-      </c>
-      <c r="Z80">
-        <v>3.04</v>
-      </c>
-      <c r="AA80">
-        <v>2</v>
-      </c>
-      <c r="AB80">
-        <v>1.71</v>
-      </c>
       <c r="AC80">
-        <v>3.42</v>
+        <v>2.81</v>
       </c>
       <c r="AD80">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
+        <v>1.1</v>
+      </c>
+      <c r="AF80">
+        <v>1.92</v>
+      </c>
+      <c r="AG80">
+        <v>1.75</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
         <v>1.04</v>
       </c>
-      <c r="AF80">
-        <v>1.79</v>
-      </c>
-      <c r="AG80">
-        <v>1.88</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.26</v>
-      </c>
       <c r="AK80">
-        <v>1.64</v>
+        <v>2.88</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="R107">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="S107">
+        <v>1.37</v>
+      </c>
+      <c r="T107">
+        <v>2.85</v>
+      </c>
+      <c r="U107">
+        <v>2.8</v>
+      </c>
+      <c r="V107">
+        <v>1.4</v>
+      </c>
+      <c r="W107">
+        <v>1.06</v>
+      </c>
+      <c r="X107">
+        <v>1.02</v>
+      </c>
+      <c r="Y107">
+        <v>1.26</v>
+      </c>
+      <c r="Z107">
+        <v>3.5</v>
+      </c>
+      <c r="AA107">
+        <v>2</v>
+      </c>
+      <c r="AB107">
+        <v>1.77</v>
+      </c>
+      <c r="AC107">
+        <v>3.3</v>
+      </c>
+      <c r="AD107">
         <v>1.27</v>
       </c>
-      <c r="T107">
-        <v>3.4</v>
-      </c>
-      <c r="U107">
-        <v>2.35</v>
-      </c>
-      <c r="V107">
-        <v>1.52</v>
-      </c>
-      <c r="W107">
-        <v>1.12</v>
-      </c>
-      <c r="X107">
-        <v>1.03</v>
-      </c>
-      <c r="Y107">
-        <v>1.16</v>
-      </c>
-      <c r="Z107">
-        <v>4.3</v>
-      </c>
-      <c r="AA107">
-        <v>1.62</v>
-      </c>
-      <c r="AB107">
-        <v>2.23</v>
-      </c>
-      <c r="AC107">
-        <v>2.4</v>
-      </c>
-      <c r="AD107">
-        <v>1.5</v>
-      </c>
       <c r="AE107">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G108">
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="R108">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="S108">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U108">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="V108">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA108">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB108">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AC108">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD108">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF108">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG108">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20693,55 +20693,55 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="O131">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P131">
+        <v>6.5</v>
+      </c>
+      <c r="Q131">
+        <v>2.05</v>
+      </c>
+      <c r="R131">
+        <v>2.27</v>
+      </c>
+      <c r="S131">
+        <v>1.32</v>
+      </c>
+      <c r="T131">
+        <v>3.1</v>
+      </c>
+      <c r="U131">
+        <v>2.41</v>
+      </c>
+      <c r="V131">
+        <v>1.5</v>
+      </c>
+      <c r="W131">
+        <v>1.1</v>
+      </c>
+      <c r="X131">
+        <v>1.02</v>
+      </c>
+      <c r="Y131">
+        <v>1.16</v>
+      </c>
+      <c r="Z131">
+        <v>4.2</v>
+      </c>
+      <c r="AA131">
+        <v>1.65</v>
+      </c>
+      <c r="AB131">
+        <v>2.3</v>
+      </c>
+      <c r="AC131">
         <v>2.45</v>
       </c>
-      <c r="Q131">
-        <v>3.44</v>
-      </c>
-      <c r="R131">
-        <v>2.13</v>
-      </c>
-      <c r="S131">
-        <v>1.36</v>
-      </c>
-      <c r="T131">
-        <v>2.89</v>
-      </c>
-      <c r="U131">
-        <v>2.73</v>
-      </c>
-      <c r="V131">
-        <v>1.4</v>
-      </c>
-      <c r="W131">
-        <v>1.05</v>
-      </c>
-      <c r="X131">
-        <v>1.01</v>
-      </c>
-      <c r="Y131">
-        <v>1.25</v>
-      </c>
-      <c r="Z131">
-        <v>3.38</v>
-      </c>
-      <c r="AA131">
-        <v>1.88</v>
-      </c>
-      <c r="AB131">
-        <v>1.9</v>
-      </c>
-      <c r="AC131">
-        <v>3.05</v>
-      </c>
       <c r="AD131">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AE131">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF131">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG131">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK131">
-        <v>1.42</v>
+        <v>2.45</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.53</v>
+        <v>2.8</v>
       </c>
       <c r="O132">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P132">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q132">
-        <v>2.05</v>
+        <v>3.44</v>
       </c>
       <c r="R132">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="S132">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T132">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U132">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="V132">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W132">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z132">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="AA132">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AB132">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC132">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="AD132">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG132">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK132">
-        <v>2.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G148">
@@ -26235,55 +26235,55 @@
         <v>0</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X266">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE266">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44002,55 +44002,55 @@
         <v>5.05</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44195,10 +44195,10 @@
         <v>0</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC269">
         <v>0</v>
@@ -44491,55 +44491,55 @@
         <v>0</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="O279">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P279">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45958,55 +45958,55 @@
         <v>2.47</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,64 +46112,64 @@
         </is>
       </c>
       <c r="N281">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O281">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P281">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="Q281">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R281">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S281">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T281">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U281">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V281">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W281">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X281">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y281">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z281">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC281">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD281">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE281">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF281">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG281">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK281">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47751,55 +47751,55 @@
         <v>4.08</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R291">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T291">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U291">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V291">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X291">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y291">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z291">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC291">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD291">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE291">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF291">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK291">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47914,55 +47914,55 @@
         <v>3</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z292">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC292">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD292">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE292">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG292">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK292">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q293">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R293">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S293">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T293">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U293">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V293">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X293">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y293">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z293">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA293">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB293">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC293">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD293">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE293">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF293">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG293">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK293">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL293">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R21">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="T21">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
         <v>1.05</v>
       </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z21">
-        <v>3.68</v>
+        <v>2.62</v>
       </c>
       <c r="AA21">
+        <v>2.25</v>
+      </c>
+      <c r="AB21">
+        <v>1.61</v>
+      </c>
+      <c r="AC21">
+        <v>3.96</v>
+      </c>
+      <c r="AD21">
+        <v>1.17</v>
+      </c>
+      <c r="AE21">
+        <v>1.02</v>
+      </c>
+      <c r="AF21">
+        <v>1.91</v>
+      </c>
+      <c r="AG21">
         <v>1.78</v>
       </c>
-      <c r="AB21">
-        <v>1.93</v>
-      </c>
-      <c r="AC21">
-        <v>2.88</v>
-      </c>
-      <c r="AD21">
-        <v>1.32</v>
-      </c>
-      <c r="AE21">
-        <v>1.08</v>
-      </c>
-      <c r="AF21">
-        <v>1.61</v>
-      </c>
-      <c r="AG21">
-        <v>2.16</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="Q22">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="S22">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>2.62</v>
+        <v>3.68</v>
       </c>
       <c r="AA22">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
+        <v>1.93</v>
+      </c>
+      <c r="AC22">
+        <v>2.88</v>
+      </c>
+      <c r="AD22">
+        <v>1.32</v>
+      </c>
+      <c r="AE22">
+        <v>1.08</v>
+      </c>
+      <c r="AF22">
         <v>1.61</v>
       </c>
-      <c r="AC22">
-        <v>3.96</v>
-      </c>
-      <c r="AD22">
-        <v>1.17</v>
-      </c>
-      <c r="AE22">
-        <v>1.02</v>
-      </c>
-      <c r="AF22">
-        <v>1.91</v>
-      </c>
       <c r="AG22">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.9</v>
+        <v>1.61</v>
       </c>
       <c r="O85">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P85">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q85">
-        <v>3.92</v>
+        <v>2.12</v>
       </c>
       <c r="R85">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T85">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U85">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="V85">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W85">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="AA85">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AB85">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="AC85">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AD85">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AE85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AG85">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.61</v>
+        <v>3.9</v>
       </c>
       <c r="O86">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P86">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q86">
-        <v>2.12</v>
+        <v>3.92</v>
       </c>
       <c r="R86">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="S86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA86">
+        <v>1.39</v>
+      </c>
+      <c r="AB86">
+        <v>2.61</v>
+      </c>
+      <c r="AC86">
+        <v>2.14</v>
+      </c>
+      <c r="AD86">
+        <v>1.74</v>
+      </c>
+      <c r="AE86">
+        <v>1.25</v>
+      </c>
+      <c r="AF86">
         <v>1.42</v>
       </c>
-      <c r="AB86">
-        <v>2.51</v>
-      </c>
-      <c r="AC86">
-        <v>2.22</v>
-      </c>
-      <c r="AD86">
-        <v>1.69</v>
-      </c>
-      <c r="AE86">
-        <v>1.22</v>
-      </c>
-      <c r="AF86">
-        <v>1.49</v>
-      </c>
       <c r="AG86">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>2.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P140">
-        <v>2.2</v>
+        <v>4.28</v>
       </c>
       <c r="Q140">
-        <v>3.36</v>
+        <v>2.14</v>
       </c>
       <c r="R140">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="S140">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T140">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="U140">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="V140">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="W140">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X140">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z140">
-        <v>4.45</v>
+        <v>5.9</v>
       </c>
       <c r="AA140">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB140">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="AC140">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AD140">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AE140">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF140">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AG140">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK140">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="O141">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
-        <v>4.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q141">
-        <v>2.14</v>
+        <v>3.36</v>
       </c>
       <c r="R141">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="S141">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T141">
-        <v>3.96</v>
+        <v>3.42</v>
       </c>
       <c r="U141">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="V141">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="W141">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X141">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y141">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z141">
-        <v>5.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA141">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB141">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="AC141">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AD141">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AE141">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AF141">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AG141">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK141">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="O279">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P279">
-        <v>3.54</v>
+        <v>2.47</v>
       </c>
       <c r="Q279">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R279">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S279">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="T279">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U279">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="V279">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W279">
         <v>1.04</v>
       </c>
       <c r="X279">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y279">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z279">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA279">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB279">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC279">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD279">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE279">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF279">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG279">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="O280">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P280">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q280">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R280">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S280">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="T280">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U280">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="V280">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W280">
         <v>1.04</v>
       </c>
       <c r="X280">
+        <v>1.14</v>
+      </c>
+      <c r="Y280">
+        <v>1.62</v>
+      </c>
+      <c r="Z280">
+        <v>2.2</v>
+      </c>
+      <c r="AA280">
+        <v>2.87</v>
+      </c>
+      <c r="AB280">
+        <v>1.4</v>
+      </c>
+      <c r="AC280">
+        <v>6</v>
+      </c>
+      <c r="AD280">
         <v>1.11</v>
       </c>
-      <c r="Y280">
-        <v>1.5</v>
-      </c>
-      <c r="Z280">
-        <v>2.45</v>
-      </c>
-      <c r="AA280">
-        <v>2.63</v>
-      </c>
-      <c r="AB280">
-        <v>1.44</v>
-      </c>
-      <c r="AC280">
-        <v>5</v>
-      </c>
-      <c r="AD280">
-        <v>1.15</v>
-      </c>
       <c r="AE280">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF280">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG280">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>1.4</v>
       </c>
       <c r="AK280">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL280">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,65 +19869,65 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="O120">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P120">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="Q120">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="R120">
+        <v>2.06</v>
+      </c>
+      <c r="S120">
+        <v>1.42</v>
+      </c>
+      <c r="T120">
+        <v>2.65</v>
+      </c>
+      <c r="U120">
+        <v>3.02</v>
+      </c>
+      <c r="V120">
+        <v>1.33</v>
+      </c>
+      <c r="W120">
+        <v>1.03</v>
+      </c>
+      <c r="X120">
+        <v>1.02</v>
+      </c>
+      <c r="Y120">
+        <v>1.32</v>
+      </c>
+      <c r="Z120">
+        <v>2.89</v>
+      </c>
+      <c r="AA120">
         <v>2.14</v>
       </c>
-      <c r="S120">
-        <v>1.39</v>
-      </c>
-      <c r="T120">
-        <v>2.77</v>
-      </c>
-      <c r="U120">
-        <v>2.85</v>
-      </c>
-      <c r="V120">
-        <v>1.37</v>
-      </c>
-      <c r="W120">
+      <c r="AB120">
+        <v>1.77</v>
+      </c>
+      <c r="AC120">
+        <v>3.54</v>
+      </c>
+      <c r="AD120">
+        <v>1.22</v>
+      </c>
+      <c r="AE120">
         <v>1.04</v>
       </c>
-      <c r="X120">
-        <v>1.03</v>
-      </c>
-      <c r="Y120">
-        <v>1.26</v>
-      </c>
-      <c r="Z120">
-        <v>3.24</v>
-      </c>
-      <c r="AA120">
-        <v>2</v>
-      </c>
-      <c r="AB120">
-        <v>1.88</v>
-      </c>
-      <c r="AC120">
-        <v>3.24</v>
-      </c>
-      <c r="AD120">
-        <v>1.26</v>
-      </c>
-      <c r="AE120">
-        <v>1.06</v>
-      </c>
       <c r="AF120">
+        <v>1.83</v>
+      </c>
+      <c r="AG120">
         <v>1.87</v>
       </c>
-      <c r="AG120">
-        <v>1.83</v>
-      </c>
       <c r="AH120" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK120">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,65 +20032,65 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="O121">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P121">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="Q121">
+        <v>2.22</v>
+      </c>
+      <c r="R121">
+        <v>2.14</v>
+      </c>
+      <c r="S121">
+        <v>1.39</v>
+      </c>
+      <c r="T121">
         <v>2.77</v>
       </c>
-      <c r="R121">
-        <v>2.06</v>
-      </c>
-      <c r="S121">
-        <v>1.42</v>
-      </c>
-      <c r="T121">
-        <v>2.65</v>
-      </c>
       <c r="U121">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="V121">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W121">
+        <v>1.04</v>
+      </c>
+      <c r="X121">
         <v>1.03</v>
       </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
       <c r="Y121">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z121">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="AA121">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB121">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AC121">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="AD121">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE121">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
+        <v>1.87</v>
+      </c>
+      <c r="AG121">
         <v>1.83</v>
       </c>
-      <c r="AG121">
-        <v>1.87</v>
-      </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK121">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q159">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="R159">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="S159">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T159">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="U159">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V159">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W159">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
         <v>1.06</v>
       </c>
       <c r="Z159">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AA159">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB159">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="AC159">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AD159">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AE159">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF159">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AG159">
-        <v>2.94</v>
+        <v>2.23</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK159">
-        <v>1.68</v>
+        <v>3.14</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q160">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="R160">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="S160">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T160">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="U160">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V160">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W160">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X160">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
         <v>1.06</v>
       </c>
       <c r="Z160">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA160">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB160">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="AC160">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AD160">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE160">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AF160">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AG160">
-        <v>2.23</v>
+        <v>2.94</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AK160">
-        <v>3.14</v>
+        <v>1.68</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -42372,55 +42372,55 @@
         <v>0</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="O279">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P279">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q279">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R279">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S279">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="T279">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="V279">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W279">
         <v>1.04</v>
       </c>
       <c r="X279">
+        <v>1.14</v>
+      </c>
+      <c r="Y279">
+        <v>1.62</v>
+      </c>
+      <c r="Z279">
+        <v>2.2</v>
+      </c>
+      <c r="AA279">
+        <v>2.87</v>
+      </c>
+      <c r="AB279">
+        <v>1.4</v>
+      </c>
+      <c r="AC279">
+        <v>6</v>
+      </c>
+      <c r="AD279">
         <v>1.11</v>
       </c>
-      <c r="Y279">
-        <v>1.5</v>
-      </c>
-      <c r="Z279">
-        <v>2.45</v>
-      </c>
-      <c r="AA279">
-        <v>2.63</v>
-      </c>
-      <c r="AB279">
-        <v>1.44</v>
-      </c>
-      <c r="AC279">
-        <v>5</v>
-      </c>
-      <c r="AD279">
-        <v>1.15</v>
-      </c>
       <c r="AE279">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF279">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG279">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="O280">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P280">
-        <v>3.54</v>
+        <v>2.47</v>
       </c>
       <c r="Q280">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R280">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S280">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="T280">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U280">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="V280">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W280">
         <v>1.04</v>
       </c>
       <c r="X280">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y280">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z280">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA280">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB280">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC280">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD280">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE280">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF280">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG280">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>1.4</v>
       </c>
       <c r="AK280">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.85</v>
+        <v>5.6</v>
       </c>
       <c r="O286">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P286">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q286">
-        <v>2.38</v>
+        <v>5.45</v>
       </c>
       <c r="R286">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S286">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T286">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U286">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="V286">
+        <v>1.44</v>
+      </c>
+      <c r="W286">
+        <v>1.06</v>
+      </c>
+      <c r="X286">
+        <v>1.03</v>
+      </c>
+      <c r="Y286">
+        <v>1.19</v>
+      </c>
+      <c r="Z286">
+        <v>3.82</v>
+      </c>
+      <c r="AA286">
+        <v>1.75</v>
+      </c>
+      <c r="AB286">
+        <v>2.05</v>
+      </c>
+      <c r="AC286">
+        <v>2.8</v>
+      </c>
+      <c r="AD286">
         <v>1.34</v>
       </c>
-      <c r="W286">
-        <v>1.04</v>
-      </c>
-      <c r="X286">
-        <v>1.02</v>
-      </c>
-      <c r="Y286">
-        <v>1.31</v>
-      </c>
-      <c r="Z286">
-        <v>2.94</v>
-      </c>
-      <c r="AA286">
-        <v>2.05</v>
-      </c>
-      <c r="AB286">
-        <v>1.75</v>
-      </c>
-      <c r="AC286">
-        <v>3.54</v>
-      </c>
-      <c r="AD286">
-        <v>1.22</v>
-      </c>
       <c r="AE286">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF286">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG286">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK286">
-        <v>1.97</v>
+        <v>1.15</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>5.6</v>
+        <v>1.91</v>
       </c>
       <c r="O287">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P287">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="Q287">
-        <v>5.45</v>
+        <v>2.4</v>
       </c>
       <c r="R287">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S287">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T287">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U287">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V287">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W287">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X287">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y287">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z287">
-        <v>3.82</v>
+        <v>3.24</v>
       </c>
       <c r="AA287">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB287">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC287">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="AD287">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE287">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF287">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG287">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK287">
-        <v>1.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P288">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q288">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R288">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S288">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T288">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U288">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="V288">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W288">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X288">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y288">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z288">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AA288">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB288">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC288">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="AD288">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE288">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF288">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AG288">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK288">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O291">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P291">
-        <v>4.08</v>
+        <v>3</v>
       </c>
       <c r="Q291">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R291">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S291">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T291">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U291">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="V291">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W291">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X291">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y291">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z291">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA291">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AB291">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC291">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD291">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE291">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF291">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AG291">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.4</v>
       </c>
       <c r="AK291">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
+        <v>2</v>
+      </c>
+      <c r="O292">
+        <v>2.8</v>
+      </c>
+      <c r="P292">
+        <v>4.08</v>
+      </c>
+      <c r="Q292">
         <v>2.7</v>
       </c>
-      <c r="O292">
-        <v>2.5</v>
-      </c>
-      <c r="P292">
-        <v>3</v>
-      </c>
-      <c r="Q292">
-        <v>3.18</v>
-      </c>
       <c r="R292">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S292">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T292">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U292">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="V292">
+        <v>1.22</v>
+      </c>
+      <c r="W292">
+        <v>1</v>
+      </c>
+      <c r="X292">
+        <v>1.11</v>
+      </c>
+      <c r="Y292">
+        <v>1.5</v>
+      </c>
+      <c r="Z292">
+        <v>2.4</v>
+      </c>
+      <c r="AA292">
+        <v>2.63</v>
+      </c>
+      <c r="AB292">
+        <v>1.44</v>
+      </c>
+      <c r="AC292">
+        <v>5</v>
+      </c>
+      <c r="AD292">
         <v>1.15</v>
       </c>
-      <c r="W292">
-        <v>1.03</v>
-      </c>
-      <c r="X292">
-        <v>1.15</v>
-      </c>
-      <c r="Y292">
-        <v>1.7</v>
-      </c>
-      <c r="Z292">
-        <v>2.05</v>
-      </c>
-      <c r="AA292">
-        <v>3.4</v>
-      </c>
-      <c r="AB292">
-        <v>1.33</v>
-      </c>
-      <c r="AC292">
-        <v>7</v>
-      </c>
-      <c r="AD292">
-        <v>1.08</v>
-      </c>
       <c r="AE292">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF292">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AG292">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>1.4</v>
       </c>
       <c r="AK292">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48892,55 +48892,55 @@
         <v>0</v>
       </c>
       <c r="Q298">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R298">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S298">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T298">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U298">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V298">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X298">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y298">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z298">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA298">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB298">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC298">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD298">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE298">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF298">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG298">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK298">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49055,55 +49055,55 @@
         <v>0</v>
       </c>
       <c r="Q299">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R299">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T299">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U299">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V299">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W299">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X299">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y299">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z299">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE299">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF299">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK299">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49218,55 +49218,55 @@
         <v>0</v>
       </c>
       <c r="Q300">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R300">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S300">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T300">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U300">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V300">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W300">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X300">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y300">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z300">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC300">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD300">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE300">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF300">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG300">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK300">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL300">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -8794,34 +8794,34 @@
         <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA52">
         <v>2.1</v>
@@ -8830,19 +8830,19 @@
         <v>1.72</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G68">
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="R68">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T68">
-        <v>3.16</v>
+        <v>4.2</v>
       </c>
       <c r="U68">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="V68">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z68">
-        <v>4.25</v>
+        <v>6.55</v>
       </c>
       <c r="AA68">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="AC68">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="AD68">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF68">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG68">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G69">
@@ -11565,71 +11565,71 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="R69">
-        <v>2.51</v>
+        <v>2.16</v>
       </c>
       <c r="S69">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="U69">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="V69">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="W69">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z69">
-        <v>6.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA69">
+        <v>1.66</v>
+      </c>
+      <c r="AB69">
+        <v>2.25</v>
+      </c>
+      <c r="AC69">
+        <v>2.42</v>
+      </c>
+      <c r="AD69">
+        <v>1.44</v>
+      </c>
+      <c r="AE69">
+        <v>1.15</v>
+      </c>
+      <c r="AF69">
+        <v>1.5</v>
+      </c>
+      <c r="AG69">
+        <v>2.42</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
         <v>1.31</v>
       </c>
-      <c r="AB69">
-        <v>2.92</v>
-      </c>
-      <c r="AC69">
-        <v>1.92</v>
-      </c>
-      <c r="AD69">
-        <v>1.9</v>
-      </c>
-      <c r="AE69">
-        <v>1.31</v>
-      </c>
-      <c r="AF69">
-        <v>1.36</v>
-      </c>
-      <c r="AG69">
-        <v>2.9</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.22</v>
-      </c>
       <c r="AK69">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O91">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q91">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="R91">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S91">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U91">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="V91">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z91">
+        <v>3.12</v>
+      </c>
+      <c r="AA91">
+        <v>2.15</v>
+      </c>
+      <c r="AB91">
+        <v>1.66</v>
+      </c>
+      <c r="AC91">
         <v>3.38</v>
       </c>
-      <c r="AA91">
-        <v>1.89</v>
-      </c>
-      <c r="AB91">
-        <v>1.88</v>
-      </c>
-      <c r="AC91">
-        <v>3.12</v>
-      </c>
       <c r="AD91">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG91">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P92">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q92">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="R92">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S92">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T92">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U92">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="V92">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
+        <v>1.31</v>
+      </c>
+      <c r="Z92">
+        <v>3.38</v>
+      </c>
+      <c r="AA92">
+        <v>1.89</v>
+      </c>
+      <c r="AB92">
+        <v>1.88</v>
+      </c>
+      <c r="AC92">
+        <v>3.12</v>
+      </c>
+      <c r="AD92">
         <v>1.28</v>
       </c>
-      <c r="Z92">
-        <v>3.12</v>
-      </c>
-      <c r="AA92">
-        <v>2.15</v>
-      </c>
-      <c r="AB92">
-        <v>1.66</v>
-      </c>
-      <c r="AC92">
-        <v>3.38</v>
-      </c>
-      <c r="AD92">
-        <v>1.24</v>
-      </c>
       <c r="AE92">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG92">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK92">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="R107">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="S107">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T107">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="V107">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA107">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB107">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD107">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF107">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG107">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G108">
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="S108">
+        <v>1.37</v>
+      </c>
+      <c r="T108">
+        <v>2.85</v>
+      </c>
+      <c r="U108">
+        <v>2.8</v>
+      </c>
+      <c r="V108">
+        <v>1.4</v>
+      </c>
+      <c r="W108">
+        <v>1.06</v>
+      </c>
+      <c r="X108">
+        <v>1.02</v>
+      </c>
+      <c r="Y108">
+        <v>1.26</v>
+      </c>
+      <c r="Z108">
+        <v>3.5</v>
+      </c>
+      <c r="AA108">
+        <v>2</v>
+      </c>
+      <c r="AB108">
+        <v>1.77</v>
+      </c>
+      <c r="AC108">
+        <v>3.3</v>
+      </c>
+      <c r="AD108">
         <v>1.27</v>
       </c>
-      <c r="T108">
-        <v>3.4</v>
-      </c>
-      <c r="U108">
-        <v>2.35</v>
-      </c>
-      <c r="V108">
-        <v>1.52</v>
-      </c>
-      <c r="W108">
-        <v>1.12</v>
-      </c>
-      <c r="X108">
-        <v>1.03</v>
-      </c>
-      <c r="Y108">
-        <v>1.16</v>
-      </c>
-      <c r="Z108">
-        <v>4.3</v>
-      </c>
-      <c r="AA108">
-        <v>1.62</v>
-      </c>
-      <c r="AB108">
-        <v>2.23</v>
-      </c>
-      <c r="AC108">
-        <v>2.4</v>
-      </c>
-      <c r="AD108">
-        <v>1.5</v>
-      </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG108">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q133">
         <v>2.33</v>
@@ -22009,16 +22009,16 @@
         <v>2.7</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
         <v>1.27</v>
@@ -22039,7 +22039,7 @@
         <v>1.28</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
         <v>1.78</v>
@@ -23464,10 +23464,10 @@
         <v>3.96</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -23476,10 +23476,10 @@
         <v>0</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W142">
         <v>0</v>
@@ -23488,31 +23488,31 @@
         <v>0</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE142">
         <v>0</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23627,55 +23627,55 @@
         <v>2.7</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G181">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G183">
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T254">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U254">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V254">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X254">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y254">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z254">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC254">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD254">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG254">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK254">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>2.17</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -45143,55 +45143,55 @@
         <v>0</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U284">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V284">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W284">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X284">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE284">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O287">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P287">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q287">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R287">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S287">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T287">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U287">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="V287">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W287">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X287">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z287">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AA287">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB287">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC287">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="AD287">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE287">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF287">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AG287">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK287">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
+        <v>1.91</v>
+      </c>
+      <c r="O288">
+        <v>3.6</v>
+      </c>
+      <c r="P288">
+        <v>4</v>
+      </c>
+      <c r="Q288">
+        <v>2.4</v>
+      </c>
+      <c r="R288">
+        <v>2.15</v>
+      </c>
+      <c r="S288">
+        <v>1.37</v>
+      </c>
+      <c r="T288">
+        <v>2.85</v>
+      </c>
+      <c r="U288">
+        <v>2.85</v>
+      </c>
+      <c r="V288">
+        <v>1.39</v>
+      </c>
+      <c r="W288">
+        <v>1.05</v>
+      </c>
+      <c r="X288">
+        <v>1.01</v>
+      </c>
+      <c r="Y288">
+        <v>1.26</v>
+      </c>
+      <c r="Z288">
+        <v>3.24</v>
+      </c>
+      <c r="AA288">
+        <v>1.94</v>
+      </c>
+      <c r="AB288">
         <v>1.85</v>
       </c>
-      <c r="O288">
-        <v>3.5</v>
-      </c>
-      <c r="P288">
-        <v>4.33</v>
-      </c>
-      <c r="Q288">
-        <v>2.38</v>
-      </c>
-      <c r="R288">
-        <v>2.08</v>
-      </c>
-      <c r="S288">
-        <v>1.42</v>
-      </c>
-      <c r="T288">
-        <v>2.65</v>
-      </c>
-      <c r="U288">
-        <v>2.99</v>
-      </c>
-      <c r="V288">
-        <v>1.34</v>
-      </c>
-      <c r="W288">
-        <v>1.04</v>
-      </c>
-      <c r="X288">
-        <v>1.02</v>
-      </c>
-      <c r="Y288">
-        <v>1.31</v>
-      </c>
-      <c r="Z288">
-        <v>2.94</v>
-      </c>
-      <c r="AA288">
-        <v>2.05</v>
-      </c>
-      <c r="AB288">
-        <v>1.75</v>
-      </c>
       <c r="AC288">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="AD288">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE288">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF288">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG288">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK288">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47588,55 +47588,55 @@
         <v>0</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
+        <v>2</v>
+      </c>
+      <c r="O291">
+        <v>2.8</v>
+      </c>
+      <c r="P291">
+        <v>4.08</v>
+      </c>
+      <c r="Q291">
         <v>2.7</v>
       </c>
-      <c r="O291">
-        <v>2.5</v>
-      </c>
-      <c r="P291">
-        <v>3</v>
-      </c>
-      <c r="Q291">
-        <v>3.18</v>
-      </c>
       <c r="R291">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S291">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T291">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U291">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="V291">
+        <v>1.22</v>
+      </c>
+      <c r="W291">
+        <v>1</v>
+      </c>
+      <c r="X291">
+        <v>1.11</v>
+      </c>
+      <c r="Y291">
+        <v>1.5</v>
+      </c>
+      <c r="Z291">
+        <v>2.4</v>
+      </c>
+      <c r="AA291">
+        <v>2.63</v>
+      </c>
+      <c r="AB291">
+        <v>1.44</v>
+      </c>
+      <c r="AC291">
+        <v>5</v>
+      </c>
+      <c r="AD291">
         <v>1.15</v>
       </c>
-      <c r="W291">
-        <v>1.03</v>
-      </c>
-      <c r="X291">
-        <v>1.15</v>
-      </c>
-      <c r="Y291">
-        <v>1.7</v>
-      </c>
-      <c r="Z291">
-        <v>2.05</v>
-      </c>
-      <c r="AA291">
-        <v>3.4</v>
-      </c>
-      <c r="AB291">
-        <v>1.33</v>
-      </c>
-      <c r="AC291">
-        <v>7</v>
-      </c>
-      <c r="AD291">
-        <v>1.08</v>
-      </c>
       <c r="AE291">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF291">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AG291">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.4</v>
       </c>
       <c r="AK291">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O292">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P292">
-        <v>4.08</v>
+        <v>3</v>
       </c>
       <c r="Q292">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R292">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S292">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T292">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U292">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="V292">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W292">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X292">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y292">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z292">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA292">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AB292">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC292">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD292">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE292">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF292">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AG292">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>1.4</v>
       </c>
       <c r="AK292">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q294">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R294">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S294">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T294">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U294">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V294">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W294">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X294">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y294">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z294">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC294">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD294">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE294">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF294">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG294">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK294">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48394,64 +48394,64 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q295">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S295">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T295">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U295">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V295">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W295">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X295">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y295">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z295">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA295">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB295">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC295">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD295">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE295">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG295">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK295">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P297">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G306">
@@ -50685,55 +50685,55 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL309">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.61</v>
+        <v>3.9</v>
       </c>
       <c r="O85">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q85">
-        <v>2.12</v>
+        <v>3.92</v>
       </c>
       <c r="R85">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="S85">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="V85">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA85">
+        <v>1.39</v>
+      </c>
+      <c r="AB85">
+        <v>2.61</v>
+      </c>
+      <c r="AC85">
+        <v>2.14</v>
+      </c>
+      <c r="AD85">
+        <v>1.74</v>
+      </c>
+      <c r="AE85">
+        <v>1.25</v>
+      </c>
+      <c r="AF85">
         <v>1.42</v>
       </c>
-      <c r="AB85">
-        <v>2.51</v>
-      </c>
-      <c r="AC85">
-        <v>2.22</v>
-      </c>
-      <c r="AD85">
-        <v>1.69</v>
-      </c>
-      <c r="AE85">
-        <v>1.22</v>
-      </c>
-      <c r="AF85">
-        <v>1.49</v>
-      </c>
       <c r="AG85">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>2.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.9</v>
+        <v>1.61</v>
       </c>
       <c r="O86">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P86">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>3.92</v>
+        <v>2.12</v>
       </c>
       <c r="R86">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="V86">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="AA86">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AB86">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="AC86">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AD86">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AG86">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK86">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,65 +20032,65 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="O121">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P121">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="Q121">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="R121">
+        <v>2.06</v>
+      </c>
+      <c r="S121">
+        <v>1.42</v>
+      </c>
+      <c r="T121">
+        <v>2.65</v>
+      </c>
+      <c r="U121">
+        <v>3.02</v>
+      </c>
+      <c r="V121">
+        <v>1.33</v>
+      </c>
+      <c r="W121">
+        <v>1.03</v>
+      </c>
+      <c r="X121">
+        <v>1.02</v>
+      </c>
+      <c r="Y121">
+        <v>1.32</v>
+      </c>
+      <c r="Z121">
+        <v>2.89</v>
+      </c>
+      <c r="AA121">
         <v>2.14</v>
       </c>
-      <c r="S121">
-        <v>1.39</v>
-      </c>
-      <c r="T121">
-        <v>2.77</v>
-      </c>
-      <c r="U121">
-        <v>2.85</v>
-      </c>
-      <c r="V121">
-        <v>1.37</v>
-      </c>
-      <c r="W121">
+      <c r="AB121">
+        <v>1.77</v>
+      </c>
+      <c r="AC121">
+        <v>3.54</v>
+      </c>
+      <c r="AD121">
+        <v>1.22</v>
+      </c>
+      <c r="AE121">
         <v>1.04</v>
       </c>
-      <c r="X121">
-        <v>1.03</v>
-      </c>
-      <c r="Y121">
-        <v>1.26</v>
-      </c>
-      <c r="Z121">
-        <v>3.24</v>
-      </c>
-      <c r="AA121">
-        <v>2</v>
-      </c>
-      <c r="AB121">
-        <v>1.88</v>
-      </c>
-      <c r="AC121">
-        <v>3.24</v>
-      </c>
-      <c r="AD121">
-        <v>1.26</v>
-      </c>
-      <c r="AE121">
-        <v>1.06</v>
-      </c>
       <c r="AF121">
+        <v>1.83</v>
+      </c>
+      <c r="AG121">
         <v>1.87</v>
       </c>
-      <c r="AG121">
-        <v>1.83</v>
-      </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK121">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,65 +20195,65 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P122">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="Q122">
+        <v>2.22</v>
+      </c>
+      <c r="R122">
+        <v>2.14</v>
+      </c>
+      <c r="S122">
+        <v>1.39</v>
+      </c>
+      <c r="T122">
         <v>2.77</v>
       </c>
-      <c r="R122">
-        <v>2.06</v>
-      </c>
-      <c r="S122">
-        <v>1.42</v>
-      </c>
-      <c r="T122">
-        <v>2.65</v>
-      </c>
       <c r="U122">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="V122">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W122">
+        <v>1.04</v>
+      </c>
+      <c r="X122">
         <v>1.03</v>
       </c>
-      <c r="X122">
-        <v>1.02</v>
-      </c>
       <c r="Y122">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z122">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="AA122">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AC122">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="AD122">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE122">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
+        <v>1.87</v>
+      </c>
+      <c r="AG122">
         <v>1.83</v>
       </c>
-      <c r="AG122">
-        <v>1.87</v>
-      </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK122">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G221">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="O244">
         <v>3.2</v>
       </c>
       <c r="P244">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q244">
-        <v>3.12</v>
+        <v>2.77</v>
       </c>
       <c r="R244">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="S244">
+        <v>1.57</v>
+      </c>
+      <c r="T244">
+        <v>2.39</v>
+      </c>
+      <c r="U244">
+        <v>3.58</v>
+      </c>
+      <c r="V244">
+        <v>1.29</v>
+      </c>
+      <c r="W244">
+        <v>1.03</v>
+      </c>
+      <c r="X244">
+        <v>1.06</v>
+      </c>
+      <c r="Y244">
         <v>1.44</v>
       </c>
-      <c r="T244">
-        <v>2.77</v>
-      </c>
-      <c r="U244">
-        <v>2.89</v>
-      </c>
-      <c r="V244">
-        <v>1.41</v>
-      </c>
-      <c r="W244">
-        <v>1.06</v>
-      </c>
-      <c r="X244">
+      <c r="Z244">
+        <v>2.55</v>
+      </c>
+      <c r="AA244">
+        <v>2.54</v>
+      </c>
+      <c r="AB244">
+        <v>1.61</v>
+      </c>
+      <c r="AC244">
+        <v>4.45</v>
+      </c>
+      <c r="AD244">
+        <v>1.16</v>
+      </c>
+      <c r="AE244">
         <v>1.01</v>
       </c>
-      <c r="Y244">
-        <v>1.27</v>
-      </c>
-      <c r="Z244">
-        <v>3.34</v>
-      </c>
-      <c r="AA244">
-        <v>1.9</v>
-      </c>
-      <c r="AB244">
-        <v>1.9</v>
-      </c>
-      <c r="AC244">
-        <v>3.14</v>
-      </c>
-      <c r="AD244">
-        <v>1.35</v>
-      </c>
-      <c r="AE244">
-        <v>1.07</v>
-      </c>
       <c r="AF244">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG244">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK244">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,80 +40244,80 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="O245">
         <v>3.2</v>
       </c>
       <c r="P245">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q245">
+        <v>3.12</v>
+      </c>
+      <c r="R245">
+        <v>2.04</v>
+      </c>
+      <c r="S245">
+        <v>1.44</v>
+      </c>
+      <c r="T245">
         <v>2.77</v>
       </c>
-      <c r="R245">
-        <v>1.92</v>
-      </c>
-      <c r="S245">
+      <c r="U245">
+        <v>2.89</v>
+      </c>
+      <c r="V245">
+        <v>1.41</v>
+      </c>
+      <c r="W245">
+        <v>1.06</v>
+      </c>
+      <c r="X245">
+        <v>1.01</v>
+      </c>
+      <c r="Y245">
+        <v>1.27</v>
+      </c>
+      <c r="Z245">
+        <v>3.34</v>
+      </c>
+      <c r="AA245">
+        <v>1.9</v>
+      </c>
+      <c r="AB245">
+        <v>1.9</v>
+      </c>
+      <c r="AC245">
+        <v>3.14</v>
+      </c>
+      <c r="AD245">
+        <v>1.35</v>
+      </c>
+      <c r="AE245">
+        <v>1.07</v>
+      </c>
+      <c r="AF245">
+        <v>1.7</v>
+      </c>
+      <c r="AG245">
+        <v>2</v>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ245">
+        <v>1.38</v>
+      </c>
+      <c r="AK245">
         <v>1.57</v>
-      </c>
-      <c r="T245">
-        <v>2.39</v>
-      </c>
-      <c r="U245">
-        <v>3.58</v>
-      </c>
-      <c r="V245">
-        <v>1.29</v>
-      </c>
-      <c r="W245">
-        <v>1.03</v>
-      </c>
-      <c r="X245">
-        <v>1.06</v>
-      </c>
-      <c r="Y245">
-        <v>1.44</v>
-      </c>
-      <c r="Z245">
-        <v>2.55</v>
-      </c>
-      <c r="AA245">
-        <v>2.54</v>
-      </c>
-      <c r="AB245">
-        <v>1.61</v>
-      </c>
-      <c r="AC245">
-        <v>4.45</v>
-      </c>
-      <c r="AD245">
-        <v>1.16</v>
-      </c>
-      <c r="AE245">
-        <v>1.01</v>
-      </c>
-      <c r="AF245">
-        <v>2</v>
-      </c>
-      <c r="AG245">
-        <v>1.72</v>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ245">
-        <v>1.4</v>
-      </c>
-      <c r="AK245">
-        <v>1.66</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="O283">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P283">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q283">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R283">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S283">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="T283">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U283">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="V283">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W283">
         <v>1.04</v>
       </c>
       <c r="X283">
+        <v>1.14</v>
+      </c>
+      <c r="Y283">
+        <v>1.62</v>
+      </c>
+      <c r="Z283">
+        <v>2.2</v>
+      </c>
+      <c r="AA283">
+        <v>2.87</v>
+      </c>
+      <c r="AB283">
+        <v>1.4</v>
+      </c>
+      <c r="AC283">
+        <v>6</v>
+      </c>
+      <c r="AD283">
         <v>1.11</v>
       </c>
-      <c r="Y283">
-        <v>1.5</v>
-      </c>
-      <c r="Z283">
-        <v>2.45</v>
-      </c>
-      <c r="AA283">
-        <v>2.63</v>
-      </c>
-      <c r="AB283">
-        <v>1.44</v>
-      </c>
-      <c r="AC283">
-        <v>5</v>
-      </c>
-      <c r="AD283">
-        <v>1.15</v>
-      </c>
       <c r="AE283">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF283">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG283">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>1.4</v>
       </c>
       <c r="AK283">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="O284">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P284">
-        <v>3.54</v>
+        <v>2.47</v>
       </c>
       <c r="Q284">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R284">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S284">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="T284">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U284">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="V284">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W284">
         <v>1.04</v>
       </c>
       <c r="X284">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y284">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z284">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA284">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB284">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC284">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD284">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE284">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF284">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG284">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>1.4</v>
       </c>
       <c r="AK284">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
+        <v>2</v>
+      </c>
+      <c r="O296">
+        <v>2.8</v>
+      </c>
+      <c r="P296">
+        <v>4.08</v>
+      </c>
+      <c r="Q296">
         <v>2.7</v>
       </c>
-      <c r="O296">
-        <v>2.5</v>
-      </c>
-      <c r="P296">
-        <v>3</v>
-      </c>
-      <c r="Q296">
-        <v>3.18</v>
-      </c>
       <c r="R296">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S296">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T296">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U296">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="V296">
+        <v>1.22</v>
+      </c>
+      <c r="W296">
+        <v>1</v>
+      </c>
+      <c r="X296">
+        <v>1.11</v>
+      </c>
+      <c r="Y296">
+        <v>1.5</v>
+      </c>
+      <c r="Z296">
+        <v>2.4</v>
+      </c>
+      <c r="AA296">
+        <v>2.63</v>
+      </c>
+      <c r="AB296">
+        <v>1.44</v>
+      </c>
+      <c r="AC296">
+        <v>5</v>
+      </c>
+      <c r="AD296">
         <v>1.15</v>
       </c>
-      <c r="W296">
-        <v>1.03</v>
-      </c>
-      <c r="X296">
-        <v>1.15</v>
-      </c>
-      <c r="Y296">
-        <v>1.7</v>
-      </c>
-      <c r="Z296">
-        <v>2.05</v>
-      </c>
-      <c r="AA296">
-        <v>3.4</v>
-      </c>
-      <c r="AB296">
-        <v>1.33</v>
-      </c>
-      <c r="AC296">
-        <v>7</v>
-      </c>
-      <c r="AD296">
-        <v>1.08</v>
-      </c>
       <c r="AE296">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF296">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AG296">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>1.4</v>
       </c>
       <c r="AK296">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O297">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P297">
-        <v>4.08</v>
+        <v>3</v>
       </c>
       <c r="Q297">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R297">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S297">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T297">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U297">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="V297">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W297">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X297">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y297">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z297">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA297">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AB297">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC297">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD297">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE297">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF297">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AG297">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>1.4</v>
       </c>
       <c r="AK297">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL297">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
+        <v>1.75</v>
+      </c>
+      <c r="O88">
+        <v>3.3</v>
+      </c>
+      <c r="P88">
+        <v>4.2</v>
+      </c>
+      <c r="Q88">
+        <v>2.37</v>
+      </c>
+      <c r="R88">
         <v>2.09</v>
       </c>
-      <c r="O88">
-        <v>3.14</v>
-      </c>
-      <c r="P88">
-        <v>3.7</v>
-      </c>
-      <c r="Q88">
-        <v>2.77</v>
-      </c>
-      <c r="R88">
-        <v>1.93</v>
-      </c>
       <c r="S88">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T88">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="U88">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="V88">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W88">
+        <v>1.03</v>
+      </c>
+      <c r="X88">
         <v>1.01</v>
       </c>
-      <c r="X88">
-        <v>1.04</v>
-      </c>
       <c r="Y88">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z88">
-        <v>2.68</v>
+        <v>3.12</v>
       </c>
       <c r="AA88">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB88">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC88">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="AD88">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE88">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF88">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG88">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK88">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="R89">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T89">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U89">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W89">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
+        <v>1.31</v>
+      </c>
+      <c r="Z89">
+        <v>3.38</v>
+      </c>
+      <c r="AA89">
+        <v>1.89</v>
+      </c>
+      <c r="AB89">
+        <v>1.88</v>
+      </c>
+      <c r="AC89">
+        <v>3.12</v>
+      </c>
+      <c r="AD89">
         <v>1.28</v>
       </c>
-      <c r="Z89">
-        <v>3.12</v>
-      </c>
-      <c r="AA89">
-        <v>2.15</v>
-      </c>
-      <c r="AB89">
-        <v>1.66</v>
-      </c>
-      <c r="AC89">
-        <v>3.38</v>
-      </c>
-      <c r="AD89">
-        <v>1.24</v>
-      </c>
       <c r="AE89">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK89">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="O90">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P90">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="Q90">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="R90">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S90">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="T90">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="U90">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="V90">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W90">
+        <v>1.01</v>
+      </c>
+      <c r="X90">
         <v>1.04</v>
       </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
       <c r="Y90">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z90">
-        <v>3.38</v>
+        <v>2.68</v>
       </c>
       <c r="AA90">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="AB90">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="AC90">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="AD90">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AG90">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="O283">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P283">
-        <v>3.54</v>
+        <v>2.47</v>
       </c>
       <c r="Q283">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R283">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S283">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="T283">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U283">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="V283">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W283">
         <v>1.04</v>
       </c>
       <c r="X283">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y283">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z283">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA283">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB283">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC283">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD283">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE283">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF283">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG283">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>1.4</v>
       </c>
       <c r="AK283">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="O284">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P284">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q284">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R284">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S284">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="T284">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U284">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="V284">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W284">
         <v>1.04</v>
       </c>
       <c r="X284">
+        <v>1.14</v>
+      </c>
+      <c r="Y284">
+        <v>1.62</v>
+      </c>
+      <c r="Z284">
+        <v>2.2</v>
+      </c>
+      <c r="AA284">
+        <v>2.87</v>
+      </c>
+      <c r="AB284">
+        <v>1.4</v>
+      </c>
+      <c r="AC284">
+        <v>6</v>
+      </c>
+      <c r="AD284">
         <v>1.11</v>
       </c>
-      <c r="Y284">
-        <v>1.5</v>
-      </c>
-      <c r="Z284">
-        <v>2.45</v>
-      </c>
-      <c r="AA284">
-        <v>2.63</v>
-      </c>
-      <c r="AB284">
-        <v>1.44</v>
-      </c>
-      <c r="AC284">
-        <v>5</v>
-      </c>
-      <c r="AD284">
-        <v>1.15</v>
-      </c>
       <c r="AE284">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF284">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG284">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>1.4</v>
       </c>
       <c r="AK284">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>5.6</v>
+        <v>1.85</v>
       </c>
       <c r="O291">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P291">
-        <v>1.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q291">
-        <v>5.45</v>
+        <v>2.38</v>
       </c>
       <c r="R291">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S291">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T291">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U291">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="V291">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W291">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X291">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="Z291">
-        <v>3.82</v>
+        <v>2.94</v>
       </c>
       <c r="AA291">
+        <v>2.05</v>
+      </c>
+      <c r="AB291">
         <v>1.75</v>
       </c>
-      <c r="AB291">
-        <v>2.05</v>
-      </c>
       <c r="AC291">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD291">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE291">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF291">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AG291">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK291">
-        <v>1.15</v>
+        <v>1.97</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.85</v>
+        <v>5.6</v>
       </c>
       <c r="O292">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P292">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q292">
-        <v>2.38</v>
+        <v>5.45</v>
       </c>
       <c r="R292">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S292">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T292">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U292">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="V292">
+        <v>1.44</v>
+      </c>
+      <c r="W292">
+        <v>1.06</v>
+      </c>
+      <c r="X292">
+        <v>1.03</v>
+      </c>
+      <c r="Y292">
+        <v>1.19</v>
+      </c>
+      <c r="Z292">
+        <v>3.82</v>
+      </c>
+      <c r="AA292">
+        <v>1.75</v>
+      </c>
+      <c r="AB292">
+        <v>2.05</v>
+      </c>
+      <c r="AC292">
+        <v>2.8</v>
+      </c>
+      <c r="AD292">
         <v>1.34</v>
       </c>
-      <c r="W292">
-        <v>1.04</v>
-      </c>
-      <c r="X292">
-        <v>1.02</v>
-      </c>
-      <c r="Y292">
-        <v>1.31</v>
-      </c>
-      <c r="Z292">
-        <v>2.94</v>
-      </c>
-      <c r="AA292">
-        <v>2.05</v>
-      </c>
-      <c r="AB292">
-        <v>1.75</v>
-      </c>
-      <c r="AC292">
-        <v>3.54</v>
-      </c>
-      <c r="AD292">
-        <v>1.22</v>
-      </c>
       <c r="AE292">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF292">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG292">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK292">
-        <v>1.97</v>
+        <v>1.15</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O296">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P296">
-        <v>4.08</v>
+        <v>3</v>
       </c>
       <c r="Q296">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R296">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S296">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T296">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U296">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="V296">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W296">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X296">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y296">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z296">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA296">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AB296">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC296">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD296">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE296">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF296">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AG296">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>1.4</v>
       </c>
       <c r="AK296">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
+        <v>2</v>
+      </c>
+      <c r="O297">
+        <v>2.8</v>
+      </c>
+      <c r="P297">
+        <v>4.08</v>
+      </c>
+      <c r="Q297">
         <v>2.7</v>
       </c>
-      <c r="O297">
-        <v>2.5</v>
-      </c>
-      <c r="P297">
-        <v>3</v>
-      </c>
-      <c r="Q297">
-        <v>3.18</v>
-      </c>
       <c r="R297">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S297">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T297">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U297">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="V297">
+        <v>1.22</v>
+      </c>
+      <c r="W297">
+        <v>1</v>
+      </c>
+      <c r="X297">
+        <v>1.11</v>
+      </c>
+      <c r="Y297">
+        <v>1.5</v>
+      </c>
+      <c r="Z297">
+        <v>2.4</v>
+      </c>
+      <c r="AA297">
+        <v>2.63</v>
+      </c>
+      <c r="AB297">
+        <v>1.44</v>
+      </c>
+      <c r="AC297">
+        <v>5</v>
+      </c>
+      <c r="AD297">
         <v>1.15</v>
       </c>
-      <c r="W297">
-        <v>1.03</v>
-      </c>
-      <c r="X297">
-        <v>1.15</v>
-      </c>
-      <c r="Y297">
-        <v>1.7</v>
-      </c>
-      <c r="Z297">
-        <v>2.05</v>
-      </c>
-      <c r="AA297">
-        <v>3.4</v>
-      </c>
-      <c r="AB297">
-        <v>1.33</v>
-      </c>
-      <c r="AC297">
-        <v>7</v>
-      </c>
-      <c r="AD297">
-        <v>1.08</v>
-      </c>
       <c r="AE297">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF297">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AG297">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>1.4</v>
       </c>
       <c r="AK297">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL297">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="R2">
         <v>2.2</v>
@@ -653,7 +653,7 @@
         <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
         <v>2.33</v>
@@ -665,34 +665,34 @@
         <v>1.09</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
+        <v>1.23</v>
+      </c>
+      <c r="Z2">
+        <v>4.3</v>
+      </c>
+      <c r="AA2">
+        <v>1.61</v>
+      </c>
+      <c r="AB2">
+        <v>2.27</v>
+      </c>
+      <c r="AC2">
+        <v>2.9</v>
+      </c>
+      <c r="AD2">
+        <v>1.5</v>
+      </c>
+      <c r="AE2">
         <v>1.15</v>
       </c>
-      <c r="Z2">
-        <v>4.25</v>
-      </c>
-      <c r="AA2">
-        <v>1.72</v>
-      </c>
-      <c r="AB2">
-        <v>2.07</v>
-      </c>
-      <c r="AC2">
-        <v>2.49</v>
-      </c>
-      <c r="AD2">
-        <v>1.47</v>
-      </c>
-      <c r="AE2">
-        <v>1.14</v>
-      </c>
       <c r="AF2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -852,10 +852,10 @@
         <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK3">
         <v>1.53</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="Q5">
-        <v>3.94</v>
+        <v>3.73</v>
       </c>
       <c r="R5">
         <v>2.07</v>
       </c>
       <c r="S5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1157,7 +1157,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
         <v>3.28</v>
@@ -1166,10 +1166,10 @@
         <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="AD5">
         <v>1.29</v>
@@ -1178,10 +1178,10 @@
         <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O6">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="Q6">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="R6">
         <v>2.03</v>
@@ -1326,13 +1326,13 @@
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC6">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD6">
         <v>1.24</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="O8">
+        <v>3.4</v>
+      </c>
+      <c r="P8">
+        <v>2.1</v>
+      </c>
+      <c r="Q8">
+        <v>3.25</v>
+      </c>
+      <c r="R8">
+        <v>2.18</v>
+      </c>
+      <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>3.04</v>
+      </c>
+      <c r="U8">
+        <v>2.53</v>
+      </c>
+      <c r="V8">
+        <v>1.46</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.2</v>
+      </c>
+      <c r="Z8">
         <v>3.72</v>
       </c>
-      <c r="P8">
-        <v>1.98</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.22</v>
+        <v>3.9</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>3.4</v>
+      </c>
+      <c r="O10">
+        <v>3.5</v>
+      </c>
+      <c r="P10">
+        <v>1.85</v>
+      </c>
+      <c r="Q10">
+        <v>4.05</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.32</v>
+      </c>
+      <c r="T10">
+        <v>3.1</v>
+      </c>
+      <c r="U10">
+        <v>2.59</v>
+      </c>
+      <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>1.19</v>
+      </c>
+      <c r="Z10">
+        <v>3.82</v>
+      </c>
+      <c r="AA10">
         <v>1.78</v>
       </c>
-      <c r="O10">
-        <v>3.86</v>
-      </c>
-      <c r="P10">
-        <v>4.4</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="Q21">
         <v>2.98</v>
@@ -3753,10 +3753,10 @@
         <v>2.38</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
         <v>1.02</v>
@@ -3771,13 +3771,13 @@
         <v>2.62</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB21">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC21">
-        <v>3.96</v>
+        <v>4.19</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
@@ -3786,7 +3786,7 @@
         <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
         <v>1.78</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P22">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="Q22">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R22">
         <v>2.11</v>
@@ -3934,13 +3934,13 @@
         <v>3.68</v>
       </c>
       <c r="AA22">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB22">
         <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD22">
         <v>1.32</v>
@@ -3949,7 +3949,7 @@
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
         <v>2.16</v>
@@ -3968,7 +3968,7 @@
         <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.56</v>
+        <v>2.07</v>
       </c>
       <c r="O23">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="P23">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="R23">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="Z23">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA23">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AB23">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q24">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="U24">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
+        <v>1.06</v>
+      </c>
+      <c r="X24">
         <v>1.03</v>
       </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
       <c r="Y24">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="AA24">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AB24">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC24">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>2.96</v>
       </c>
       <c r="R25">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S25">
         <v>1.5</v>
@@ -4417,31 +4417,31 @@
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z25">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AA25">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AB25">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AC25">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD25">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
         <v>1</v>
       </c>
       <c r="AF25">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AG25">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.43</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="P29">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.86</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.43</v>
       </c>
       <c r="P42">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="Q42">
         <v>3.64</v>
       </c>
       <c r="R42">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S42">
         <v>1.24</v>
@@ -7176,43 +7176,43 @@
         <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W42">
         <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA42">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB42">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC42">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD42">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE42">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF42">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O43">
-        <v>4.03</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8625,13 +8625,13 @@
         <v>2.2</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q51">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="R51">
         <v>2.14</v>
@@ -8664,7 +8664,7 @@
         <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC51">
         <v>2.43</v>
@@ -8679,7 +8679,7 @@
         <v>1.51</v>
       </c>
       <c r="AG51">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="O52">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q52">
         <v>3.81</v>
@@ -8800,10 +8800,10 @@
         <v>1.97</v>
       </c>
       <c r="S52">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T52">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="U52">
         <v>3.02</v>
@@ -8812,22 +8812,22 @@
         <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z52">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AA52">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB52">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC52">
         <v>3.52</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="O61">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q61">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S61">
         <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U61">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="V61">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>4.25</v>
+        <v>4.87</v>
       </c>
       <c r="AA61">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AB61">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AC61">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD61">
+        <v>1.57</v>
+      </c>
+      <c r="AE61">
+        <v>1.18</v>
+      </c>
+      <c r="AF61">
         <v>1.46</v>
       </c>
-      <c r="AE61">
-        <v>1.16</v>
-      </c>
-      <c r="AF61">
-        <v>1.49</v>
-      </c>
       <c r="AG61">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="O62">
         <v>3.65</v>
@@ -10424,7 +10424,7 @@
         <v>2.24</v>
       </c>
       <c r="Q62">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="R62">
         <v>2.29</v>
@@ -10436,10 +10436,10 @@
         <v>3.5</v>
       </c>
       <c r="U62">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="V62">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W62">
         <v>1.12</v>
@@ -10454,13 +10454,13 @@
         <v>5.1</v>
       </c>
       <c r="AA62">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
         <v>2.39</v>
       </c>
       <c r="AC62">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD62">
         <v>1.62</v>
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="O63">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q63">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R63">
         <v>2.14</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T63">
-        <v>2.94</v>
+        <v>3.33</v>
       </c>
       <c r="U63">
         <v>2.56</v>
@@ -10611,19 +10611,19 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z63">
         <v>3.62</v>
       </c>
       <c r="AA63">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB63">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC63">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="AD63">
         <v>1.36</v>
@@ -10635,7 +10635,7 @@
         <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,19 +10750,19 @@
         <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="R64">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T64">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="U64">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="V64">
         <v>1.66</v>
@@ -10780,13 +10780,13 @@
         <v>5.45</v>
       </c>
       <c r="AA64">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB64">
         <v>2.54</v>
       </c>
       <c r="AC64">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AD64">
         <v>1.69</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q65">
-        <v>5.18</v>
+        <v>5.19</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S65">
         <v>1.22</v>
@@ -10943,10 +10943,10 @@
         <v>4.95</v>
       </c>
       <c r="AA65">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB65">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AC65">
         <v>2.19</v>
@@ -10958,10 +10958,10 @@
         <v>1.21</v>
       </c>
       <c r="AF65">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG65">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O67">
         <v>3.7</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="O72">
         <v>3.5</v>
@@ -12057,52 +12057,52 @@
         <v>2.75</v>
       </c>
       <c r="R72">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T72">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U72">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V72">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W72">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z72">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="AA72">
         <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AC72">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AD72">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF72">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG72">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK72">
         <v>1.61</v>
@@ -12211,77 +12211,77 @@
         <v>1.38</v>
       </c>
       <c r="O73">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="P73">
         <v>5.8</v>
       </c>
       <c r="Q73">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R73">
         <v>2.33</v>
       </c>
       <c r="S73">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T73">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U73">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V73">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
+        <v>1.17</v>
+      </c>
+      <c r="Z73">
+        <v>4</v>
+      </c>
+      <c r="AA73">
+        <v>1.72</v>
+      </c>
+      <c r="AB73">
+        <v>2.15</v>
+      </c>
+      <c r="AC73">
+        <v>2.59</v>
+      </c>
+      <c r="AD73">
+        <v>1.39</v>
+      </c>
+      <c r="AE73">
+        <v>1.12</v>
+      </c>
+      <c r="AF73">
+        <v>1.99</v>
+      </c>
+      <c r="AG73">
+        <v>1.73</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
         <v>1.18</v>
       </c>
-      <c r="Z73">
-        <v>3.84</v>
-      </c>
-      <c r="AA73">
-        <v>1.77</v>
-      </c>
-      <c r="AB73">
-        <v>2.08</v>
-      </c>
-      <c r="AC73">
-        <v>2.74</v>
-      </c>
-      <c r="AD73">
-        <v>1.35</v>
-      </c>
-      <c r="AE73">
-        <v>1.1</v>
-      </c>
-      <c r="AF73">
-        <v>1.95</v>
-      </c>
-      <c r="AG73">
-        <v>1.76</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.19</v>
-      </c>
       <c r="AK73">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12383,13 +12383,13 @@
         <v>2.48</v>
       </c>
       <c r="R74">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S74">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T74">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U74">
         <v>3.04</v>
@@ -12404,16 +12404,16 @@
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z74">
         <v>2.85</v>
       </c>
       <c r="AA74">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB74">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC74">
         <v>3.62</v>
@@ -12425,7 +12425,7 @@
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG74">
         <v>1.75</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK74">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12703,7 +12703,7 @@
         <v>4.85</v>
       </c>
       <c r="P76">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q76">
         <v>1.82</v>
@@ -12718,28 +12718,28 @@
         <v>3.78</v>
       </c>
       <c r="U76">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V76">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W76">
         <v>1.16</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z76">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AA76">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AB76">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="AC76">
         <v>2.02</v>
@@ -12754,7 +12754,7 @@
         <v>1.57</v>
       </c>
       <c r="AG76">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12866,22 +12866,22 @@
         <v>3.1</v>
       </c>
       <c r="P77">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="R77">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S77">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T77">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U77">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="V77">
         <v>1.34</v>
@@ -12899,13 +12899,13 @@
         <v>2.92</v>
       </c>
       <c r="AA77">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB77">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC77">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AD77">
         <v>1.22</v>
@@ -12933,7 +12933,7 @@
         <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
         <v>3.38</v>
       </c>
       <c r="P78">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="Q78">
         <v>2.73</v>
@@ -13038,16 +13038,16 @@
         <v>2.1</v>
       </c>
       <c r="S78">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="U78">
         <v>2.6</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W78">
         <v>1.05</v>
@@ -13056,7 +13056,7 @@
         <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
         <v>3.62</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
         <v>1.67</v>
@@ -13850,13 +13850,13 @@
         <v>2.92</v>
       </c>
       <c r="R83">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U83">
         <v>2.7</v>
@@ -13871,22 +13871,22 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z83">
         <v>3.34</v>
       </c>
       <c r="AA83">
+        <v>1.95</v>
+      </c>
+      <c r="AB83">
         <v>1.87</v>
-      </c>
-      <c r="AB83">
-        <v>1.83</v>
       </c>
       <c r="AC83">
         <v>3.22</v>
       </c>
       <c r="AD83">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE83">
         <v>1.06</v>
@@ -14022,7 +14022,7 @@
         <v>3.04</v>
       </c>
       <c r="U84">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V84">
         <v>1.46</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="O85">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P85">
-        <v>1.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q85">
-        <v>3.92</v>
+        <v>2</v>
       </c>
       <c r="R85">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S85">
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="U85">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="V85">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W85">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14200,28 +14200,28 @@
         <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA85">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AC85">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD85">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE85">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AG85">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.61</v>
+        <v>3.6</v>
       </c>
       <c r="O86">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P86">
-        <v>4.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q86">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="R86">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="U86">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA86">
+        <v>1.44</v>
+      </c>
+      <c r="AB86">
+        <v>2.7</v>
+      </c>
+      <c r="AC86">
+        <v>2.12</v>
+      </c>
+      <c r="AD86">
+        <v>1.75</v>
+      </c>
+      <c r="AE86">
+        <v>1.25</v>
+      </c>
+      <c r="AF86">
         <v>1.42</v>
       </c>
-      <c r="AB86">
-        <v>2.51</v>
-      </c>
-      <c r="AC86">
-        <v>2.22</v>
-      </c>
-      <c r="AD86">
-        <v>1.69</v>
-      </c>
-      <c r="AE86">
-        <v>1.22</v>
-      </c>
-      <c r="AF86">
-        <v>1.49</v>
-      </c>
       <c r="AG86">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,10 +14493,10 @@
         <v>2.37</v>
       </c>
       <c r="O87">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -14505,10 +14505,10 @@
         <v>2</v>
       </c>
       <c r="S87">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T87">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U87">
         <v>3.1</v>
@@ -14520,7 +14520,7 @@
         <v>1.02</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y87">
         <v>1.33</v>
@@ -14529,7 +14529,7 @@
         <v>2.83</v>
       </c>
       <c r="AA87">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB87">
         <v>1.67</v>
@@ -14653,16 +14653,16 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O88">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
         <v>4.2</v>
       </c>
       <c r="Q88">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R88">
         <v>2.09</v>
@@ -14692,25 +14692,25 @@
         <v>3.12</v>
       </c>
       <c r="AA88">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB88">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AC88">
         <v>3.38</v>
       </c>
       <c r="AD88">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE88">
         <v>1.05</v>
       </c>
       <c r="AF88">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG88">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14819,16 +14819,16 @@
         <v>2.47</v>
       </c>
       <c r="O89">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
       </c>
       <c r="R89">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S89">
         <v>1.38</v>
@@ -14837,7 +14837,7 @@
         <v>2.81</v>
       </c>
       <c r="U89">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V89">
         <v>1.39</v>
@@ -14849,7 +14849,7 @@
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z89">
         <v>3.38</v>
@@ -14858,10 +14858,10 @@
         <v>1.89</v>
       </c>
       <c r="AB89">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC89">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="AD89">
         <v>1.28</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK89">
         <v>1.5</v>
@@ -14982,10 +14982,10 @@
         <v>2.09</v>
       </c>
       <c r="O90">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="P90">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q90">
         <v>2.77</v>
@@ -15018,13 +15018,13 @@
         <v>2.68</v>
       </c>
       <c r="AA90">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AB90">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC90">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD90">
         <v>1.17</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="O91">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P91">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q91">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R91">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S91">
         <v>1.48</v>
@@ -15172,7 +15172,7 @@
         <v>1.01</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y91">
         <v>1.34</v>
@@ -15184,22 +15184,22 @@
         <v>2.3</v>
       </c>
       <c r="AB91">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AC91">
-        <v>3.94</v>
+        <v>4.49</v>
       </c>
       <c r="AD91">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
         <v>1.85</v>
       </c>
       <c r="AG91">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P92">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,65 +15468,65 @@
         </is>
       </c>
       <c r="N93">
+        <v>1.75</v>
+      </c>
+      <c r="O93">
+        <v>3.2</v>
+      </c>
+      <c r="P93">
+        <v>4.2</v>
+      </c>
+      <c r="Q93">
+        <v>2.41</v>
+      </c>
+      <c r="R93">
+        <v>1.98</v>
+      </c>
+      <c r="S93">
+        <v>1.44</v>
+      </c>
+      <c r="T93">
+        <v>2.47</v>
+      </c>
+      <c r="U93">
+        <v>2.97</v>
+      </c>
+      <c r="V93">
+        <v>1.31</v>
+      </c>
+      <c r="W93">
+        <v>1.03</v>
+      </c>
+      <c r="X93">
+        <v>1.03</v>
+      </c>
+      <c r="Y93">
+        <v>1.33</v>
+      </c>
+      <c r="Z93">
+        <v>2.83</v>
+      </c>
+      <c r="AA93">
+        <v>2.08</v>
+      </c>
+      <c r="AB93">
+        <v>1.66</v>
+      </c>
+      <c r="AC93">
+        <v>3.58</v>
+      </c>
+      <c r="AD93">
+        <v>1.21</v>
+      </c>
+      <c r="AE93">
+        <v>1.04</v>
+      </c>
+      <c r="AF93">
+        <v>1.91</v>
+      </c>
+      <c r="AG93">
         <v>1.77</v>
       </c>
-      <c r="O93">
-        <v>3.3</v>
-      </c>
-      <c r="P93">
-        <v>4.8</v>
-      </c>
-      <c r="Q93">
-        <v>0</v>
-      </c>
-      <c r="R93">
-        <v>0</v>
-      </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-      <c r="T93">
-        <v>0</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <v>0</v>
-      </c>
-      <c r="W93">
-        <v>0</v>
-      </c>
-      <c r="X93">
-        <v>0</v>
-      </c>
-      <c r="Y93">
-        <v>0</v>
-      </c>
-      <c r="Z93">
-        <v>0</v>
-      </c>
-      <c r="AA93">
-        <v>0</v>
-      </c>
-      <c r="AB93">
-        <v>0</v>
-      </c>
-      <c r="AC93">
-        <v>0</v>
-      </c>
-      <c r="AD93">
-        <v>0</v>
-      </c>
-      <c r="AE93">
-        <v>0</v>
-      </c>
-      <c r="AF93">
-        <v>0</v>
-      </c>
-      <c r="AG93">
-        <v>0</v>
-      </c>
       <c r="AH93" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="O95">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P95">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q95">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="R95">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S95">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T95">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W95">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z95">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA95">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB95">
         <v>2.2</v>
       </c>
       <c r="AC95">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AD95">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG95">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16123,25 +16123,25 @@
         <v>3.1</v>
       </c>
       <c r="O97">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q97">
         <v>3.72</v>
       </c>
       <c r="R97">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S97">
         <v>1.4</v>
       </c>
       <c r="T97">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="U97">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V97">
         <v>1.44</v>
@@ -16153,16 +16153,16 @@
         <v>1.05</v>
       </c>
       <c r="Y97">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z97">
         <v>3.48</v>
       </c>
       <c r="AA97">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB97">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AC97">
         <v>3.25</v>
@@ -16174,10 +16174,10 @@
         <v>1.11</v>
       </c>
       <c r="AF97">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O98">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P98">
         <v>3.1</v>
       </c>
       <c r="Q98">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R98">
         <v>2</v>
@@ -16304,37 +16304,37 @@
         <v>2.62</v>
       </c>
       <c r="U98">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V98">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W98">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X98">
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z98">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="AA98">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB98">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC98">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD98">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE98">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
         <v>1.83</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16612,22 +16612,22 @@
         <v>2.3</v>
       </c>
       <c r="O100">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P100">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q100">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="R100">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S100">
         <v>1.36</v>
       </c>
       <c r="T100">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U100">
         <v>2.77</v>
@@ -16645,13 +16645,13 @@
         <v>1.24</v>
       </c>
       <c r="Z100">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AA100">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB100">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC100">
         <v>3.14</v>
@@ -16663,7 +16663,7 @@
         <v>1.06</v>
       </c>
       <c r="AF100">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG100">
         <v>2.05</v>
@@ -16682,7 +16682,7 @@
         <v>1.28</v>
       </c>
       <c r="AK100">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16787,13 +16787,13 @@
         <v>2</v>
       </c>
       <c r="S101">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T101">
         <v>2.66</v>
       </c>
       <c r="U101">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V101">
         <v>1.36</v>
@@ -16802,34 +16802,34 @@
         <v>1.04</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA101">
         <v>2</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC101">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="AD101">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE101">
         <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AG101">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.26</v>
       </c>
       <c r="AK101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17101,10 +17101,10 @@
         <v>1.52</v>
       </c>
       <c r="O103">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17611,34 +17611,34 @@
         <v>2.35</v>
       </c>
       <c r="V106">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W106">
         <v>1.12</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z106">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AA106">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB106">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC106">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD106">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE106">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
         <v>1.57</v>
@@ -17795,13 +17795,13 @@
         <v>1.77</v>
       </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD107">
         <v>1.27</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
         <v>1.8</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G108">
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="R108">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S108">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T108">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U108">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V108">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W108">
         <v>1.02</v>
       </c>
       <c r="X108">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Z108">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA108">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AB108">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC108">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AD108">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE108">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF108">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG108">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q109">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="R109">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T109">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U109">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="V109">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W109">
         <v>1.02</v>
       </c>
       <c r="X109">
+        <v>1.05</v>
+      </c>
+      <c r="Y109">
+        <v>1.43</v>
+      </c>
+      <c r="Z109">
+        <v>2.6</v>
+      </c>
+      <c r="AA109">
+        <v>2.35</v>
+      </c>
+      <c r="AB109">
+        <v>1.57</v>
+      </c>
+      <c r="AC109">
+        <v>4.3</v>
+      </c>
+      <c r="AD109">
+        <v>1.16</v>
+      </c>
+      <c r="AE109">
         <v>1.02</v>
       </c>
-      <c r="Y109">
-        <v>1.32</v>
-      </c>
-      <c r="Z109">
-        <v>2.88</v>
-      </c>
-      <c r="AA109">
-        <v>2.08</v>
-      </c>
-      <c r="AB109">
-        <v>1.65</v>
-      </c>
-      <c r="AC109">
-        <v>3.74</v>
-      </c>
-      <c r="AD109">
-        <v>1.19</v>
-      </c>
-      <c r="AE109">
-        <v>1.03</v>
-      </c>
       <c r="AF109">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG109">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O110">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
         <v>2.5</v>
@@ -18251,7 +18251,7 @@
         <v>3.4</v>
       </c>
       <c r="R110">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S110">
         <v>1.38</v>
@@ -18269,7 +18269,7 @@
         <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
         <v>1.24</v>
@@ -18278,13 +18278,13 @@
         <v>3.6</v>
       </c>
       <c r="AA110">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB110">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC110">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AD110">
         <v>1.33</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AK110">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O111">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
         <v>3</v>
@@ -18414,7 +18414,7 @@
         <v>3.22</v>
       </c>
       <c r="R111">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S111">
         <v>1.53</v>
@@ -18423,10 +18423,10 @@
         <v>2.47</v>
       </c>
       <c r="U111">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="V111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W111">
         <v>1.02</v>
@@ -18435,19 +18435,19 @@
         <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="Z111">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="AA111">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB111">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC111">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD111">
         <v>1.17</v>
@@ -18568,13 +18568,13 @@
         <v>1.78</v>
       </c>
       <c r="O112">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="P112">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="Q112">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="R112">
         <v>2.25</v>
@@ -18728,19 +18728,19 @@
         </is>
       </c>
       <c r="N113">
+        <v>3.05</v>
+      </c>
+      <c r="O113">
         <v>3</v>
       </c>
-      <c r="O113">
-        <v>2.95</v>
-      </c>
       <c r="P113">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q113">
-        <v>3.73</v>
+        <v>3.04</v>
       </c>
       <c r="R113">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="S113">
         <v>1.36</v>
@@ -18749,7 +18749,7 @@
         <v>2.77</v>
       </c>
       <c r="U113">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V113">
         <v>1.46</v>
@@ -18767,16 +18767,16 @@
         <v>3.95</v>
       </c>
       <c r="AA113">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB113">
         <v>2.07</v>
       </c>
       <c r="AC113">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD113">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE113">
         <v>1.14</v>
@@ -19220,28 +19220,28 @@
         <v>2.87</v>
       </c>
       <c r="O116">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P116">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q116">
         <v>3.1</v>
       </c>
       <c r="R116">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S116">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T116">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U116">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V116">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W116">
         <v>1.1</v>
@@ -19256,19 +19256,19 @@
         <v>4.33</v>
       </c>
       <c r="AA116">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB116">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AC116">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="AD116">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE116">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
         <v>1.58</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AK116">
         <v>1.36</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="O121">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P121">
-        <v>3.26</v>
+        <v>4.55</v>
       </c>
       <c r="Q121">
+        <v>2.26</v>
+      </c>
+      <c r="R121">
+        <v>2.13</v>
+      </c>
+      <c r="S121">
+        <v>1.39</v>
+      </c>
+      <c r="T121">
         <v>2.77</v>
       </c>
-      <c r="R121">
-        <v>2.06</v>
-      </c>
-      <c r="S121">
-        <v>1.42</v>
-      </c>
-      <c r="T121">
-        <v>2.65</v>
-      </c>
       <c r="U121">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="V121">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W121">
+        <v>1.04</v>
+      </c>
+      <c r="X121">
         <v>1.03</v>
       </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
       <c r="Y121">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z121">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="AA121">
+        <v>2.01</v>
+      </c>
+      <c r="AB121">
+        <v>1.88</v>
+      </c>
+      <c r="AC121">
+        <v>3.45</v>
+      </c>
+      <c r="AD121">
+        <v>1.26</v>
+      </c>
+      <c r="AE121">
+        <v>1.06</v>
+      </c>
+      <c r="AF121">
+        <v>1.86</v>
+      </c>
+      <c r="AG121">
+        <v>1.84</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>1.29</v>
+      </c>
+      <c r="AK121">
         <v>2.14</v>
-      </c>
-      <c r="AB121">
-        <v>1.77</v>
-      </c>
-      <c r="AC121">
-        <v>3.54</v>
-      </c>
-      <c r="AD121">
-        <v>1.22</v>
-      </c>
-      <c r="AE121">
-        <v>1.04</v>
-      </c>
-      <c r="AF121">
-        <v>1.83</v>
-      </c>
-      <c r="AG121">
-        <v>1.87</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.34</v>
-      </c>
-      <c r="AK121">
-        <v>1.68</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,65 +20195,65 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="O122">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="Q122">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="R122">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="S122">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T122">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U122">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="V122">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W122">
+        <v>1.03</v>
+      </c>
+      <c r="X122">
+        <v>1.02</v>
+      </c>
+      <c r="Y122">
+        <v>1.33</v>
+      </c>
+      <c r="Z122">
+        <v>3.1</v>
+      </c>
+      <c r="AA122">
+        <v>2.1</v>
+      </c>
+      <c r="AB122">
+        <v>1.7</v>
+      </c>
+      <c r="AC122">
+        <v>3.54</v>
+      </c>
+      <c r="AD122">
+        <v>1.22</v>
+      </c>
+      <c r="AE122">
         <v>1.04</v>
       </c>
-      <c r="X122">
-        <v>1.03</v>
-      </c>
-      <c r="Y122">
-        <v>1.26</v>
-      </c>
-      <c r="Z122">
-        <v>3.24</v>
-      </c>
-      <c r="AA122">
-        <v>2</v>
-      </c>
-      <c r="AB122">
-        <v>1.88</v>
-      </c>
-      <c r="AC122">
-        <v>3.24</v>
-      </c>
-      <c r="AD122">
-        <v>1.26</v>
-      </c>
-      <c r="AE122">
-        <v>1.06</v>
-      </c>
       <c r="AF122">
+        <v>1.83</v>
+      </c>
+      <c r="AG122">
         <v>1.87</v>
       </c>
-      <c r="AG122">
-        <v>1.83</v>
-      </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK122">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -20847,19 +20847,19 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q126">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="R126">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S126">
         <v>1.22</v>
@@ -20874,19 +20874,19 @@
         <v>1.63</v>
       </c>
       <c r="W126">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X126">
         <v>1</v>
       </c>
       <c r="Y126">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z126">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA126">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB126">
         <v>2.5</v>
@@ -20920,7 +20920,7 @@
         <v>1.2</v>
       </c>
       <c r="AK126">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O127">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="P127">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="Q127">
         <v>3.64</v>
@@ -21025,10 +21025,10 @@
         <v>2.35</v>
       </c>
       <c r="S127">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T127">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="U127">
         <v>2.11</v>
@@ -21037,25 +21037,25 @@
         <v>1.67</v>
       </c>
       <c r="W127">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z127">
-        <v>5.05</v>
+        <v>5.22</v>
       </c>
       <c r="AA127">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB127">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AC127">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD127">
         <v>1.67</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O128">
         <v>4</v>
       </c>
       <c r="P128">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q128">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R128">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S128">
         <v>1.14</v>
@@ -21194,7 +21194,7 @@
         <v>4.6</v>
       </c>
       <c r="U128">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V128">
         <v>1.89</v>
@@ -21206,25 +21206,25 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z128">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA128">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AB128">
         <v>3.28</v>
       </c>
       <c r="AC128">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AD128">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AE128">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF128">
         <v>1.28</v>
@@ -21246,7 +21246,7 @@
         <v>1.2</v>
       </c>
       <c r="AK128">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,58 +21336,58 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="O129">
-        <v>4.8</v>
+        <v>4.35</v>
       </c>
       <c r="P129">
-        <v>4.84</v>
+        <v>4.95</v>
       </c>
       <c r="Q129">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R129">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="S129">
         <v>1.14</v>
       </c>
       <c r="T129">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="U129">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V129">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W129">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X129">
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z129">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA129">
         <v>1.28</v>
       </c>
       <c r="AB129">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="AC129">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD129">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AE129">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AF129">
         <v>1.36</v>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK129">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21505,10 +21505,10 @@
         <v>4.1</v>
       </c>
       <c r="P130">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q130">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R130">
         <v>2.55</v>
@@ -21520,37 +21520,37 @@
         <v>4.25</v>
       </c>
       <c r="U130">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V130">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W130">
         <v>1.2</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
         <v>1.05</v>
       </c>
       <c r="Z130">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AA130">
         <v>1.36</v>
       </c>
       <c r="AB130">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AC130">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AD130">
         <v>1.88</v>
       </c>
       <c r="AE130">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AF130">
         <v>1.35</v>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK130">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21665,61 +21665,61 @@
         <v>3.2</v>
       </c>
       <c r="O131">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="P131">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q131">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="R131">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="S131">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="T131">
-        <v>5.35</v>
+        <v>6.8</v>
       </c>
       <c r="U131">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V131">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="W131">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X131">
         <v>1</v>
       </c>
       <c r="Y131">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z131">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AA131">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB131">
-        <v>4.33</v>
+        <v>5.21</v>
       </c>
       <c r="AC131">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AD131">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AE131">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF131">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AG131">
-        <v>4.06</v>
+        <v>4.4</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
       <c r="AK131">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,19 +21825,19 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O132">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P132">
         <v>6.5</v>
       </c>
       <c r="Q132">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R132">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S132">
         <v>1.32</v>
@@ -21846,28 +21846,28 @@
         <v>3.1</v>
       </c>
       <c r="U132">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V132">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W132">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X132">
         <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z132">
         <v>4.2</v>
       </c>
       <c r="AA132">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB132">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC132">
         <v>2.45</v>
@@ -21876,13 +21876,13 @@
         <v>1.44</v>
       </c>
       <c r="AE132">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF132">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG132">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.21</v>
       </c>
       <c r="AK132">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21994,10 +21994,10 @@
         <v>3.4</v>
       </c>
       <c r="P133">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q133">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="R133">
         <v>2.13</v>
@@ -22021,22 +22021,22 @@
         <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z133">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AA133">
         <v>1.88</v>
       </c>
       <c r="AB133">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC133">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD133">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE133">
         <v>1.07</v>
@@ -22045,7 +22045,7 @@
         <v>1.67</v>
       </c>
       <c r="AG133">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>1.28</v>
       </c>
       <c r="AK133">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="O134">
         <v>3.2</v>
       </c>
       <c r="P134">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q134">
         <v>2.33</v>
@@ -22166,49 +22166,49 @@
         <v>2.2</v>
       </c>
       <c r="S134">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T134">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U134">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V134">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W134">
         <v>1.04</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z134">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AA134">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB134">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC134">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD134">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE134">
         <v>1.05</v>
       </c>
       <c r="AF134">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG134">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O135">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P135">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q135">
         <v>3.02</v>
@@ -22344,7 +22344,7 @@
         <v>1.06</v>
       </c>
       <c r="X135">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y135">
         <v>1.19</v>
@@ -22356,10 +22356,10 @@
         <v>1.8</v>
       </c>
       <c r="AB135">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC135">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AD135">
         <v>1.39</v>
@@ -22368,10 +22368,10 @@
         <v>1.15</v>
       </c>
       <c r="AF135">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG135">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK135">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="O136">
         <v>3.7</v>
@@ -22486,7 +22486,7 @@
         <v>1.67</v>
       </c>
       <c r="Q136">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="R136">
         <v>2.33</v>
@@ -22501,25 +22501,25 @@
         <v>2.31</v>
       </c>
       <c r="V136">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W136">
         <v>1.11</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
         <v>1.12</v>
       </c>
       <c r="Z136">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA136">
         <v>1.56</v>
       </c>
       <c r="AB136">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC136">
         <v>2.29</v>
@@ -22528,13 +22528,13 @@
         <v>1.5</v>
       </c>
       <c r="AE136">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF136">
         <v>1.53</v>
       </c>
       <c r="AG136">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.22</v>
       </c>
       <c r="AK136">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O137">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P137">
+        <v>3</v>
+      </c>
+      <c r="Q137">
         <v>2.87</v>
       </c>
-      <c r="Q137">
-        <v>3.12</v>
-      </c>
       <c r="R137">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S137">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T137">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="U137">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V137">
+        <v>1.33</v>
+      </c>
+      <c r="W137">
+        <v>1.02</v>
+      </c>
+      <c r="X137">
+        <v>1.01</v>
+      </c>
+      <c r="Y137">
+        <v>1.3</v>
+      </c>
+      <c r="Z137">
+        <v>3.04</v>
+      </c>
+      <c r="AA137">
+        <v>2.1</v>
+      </c>
+      <c r="AB137">
+        <v>1.72</v>
+      </c>
+      <c r="AC137">
+        <v>3.78</v>
+      </c>
+      <c r="AD137">
+        <v>1.21</v>
+      </c>
+      <c r="AE137">
+        <v>1.08</v>
+      </c>
+      <c r="AF137">
+        <v>1.8</v>
+      </c>
+      <c r="AG137">
+        <v>1.9</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
         <v>1.31</v>
       </c>
-      <c r="W137">
-        <v>1.01</v>
-      </c>
-      <c r="X137">
-        <v>1.02</v>
-      </c>
-      <c r="Y137">
-        <v>1.33</v>
-      </c>
-      <c r="Z137">
-        <v>2.83</v>
-      </c>
-      <c r="AA137">
-        <v>2.25</v>
-      </c>
-      <c r="AB137">
+      <c r="AK137">
         <v>1.61</v>
-      </c>
-      <c r="AC137">
-        <v>3.9</v>
-      </c>
-      <c r="AD137">
-        <v>1.18</v>
-      </c>
-      <c r="AE137">
-        <v>1.02</v>
-      </c>
-      <c r="AF137">
-        <v>1.85</v>
-      </c>
-      <c r="AG137">
-        <v>1.85</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.36</v>
-      </c>
-      <c r="AK137">
-        <v>1.51</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O138">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P138">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22969,10 +22969,10 @@
         <v>1.91</v>
       </c>
       <c r="O139">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P139">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q139">
         <v>2.6</v>
@@ -22987,7 +22987,7 @@
         <v>2.39</v>
       </c>
       <c r="U139">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="V139">
         <v>1.26</v>
@@ -22999,10 +22999,10 @@
         <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Z139">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AA139">
         <v>2.6</v>
@@ -23020,10 +23020,10 @@
         <v>1.01</v>
       </c>
       <c r="AF139">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG139">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.34</v>
       </c>
       <c r="AK139">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,7 +23129,7 @@
         </is>
       </c>
       <c r="N140">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="O140">
         <v>5.5</v>
@@ -23141,52 +23141,52 @@
         <v>6.5</v>
       </c>
       <c r="R140">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="S140">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T140">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U140">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="V140">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W140">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X140">
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z140">
         <v>6.05</v>
       </c>
       <c r="AA140">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB140">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AC140">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD140">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE140">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF140">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG140">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="AK140">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23292,10 +23292,10 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O141">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P141">
         <v>4.28</v>
@@ -23304,7 +23304,7 @@
         <v>2.14</v>
       </c>
       <c r="R141">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S141">
         <v>1.19</v>
@@ -23328,19 +23328,19 @@
         <v>1.07</v>
       </c>
       <c r="Z141">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA141">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB141">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AC141">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AD141">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE141">
         <v>1.26</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK141">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O142">
         <v>3.5</v>
@@ -23464,13 +23464,13 @@
         <v>2.2</v>
       </c>
       <c r="Q142">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R142">
         <v>2.34</v>
       </c>
       <c r="S142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T142">
         <v>3.42</v>
@@ -23500,7 +23500,7 @@
         <v>2.35</v>
       </c>
       <c r="AC142">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AD142">
         <v>1.49</v>
@@ -23512,7 +23512,7 @@
         <v>1.48</v>
       </c>
       <c r="AG142">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>1.25</v>
       </c>
       <c r="AK142">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23781,31 +23781,31 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="O144">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q144">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="R144">
         <v>2.38</v>
       </c>
       <c r="S144">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T144">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U144">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V144">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W144">
         <v>1.1</v>
@@ -23817,7 +23817,7 @@
         <v>1.15</v>
       </c>
       <c r="Z144">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA144">
         <v>1.59</v>
@@ -23826,7 +23826,7 @@
         <v>2.21</v>
       </c>
       <c r="AC144">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AD144">
         <v>1.46</v>
@@ -23835,10 +23835,10 @@
         <v>1.16</v>
       </c>
       <c r="AF144">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG144">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.22</v>
       </c>
       <c r="AK144">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P146">
         <v>4.5</v>
@@ -24119,16 +24119,16 @@
         <v>2.38</v>
       </c>
       <c r="R146">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="S146">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T146">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U146">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="V146">
         <v>1.31</v>
@@ -24140,19 +24140,19 @@
         <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z146">
         <v>2.76</v>
       </c>
       <c r="AA146">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB146">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC146">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="AD146">
         <v>1.19</v>
@@ -24164,7 +24164,7 @@
         <v>2.01</v>
       </c>
       <c r="AG146">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK146">
         <v>2.02</v>
@@ -24925,13 +24925,13 @@
         <v>2.06</v>
       </c>
       <c r="O151">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P151">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="Q151">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R151">
         <v>2.46</v>
@@ -24940,25 +24940,25 @@
         <v>1.2</v>
       </c>
       <c r="T151">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="U151">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="V151">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W151">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X151">
         <v>1.02</v>
       </c>
       <c r="Y151">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z151">
-        <v>5.45</v>
+        <v>6.14</v>
       </c>
       <c r="AA151">
         <v>1.38</v>
@@ -24967,7 +24967,7 @@
         <v>2.64</v>
       </c>
       <c r="AC151">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD151">
         <v>1.78</v>
@@ -24976,10 +24976,10 @@
         <v>1.28</v>
       </c>
       <c r="AF151">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG151">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25085,16 +25085,16 @@
         </is>
       </c>
       <c r="N152">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="O152">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P152">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q152">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="R152">
         <v>2.14</v>
@@ -25130,7 +25130,7 @@
         <v>2.09</v>
       </c>
       <c r="AC152">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD152">
         <v>1.4</v>
@@ -25139,7 +25139,7 @@
         <v>1.16</v>
       </c>
       <c r="AF152">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
         <v>2.26</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AK152">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25411,19 +25411,19 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O154">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P154">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q154">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="R154">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="S154">
         <v>1.28</v>
@@ -25444,19 +25444,19 @@
         <v>1.02</v>
       </c>
       <c r="Y154">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z154">
         <v>4.1</v>
       </c>
       <c r="AA154">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB154">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC154">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AD154">
         <v>1.41</v>
@@ -25465,10 +25465,10 @@
         <v>1.13</v>
       </c>
       <c r="AF154">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK154">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27693,10 +27693,10 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="O168">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P168">
         <v>2.81</v>
@@ -27705,7 +27705,7 @@
         <v>2.56</v>
       </c>
       <c r="R168">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S168">
         <v>1.18</v>
@@ -27735,7 +27735,7 @@
         <v>1.34</v>
       </c>
       <c r="AB168">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="AC168">
         <v>1.96</v>
@@ -27744,13 +27744,13 @@
         <v>1.8</v>
       </c>
       <c r="AE168">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF168">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG168">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31614,55 +31614,55 @@
         <v>0</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T192">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U192">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V192">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X192">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -36504,55 +36504,55 @@
         <v>3.3</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S222">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T222">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U222">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V222">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W222">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X222">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y222">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z222">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA222">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB222">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC222">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD222">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG222">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK222">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -39112,55 +39112,55 @@
         <v>0</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,80 +46438,80 @@
         </is>
       </c>
       <c r="N283">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O283">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P283">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q283">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R283">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="S283">
+        <v>1.62</v>
+      </c>
+      <c r="T283">
+        <v>2.2</v>
+      </c>
+      <c r="U283">
+        <v>4.2</v>
+      </c>
+      <c r="V283">
+        <v>1.15</v>
+      </c>
+      <c r="W283">
+        <v>1.03</v>
+      </c>
+      <c r="X283">
+        <v>1.15</v>
+      </c>
+      <c r="Y283">
+        <v>1.67</v>
+      </c>
+      <c r="Z283">
+        <v>2.1</v>
+      </c>
+      <c r="AA283">
+        <v>3.4</v>
+      </c>
+      <c r="AB283">
+        <v>1.33</v>
+      </c>
+      <c r="AC283">
+        <v>7</v>
+      </c>
+      <c r="AD283">
+        <v>1.1</v>
+      </c>
+      <c r="AE283">
+        <v>1.03</v>
+      </c>
+      <c r="AF283">
+        <v>2.34</v>
+      </c>
+      <c r="AG283">
         <v>1.5</v>
       </c>
-      <c r="T283">
-        <v>2.5</v>
-      </c>
-      <c r="U283">
-        <v>3.5</v>
-      </c>
-      <c r="V283">
-        <v>1.25</v>
-      </c>
-      <c r="W283">
-        <v>1.04</v>
-      </c>
-      <c r="X283">
-        <v>1.11</v>
-      </c>
-      <c r="Y283">
-        <v>1.5</v>
-      </c>
-      <c r="Z283">
-        <v>2.45</v>
-      </c>
-      <c r="AA283">
-        <v>2.63</v>
-      </c>
-      <c r="AB283">
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ283">
         <v>1.44</v>
       </c>
-      <c r="AC283">
-        <v>5</v>
-      </c>
-      <c r="AD283">
-        <v>1.15</v>
-      </c>
-      <c r="AE283">
-        <v>1.04</v>
-      </c>
-      <c r="AF283">
-        <v>2.1</v>
-      </c>
-      <c r="AG283">
-        <v>1.67</v>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ283">
-        <v>1.4</v>
-      </c>
       <c r="AK283">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="O284">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P284">
-        <v>3.54</v>
+        <v>2.47</v>
       </c>
       <c r="Q284">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R284">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S284">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="T284">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U284">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="V284">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W284">
         <v>1.04</v>
       </c>
       <c r="X284">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y284">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z284">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA284">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AB284">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC284">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD284">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE284">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF284">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG284">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>1.4</v>
       </c>
       <c r="AK284">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="O285">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P285">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="Q285">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R285">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S285">
+        <v>1.65</v>
+      </c>
+      <c r="T285">
+        <v>2.1</v>
+      </c>
+      <c r="U285">
+        <v>3.95</v>
+      </c>
+      <c r="V285">
+        <v>1.17</v>
+      </c>
+      <c r="W285">
+        <v>1.04</v>
+      </c>
+      <c r="X285">
+        <v>1.14</v>
+      </c>
+      <c r="Y285">
         <v>1.62</v>
       </c>
-      <c r="T285">
+      <c r="Z285">
         <v>2.2</v>
       </c>
-      <c r="U285">
-        <v>4.2</v>
-      </c>
-      <c r="V285">
-        <v>1.15</v>
-      </c>
-      <c r="W285">
-        <v>1.03</v>
-      </c>
-      <c r="X285">
-        <v>1.15</v>
-      </c>
-      <c r="Y285">
-        <v>1.67</v>
-      </c>
-      <c r="Z285">
-        <v>2.1</v>
-      </c>
       <c r="AA285">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="AB285">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC285">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD285">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE285">
         <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG285">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK285">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.85</v>
+        <v>5.6</v>
       </c>
       <c r="O291">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P291">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q291">
-        <v>2.38</v>
+        <v>5.45</v>
       </c>
       <c r="R291">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S291">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T291">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U291">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="V291">
+        <v>1.44</v>
+      </c>
+      <c r="W291">
+        <v>1.06</v>
+      </c>
+      <c r="X291">
+        <v>1.03</v>
+      </c>
+      <c r="Y291">
+        <v>1.19</v>
+      </c>
+      <c r="Z291">
+        <v>3.82</v>
+      </c>
+      <c r="AA291">
+        <v>1.75</v>
+      </c>
+      <c r="AB291">
+        <v>2.05</v>
+      </c>
+      <c r="AC291">
+        <v>2.8</v>
+      </c>
+      <c r="AD291">
         <v>1.34</v>
       </c>
-      <c r="W291">
-        <v>1.04</v>
-      </c>
-      <c r="X291">
-        <v>1.02</v>
-      </c>
-      <c r="Y291">
-        <v>1.31</v>
-      </c>
-      <c r="Z291">
-        <v>2.94</v>
-      </c>
-      <c r="AA291">
-        <v>2.05</v>
-      </c>
-      <c r="AB291">
-        <v>1.75</v>
-      </c>
-      <c r="AC291">
-        <v>3.54</v>
-      </c>
-      <c r="AD291">
-        <v>1.22</v>
-      </c>
       <c r="AE291">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF291">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG291">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK291">
-        <v>1.97</v>
+        <v>1.15</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>5.6</v>
+        <v>1.85</v>
       </c>
       <c r="O292">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P292">
-        <v>1.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q292">
-        <v>5.45</v>
+        <v>2.38</v>
       </c>
       <c r="R292">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S292">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T292">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U292">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="V292">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W292">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X292">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y292">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="Z292">
-        <v>3.82</v>
+        <v>2.94</v>
       </c>
       <c r="AA292">
+        <v>2.05</v>
+      </c>
+      <c r="AB292">
         <v>1.75</v>
       </c>
-      <c r="AB292">
-        <v>2.05</v>
-      </c>
       <c r="AC292">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD292">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE292">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF292">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AG292">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK292">
-        <v>1.15</v>
+        <v>1.97</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
+        <v>2</v>
+      </c>
+      <c r="O296">
+        <v>2.8</v>
+      </c>
+      <c r="P296">
+        <v>4.08</v>
+      </c>
+      <c r="Q296">
         <v>2.7</v>
       </c>
-      <c r="O296">
-        <v>2.5</v>
-      </c>
-      <c r="P296">
-        <v>3</v>
-      </c>
-      <c r="Q296">
-        <v>3.18</v>
-      </c>
       <c r="R296">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S296">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T296">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U296">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="V296">
+        <v>1.22</v>
+      </c>
+      <c r="W296">
+        <v>1</v>
+      </c>
+      <c r="X296">
+        <v>1.11</v>
+      </c>
+      <c r="Y296">
+        <v>1.5</v>
+      </c>
+      <c r="Z296">
+        <v>2.4</v>
+      </c>
+      <c r="AA296">
+        <v>2.63</v>
+      </c>
+      <c r="AB296">
+        <v>1.44</v>
+      </c>
+      <c r="AC296">
+        <v>5</v>
+      </c>
+      <c r="AD296">
         <v>1.15</v>
       </c>
-      <c r="W296">
-        <v>1.03</v>
-      </c>
-      <c r="X296">
-        <v>1.15</v>
-      </c>
-      <c r="Y296">
-        <v>1.7</v>
-      </c>
-      <c r="Z296">
-        <v>2.05</v>
-      </c>
-      <c r="AA296">
-        <v>3.4</v>
-      </c>
-      <c r="AB296">
-        <v>1.33</v>
-      </c>
-      <c r="AC296">
-        <v>7</v>
-      </c>
-      <c r="AD296">
-        <v>1.08</v>
-      </c>
       <c r="AE296">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF296">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AG296">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>1.4</v>
       </c>
       <c r="AK296">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O297">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P297">
-        <v>4.08</v>
+        <v>3</v>
       </c>
       <c r="Q297">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R297">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S297">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T297">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U297">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="V297">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W297">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X297">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y297">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z297">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA297">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AB297">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC297">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD297">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE297">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF297">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AG297">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>1.4</v>
       </c>
       <c r="AK297">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49381,55 +49381,55 @@
         <v>4</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G305">
@@ -50033,55 +50033,55 @@
         <v>0</v>
       </c>
       <c r="Q305">
-        <v>3.14</v>
+        <v>2.36</v>
       </c>
       <c r="R305">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="S305">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="T305">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="U305">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V305">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W305">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X305">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y305">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z305">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="AA305">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="AB305">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC305">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD305">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AE305">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF305">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG305">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK305">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G306">
@@ -50196,71 +50196,71 @@
         <v>0</v>
       </c>
       <c r="Q306">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="R306">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="S306">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="T306">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="U306">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V306">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W306">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X306">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y306">
+        <v>1.5</v>
+      </c>
+      <c r="Z306">
+        <v>2.38</v>
+      </c>
+      <c r="AA306">
+        <v>2.46</v>
+      </c>
+      <c r="AB306">
+        <v>1.5</v>
+      </c>
+      <c r="AC306">
+        <v>4.8</v>
+      </c>
+      <c r="AD306">
+        <v>1.12</v>
+      </c>
+      <c r="AE306">
+        <v>1.05</v>
+      </c>
+      <c r="AF306">
+        <v>2.08</v>
+      </c>
+      <c r="AG306">
+        <v>1.64</v>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ306">
         <v>1.3</v>
       </c>
-      <c r="Z306">
-        <v>2.97</v>
-      </c>
-      <c r="AA306">
-        <v>2.04</v>
-      </c>
-      <c r="AB306">
-        <v>1.68</v>
-      </c>
-      <c r="AC306">
-        <v>3.58</v>
-      </c>
-      <c r="AD306">
-        <v>1.21</v>
-      </c>
-      <c r="AE306">
-        <v>1.03</v>
-      </c>
-      <c r="AF306">
-        <v>1.91</v>
-      </c>
-      <c r="AG306">
-        <v>1.77</v>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ306">
-        <v>1.24</v>
-      </c>
       <c r="AK306">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AL306">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="R7">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.54</v>
+        <v>3.72</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB7">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC7">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="AD7">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
         <v>1.33</v>
@@ -1634,43 +1634,43 @@
         <v>3.04</v>
       </c>
       <c r="U8">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.21</v>
+      </c>
+      <c r="Z8">
+        <v>3.62</v>
+      </c>
+      <c r="AA8">
+        <v>1.83</v>
+      </c>
+      <c r="AB8">
+        <v>1.99</v>
+      </c>
+      <c r="AC8">
+        <v>2.89</v>
+      </c>
+      <c r="AD8">
+        <v>1.32</v>
+      </c>
+      <c r="AE8">
         <v>1.08</v>
       </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.2</v>
-      </c>
-      <c r="Z8">
-        <v>3.72</v>
-      </c>
-      <c r="AA8">
-        <v>1.77</v>
-      </c>
-      <c r="AB8">
-        <v>2.07</v>
-      </c>
-      <c r="AC8">
-        <v>2.72</v>
-      </c>
-      <c r="AD8">
-        <v>1.36</v>
-      </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
       <c r="AF8">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="R9">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="U9">
         <v>2.65</v>
@@ -1803,22 +1803,22 @@
         <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
         <v>2.89</v>
@@ -1830,10 +1830,10 @@
         <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG9">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="P19">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q19">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
         <v>2.19</v>
@@ -3445,16 +3445,16 @@
         <v>3.24</v>
       </c>
       <c r="AA19">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
         <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE19">
         <v>1.08</v>
@@ -3463,7 +3463,7 @@
         <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q20">
         <v>4.22</v>
@@ -3593,31 +3593,31 @@
         <v>2.94</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
+        <v>1.33</v>
+      </c>
+      <c r="Z20">
+        <v>3.28</v>
+      </c>
+      <c r="AA20">
+        <v>2.04</v>
+      </c>
+      <c r="AB20">
+        <v>1.76</v>
+      </c>
+      <c r="AC20">
+        <v>3.44</v>
+      </c>
+      <c r="AD20">
         <v>1.28</v>
-      </c>
-      <c r="Z20">
-        <v>3.08</v>
-      </c>
-      <c r="AA20">
-        <v>2.05</v>
-      </c>
-      <c r="AB20">
-        <v>1.75</v>
-      </c>
-      <c r="AC20">
-        <v>3.65</v>
-      </c>
-      <c r="AD20">
-        <v>1.23</v>
       </c>
       <c r="AE20">
         <v>1.04</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="P23">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S23">
         <v>1.41</v>
@@ -4079,7 +4079,7 @@
         <v>2.59</v>
       </c>
       <c r="U23">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="V23">
         <v>1.33</v>
@@ -4088,7 +4088,7 @@
         <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.34</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q24">
         <v>2.1</v>
@@ -4260,7 +4260,7 @@
         <v>3.9</v>
       </c>
       <c r="AA24">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB24">
         <v>2.02</v>
@@ -4272,7 +4272,7 @@
         <v>1.35</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
         <v>1.73</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.88</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="U29">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>3.24</v>
+        <v>4.25</v>
       </c>
       <c r="AA29">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AB29">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AC29">
-        <v>3.12</v>
+        <v>2.39</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>4.88</v>
       </c>
       <c r="Q30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R30">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T30">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="U30">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="AA30">
+        <v>1.94</v>
+      </c>
+      <c r="AB30">
+        <v>1.88</v>
+      </c>
+      <c r="AC30">
+        <v>3.12</v>
+      </c>
+      <c r="AD30">
+        <v>1.28</v>
+      </c>
+      <c r="AE30">
+        <v>1.07</v>
+      </c>
+      <c r="AF30">
         <v>1.83</v>
       </c>
-      <c r="AB30">
-        <v>1.99</v>
-      </c>
-      <c r="AC30">
-        <v>2.89</v>
-      </c>
-      <c r="AD30">
-        <v>1.32</v>
-      </c>
-      <c r="AE30">
-        <v>1.08</v>
-      </c>
-      <c r="AF30">
-        <v>1.77</v>
-      </c>
       <c r="AG30">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
         <v>3.6</v>
       </c>
       <c r="P31">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA31">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB31">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="AC31">
-        <v>2.39</v>
+        <v>2.89</v>
       </c>
       <c r="AD31">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O50">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q50">
         <v>3.82</v>
@@ -8477,7 +8477,7 @@
         <v>1.28</v>
       </c>
       <c r="T50">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
         <v>2.41</v>
@@ -8486,34 +8486,34 @@
         <v>1.49</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z50">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB50">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AC50">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
         <v>2.28</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="O52">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P52">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="R52">
         <v>1.97</v>
@@ -8827,7 +8827,7 @@
         <v>2.12</v>
       </c>
       <c r="AB52">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC52">
         <v>3.52</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G68">
@@ -11402,71 +11402,71 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="R68">
-        <v>2.51</v>
+        <v>2.16</v>
       </c>
       <c r="S68">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="U68">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
       <c r="V68">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>6.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA68">
+        <v>1.66</v>
+      </c>
+      <c r="AB68">
+        <v>2.25</v>
+      </c>
+      <c r="AC68">
+        <v>2.55</v>
+      </c>
+      <c r="AD68">
+        <v>1.44</v>
+      </c>
+      <c r="AE68">
+        <v>1.15</v>
+      </c>
+      <c r="AF68">
+        <v>1.5</v>
+      </c>
+      <c r="AG68">
+        <v>2.42</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.31</v>
       </c>
-      <c r="AB68">
-        <v>2.92</v>
-      </c>
-      <c r="AC68">
-        <v>1.92</v>
-      </c>
-      <c r="AD68">
-        <v>1.9</v>
-      </c>
-      <c r="AE68">
-        <v>1.31</v>
-      </c>
-      <c r="AF68">
-        <v>1.36</v>
-      </c>
-      <c r="AG68">
-        <v>2.9</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.22</v>
-      </c>
       <c r="AK68">
-        <v>2.06</v>
+        <v>1.44</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G69">
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.22</v>
+        <v>2.14</v>
       </c>
       <c r="R69">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T69">
-        <v>3.16</v>
+        <v>4.25</v>
       </c>
       <c r="U69">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="V69">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="W69">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
         <v>1.04</v>
       </c>
-      <c r="Y69">
-        <v>1.15</v>
-      </c>
       <c r="Z69">
-        <v>4.25</v>
+        <v>6.75</v>
       </c>
       <c r="AA69">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AB69">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="AC69">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="AD69">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AE69">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF69">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG69">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK69">
-        <v>1.45</v>
+        <v>2.09</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="O71">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -11903,7 +11903,7 @@
         <v>3.16</v>
       </c>
       <c r="U71">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="V71">
         <v>1.53</v>
@@ -11927,19 +11927,19 @@
         <v>2.25</v>
       </c>
       <c r="AC71">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="AD71">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AE71">
         <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG71">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12048,16 +12048,16 @@
         <v>2.24</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P72">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
       </c>
       <c r="R72">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S72">
         <v>1.24</v>
@@ -12090,7 +12090,7 @@
         <v>2.38</v>
       </c>
       <c r="AC72">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD72">
         <v>1.61</v>
@@ -12540,25 +12540,25 @@
         <v>5.5</v>
       </c>
       <c r="P75">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Q75">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="R75">
         <v>2.94</v>
       </c>
       <c r="S75">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
         <v>4.3</v>
       </c>
       <c r="U75">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V75">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="W75">
         <v>1.21</v>
@@ -12570,13 +12570,13 @@
         <v>1.05</v>
       </c>
       <c r="Z75">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA75">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AB75">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AC75">
         <v>1.85</v>
@@ -12585,13 +12585,13 @@
         <v>1.92</v>
       </c>
       <c r="AE75">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF75">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG75">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.09</v>
+        <v>3.63</v>
       </c>
       <c r="AK75">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O90">
         <v>3</v>
       </c>
       <c r="P90">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q90">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="R90">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S90">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T90">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="V90">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
         <v>1.01</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y90">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z90">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AA90">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB90">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC90">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE90">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG90">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK90">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="O91">
         <v>3</v>
       </c>
       <c r="P91">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q91">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="R91">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S91">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T91">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U91">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="V91">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W91">
         <v>1.01</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z91">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AA91">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB91">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC91">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="AD91">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF91">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG91">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK91">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="O92">
+        <v>3.05</v>
+      </c>
+      <c r="P92">
         <v>3.1</v>
       </c>
-      <c r="P92">
-        <v>1.98</v>
-      </c>
       <c r="Q92">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S92">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T92">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U92">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V92">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA92">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC92">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK92">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,37 +15468,37 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="O93">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P93">
-        <v>4.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q93">
-        <v>2.41</v>
+        <v>4.45</v>
       </c>
       <c r="R93">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S93">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T93">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U93">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="V93">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
         <v>1.33</v>
@@ -15507,25 +15507,25 @@
         <v>2.83</v>
       </c>
       <c r="AA93">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB93">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC93">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AD93">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE93">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF93">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG93">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK93">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="O94">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK99">
         <v>1.33</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="R100">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S100">
+        <v>1.4</v>
+      </c>
+      <c r="T100">
+        <v>2.66</v>
+      </c>
+      <c r="U100">
+        <v>3</v>
+      </c>
+      <c r="V100">
         <v>1.36</v>
-      </c>
-      <c r="T100">
-        <v>2.84</v>
-      </c>
-      <c r="U100">
-        <v>2.77</v>
-      </c>
-      <c r="V100">
-        <v>1.38</v>
       </c>
       <c r="W100">
         <v>1.04</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z100">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AA100">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AC100">
         <v>3.14</v>
       </c>
       <c r="AD100">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE100">
         <v>1.06</v>
       </c>
       <c r="AF100">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q101">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="R101">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S101">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="U101">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W101">
         <v>1.04</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z101">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AA101">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB101">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC101">
         <v>3.14</v>
       </c>
       <c r="AD101">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE101">
         <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AG101">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK101">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O123">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P123">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="Q123">
         <v>2.88</v>
@@ -20394,19 +20394,19 @@
         <v>1.36</v>
       </c>
       <c r="Z123">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AA123">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AB123">
         <v>1.61</v>
       </c>
       <c r="AC123">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD123">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE123">
         <v>1.03</v>
@@ -20415,7 +20415,7 @@
         <v>1.89</v>
       </c>
       <c r="AG123">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>4</v>
       </c>
       <c r="P132">
-        <v>6.5</v>
+        <v>6.21</v>
       </c>
       <c r="Q132">
         <v>2</v>
@@ -21846,19 +21846,19 @@
         <v>3.1</v>
       </c>
       <c r="U132">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V132">
         <v>1.51</v>
       </c>
       <c r="W132">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X132">
         <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z132">
         <v>4.2</v>
@@ -21882,7 +21882,7 @@
         <v>1.7</v>
       </c>
       <c r="AG132">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21994,10 +21994,10 @@
         <v>3.4</v>
       </c>
       <c r="P133">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q133">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="R133">
         <v>2.13</v>
@@ -22030,13 +22030,13 @@
         <v>1.88</v>
       </c>
       <c r="AB133">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC133">
         <v>3.1</v>
       </c>
       <c r="AD133">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE133">
         <v>1.07</v>
@@ -22061,7 +22061,7 @@
         <v>1.28</v>
       </c>
       <c r="AK133">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O141">
         <v>4.2</v>
@@ -23313,10 +23313,10 @@
         <v>3.96</v>
       </c>
       <c r="U141">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V141">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W141">
         <v>1.16</v>
@@ -23328,19 +23328,19 @@
         <v>1.07</v>
       </c>
       <c r="Z141">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA141">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB141">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AC141">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AD141">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE141">
         <v>1.26</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O142">
         <v>3.5</v>
@@ -23464,7 +23464,7 @@
         <v>2.2</v>
       </c>
       <c r="Q142">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="R142">
         <v>2.34</v>
@@ -23476,13 +23476,13 @@
         <v>3.42</v>
       </c>
       <c r="U142">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="V142">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W142">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X142">
         <v>1.02</v>
@@ -23500,7 +23500,7 @@
         <v>2.35</v>
       </c>
       <c r="AC142">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD142">
         <v>1.49</v>
@@ -23944,31 +23944,31 @@
         </is>
       </c>
       <c r="N145">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O145">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q145">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="R145">
         <v>2.17</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T145">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U145">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V145">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W145">
         <v>1.07</v>
@@ -23983,13 +23983,13 @@
         <v>3.78</v>
       </c>
       <c r="AA145">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB145">
         <v>2.04</v>
       </c>
       <c r="AC145">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="AD145">
         <v>1.36</v>
@@ -23998,10 +23998,10 @@
         <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -25909,10 +25909,10 @@
         <v>6.5</v>
       </c>
       <c r="Q157">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R157">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="S157">
         <v>1.18</v>
@@ -25921,7 +25921,7 @@
         <v>4.1</v>
       </c>
       <c r="U157">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V157">
         <v>1.76</v>
@@ -25933,16 +25933,16 @@
         <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z157">
-        <v>6.05</v>
+        <v>6.72</v>
       </c>
       <c r="AA157">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB157">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AC157">
         <v>1.97</v>
@@ -25954,7 +25954,7 @@
         <v>1.31</v>
       </c>
       <c r="AF157">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG157">
         <v>2.23</v>
@@ -25973,7 +25973,7 @@
         <v>1.15</v>
       </c>
       <c r="AK157">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26072,10 +26072,10 @@
         <v>0</v>
       </c>
       <c r="Q158">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R158">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S158">
         <v>1.21</v>
@@ -26090,7 +26090,7 @@
         <v>1.72</v>
       </c>
       <c r="W158">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X158">
         <v>1.02</v>
@@ -26102,25 +26102,25 @@
         <v>6</v>
       </c>
       <c r="AA158">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB158">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="AC158">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AD158">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE158">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF158">
         <v>1.35</v>
       </c>
       <c r="AG158">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="O160">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P160">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G164">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,25 +39103,25 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q238">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R238">
         <v>1.96</v>
       </c>
       <c r="S238">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T238">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U238">
         <v>3.18</v>
@@ -39130,22 +39130,22 @@
         <v>1.28</v>
       </c>
       <c r="W238">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X238">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y238">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z238">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA238">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB238">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC238">
         <v>4.05</v>
@@ -39157,10 +39157,10 @@
         <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG238">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK238">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,25 +39266,25 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O239">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P239">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q239">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R239">
         <v>1.96</v>
       </c>
       <c r="S239">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T239">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U239">
         <v>3.18</v>
@@ -39293,22 +39293,22 @@
         <v>1.28</v>
       </c>
       <c r="W239">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X239">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y239">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z239">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA239">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB239">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC239">
         <v>4.05</v>
@@ -39320,10 +39320,10 @@
         <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG239">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK239">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,80 +46438,80 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O283">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P283">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="Q283">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R283">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="S283">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T283">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U283">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="V283">
+        <v>1.25</v>
+      </c>
+      <c r="W283">
+        <v>1.04</v>
+      </c>
+      <c r="X283">
+        <v>1.11</v>
+      </c>
+      <c r="Y283">
+        <v>1.5</v>
+      </c>
+      <c r="Z283">
+        <v>2.45</v>
+      </c>
+      <c r="AA283">
+        <v>2.63</v>
+      </c>
+      <c r="AB283">
+        <v>1.44</v>
+      </c>
+      <c r="AC283">
+        <v>5</v>
+      </c>
+      <c r="AD283">
         <v>1.15</v>
       </c>
-      <c r="W283">
-        <v>1.03</v>
-      </c>
-      <c r="X283">
-        <v>1.15</v>
-      </c>
-      <c r="Y283">
+      <c r="AE283">
+        <v>1.04</v>
+      </c>
+      <c r="AF283">
+        <v>2.1</v>
+      </c>
+      <c r="AG283">
         <v>1.67</v>
       </c>
-      <c r="Z283">
-        <v>2.1</v>
-      </c>
-      <c r="AA283">
-        <v>3.4</v>
-      </c>
-      <c r="AB283">
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ283">
+        <v>1.4</v>
+      </c>
+      <c r="AK283">
         <v>1.33</v>
-      </c>
-      <c r="AC283">
-        <v>7</v>
-      </c>
-      <c r="AD283">
-        <v>1.1</v>
-      </c>
-      <c r="AE283">
-        <v>1.03</v>
-      </c>
-      <c r="AF283">
-        <v>2.34</v>
-      </c>
-      <c r="AG283">
-        <v>1.5</v>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ283">
-        <v>1.44</v>
-      </c>
-      <c r="AK283">
-        <v>1.36</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="O284">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P284">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q284">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R284">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S284">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="T284">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U284">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="V284">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W284">
         <v>1.04</v>
       </c>
       <c r="X284">
+        <v>1.14</v>
+      </c>
+      <c r="Y284">
+        <v>1.62</v>
+      </c>
+      <c r="Z284">
+        <v>2.2</v>
+      </c>
+      <c r="AA284">
+        <v>2.87</v>
+      </c>
+      <c r="AB284">
+        <v>1.4</v>
+      </c>
+      <c r="AC284">
+        <v>6</v>
+      </c>
+      <c r="AD284">
         <v>1.11</v>
       </c>
-      <c r="Y284">
-        <v>1.5</v>
-      </c>
-      <c r="Z284">
-        <v>2.45</v>
-      </c>
-      <c r="AA284">
-        <v>2.63</v>
-      </c>
-      <c r="AB284">
-        <v>1.44</v>
-      </c>
-      <c r="AC284">
-        <v>5</v>
-      </c>
-      <c r="AD284">
-        <v>1.15</v>
-      </c>
       <c r="AE284">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF284">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG284">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>1.4</v>
       </c>
       <c r="AK284">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O285">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P285">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="Q285">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R285">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S285">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="T285">
+        <v>2.2</v>
+      </c>
+      <c r="U285">
+        <v>4.2</v>
+      </c>
+      <c r="V285">
+        <v>1.15</v>
+      </c>
+      <c r="W285">
+        <v>1.03</v>
+      </c>
+      <c r="X285">
+        <v>1.15</v>
+      </c>
+      <c r="Y285">
+        <v>1.67</v>
+      </c>
+      <c r="Z285">
         <v>2.1</v>
       </c>
-      <c r="U285">
-        <v>3.95</v>
-      </c>
-      <c r="V285">
-        <v>1.17</v>
-      </c>
-      <c r="W285">
-        <v>1.04</v>
-      </c>
-      <c r="X285">
-        <v>1.14</v>
-      </c>
-      <c r="Y285">
-        <v>1.62</v>
-      </c>
-      <c r="Z285">
-        <v>2.2</v>
-      </c>
       <c r="AA285">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB285">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC285">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD285">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE285">
         <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG285">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK285">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G311">
@@ -51011,55 +51011,55 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>5</v>
+        <v>3.26</v>
       </c>
       <c r="R311">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="S311">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T311">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="U311">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="V311">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="W311">
+        <v>1.12</v>
+      </c>
+      <c r="X311">
+        <v>1.03</v>
+      </c>
+      <c r="Y311">
         <v>1.13</v>
       </c>
-      <c r="X311">
-        <v>0</v>
-      </c>
-      <c r="Y311">
-        <v>1.07</v>
-      </c>
       <c r="Z311">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA311">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AB311">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="AC311">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="AD311">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AE311">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AF311">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG311">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK311">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G312">
@@ -51174,55 +51174,55 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="R312">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="S312">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T312">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="U312">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="V312">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="W312">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z312">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA312">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AB312">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="AC312">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AD312">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE312">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AF312">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG312">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK312">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AL312">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="U8">
         <v>2.65</v>
@@ -1640,22 +1640,22 @@
         <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
         <v>2.89</v>
@@ -1667,10 +1667,10 @@
         <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>3.54</v>
+        <v>3.82</v>
       </c>
       <c r="AA9">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC9">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG9">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
         <v>3.5</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q10">
-        <v>4.05</v>
+        <v>2.28</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>3.04</v>
+      </c>
+      <c r="U10">
+        <v>2.65</v>
+      </c>
+      <c r="V10">
+        <v>1.42</v>
+      </c>
+      <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.21</v>
+      </c>
+      <c r="Z10">
+        <v>3.62</v>
+      </c>
+      <c r="AA10">
+        <v>1.83</v>
+      </c>
+      <c r="AB10">
+        <v>1.99</v>
+      </c>
+      <c r="AC10">
+        <v>2.89</v>
+      </c>
+      <c r="AD10">
         <v>1.32</v>
       </c>
-      <c r="T10">
-        <v>3.1</v>
-      </c>
-      <c r="U10">
-        <v>2.59</v>
-      </c>
-      <c r="V10">
-        <v>1.44</v>
-      </c>
-      <c r="W10">
-        <v>1.06</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.19</v>
-      </c>
-      <c r="Z10">
-        <v>3.82</v>
-      </c>
-      <c r="AA10">
-        <v>1.78</v>
-      </c>
-      <c r="AB10">
-        <v>2.06</v>
-      </c>
-      <c r="AC10">
-        <v>2.8</v>
-      </c>
-      <c r="AD10">
-        <v>1.34</v>
-      </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="O85">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P85">
-        <v>4.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q85">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="R85">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="U85">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="V85">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W85">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14200,7 +14200,7 @@
         <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA85">
         <v>1.44</v>
@@ -14209,35 +14209,35 @@
         <v>2.7</v>
       </c>
       <c r="AC85">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD85">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE85">
+        <v>1.25</v>
+      </c>
+      <c r="AF85">
+        <v>1.42</v>
+      </c>
+      <c r="AG85">
+        <v>2.61</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.24</v>
       </c>
-      <c r="AF85">
-        <v>1.56</v>
-      </c>
-      <c r="AG85">
-        <v>2.46</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.22</v>
-      </c>
       <c r="AK85">
-        <v>2.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,34 +14327,34 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="O86">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P86">
-        <v>1.81</v>
+        <v>4.25</v>
       </c>
       <c r="Q86">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S86">
         <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="U86">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W86">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X86">
         <v>1.02</v>
@@ -14363,7 +14363,7 @@
         <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA86">
         <v>1.44</v>
@@ -14372,19 +14372,19 @@
         <v>2.7</v>
       </c>
       <c r="AC86">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AD86">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF86">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AG86">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.27</v>
+        <v>2.26</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="O121">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P121">
-        <v>4.55</v>
+        <v>3.26</v>
       </c>
       <c r="Q121">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="R121">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="S121">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T121">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U121">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="V121">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W121">
+        <v>1.03</v>
+      </c>
+      <c r="X121">
+        <v>1.02</v>
+      </c>
+      <c r="Y121">
+        <v>1.33</v>
+      </c>
+      <c r="Z121">
+        <v>3.1</v>
+      </c>
+      <c r="AA121">
+        <v>2.1</v>
+      </c>
+      <c r="AB121">
+        <v>1.7</v>
+      </c>
+      <c r="AC121">
+        <v>3.54</v>
+      </c>
+      <c r="AD121">
+        <v>1.22</v>
+      </c>
+      <c r="AE121">
         <v>1.04</v>
       </c>
-      <c r="X121">
-        <v>1.03</v>
-      </c>
-      <c r="Y121">
-        <v>1.27</v>
-      </c>
-      <c r="Z121">
-        <v>3.18</v>
-      </c>
-      <c r="AA121">
-        <v>2.01</v>
-      </c>
-      <c r="AB121">
-        <v>1.88</v>
-      </c>
-      <c r="AC121">
-        <v>3.45</v>
-      </c>
-      <c r="AD121">
-        <v>1.26</v>
-      </c>
-      <c r="AE121">
-        <v>1.06</v>
-      </c>
       <c r="AF121">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK121">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P122">
-        <v>3.26</v>
+        <v>4.55</v>
       </c>
       <c r="Q122">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="R122">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="S122">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T122">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U122">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="V122">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W122">
+        <v>1.04</v>
+      </c>
+      <c r="X122">
         <v>1.03</v>
       </c>
-      <c r="X122">
-        <v>1.02</v>
-      </c>
       <c r="Y122">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA122">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB122">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AC122">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="AD122">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE122">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG122">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK122">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="O123">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="Q123">
         <v>2.88</v>
@@ -20385,7 +20385,7 @@
         <v>1.31</v>
       </c>
       <c r="W123">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
         <v>1.03</v>
@@ -20397,25 +20397,25 @@
         <v>2.72</v>
       </c>
       <c r="AA123">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AB123">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC123">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD123">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE123">
         <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG123">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -22643,13 +22643,13 @@
         <v>2.2</v>
       </c>
       <c r="O137">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P137">
         <v>3</v>
       </c>
       <c r="Q137">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="R137">
         <v>2</v>
@@ -22658,7 +22658,7 @@
         <v>1.41</v>
       </c>
       <c r="T137">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="U137">
         <v>2.95</v>
@@ -22676,25 +22676,25 @@
         <v>1.3</v>
       </c>
       <c r="Z137">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA137">
         <v>2.1</v>
       </c>
       <c r="AB137">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC137">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AD137">
         <v>1.21</v>
       </c>
       <c r="AE137">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF137">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG137">
         <v>1.9</v>
@@ -22713,7 +22713,7 @@
         <v>1.31</v>
       </c>
       <c r="AK137">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -28837,16 +28837,16 @@
         <v>2.2</v>
       </c>
       <c r="O175">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P175">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q175">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="R175">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S175">
         <v>1.4</v>
@@ -28867,25 +28867,25 @@
         <v>1.04</v>
       </c>
       <c r="Y175">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z175">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AA175">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB175">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC175">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD175">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE175">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF175">
         <v>1.75</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G231">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O271">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P271">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q271">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R271">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S271">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T271">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U271">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="V271">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W271">
         <v>1.08</v>
       </c>
       <c r="X271">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y271">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z271">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA271">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB271">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC271">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="AD271">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE271">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF271">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG271">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>1.25</v>
       </c>
       <c r="AK271">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
+        <v>2.5</v>
+      </c>
+      <c r="O273">
         <v>1.85</v>
       </c>
-      <c r="O273">
-        <v>2.87</v>
-      </c>
       <c r="P273">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="Q273">
         <v>2.5</v>
@@ -44823,19 +44823,19 @@
         <v>1.91</v>
       </c>
       <c r="S273">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T273">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U273">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V273">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W273">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X273">
         <v>1.14</v>
@@ -44844,16 +44844,16 @@
         <v>1.62</v>
       </c>
       <c r="Z273">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AA273">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB273">
         <v>1.36</v>
       </c>
       <c r="AC273">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD273">
         <v>1.11</v>
@@ -44862,10 +44862,10 @@
         <v>1.03</v>
       </c>
       <c r="AF273">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG273">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK273">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O274">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P274">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="O283">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P283">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q283">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R283">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S283">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T283">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U283">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V283">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W283">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X283">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y283">
         <v>1.5</v>
       </c>
       <c r="Z283">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA283">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="AB283">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC283">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD283">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE283">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF283">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG283">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK283">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,80 +46601,80 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="O284">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="P284">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="Q284">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R284">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S284">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="T284">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U284">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="V284">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="W284">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X284">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y284">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z284">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA284">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB284">
+        <v>1.5</v>
+      </c>
+      <c r="AC284">
+        <v>5</v>
+      </c>
+      <c r="AD284">
+        <v>1.15</v>
+      </c>
+      <c r="AE284">
+        <v>1.05</v>
+      </c>
+      <c r="AF284">
+        <v>2</v>
+      </c>
+      <c r="AG284">
+        <v>1.73</v>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ284">
+        <v>1.36</v>
+      </c>
+      <c r="AK284">
         <v>1.4</v>
-      </c>
-      <c r="AC284">
-        <v>6</v>
-      </c>
-      <c r="AD284">
-        <v>1.11</v>
-      </c>
-      <c r="AE284">
-        <v>1.03</v>
-      </c>
-      <c r="AF284">
-        <v>2.3</v>
-      </c>
-      <c r="AG284">
-        <v>1.53</v>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI284" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ284">
-        <v>1.4</v>
-      </c>
-      <c r="AK284">
-        <v>1.57</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="O285">
         <v>2.6</v>
       </c>
       <c r="P285">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q285">
         <v>3.7</v>
@@ -46779,37 +46779,37 @@
         <v>1.8</v>
       </c>
       <c r="S285">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="T285">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="U285">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V285">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W285">
         <v>1.03</v>
       </c>
       <c r="X285">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y285">
         <v>1.67</v>
       </c>
       <c r="Z285">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA285">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB285">
         <v>1.33</v>
       </c>
       <c r="AC285">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="AD285">
         <v>1.1</v>
@@ -46818,10 +46818,10 @@
         <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG285">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
+        <v>1.38</v>
+      </c>
+      <c r="AK285">
         <v>1.44</v>
-      </c>
-      <c r="AK285">
-        <v>1.36</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47579,28 +47579,28 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O290">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P290">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q290">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R290">
         <v>2.15</v>
       </c>
       <c r="S290">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T290">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U290">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V290">
         <v>1.39</v>
@@ -47612,31 +47612,31 @@
         <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z290">
-        <v>3.24</v>
+        <v>3.59</v>
       </c>
       <c r="AA290">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB290">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC290">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AD290">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE290">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF290">
         <v>1.77</v>
       </c>
       <c r="AG290">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK290">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47742,22 +47742,22 @@
         </is>
       </c>
       <c r="N291">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="O291">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P291">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="Q291">
-        <v>5.45</v>
+        <v>6.3</v>
       </c>
       <c r="R291">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S291">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T291">
         <v>3.1</v>
@@ -47769,22 +47769,22 @@
         <v>1.44</v>
       </c>
       <c r="W291">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X291">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y291">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z291">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AA291">
         <v>1.75</v>
       </c>
       <c r="AB291">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC291">
         <v>2.8</v>
@@ -47796,10 +47796,10 @@
         <v>1.09</v>
       </c>
       <c r="AF291">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AG291">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK291">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47917,43 +47917,43 @@
         <v>2.38</v>
       </c>
       <c r="R292">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S292">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T292">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U292">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="V292">
+        <v>1.36</v>
+      </c>
+      <c r="W292">
+        <v>1.05</v>
+      </c>
+      <c r="X292">
+        <v>1.05</v>
+      </c>
+      <c r="Y292">
         <v>1.34</v>
-      </c>
-      <c r="W292">
-        <v>1.04</v>
-      </c>
-      <c r="X292">
-        <v>1.02</v>
-      </c>
-      <c r="Y292">
-        <v>1.31</v>
       </c>
       <c r="Z292">
         <v>2.94</v>
       </c>
       <c r="AA292">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB292">
         <v>1.75</v>
       </c>
       <c r="AC292">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="AD292">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE292">
         <v>1.04</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="O296">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P296">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="Q296">
         <v>2.7</v>
@@ -48572,10 +48572,10 @@
         <v>1.95</v>
       </c>
       <c r="S296">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T296">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U296">
         <v>3.5</v>
@@ -48593,13 +48593,13 @@
         <v>1.5</v>
       </c>
       <c r="Z296">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA296">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB296">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC296">
         <v>5</v>
@@ -48608,10 +48608,10 @@
         <v>1.15</v>
       </c>
       <c r="AE296">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF296">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AG296">
         <v>1.62</v>
@@ -48720,25 +48720,25 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O297">
         <v>2.5</v>
       </c>
       <c r="P297">
+        <v>3.1</v>
+      </c>
+      <c r="Q297">
         <v>3</v>
-      </c>
-      <c r="Q297">
-        <v>3.18</v>
       </c>
       <c r="R297">
         <v>1.83</v>
       </c>
       <c r="S297">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="T297">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U297">
         <v>4.3</v>
@@ -48750,34 +48750,34 @@
         <v>1.03</v>
       </c>
       <c r="X297">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Y297">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z297">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="AA297">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB297">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC297">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AD297">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE297">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF297">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG297">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,7 +48790,7 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK297">
         <v>1.57</v>
@@ -48889,7 +48889,7 @@
         <v>3.3</v>
       </c>
       <c r="P298">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q298">
         <v>2.33</v>
@@ -48898,22 +48898,22 @@
         <v>1.89</v>
       </c>
       <c r="S298">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T298">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="U298">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V298">
         <v>1.22</v>
       </c>
       <c r="W298">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X298">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y298">
         <v>1.51</v>
@@ -48922,25 +48922,25 @@
         <v>2.39</v>
       </c>
       <c r="AA298">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AB298">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AC298">
         <v>4.8</v>
       </c>
       <c r="AD298">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE298">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF298">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG298">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK298">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -50679,10 +50679,10 @@
         <v>2.5</v>
       </c>
       <c r="O309">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="P309">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50715,10 +50715,10 @@
         <v>0</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC309">
         <v>0</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O310">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P310">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G311">
@@ -51011,55 +51011,55 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="R311">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="S311">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T311">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="U311">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="V311">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="W311">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X311">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y311">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z311">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA311">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AB311">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="AC311">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AD311">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE311">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AF311">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG311">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK311">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G312">
@@ -51174,55 +51174,55 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>5</v>
+        <v>3.26</v>
       </c>
       <c r="R312">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="S312">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T312">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="U312">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="V312">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="W312">
+        <v>1.12</v>
+      </c>
+      <c r="X312">
+        <v>1.03</v>
+      </c>
+      <c r="Y312">
         <v>1.13</v>
       </c>
-      <c r="X312">
-        <v>1.02</v>
-      </c>
-      <c r="Y312">
-        <v>1.07</v>
-      </c>
       <c r="Z312">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA312">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AB312">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="AC312">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="AD312">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AE312">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AF312">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG312">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK312">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51494,34 +51494,34 @@
         <v>3.26</v>
       </c>
       <c r="O314">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P314">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q314">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="R314">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S314">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T314">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U314">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V314">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W314">
         <v>1.06</v>
       </c>
       <c r="X314">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y314">
         <v>1.28</v>
@@ -51530,25 +51530,25 @@
         <v>3.3</v>
       </c>
       <c r="AA314">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB314">
         <v>1.9</v>
       </c>
       <c r="AC314">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD314">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE314">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF314">
         <v>1.69</v>
       </c>
       <c r="AG314">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK314">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -52143,10 +52143,10 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="O318">
-        <v>4.65</v>
+        <v>2.35</v>
       </c>
       <c r="P318">
         <v>8.4</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -807,25 +807,25 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R3">
         <v>2.11</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
         <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.53</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q8">
-        <v>3.7</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U8">
         <v>2.65</v>
@@ -1640,22 +1640,22 @@
         <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA8">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC8">
         <v>2.89</v>
@@ -1667,10 +1667,10 @@
         <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.35</v>
+        <v>2.04</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U9">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
       <c r="AA9">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AD9">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG9">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
         <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q10">
-        <v>2.28</v>
+        <v>4.05</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB10">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="R17">
         <v>1.99</v>
@@ -7170,10 +7170,10 @@
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U42">
         <v>2.2</v>
@@ -7182,37 +7182,37 @@
         <v>1.63</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AC42">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AD42">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE42">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG42">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AK42">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="O61">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q61">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R61">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
         <v>1.25</v>
@@ -10279,28 +10279,28 @@
         <v>1.56</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>4.87</v>
+        <v>4.81</v>
       </c>
       <c r="AA61">
         <v>1.54</v>
       </c>
       <c r="AB61">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AC61">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD61">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE61">
         <v>1.18</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
         <v>1.54</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G68">
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="R68">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T68">
-        <v>3.16</v>
+        <v>4.25</v>
       </c>
       <c r="U68">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
         <v>1.04</v>
       </c>
-      <c r="Y68">
-        <v>1.2</v>
-      </c>
       <c r="Z68">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA68">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="AC68">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AD68">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF68">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG68">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G69">
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="R69">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="S69">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>4.25</v>
+        <v>3.16</v>
       </c>
       <c r="U69">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="V69">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="W69">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA69">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="AB69">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="AC69">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AD69">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AE69">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF69">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK69">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O74">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
         <v>3.8</v>
@@ -12386,31 +12386,31 @@
         <v>2.07</v>
       </c>
       <c r="S74">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U74">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="V74">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W74">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z74">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AA74">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AB74">
         <v>1.72</v>
@@ -12425,10 +12425,10 @@
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK74">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="O76">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="P76">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q76">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R76">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S76">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T76">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="U76">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V76">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W76">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z76">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="AA76">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB76">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AC76">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AD76">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE76">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF76">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG76">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK76">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12866,58 +12866,58 @@
         <v>3.1</v>
       </c>
       <c r="P77">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="Q77">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="R77">
         <v>2</v>
       </c>
       <c r="S77">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T77">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U77">
         <v>2.75</v>
       </c>
       <c r="V77">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X77">
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z77">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA77">
         <v>2.03</v>
       </c>
       <c r="AB77">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC77">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD77">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG77">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AK77">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,52 +13026,52 @@
         <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="Q78">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="R78">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T78">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="U78">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V78">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
         <v>1.05</v>
       </c>
-      <c r="X78">
-        <v>1</v>
-      </c>
       <c r="Y78">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z78">
         <v>3.62</v>
       </c>
       <c r="AA78">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB78">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC78">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="AD78">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE78">
         <v>1.08</v>
@@ -13080,7 +13080,7 @@
         <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK78">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="O79">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P79">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q79">
         <v>2.67</v>
@@ -13225,10 +13225,10 @@
         <v>3.04</v>
       </c>
       <c r="AA79">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB79">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC79">
         <v>3.42</v>
@@ -13240,10 +13240,10 @@
         <v>1.04</v>
       </c>
       <c r="AF79">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG79">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13355,13 +13355,13 @@
         <v>4.3</v>
       </c>
       <c r="P80">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="Q80">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S80">
         <v>1.32</v>
@@ -13382,16 +13382,16 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z80">
         <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB80">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC80">
         <v>2.81</v>
@@ -13403,7 +13403,7 @@
         <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG80">
         <v>1.75</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK80">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13844,7 +13844,7 @@
         <v>3.2</v>
       </c>
       <c r="P83">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q83">
         <v>2.92</v>
@@ -13853,16 +13853,16 @@
         <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T83">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
         <v>2.7</v>
       </c>
       <c r="V83">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
         <v>1.07</v>
@@ -13880,7 +13880,7 @@
         <v>1.95</v>
       </c>
       <c r="AB83">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
         <v>3.22</v>
@@ -13889,13 +13889,13 @@
         <v>1.32</v>
       </c>
       <c r="AE83">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF83">
         <v>1.68</v>
       </c>
       <c r="AG83">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="R84">
         <v>2.23</v>
@@ -14028,7 +14028,7 @@
         <v>1.46</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
         <v>1</v>
@@ -14043,7 +14043,7 @@
         <v>1.67</v>
       </c>
       <c r="AB84">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC84">
         <v>2.59</v>
@@ -14055,10 +14055,10 @@
         <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG84">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
         <v>1.81</v>
@@ -14185,13 +14185,13 @@
         <v>3.88</v>
       </c>
       <c r="U85">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="V85">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W85">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14206,7 +14206,7 @@
         <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AC85">
         <v>2.12</v>
@@ -14218,7 +14218,7 @@
         <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
         <v>2.61</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O86">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="P86">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="Q86">
         <v>2</v>
@@ -14342,10 +14342,10 @@
         <v>2.44</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
         <v>2.2</v>
@@ -14354,7 +14354,7 @@
         <v>1.69</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
         <v>1.02</v>
@@ -14366,25 +14366,25 @@
         <v>5.55</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB86">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC86">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AD86">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE86">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF86">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AG86">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,58 +14653,58 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="P88">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
       </c>
       <c r="R88">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="S88">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T88">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U88">
         <v>2.89</v>
       </c>
       <c r="V88">
+        <v>1.4</v>
+      </c>
+      <c r="W88">
+        <v>1.05</v>
+      </c>
+      <c r="X88">
+        <v>1.07</v>
+      </c>
+      <c r="Y88">
         <v>1.36</v>
       </c>
-      <c r="W88">
-        <v>1.03</v>
-      </c>
-      <c r="X88">
-        <v>1.01</v>
-      </c>
-      <c r="Y88">
-        <v>1.28</v>
-      </c>
       <c r="Z88">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA88">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB88">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC88">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="AD88">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE88">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF88">
         <v>1.93</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R89">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S89">
         <v>1.38</v>
@@ -14843,13 +14843,13 @@
         <v>1.39</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
         <v>3.38</v>
@@ -14858,7 +14858,7 @@
         <v>1.89</v>
       </c>
       <c r="AB89">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC89">
         <v>3.45</v>
@@ -14870,10 +14870,10 @@
         <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG89">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK89">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,46 +14979,46 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="O90">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P90">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q90">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="R90">
         <v>1.92</v>
       </c>
       <c r="S90">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T90">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U90">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V90">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z90">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA90">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AB90">
         <v>1.59</v>
@@ -15027,10 +15027,10 @@
         <v>4.49</v>
       </c>
       <c r="AD90">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF90">
         <v>1.85</v>
@@ -15052,7 +15052,7 @@
         <v>1.35</v>
       </c>
       <c r="AK90">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,28 +15142,28 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="O91">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q91">
         <v>2.77</v>
       </c>
       <c r="R91">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S91">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T91">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="U91">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V91">
         <v>1.29</v>
@@ -15175,16 +15175,16 @@
         <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z91">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AA91">
         <v>2.35</v>
       </c>
       <c r="AB91">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC91">
         <v>4.5</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,37 +15468,37 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="O93">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P93">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q93">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="R93">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S93">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T93">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U93">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V93">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
         <v>1.33</v>
@@ -15507,25 +15507,25 @@
         <v>2.83</v>
       </c>
       <c r="AA93">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB93">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC93">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AD93">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE93">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG93">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,37 +15631,37 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="O94">
+        <v>3.1</v>
+      </c>
+      <c r="P94">
+        <v>2</v>
+      </c>
+      <c r="Q94">
+        <v>4.45</v>
+      </c>
+      <c r="R94">
+        <v>2</v>
+      </c>
+      <c r="S94">
+        <v>1.4</v>
+      </c>
+      <c r="T94">
+        <v>2.75</v>
+      </c>
+      <c r="U94">
         <v>3.2</v>
       </c>
-      <c r="P94">
-        <v>4.2</v>
-      </c>
-      <c r="Q94">
-        <v>2.41</v>
-      </c>
-      <c r="R94">
-        <v>1.98</v>
-      </c>
-      <c r="S94">
-        <v>1.44</v>
-      </c>
-      <c r="T94">
-        <v>2.47</v>
-      </c>
-      <c r="U94">
-        <v>2.97</v>
-      </c>
       <c r="V94">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.33</v>
@@ -15670,25 +15670,25 @@
         <v>2.83</v>
       </c>
       <c r="AA94">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB94">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC94">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AD94">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF94">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG94">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17934,7 +17934,7 @@
         <v>2.56</v>
       </c>
       <c r="U108">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V108">
         <v>1.3</v>
@@ -17986,7 +17986,7 @@
         <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,43 +18076,43 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O109">
         <v>3</v>
       </c>
       <c r="P109">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q109">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="R109">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S109">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T109">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U109">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="V109">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W109">
         <v>1.02</v>
       </c>
       <c r="X109">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z109">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AA109">
         <v>2.35</v>
@@ -18121,19 +18121,19 @@
         <v>1.57</v>
       </c>
       <c r="AC109">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD109">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE109">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF109">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AG109">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK109">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="O110">
         <v>3.4</v>
@@ -18254,49 +18254,49 @@
         <v>2.1</v>
       </c>
       <c r="S110">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T110">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U110">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X110">
         <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z110">
-        <v>3.6</v>
+        <v>4.02</v>
       </c>
       <c r="AA110">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB110">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC110">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD110">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE110">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF110">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG110">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>3</v>
       </c>
       <c r="Q111">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="R111">
         <v>2</v>
@@ -18426,25 +18426,25 @@
         <v>3.4</v>
       </c>
       <c r="V111">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W111">
         <v>1.02</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y111">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z111">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="AA111">
         <v>2.3</v>
       </c>
       <c r="AB111">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC111">
         <v>4.33</v>
@@ -18475,7 +18475,7 @@
         <v>1.4</v>
       </c>
       <c r="AK111">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19220,22 +19220,22 @@
         <v>2.87</v>
       </c>
       <c r="O116">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P116">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q116">
         <v>3.1</v>
       </c>
       <c r="R116">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S116">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U116">
         <v>2.52</v>
@@ -19244,37 +19244,37 @@
         <v>1.52</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y116">
         <v>1.2</v>
       </c>
       <c r="Z116">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="AA116">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AB116">
         <v>2.21</v>
       </c>
       <c r="AC116">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="AD116">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE116">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF116">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG116">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19552,7 +19552,7 @@
         <v>3.25</v>
       </c>
       <c r="Q118">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R118">
         <v>2.3</v>
@@ -19564,7 +19564,7 @@
         <v>3.18</v>
       </c>
       <c r="U118">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V118">
         <v>1.46</v>
@@ -19573,25 +19573,25 @@
         <v>1.07</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z118">
         <v>4.1</v>
       </c>
       <c r="AA118">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB118">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AC118">
         <v>2.62</v>
       </c>
       <c r="AD118">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE118">
         <v>1.11</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="O121">
+        <v>3.7</v>
+      </c>
+      <c r="P121">
+        <v>4.6</v>
+      </c>
+      <c r="Q121">
+        <v>2.17</v>
+      </c>
+      <c r="R121">
+        <v>2.23</v>
+      </c>
+      <c r="S121">
+        <v>1.36</v>
+      </c>
+      <c r="T121">
+        <v>2.88</v>
+      </c>
+      <c r="U121">
+        <v>2.66</v>
+      </c>
+      <c r="V121">
+        <v>1.4</v>
+      </c>
+      <c r="W121">
+        <v>1.04</v>
+      </c>
+      <c r="X121">
+        <v>1.03</v>
+      </c>
+      <c r="Y121">
+        <v>1.31</v>
+      </c>
+      <c r="Z121">
+        <v>3.42</v>
+      </c>
+      <c r="AA121">
+        <v>2.01</v>
+      </c>
+      <c r="AB121">
+        <v>1.78</v>
+      </c>
+      <c r="AC121">
         <v>3.4</v>
       </c>
-      <c r="P121">
-        <v>3.26</v>
-      </c>
-      <c r="Q121">
-        <v>2.7</v>
-      </c>
-      <c r="R121">
-        <v>1.96</v>
-      </c>
-      <c r="S121">
-        <v>1.42</v>
-      </c>
-      <c r="T121">
-        <v>2.65</v>
-      </c>
-      <c r="U121">
-        <v>3.02</v>
-      </c>
-      <c r="V121">
-        <v>1.33</v>
-      </c>
-      <c r="W121">
-        <v>1.03</v>
-      </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
-      <c r="Y121">
-        <v>1.33</v>
-      </c>
-      <c r="Z121">
-        <v>3.1</v>
-      </c>
-      <c r="AA121">
-        <v>2.1</v>
-      </c>
-      <c r="AB121">
-        <v>1.7</v>
-      </c>
-      <c r="AC121">
-        <v>3.54</v>
-      </c>
       <c r="AD121">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE121">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG121">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AK121">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,80 +20195,80 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="O122">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>4.55</v>
+        <v>3.26</v>
       </c>
       <c r="Q122">
-        <v>2.26</v>
+        <v>2.77</v>
       </c>
       <c r="R122">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="S122">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U122">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="V122">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W122">
+        <v>1.03</v>
+      </c>
+      <c r="X122">
         <v>1.04</v>
       </c>
-      <c r="X122">
-        <v>1.03</v>
-      </c>
       <c r="Y122">
+        <v>1.32</v>
+      </c>
+      <c r="Z122">
+        <v>2.89</v>
+      </c>
+      <c r="AA122">
+        <v>2.08</v>
+      </c>
+      <c r="AB122">
+        <v>1.67</v>
+      </c>
+      <c r="AC122">
+        <v>3.9</v>
+      </c>
+      <c r="AD122">
+        <v>1.22</v>
+      </c>
+      <c r="AE122">
+        <v>1.05</v>
+      </c>
+      <c r="AF122">
+        <v>1.83</v>
+      </c>
+      <c r="AG122">
+        <v>1.87</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ122">
         <v>1.27</v>
       </c>
-      <c r="Z122">
-        <v>3.18</v>
-      </c>
-      <c r="AA122">
-        <v>2.01</v>
-      </c>
-      <c r="AB122">
-        <v>1.88</v>
-      </c>
-      <c r="AC122">
-        <v>3.45</v>
-      </c>
-      <c r="AD122">
-        <v>1.26</v>
-      </c>
-      <c r="AE122">
-        <v>1.06</v>
-      </c>
-      <c r="AF122">
-        <v>1.86</v>
-      </c>
-      <c r="AG122">
-        <v>1.84</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.29</v>
-      </c>
       <c r="AK122">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O124">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P124">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O134">
         <v>3.2</v>
@@ -22166,49 +22166,49 @@
         <v>2.2</v>
       </c>
       <c r="S134">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T134">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U134">
         <v>3</v>
       </c>
       <c r="V134">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W134">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z134">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA134">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB134">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC134">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AD134">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG134">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22480,28 +22480,28 @@
         <v>4</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P136">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q136">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R136">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S136">
         <v>1.25</v>
       </c>
       <c r="T136">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U136">
         <v>2.31</v>
       </c>
       <c r="V136">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W136">
         <v>1.11</v>
@@ -22510,13 +22510,13 @@
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA136">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB136">
         <v>2.4</v>
@@ -22525,7 +22525,7 @@
         <v>2.29</v>
       </c>
       <c r="AD136">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE136">
         <v>1.22</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="AK136">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O138">
         <v>3.54</v>
       </c>
       <c r="P138">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22969,22 +22969,22 @@
         <v>1.91</v>
       </c>
       <c r="O139">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P139">
         <v>3.9</v>
       </c>
       <c r="Q139">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R139">
         <v>1.93</v>
       </c>
       <c r="S139">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="T139">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="U139">
         <v>3.3</v>
@@ -22993,37 +22993,37 @@
         <v>1.26</v>
       </c>
       <c r="W139">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y139">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z139">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AA139">
         <v>2.6</v>
       </c>
       <c r="AB139">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC139">
-        <v>5.16</v>
+        <v>5.25</v>
       </c>
       <c r="AD139">
         <v>1.13</v>
       </c>
       <c r="AE139">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF139">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG139">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.34</v>
       </c>
       <c r="AK139">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23781,16 +23781,16 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O144">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P144">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q144">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R144">
         <v>2.38</v>
@@ -23802,19 +23802,19 @@
         <v>3.5</v>
       </c>
       <c r="U144">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V144">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W144">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X144">
         <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
         <v>4.25</v>
@@ -23826,7 +23826,7 @@
         <v>2.21</v>
       </c>
       <c r="AC144">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AD144">
         <v>1.46</v>
@@ -23835,10 +23835,10 @@
         <v>1.16</v>
       </c>
       <c r="AF144">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG144">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O151">
         <v>4</v>
@@ -24934,22 +24934,22 @@
         <v>2.5</v>
       </c>
       <c r="R151">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S151">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T151">
         <v>4</v>
       </c>
       <c r="U151">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="V151">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W151">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X151">
         <v>1.02</v>
@@ -24958,7 +24958,7 @@
         <v>1.13</v>
       </c>
       <c r="Z151">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="AA151">
         <v>1.38</v>
@@ -24970,16 +24970,16 @@
         <v>2.08</v>
       </c>
       <c r="AD151">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE151">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF151">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG151">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25085,31 +25085,31 @@
         </is>
       </c>
       <c r="N152">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O152">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P152">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q152">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="R152">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S152">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T152">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="U152">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="V152">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W152">
         <v>1.08</v>
@@ -25121,7 +25121,7 @@
         <v>1.18</v>
       </c>
       <c r="Z152">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA152">
         <v>1.7</v>
@@ -25136,13 +25136,13 @@
         <v>1.4</v>
       </c>
       <c r="AE152">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF152">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG152">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AK152">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25414,25 +25414,25 @@
         <v>2.25</v>
       </c>
       <c r="O154">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q154">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R154">
         <v>2.19</v>
       </c>
       <c r="S154">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T154">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U154">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V154">
         <v>1.49</v>
@@ -25447,19 +25447,19 @@
         <v>1.19</v>
       </c>
       <c r="Z154">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA154">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB154">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AC154">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AD154">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE154">
         <v>1.13</v>
@@ -25468,7 +25468,7 @@
         <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK154">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -27539,34 +27539,34 @@
         <v>2.05</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA167">
         <v>2</v>
@@ -27575,19 +27575,19 @@
         <v>1.8</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27859,16 +27859,16 @@
         <v>1.67</v>
       </c>
       <c r="O169">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P169">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q169">
         <v>2.23</v>
       </c>
       <c r="R169">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S169">
         <v>1.36</v>
@@ -27877,10 +27877,10 @@
         <v>2.88</v>
       </c>
       <c r="U169">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V169">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W169">
         <v>1.04</v>
@@ -27889,19 +27889,19 @@
         <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z169">
         <v>3.54</v>
       </c>
       <c r="AA169">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB169">
         <v>1.85</v>
       </c>
       <c r="AC169">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD169">
         <v>1.3</v>
@@ -27910,10 +27910,10 @@
         <v>1.07</v>
       </c>
       <c r="AF169">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG169">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -28834,16 +28834,16 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O175">
         <v>3.1</v>
       </c>
       <c r="P175">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q175">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="R175">
         <v>2.04</v>
@@ -28852,7 +28852,7 @@
         <v>1.4</v>
       </c>
       <c r="T175">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U175">
         <v>2.95</v>
@@ -28864,34 +28864,34 @@
         <v>1.05</v>
       </c>
       <c r="X175">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y175">
+        <v>1.28</v>
+      </c>
+      <c r="Z175">
+        <v>3.35</v>
+      </c>
+      <c r="AA175">
+        <v>2.04</v>
+      </c>
+      <c r="AB175">
+        <v>1.78</v>
+      </c>
+      <c r="AC175">
+        <v>3.42</v>
+      </c>
+      <c r="AD175">
         <v>1.3</v>
       </c>
-      <c r="Z175">
-        <v>3.15</v>
-      </c>
-      <c r="AA175">
-        <v>2</v>
-      </c>
-      <c r="AB175">
-        <v>1.7</v>
-      </c>
-      <c r="AC175">
-        <v>3.6</v>
-      </c>
-      <c r="AD175">
-        <v>1.24</v>
-      </c>
       <c r="AE175">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF175">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG175">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -30799,55 +30799,55 @@
         <v>3.5</v>
       </c>
       <c r="Q187">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R187">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S187">
         <v>1.22</v>
       </c>
       <c r="T187">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="U187">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V187">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="W187">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X187">
         <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z187">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="AA187">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB187">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AC187">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD187">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AE187">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF187">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG187">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK187">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O190">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P190">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G191">
@@ -31451,55 +31451,55 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q192">
-        <v>1.97</v>
+        <v>3.12</v>
       </c>
       <c r="R192">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="S192">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T192">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U192">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="V192">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W192">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X192">
         <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z192">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA192">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AB192">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC192">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD192">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE192">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF192">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AG192">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK192">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -36006,34 +36006,34 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O219">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P219">
         <v>3.8</v>
       </c>
       <c r="Q219">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R219">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S219">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T219">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="U219">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V219">
         <v>1.35</v>
       </c>
       <c r="W219">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X219">
         <v>1.01</v>
@@ -36042,25 +36042,25 @@
         <v>1.28</v>
       </c>
       <c r="Z219">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AA219">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB219">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC219">
         <v>3.44</v>
       </c>
       <c r="AD219">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE219">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF219">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG219">
         <v>1.85</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK219">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36495,28 +36495,28 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O222">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P222">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q222">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R222">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S222">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T222">
         <v>2.5</v>
       </c>
       <c r="U222">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V222">
         <v>1.28</v>
@@ -36528,31 +36528,31 @@
         <v>1.02</v>
       </c>
       <c r="Y222">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z222">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA222">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB222">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC222">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="AD222">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE222">
         <v>1.02</v>
       </c>
       <c r="AF222">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG222">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>1.26</v>
       </c>
       <c r="AK222">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O225">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P225">
-        <v>5</v>
+        <v>5.39</v>
       </c>
       <c r="Q225">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="R225">
         <v>2.38</v>
       </c>
       <c r="S225">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T225">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U225">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V225">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W225">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X225">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y225">
         <v>1.14</v>
       </c>
       <c r="Z225">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AA225">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB225">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AC225">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD225">
         <v>1.51</v>
       </c>
       <c r="AE225">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF225">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG225">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O232">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="P232">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="Q232">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R232">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="S232">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T232">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="U232">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="V232">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W232">
+        <v>1.06</v>
+      </c>
+      <c r="X232">
+        <v>1.03</v>
+      </c>
+      <c r="Y232">
+        <v>1.36</v>
+      </c>
+      <c r="Z232">
+        <v>2.7</v>
+      </c>
+      <c r="AA232">
+        <v>2.25</v>
+      </c>
+      <c r="AB232">
+        <v>1.61</v>
+      </c>
+      <c r="AC232">
+        <v>4.25</v>
+      </c>
+      <c r="AD232">
+        <v>1.16</v>
+      </c>
+      <c r="AE232">
         <v>1.01</v>
       </c>
-      <c r="X232">
-        <v>1.1</v>
-      </c>
-      <c r="Y232">
-        <v>1.46</v>
-      </c>
-      <c r="Z232">
-        <v>2.64</v>
-      </c>
-      <c r="AA232">
-        <v>2.46</v>
-      </c>
-      <c r="AB232">
-        <v>1.52</v>
-      </c>
-      <c r="AC232">
-        <v>4.62</v>
-      </c>
-      <c r="AD232">
-        <v>1.17</v>
-      </c>
-      <c r="AE232">
-        <v>1.05</v>
-      </c>
       <c r="AF232">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG232">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38297,16 +38297,16 @@
         <v>0</v>
       </c>
       <c r="Q233">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="R233">
         <v>2.19</v>
       </c>
       <c r="S233">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T233">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U233">
         <v>2.59</v>
@@ -38315,7 +38315,7 @@
         <v>1.43</v>
       </c>
       <c r="W233">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X233">
         <v>1.01</v>
@@ -38327,13 +38327,13 @@
         <v>3.42</v>
       </c>
       <c r="AA233">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB233">
         <v>1.95</v>
       </c>
       <c r="AC233">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD233">
         <v>1.32</v>
@@ -38451,16 +38451,16 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q234">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R234">
         <v>2.03</v>
@@ -38472,13 +38472,13 @@
         <v>2.5</v>
       </c>
       <c r="U234">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V234">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W234">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X234">
         <v>1.03</v>
@@ -38490,10 +38490,10 @@
         <v>2.88</v>
       </c>
       <c r="AA234">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB234">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC234">
         <v>3.5</v>
@@ -38505,7 +38505,7 @@
         <v>1.04</v>
       </c>
       <c r="AF234">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG234">
         <v>1.7</v>
@@ -38524,7 +38524,7 @@
         <v>1.22</v>
       </c>
       <c r="AK234">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38620,10 +38620,10 @@
         <v>3.4</v>
       </c>
       <c r="P235">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q235">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R235">
         <v>2.06</v>
@@ -38632,7 +38632,7 @@
         <v>1.45</v>
       </c>
       <c r="T235">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="U235">
         <v>3</v>
@@ -38647,31 +38647,31 @@
         <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z235">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AA235">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB235">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC235">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD235">
         <v>1.26</v>
       </c>
       <c r="AE235">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF235">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG235">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK235">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,52 +39103,52 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O238">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P238">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q238">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R238">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S238">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T238">
         <v>2.44</v>
       </c>
       <c r="U238">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V238">
         <v>1.28</v>
       </c>
       <c r="W238">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X238">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z238">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA238">
         <v>2.25</v>
       </c>
       <c r="AB238">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC238">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="AD238">
         <v>1.17</v>
@@ -39157,10 +39157,10 @@
         <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG238">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>1.28</v>
       </c>
       <c r="AK238">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,52 +39266,52 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q239">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R239">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S239">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T239">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="U239">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V239">
         <v>1.28</v>
       </c>
       <c r="W239">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X239">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y239">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z239">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA239">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB239">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC239">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD239">
         <v>1.17</v>
@@ -39320,10 +39320,10 @@
         <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG239">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK239">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39598,22 +39598,22 @@
         <v>3.9</v>
       </c>
       <c r="P241">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q241">
         <v>2.09</v>
       </c>
       <c r="R241">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S241">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T241">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U241">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V241">
         <v>1.52</v>
@@ -39628,44 +39628,44 @@
         <v>1.16</v>
       </c>
       <c r="Z241">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA241">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB241">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AC241">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AD241">
         <v>1.45</v>
       </c>
       <c r="AE241">
+        <v>1.18</v>
+      </c>
+      <c r="AF241">
+        <v>1.73</v>
+      </c>
+      <c r="AG241">
+        <v>1.95</v>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ241">
         <v>1.16</v>
       </c>
-      <c r="AF241">
-        <v>1.66</v>
-      </c>
-      <c r="AG241">
-        <v>2.09</v>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ241">
-        <v>1.24</v>
-      </c>
       <c r="AK241">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39921,61 +39921,61 @@
         <v>2.15</v>
       </c>
       <c r="O243">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P243">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q243">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="R243">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S243">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T243">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U243">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="V243">
+        <v>1.36</v>
+      </c>
+      <c r="W243">
+        <v>1.07</v>
+      </c>
+      <c r="X243">
+        <v>1.06</v>
+      </c>
+      <c r="Y243">
         <v>1.32</v>
       </c>
-      <c r="W243">
-        <v>1.03</v>
-      </c>
-      <c r="X243">
-        <v>1.03</v>
-      </c>
-      <c r="Y243">
-        <v>1.35</v>
-      </c>
       <c r="Z243">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="AA243">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB243">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC243">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AD243">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE243">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF243">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG243">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK243">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40905,25 +40905,25 @@
         <v>0</v>
       </c>
       <c r="Q249">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="R249">
         <v>2.01</v>
       </c>
       <c r="S249">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T249">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U249">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="V249">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W249">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X249">
         <v>1.02</v>
@@ -40935,25 +40935,25 @@
         <v>2.92</v>
       </c>
       <c r="AA249">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB249">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC249">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD249">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE249">
         <v>1.05</v>
       </c>
       <c r="AF249">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG249">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AK249">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41059,37 +41059,37 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O250">
         <v>3.1</v>
       </c>
       <c r="P250">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="Q250">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="R250">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="S250">
         <v>1.5</v>
       </c>
       <c r="T250">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="U250">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V250">
         <v>1.31</v>
       </c>
       <c r="W250">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X250">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y250">
         <v>1.33</v>
@@ -41098,10 +41098,10 @@
         <v>2.85</v>
       </c>
       <c r="AA250">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AB250">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC250">
         <v>3.93</v>
@@ -41132,7 +41132,7 @@
         <v>1.41</v>
       </c>
       <c r="AK250">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41225,16 +41225,16 @@
         <v>1.6</v>
       </c>
       <c r="O251">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P251">
         <v>5.25</v>
       </c>
       <c r="Q251">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R251">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S251">
         <v>1.33</v>
@@ -41243,10 +41243,10 @@
         <v>3.04</v>
       </c>
       <c r="U251">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="V251">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W251">
         <v>1.06</v>
@@ -41255,31 +41255,31 @@
         <v>1.01</v>
       </c>
       <c r="Y251">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z251">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA251">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB251">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC251">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD251">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE251">
         <v>1.1</v>
       </c>
       <c r="AF251">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG251">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>1.25</v>
       </c>
       <c r="AK251">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41874,19 +41874,19 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O255">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P255">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q255">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R255">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S255">
         <v>1.41</v>
@@ -41913,41 +41913,41 @@
         <v>3.18</v>
       </c>
       <c r="AA255">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB255">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC255">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD255">
+        <v>1.3</v>
+      </c>
+      <c r="AE255">
+        <v>1.1</v>
+      </c>
+      <c r="AF255">
+        <v>1.9</v>
+      </c>
+      <c r="AG255">
+        <v>1.87</v>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ255">
         <v>1.25</v>
       </c>
-      <c r="AE255">
-        <v>1.05</v>
-      </c>
-      <c r="AF255">
-        <v>1.84</v>
-      </c>
-      <c r="AG255">
-        <v>1.86</v>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ255">
-        <v>1.28</v>
-      </c>
       <c r="AK255">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O258">
         <v>3.1</v>
       </c>
       <c r="P258">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q258">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="R258">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S258">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T258">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U258">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V258">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W258">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X258">
         <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z258">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA258">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB258">
         <v>1.82</v>
       </c>
       <c r="AC258">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD258">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE258">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF258">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG258">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK258">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O259">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P259">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q259">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R259">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S259">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T259">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="U259">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V259">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W259">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X259">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z259">
         <v>3.2</v>
       </c>
       <c r="AA259">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB259">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AC259">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AD259">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE259">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF259">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG259">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK259">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -43187,10 +43187,10 @@
         <v>0</v>
       </c>
       <c r="Q263">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
       <c r="R263">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S263">
         <v>1.34</v>
@@ -43232,10 +43232,10 @@
         <v>1.08</v>
       </c>
       <c r="AF263">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG263">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="AK263">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43830,16 +43830,16 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O267">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P267">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="Q267">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="R267">
         <v>2.09</v>
@@ -43851,7 +43851,7 @@
         <v>2.73</v>
       </c>
       <c r="U267">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V267">
         <v>1.38</v>
@@ -43863,19 +43863,19 @@
         <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z267">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA267">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB267">
         <v>1.8</v>
       </c>
       <c r="AC267">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AD267">
         <v>1.27</v>
@@ -43884,7 +43884,7 @@
         <v>1.06</v>
       </c>
       <c r="AF267">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG267">
         <v>1.9</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK267">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="O268">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P268">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q268">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R268">
         <v>2.14</v>
       </c>
       <c r="S268">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T268">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U268">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="V268">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W268">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X268">
         <v>1.03</v>
       </c>
       <c r="Y268">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z268">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="AA268">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB268">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC268">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AD268">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE268">
         <v>1.09</v>
       </c>
       <c r="AF268">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG268">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK268">
         <v>1.31</v>
@@ -44319,37 +44319,37 @@
         </is>
       </c>
       <c r="N270">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="O270">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P270">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q270">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="R270">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S270">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T270">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U270">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V270">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W270">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X270">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y270">
         <v>1.31</v>
@@ -44358,25 +44358,25 @@
         <v>2.92</v>
       </c>
       <c r="AA270">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB270">
         <v>1.73</v>
       </c>
       <c r="AC270">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AD270">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE270">
         <v>1.05</v>
       </c>
       <c r="AF270">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG270">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK270">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44482,19 +44482,19 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O271">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P271">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q271">
         <v>2.38</v>
       </c>
       <c r="R271">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S271">
         <v>1.36</v>
@@ -44503,19 +44503,19 @@
         <v>2.85</v>
       </c>
       <c r="U271">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V271">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W271">
         <v>1.08</v>
       </c>
       <c r="X271">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y271">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z271">
         <v>3.34</v>
@@ -44527,13 +44527,13 @@
         <v>1.88</v>
       </c>
       <c r="AC271">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AD271">
         <v>1.28</v>
       </c>
       <c r="AE271">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF271">
         <v>1.77</v>
@@ -46121,55 +46121,55 @@
         <v>1.49</v>
       </c>
       <c r="Q281">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R281">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="S281">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T281">
         <v>2.99</v>
       </c>
       <c r="U281">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="V281">
         <v>1.44</v>
       </c>
       <c r="W281">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X281">
         <v>1.03</v>
       </c>
       <c r="Y281">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z281">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA281">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB281">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC281">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD281">
         <v>1.33</v>
       </c>
       <c r="AE281">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF281">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG281">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK281">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,65 +46601,65 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="O284">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="P284">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q284">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R284">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S284">
+        <v>1.7</v>
+      </c>
+      <c r="T284">
+        <v>2.02</v>
+      </c>
+      <c r="U284">
+        <v>4.5</v>
+      </c>
+      <c r="V284">
+        <v>1.16</v>
+      </c>
+      <c r="W284">
+        <v>1.03</v>
+      </c>
+      <c r="X284">
+        <v>1.17</v>
+      </c>
+      <c r="Y284">
+        <v>1.67</v>
+      </c>
+      <c r="Z284">
+        <v>2.05</v>
+      </c>
+      <c r="AA284">
+        <v>3.1</v>
+      </c>
+      <c r="AB284">
+        <v>1.33</v>
+      </c>
+      <c r="AC284">
+        <v>6.15</v>
+      </c>
+      <c r="AD284">
+        <v>1.1</v>
+      </c>
+      <c r="AE284">
+        <v>1.03</v>
+      </c>
+      <c r="AF284">
+        <v>2.3</v>
+      </c>
+      <c r="AG284">
         <v>1.53</v>
       </c>
-      <c r="T284">
-        <v>2.33</v>
-      </c>
-      <c r="U284">
-        <v>3.5</v>
-      </c>
-      <c r="V284">
-        <v>1.24</v>
-      </c>
-      <c r="W284">
-        <v>1.01</v>
-      </c>
-      <c r="X284">
-        <v>1.1</v>
-      </c>
-      <c r="Y284">
-        <v>1.5</v>
-      </c>
-      <c r="Z284">
-        <v>2.5</v>
-      </c>
-      <c r="AA284">
-        <v>2.5</v>
-      </c>
-      <c r="AB284">
-        <v>1.5</v>
-      </c>
-      <c r="AC284">
-        <v>5</v>
-      </c>
-      <c r="AD284">
-        <v>1.15</v>
-      </c>
-      <c r="AE284">
-        <v>1.05</v>
-      </c>
-      <c r="AF284">
-        <v>2</v>
-      </c>
-      <c r="AG284">
-        <v>1.73</v>
-      </c>
       <c r="AH284" t="inlineStr">
         <is>
           <t>[]</t>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK284">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="O285">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P285">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q285">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R285">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S285">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="T285">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="U285">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="V285">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="W285">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X285">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y285">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z285">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA285">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB285">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC285">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="AD285">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE285">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF285">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG285">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK285">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46927,19 +46927,19 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O286">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P286">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q286">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R286">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="S286">
         <v>1.42</v>
@@ -46948,7 +46948,7 @@
         <v>2.65</v>
       </c>
       <c r="U286">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="V286">
         <v>1.36</v>
@@ -46957,19 +46957,19 @@
         <v>1.03</v>
       </c>
       <c r="X286">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y286">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z286">
         <v>3.12</v>
       </c>
       <c r="AA286">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB286">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC286">
         <v>3.3</v>
@@ -46978,13 +46978,13 @@
         <v>1.25</v>
       </c>
       <c r="AE286">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF286">
         <v>1.77</v>
       </c>
       <c r="AG286">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK286">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47416,34 +47416,34 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="O289">
         <v>3.3</v>
       </c>
       <c r="P289">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q289">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R289">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S289">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T289">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U289">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="V289">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W289">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X289">
         <v>1.01</v>
@@ -47452,19 +47452,19 @@
         <v>1.32</v>
       </c>
       <c r="Z289">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA289">
         <v>2.1</v>
       </c>
       <c r="AB289">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC289">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AD289">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE289">
         <v>1.03</v>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK289">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,80 +47742,80 @@
         </is>
       </c>
       <c r="N291">
-        <v>6.1</v>
+        <v>1.85</v>
       </c>
       <c r="O291">
+        <v>3.5</v>
+      </c>
+      <c r="P291">
         <v>4.33</v>
       </c>
-      <c r="P291">
-        <v>1.46</v>
-      </c>
       <c r="Q291">
-        <v>6.3</v>
+        <v>2.38</v>
       </c>
       <c r="R291">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S291">
+        <v>1.43</v>
+      </c>
+      <c r="T291">
+        <v>2.55</v>
+      </c>
+      <c r="U291">
+        <v>2.82</v>
+      </c>
+      <c r="V291">
+        <v>1.36</v>
+      </c>
+      <c r="W291">
+        <v>1.05</v>
+      </c>
+      <c r="X291">
+        <v>1.05</v>
+      </c>
+      <c r="Y291">
+        <v>1.34</v>
+      </c>
+      <c r="Z291">
+        <v>2.94</v>
+      </c>
+      <c r="AA291">
+        <v>2.1</v>
+      </c>
+      <c r="AB291">
+        <v>1.75</v>
+      </c>
+      <c r="AC291">
+        <v>3.9</v>
+      </c>
+      <c r="AD291">
+        <v>1.24</v>
+      </c>
+      <c r="AE291">
+        <v>1.04</v>
+      </c>
+      <c r="AF291">
+        <v>1.9</v>
+      </c>
+      <c r="AG291">
+        <v>1.8</v>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ291">
         <v>1.3</v>
       </c>
-      <c r="T291">
-        <v>3.1</v>
-      </c>
-      <c r="U291">
-        <v>2.59</v>
-      </c>
-      <c r="V291">
-        <v>1.44</v>
-      </c>
-      <c r="W291">
-        <v>1.12</v>
-      </c>
-      <c r="X291">
-        <v>1.04</v>
-      </c>
-      <c r="Y291">
-        <v>1.25</v>
-      </c>
-      <c r="Z291">
-        <v>3.9</v>
-      </c>
-      <c r="AA291">
-        <v>1.75</v>
-      </c>
-      <c r="AB291">
-        <v>2.07</v>
-      </c>
-      <c r="AC291">
-        <v>2.8</v>
-      </c>
-      <c r="AD291">
-        <v>1.34</v>
-      </c>
-      <c r="AE291">
-        <v>1.09</v>
-      </c>
-      <c r="AF291">
-        <v>1.88</v>
-      </c>
-      <c r="AG291">
-        <v>1.82</v>
-      </c>
-      <c r="AH291" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI291" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ291">
-        <v>1.21</v>
-      </c>
       <c r="AK291">
-        <v>1.1</v>
+        <v>1.97</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.85</v>
+        <v>6.1</v>
       </c>
       <c r="O292">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P292">
-        <v>4.33</v>
+        <v>1.46</v>
       </c>
       <c r="Q292">
-        <v>2.38</v>
+        <v>6.3</v>
       </c>
       <c r="R292">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S292">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T292">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="U292">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="V292">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W292">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X292">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y292">
+        <v>1.25</v>
+      </c>
+      <c r="Z292">
+        <v>3.9</v>
+      </c>
+      <c r="AA292">
+        <v>1.75</v>
+      </c>
+      <c r="AB292">
+        <v>2.07</v>
+      </c>
+      <c r="AC292">
+        <v>2.8</v>
+      </c>
+      <c r="AD292">
         <v>1.34</v>
       </c>
-      <c r="Z292">
-        <v>2.94</v>
-      </c>
-      <c r="AA292">
-        <v>2.1</v>
-      </c>
-      <c r="AB292">
-        <v>1.75</v>
-      </c>
-      <c r="AC292">
-        <v>3.9</v>
-      </c>
-      <c r="AD292">
-        <v>1.24</v>
-      </c>
       <c r="AE292">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF292">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG292">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK292">
-        <v>1.97</v>
+        <v>1.1</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,80 +48557,80 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="O296">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="P296">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q296">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R296">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S296">
+        <v>1.6</v>
+      </c>
+      <c r="T296">
+        <v>2.1</v>
+      </c>
+      <c r="U296">
+        <v>4.3</v>
+      </c>
+      <c r="V296">
+        <v>1.15</v>
+      </c>
+      <c r="W296">
+        <v>1.03</v>
+      </c>
+      <c r="X296">
+        <v>1.08</v>
+      </c>
+      <c r="Y296">
+        <v>1.49</v>
+      </c>
+      <c r="Z296">
+        <v>2.43</v>
+      </c>
+      <c r="AA296">
+        <v>2.97</v>
+      </c>
+      <c r="AB296">
+        <v>1.3</v>
+      </c>
+      <c r="AC296">
+        <v>6.6</v>
+      </c>
+      <c r="AD296">
+        <v>1.05</v>
+      </c>
+      <c r="AE296">
+        <v>1.02</v>
+      </c>
+      <c r="AF296">
+        <v>2.4</v>
+      </c>
+      <c r="AG296">
+        <v>1.5</v>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ296">
+        <v>1.25</v>
+      </c>
+      <c r="AK296">
         <v>1.57</v>
-      </c>
-      <c r="T296">
-        <v>2.24</v>
-      </c>
-      <c r="U296">
-        <v>3.5</v>
-      </c>
-      <c r="V296">
-        <v>1.22</v>
-      </c>
-      <c r="W296">
-        <v>1</v>
-      </c>
-      <c r="X296">
-        <v>1.11</v>
-      </c>
-      <c r="Y296">
-        <v>1.5</v>
-      </c>
-      <c r="Z296">
-        <v>2.41</v>
-      </c>
-      <c r="AA296">
-        <v>2.6</v>
-      </c>
-      <c r="AB296">
-        <v>1.47</v>
-      </c>
-      <c r="AC296">
-        <v>5</v>
-      </c>
-      <c r="AD296">
-        <v>1.15</v>
-      </c>
-      <c r="AE296">
-        <v>1</v>
-      </c>
-      <c r="AF296">
-        <v>2.12</v>
-      </c>
-      <c r="AG296">
-        <v>1.62</v>
-      </c>
-      <c r="AH296" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI296" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ296">
-        <v>1.4</v>
-      </c>
-      <c r="AK296">
-        <v>1.62</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="O297">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="P297">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q297">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R297">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S297">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T297">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="U297">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="V297">
+        <v>1.22</v>
+      </c>
+      <c r="W297">
+        <v>1</v>
+      </c>
+      <c r="X297">
+        <v>1.11</v>
+      </c>
+      <c r="Y297">
+        <v>1.5</v>
+      </c>
+      <c r="Z297">
+        <v>2.41</v>
+      </c>
+      <c r="AA297">
+        <v>2.6</v>
+      </c>
+      <c r="AB297">
+        <v>1.47</v>
+      </c>
+      <c r="AC297">
+        <v>5</v>
+      </c>
+      <c r="AD297">
         <v>1.15</v>
       </c>
-      <c r="W297">
-        <v>1.03</v>
-      </c>
-      <c r="X297">
-        <v>1.08</v>
-      </c>
-      <c r="Y297">
-        <v>1.49</v>
-      </c>
-      <c r="Z297">
-        <v>2.43</v>
-      </c>
-      <c r="AA297">
-        <v>2.97</v>
-      </c>
-      <c r="AB297">
-        <v>1.3</v>
-      </c>
-      <c r="AC297">
-        <v>6.6</v>
-      </c>
-      <c r="AD297">
-        <v>1.05</v>
-      </c>
       <c r="AE297">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF297">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AG297">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK297">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49049,16 +49049,16 @@
         <v>1.5</v>
       </c>
       <c r="O299">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="P299">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="Q299">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R299">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="S299">
         <v>1.3</v>
@@ -49067,37 +49067,37 @@
         <v>3.25</v>
       </c>
       <c r="U299">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V299">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W299">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X299">
         <v>1.02</v>
       </c>
       <c r="Y299">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z299">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA299">
         <v>1.72</v>
       </c>
       <c r="AB299">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AC299">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD299">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE299">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF299">
         <v>1.77</v>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK299">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O301">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P301">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q301">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="R301">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S301">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T301">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="U301">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="V301">
+        <v>1.3</v>
+      </c>
+      <c r="W301">
+        <v>1.01</v>
+      </c>
+      <c r="X301">
+        <v>1.02</v>
+      </c>
+      <c r="Y301">
         <v>1.32</v>
       </c>
-      <c r="W301">
-        <v>1.02</v>
-      </c>
-      <c r="X301">
-        <v>1</v>
-      </c>
-      <c r="Y301">
-        <v>1.28</v>
-      </c>
       <c r="Z301">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA301">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AB301">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC301">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD301">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE301">
         <v>1.03</v>
       </c>
       <c r="AF301">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG301">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK301">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49538,61 +49538,61 @@
         <v>2.1</v>
       </c>
       <c r="O302">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P302">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q302">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R302">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S302">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T302">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U302">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V302">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W302">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X302">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y302">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z302">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA302">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB302">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC302">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD302">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE302">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF302">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG302">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK302">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49861,49 +49861,49 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q304">
         <v>1.83</v>
       </c>
       <c r="R304">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S304">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T304">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U304">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V304">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W304">
         <v>1.03</v>
       </c>
       <c r="X304">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z304">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA304">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB304">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC304">
         <v>3.42</v>
@@ -49915,10 +49915,10 @@
         <v>1.05</v>
       </c>
       <c r="AF304">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="AG304">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>1.15</v>
       </c>
       <c r="AK304">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50024,55 +50024,55 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q305">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R305">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S305">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T305">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U305">
         <v>3</v>
       </c>
       <c r="V305">
+        <v>1.33</v>
+      </c>
+      <c r="W305">
+        <v>1.06</v>
+      </c>
+      <c r="X305">
+        <v>1.02</v>
+      </c>
+      <c r="Y305">
         <v>1.31</v>
       </c>
-      <c r="W305">
-        <v>1.02</v>
-      </c>
-      <c r="X305">
-        <v>1.01</v>
-      </c>
-      <c r="Y305">
-        <v>1.3</v>
-      </c>
       <c r="Z305">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA305">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB305">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC305">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD305">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE305">
         <v>1.03</v>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK305">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50187,19 +50187,19 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q306">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="R306">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S306">
         <v>1.53</v>
@@ -50516,61 +50516,61 @@
         <v>3.75</v>
       </c>
       <c r="O308">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P308">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q308">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R308">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S308">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T308">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="U308">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V308">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W308">
         <v>1.13</v>
       </c>
       <c r="X308">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z308">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA308">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB308">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC308">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD308">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE308">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF308">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG308">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK308">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -52306,19 +52306,19 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O319">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P319">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q319">
         <v>2.1</v>
       </c>
       <c r="R319">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S319">
         <v>1.3</v>
@@ -52327,43 +52327,43 @@
         <v>3.2</v>
       </c>
       <c r="U319">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V319">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W319">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X319">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y319">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z319">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA319">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB319">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC319">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD319">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE319">
         <v>1.1</v>
       </c>
       <c r="AF319">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG319">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK319">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL319">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
         <v>3.62</v>
@@ -1821,10 +1821,10 @@
         <v>1.97</v>
       </c>
       <c r="AC9">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
         <v>1.11</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1969,25 +1969,25 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA10">
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q11">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
+        <v>1.34</v>
+      </c>
+      <c r="T11">
+        <v>3.17</v>
+      </c>
+      <c r="U11">
+        <v>2.7</v>
+      </c>
+      <c r="V11">
+        <v>1.44</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.22</v>
+      </c>
+      <c r="Z11">
+        <v>3.54</v>
+      </c>
+      <c r="AA11">
+        <v>1.83</v>
+      </c>
+      <c r="AB11">
+        <v>2.01</v>
+      </c>
+      <c r="AC11">
+        <v>3.09</v>
+      </c>
+      <c r="AD11">
         <v>1.32</v>
-      </c>
-      <c r="T11">
-        <v>3.25</v>
-      </c>
-      <c r="U11">
-        <v>2.63</v>
-      </c>
-      <c r="V11">
-        <v>1.46</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.25</v>
-      </c>
-      <c r="Z11">
-        <v>3.95</v>
-      </c>
-      <c r="AA11">
-        <v>1.76</v>
-      </c>
-      <c r="AB11">
-        <v>2.05</v>
-      </c>
-      <c r="AC11">
-        <v>2.85</v>
-      </c>
-      <c r="AD11">
-        <v>1.42</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -5235,22 +5235,22 @@
         <v>1.35</v>
       </c>
       <c r="Z30">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AA30">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AB30">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AD30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
         <v>1.88</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q31">
         <v>2.34</v>
@@ -5383,16 +5383,16 @@
         <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
         <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.15</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
         <v>1.92</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
         <v>2.29</v>
@@ -5739,7 +5739,7 @@
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
         <v>1.77</v>
@@ -7683,10 +7683,10 @@
         <v>3.62</v>
       </c>
       <c r="AA45">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB45">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AC45">
         <v>2.85</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>2.1</v>
@@ -22483,7 +22483,7 @@
         <v>3.2</v>
       </c>
       <c r="P136">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q136">
         <v>2.33</v>
@@ -22492,40 +22492,40 @@
         <v>2.2</v>
       </c>
       <c r="S136">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="T136">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U136">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="V136">
         <v>1.31</v>
       </c>
       <c r="W136">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X136">
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z136">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AA136">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB136">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC136">
         <v>3.78</v>
       </c>
       <c r="AD136">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE136">
         <v>1.04</v>
@@ -43344,28 +43344,28 @@
         <v>2.1</v>
       </c>
       <c r="O264">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P264">
         <v>3.1</v>
       </c>
       <c r="Q264">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R264">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S264">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T264">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="U264">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V264">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W264">
         <v>1.05</v>
@@ -43374,22 +43374,22 @@
         <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z264">
         <v>3.2</v>
       </c>
       <c r="AA264">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB264">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC264">
         <v>3.08</v>
       </c>
       <c r="AD264">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE264">
         <v>1.07</v>
@@ -43507,13 +43507,13 @@
         <v>2</v>
       </c>
       <c r="O265">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P265">
         <v>3.2</v>
       </c>
       <c r="Q265">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R265">
         <v>2.1</v>
@@ -43522,13 +43522,13 @@
         <v>1.36</v>
       </c>
       <c r="T265">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="U265">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="V265">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W265">
         <v>1.05</v>
@@ -43540,25 +43540,25 @@
         <v>1.26</v>
       </c>
       <c r="Z265">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="AA265">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB265">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC265">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="AD265">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE265">
         <v>1.07</v>
       </c>
       <c r="AF265">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG265">
         <v>1.98</v>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK265">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="O289">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P289">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q289">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R289">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S289">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T289">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U289">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V289">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W289">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X289">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y289">
         <v>1.5</v>
       </c>
       <c r="Z289">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA289">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB289">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AC289">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD289">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF289">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG289">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK289">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O291">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P291">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q291">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="R291">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S291">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T291">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U291">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V291">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W291">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X291">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y291">
         <v>1.5</v>
       </c>
       <c r="Z291">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA291">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AB291">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC291">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD291">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE291">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF291">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG291">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK291">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="O302">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P302">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q302">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R302">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S302">
+        <v>1.65</v>
+      </c>
+      <c r="T302">
+        <v>2.1</v>
+      </c>
+      <c r="U302">
+        <v>4.25</v>
+      </c>
+      <c r="V302">
+        <v>1.15</v>
+      </c>
+      <c r="W302">
+        <v>1.03</v>
+      </c>
+      <c r="X302">
+        <v>1.08</v>
+      </c>
+      <c r="Y302">
+        <v>1.49</v>
+      </c>
+      <c r="Z302">
+        <v>2.43</v>
+      </c>
+      <c r="AA302">
+        <v>3.4</v>
+      </c>
+      <c r="AB302">
+        <v>1.33</v>
+      </c>
+      <c r="AC302">
+        <v>6.55</v>
+      </c>
+      <c r="AD302">
+        <v>1.05</v>
+      </c>
+      <c r="AE302">
+        <v>1.02</v>
+      </c>
+      <c r="AF302">
+        <v>2.4</v>
+      </c>
+      <c r="AG302">
         <v>1.53</v>
-      </c>
-      <c r="T302">
-        <v>2.24</v>
-      </c>
-      <c r="U302">
-        <v>3.5</v>
-      </c>
-      <c r="V302">
-        <v>1.22</v>
-      </c>
-      <c r="W302">
-        <v>1.04</v>
-      </c>
-      <c r="X302">
-        <v>1.11</v>
-      </c>
-      <c r="Y302">
-        <v>1.5</v>
-      </c>
-      <c r="Z302">
-        <v>2.41</v>
-      </c>
-      <c r="AA302">
-        <v>2.46</v>
-      </c>
-      <c r="AB302">
-        <v>1.47</v>
-      </c>
-      <c r="AC302">
-        <v>5</v>
-      </c>
-      <c r="AD302">
-        <v>1.15</v>
-      </c>
-      <c r="AE302">
-        <v>1</v>
-      </c>
-      <c r="AF302">
-        <v>2.14</v>
-      </c>
-      <c r="AG302">
-        <v>1.62</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         <v>1.4</v>
       </c>
       <c r="AK302">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="O303">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P303">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="Q303">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R303">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S303">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="T303">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="U303">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="V303">
+        <v>1.22</v>
+      </c>
+      <c r="W303">
+        <v>1.04</v>
+      </c>
+      <c r="X303">
+        <v>1.11</v>
+      </c>
+      <c r="Y303">
+        <v>1.5</v>
+      </c>
+      <c r="Z303">
+        <v>2.41</v>
+      </c>
+      <c r="AA303">
+        <v>2.46</v>
+      </c>
+      <c r="AB303">
+        <v>1.47</v>
+      </c>
+      <c r="AC303">
+        <v>5</v>
+      </c>
+      <c r="AD303">
         <v>1.15</v>
       </c>
-      <c r="W303">
-        <v>1.03</v>
-      </c>
-      <c r="X303">
-        <v>1.08</v>
-      </c>
-      <c r="Y303">
-        <v>1.49</v>
-      </c>
-      <c r="Z303">
-        <v>2.43</v>
-      </c>
-      <c r="AA303">
-        <v>3.4</v>
-      </c>
-      <c r="AB303">
-        <v>1.33</v>
-      </c>
-      <c r="AC303">
-        <v>6.55</v>
-      </c>
-      <c r="AD303">
-        <v>1.05</v>
-      </c>
       <c r="AE303">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF303">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AG303">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>1.4</v>
       </c>
       <c r="AK303">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL303">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="R5">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z5">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB5">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="AC5">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="AD5">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
+        <v>1.95</v>
+      </c>
+      <c r="Q11">
+        <v>4.05</v>
+      </c>
+      <c r="R11">
         <v>2.2</v>
       </c>
-      <c r="Q11">
-        <v>3.4</v>
-      </c>
-      <c r="R11">
-        <v>2.12</v>
-      </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB11">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK11">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
+        <v>1.34</v>
+      </c>
+      <c r="T12">
+        <v>3.17</v>
+      </c>
+      <c r="U12">
+        <v>2.7</v>
+      </c>
+      <c r="V12">
+        <v>1.44</v>
+      </c>
+      <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.22</v>
+      </c>
+      <c r="Z12">
+        <v>3.54</v>
+      </c>
+      <c r="AA12">
+        <v>1.83</v>
+      </c>
+      <c r="AB12">
+        <v>2.01</v>
+      </c>
+      <c r="AC12">
+        <v>3.09</v>
+      </c>
+      <c r="AD12">
         <v>1.32</v>
-      </c>
-      <c r="T12">
-        <v>3.25</v>
-      </c>
-      <c r="U12">
-        <v>2.63</v>
-      </c>
-      <c r="V12">
-        <v>1.46</v>
-      </c>
-      <c r="W12">
-        <v>1.06</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.25</v>
-      </c>
-      <c r="Z12">
-        <v>3.95</v>
-      </c>
-      <c r="AA12">
-        <v>1.76</v>
-      </c>
-      <c r="AB12">
-        <v>2.05</v>
-      </c>
-      <c r="AC12">
-        <v>2.85</v>
-      </c>
-      <c r="AD12">
-        <v>1.42</v>
       </c>
       <c r="AE12">
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.65</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="S19">
+        <v>1.55</v>
+      </c>
+      <c r="T19">
+        <v>2.36</v>
+      </c>
+      <c r="U19">
+        <v>3.5</v>
+      </c>
+      <c r="V19">
+        <v>1.22</v>
+      </c>
+      <c r="W19">
+        <v>1.02</v>
+      </c>
+      <c r="X19">
+        <v>1.05</v>
+      </c>
+      <c r="Y19">
         <v>1.43</v>
       </c>
-      <c r="T19">
-        <v>2.53</v>
-      </c>
-      <c r="U19">
-        <v>3.25</v>
-      </c>
-      <c r="V19">
-        <v>1.27</v>
-      </c>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.36</v>
-      </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA19">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="AB19">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AC19">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG19">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="O44">
-        <v>3.43</v>
+        <v>3.68</v>
       </c>
       <c r="P44">
         <v>2.01</v>
@@ -7496,7 +7496,7 @@
         <v>2.34</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
         <v>3.8</v>
@@ -7511,7 +7511,7 @@
         <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.11</v>
@@ -7532,13 +7532,13 @@
         <v>1.61</v>
       </c>
       <c r="AE44">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AK44">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -10581,16 +10581,16 @@
         <v>2.25</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q63">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S63">
         <v>1.25</v>
@@ -10605,28 +10605,28 @@
         <v>1.56</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>4.81</v>
+        <v>4.45</v>
       </c>
       <c r="AA63">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB63">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AC63">
         <v>2.38</v>
       </c>
       <c r="AD63">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AE63">
         <v>1.18</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="O69">
         <v>3.6</v>
@@ -12700,7 +12700,7 @@
         <v>1.93</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
         <v>3.8</v>
@@ -12733,10 +12733,10 @@
         <v>1.4</v>
       </c>
       <c r="Z76">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AA76">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB76">
         <v>1.72</v>
@@ -12754,7 +12754,7 @@
         <v>2</v>
       </c>
       <c r="AG76">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13023,34 +13023,34 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="O78">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P78">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q78">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R78">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="S78">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T78">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="U78">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V78">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W78">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X78">
         <v>1.02</v>
@@ -13059,44 +13059,44 @@
         <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA78">
         <v>1.44</v>
       </c>
       <c r="AB78">
+        <v>2.62</v>
+      </c>
+      <c r="AC78">
+        <v>2.03</v>
+      </c>
+      <c r="AD78">
+        <v>1.7</v>
+      </c>
+      <c r="AE78">
+        <v>1.29</v>
+      </c>
+      <c r="AF78">
+        <v>1.57</v>
+      </c>
+      <c r="AG78">
+        <v>2.23</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.11</v>
+      </c>
+      <c r="AK78">
         <v>2.68</v>
-      </c>
-      <c r="AC78">
-        <v>2.08</v>
-      </c>
-      <c r="AD78">
-        <v>1.67</v>
-      </c>
-      <c r="AE78">
-        <v>1.28</v>
-      </c>
-      <c r="AF78">
-        <v>1.54</v>
-      </c>
-      <c r="AG78">
-        <v>2.29</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.13</v>
-      </c>
-      <c r="AK78">
-        <v>2.47</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,10 +13195,10 @@
         <v>2.79</v>
       </c>
       <c r="Q79">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S79">
         <v>1.43</v>
@@ -13207,7 +13207,7 @@
         <v>2.59</v>
       </c>
       <c r="U79">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="V79">
         <v>1.33</v>
@@ -13231,7 +13231,7 @@
         <v>1.66</v>
       </c>
       <c r="AC79">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
         <v>1.24</v>
@@ -13259,7 +13259,7 @@
         <v>1.46</v>
       </c>
       <c r="AK79">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,37 +13355,37 @@
         <v>3.3</v>
       </c>
       <c r="P80">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q80">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="R80">
         <v>2.09</v>
       </c>
       <c r="S80">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T80">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U80">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="V80">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA80">
         <v>1.84</v>
@@ -13394,7 +13394,7 @@
         <v>1.98</v>
       </c>
       <c r="AC80">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="AD80">
         <v>1.37</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK80">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13533,28 +13533,28 @@
         <v>2.56</v>
       </c>
       <c r="U81">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="V81">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W81">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z81">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA81">
         <v>2.06</v>
       </c>
       <c r="AB81">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC81">
         <v>3.42</v>
@@ -13563,10 +13563,10 @@
         <v>1.23</v>
       </c>
       <c r="AE81">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG81">
         <v>2</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK81">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="O82">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P82">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="Q82">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R82">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S82">
         <v>1.32</v>
@@ -13696,10 +13696,10 @@
         <v>2.92</v>
       </c>
       <c r="U82">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
         <v>1.07</v>
@@ -13708,19 +13708,19 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z82">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="AA82">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB82">
         <v>2</v>
       </c>
       <c r="AC82">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD82">
         <v>1.33</v>
@@ -13729,7 +13729,7 @@
         <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG82">
         <v>1.75</v>
@@ -13748,7 +13748,7 @@
         <v>1.14</v>
       </c>
       <c r="AK82">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O85">
         <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="Q85">
         <v>2.92</v>
@@ -14188,16 +14188,16 @@
         <v>2.7</v>
       </c>
       <c r="V85">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
         <v>3.34</v>
@@ -14209,19 +14209,19 @@
         <v>1.85</v>
       </c>
       <c r="AC85">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="AD85">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q86">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="R86">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T86">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U86">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V86">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W86">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z86">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="AA86">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB86">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC86">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD86">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF86">
         <v>1.67</v>
       </c>
       <c r="AG86">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14508,16 +14508,16 @@
         <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="U87">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="V87">
         <v>1.69</v>
       </c>
       <c r="W87">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14526,7 +14526,7 @@
         <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA87">
         <v>1.44</v>
@@ -14535,16 +14535,16 @@
         <v>2.61</v>
       </c>
       <c r="AC87">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD87">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE87">
         <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG87">
         <v>2.61</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="O88">
         <v>4.35</v>
       </c>
       <c r="P88">
-        <v>4.45</v>
+        <v>4.72</v>
       </c>
       <c r="Q88">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="R88">
         <v>2.44</v>
       </c>
       <c r="S88">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U88">
         <v>2.2</v>
@@ -14695,16 +14695,16 @@
         <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC88">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AD88">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE88">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF88">
         <v>1.47</v>
@@ -14985,52 +14985,52 @@
         <v>3.58</v>
       </c>
       <c r="P90">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="Q90">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="R90">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="S90">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U90">
         <v>2.89</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W90">
         <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z90">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AA90">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB90">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC90">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD90">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF90">
         <v>1.93</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O91">
         <v>3.1</v>
@@ -15163,13 +15163,13 @@
         <v>2.81</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="V91">
         <v>1.39</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15181,13 +15181,13 @@
         <v>3.38</v>
       </c>
       <c r="AA91">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD91">
         <v>1.28</v>
@@ -15196,10 +15196,10 @@
         <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15305,37 +15305,37 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="O92">
         <v>2.9</v>
       </c>
       <c r="P92">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q92">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="R92">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S92">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T92">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U92">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="V92">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W92">
         <v>1.03</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
         <v>1.42</v>
@@ -15344,7 +15344,7 @@
         <v>2.85</v>
       </c>
       <c r="AA92">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AB92">
         <v>1.59</v>
@@ -15353,16 +15353,16 @@
         <v>4.49</v>
       </c>
       <c r="AD92">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE92">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF92">
         <v>1.85</v>
       </c>
       <c r="AG92">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O93">
         <v>3.1</v>
@@ -15480,16 +15480,16 @@
         <v>2.77</v>
       </c>
       <c r="R93">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S93">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T93">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="U93">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V93">
         <v>1.29</v>
@@ -15498,7 +15498,7 @@
         <v>1.01</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y93">
         <v>1.44</v>
@@ -15507,10 +15507,10 @@
         <v>2.53</v>
       </c>
       <c r="AA93">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB93">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC93">
         <v>4.5</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O94">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P94">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15797,61 +15797,61 @@
         <v>1.75</v>
       </c>
       <c r="O95">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P95">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q95">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R95">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="S95">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T95">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="U95">
         <v>3.2</v>
       </c>
       <c r="V95">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W95">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y95">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z95">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AA95">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB95">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC95">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD95">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE95">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF95">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG95">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK95">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O96">
         <v>3.1</v>
       </c>
       <c r="P96">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q96">
-        <v>4.45</v>
+        <v>4.78</v>
       </c>
       <c r="R96">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S96">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T96">
         <v>2.75</v>
       </c>
       <c r="U96">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="V96">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W96">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA96">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB96">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC96">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="AD96">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF96">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AG96">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK96">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="O105">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P105">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q105">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="R105">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="S105">
+        <v>1.51</v>
+      </c>
+      <c r="T105">
+        <v>2.29</v>
+      </c>
+      <c r="U105">
+        <v>3.14</v>
+      </c>
+      <c r="V105">
+        <v>1.28</v>
+      </c>
+      <c r="W105">
+        <v>1.02</v>
+      </c>
+      <c r="X105">
+        <v>1.06</v>
+      </c>
+      <c r="Y105">
         <v>1.4</v>
       </c>
-      <c r="T105">
-        <v>2.6</v>
-      </c>
-      <c r="U105">
-        <v>2.88</v>
-      </c>
-      <c r="V105">
-        <v>1.33</v>
-      </c>
-      <c r="W105">
-        <v>1.04</v>
-      </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
-      <c r="Y105">
-        <v>1.31</v>
-      </c>
       <c r="Z105">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="AA105">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="AB105">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AC105">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD105">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE105">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF105">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AG105">
+        <v>1.72</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
+        <v>1.3</v>
+      </c>
+      <c r="AK105">
         <v>1.77</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.22</v>
-      </c>
-      <c r="AK105">
-        <v>1.97</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="R110">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S110">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T110">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="U110">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="V110">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W110">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z110">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA110">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AB110">
         <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="AD110">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE110">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF110">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG110">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O111">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P111">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q111">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="R111">
         <v>1.92</v>
       </c>
       <c r="S111">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T111">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="U111">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="V111">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W111">
         <v>1.02</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z111">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AA111">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AB111">
         <v>1.57</v>
       </c>
       <c r="AC111">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AD111">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE111">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AG111">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.27</v>
       </c>
       <c r="AK111">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18568,13 +18568,13 @@
         <v>2.75</v>
       </c>
       <c r="O112">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P112">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q112">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="R112">
         <v>2.1</v>
@@ -18586,13 +18586,13 @@
         <v>2.96</v>
       </c>
       <c r="U112">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="V112">
         <v>1.43</v>
       </c>
       <c r="W112">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
         <v>1.03</v>
@@ -18604,22 +18604,22 @@
         <v>4.02</v>
       </c>
       <c r="AA112">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB112">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AC112">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AD112">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE112">
         <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG112">
         <v>2.14</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AK112">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18737,10 +18737,10 @@
         <v>3</v>
       </c>
       <c r="Q113">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="R113">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S113">
         <v>1.53</v>
@@ -18752,16 +18752,16 @@
         <v>3.4</v>
       </c>
       <c r="V113">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
         <v>1.02</v>
       </c>
       <c r="X113">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y113">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z113">
         <v>2.73</v>
@@ -18770,13 +18770,13 @@
         <v>2.3</v>
       </c>
       <c r="AB113">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC113">
         <v>4.33</v>
       </c>
       <c r="AD113">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE113">
         <v>1.01</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK113">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19392,22 +19392,22 @@
         <v>1.2</v>
       </c>
       <c r="R117">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="S117">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T117">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="U117">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V117">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="W117">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X117">
         <v>1</v>
@@ -19416,28 +19416,28 @@
         <v>1.04</v>
       </c>
       <c r="Z117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA117">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AB117">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AC117">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD117">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AE117">
         <v>1.8</v>
       </c>
       <c r="AF117">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG117">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK117">
-        <v>9.9</v>
+        <v>7.8</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,22 +19543,22 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.87</v>
+        <v>2.57</v>
       </c>
       <c r="O118">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
         <v>2.3</v>
       </c>
       <c r="Q118">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R118">
         <v>2.23</v>
       </c>
       <c r="S118">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T118">
         <v>3.3</v>
@@ -19567,37 +19567,37 @@
         <v>2.52</v>
       </c>
       <c r="V118">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W118">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X118">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
         <v>1.2</v>
       </c>
       <c r="Z118">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="AA118">
         <v>1.74</v>
       </c>
       <c r="AB118">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AC118">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AD118">
         <v>1.45</v>
       </c>
       <c r="AE118">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF118">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG118">
         <v>2.28</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AK118">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19878,25 +19878,25 @@
         <v>3.25</v>
       </c>
       <c r="Q120">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R120">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S120">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T120">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U120">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V120">
         <v>1.46</v>
       </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X120">
         <v>1.04</v>
@@ -19905,19 +19905,19 @@
         <v>1.2</v>
       </c>
       <c r="Z120">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="AA120">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB120">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC120">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AD120">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE120">
         <v>1.11</v>
@@ -20367,16 +20367,16 @@
         <v>4.6</v>
       </c>
       <c r="Q123">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="R123">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U123">
         <v>2.66</v>
@@ -20388,7 +20388,7 @@
         <v>1.04</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y123">
         <v>1.31</v>
@@ -20397,25 +20397,25 @@
         <v>3.42</v>
       </c>
       <c r="AA123">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB123">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC123">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD123">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE123">
         <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG123">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK123">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20536,10 +20536,10 @@
         <v>1.96</v>
       </c>
       <c r="S124">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U124">
         <v>3.02</v>
@@ -20551,19 +20551,19 @@
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z124">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="AA124">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB124">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC124">
         <v>3.9</v>
@@ -20572,7 +20572,7 @@
         <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
         <v>1.83</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK124">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="O126">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>4.53</v>
+        <v>4.18</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB126">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="O138">
         <v>3.9</v>
       </c>
       <c r="P138">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -22818,10 +22818,10 @@
         <v>2.5</v>
       </c>
       <c r="S138">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T138">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U138">
         <v>2.31</v>
@@ -22836,7 +22836,7 @@
         <v>1.03</v>
       </c>
       <c r="Y138">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z138">
         <v>5</v>
@@ -22845,13 +22845,13 @@
         <v>1.53</v>
       </c>
       <c r="AB138">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC138">
         <v>2.29</v>
       </c>
       <c r="AD138">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE138">
         <v>1.22</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK138">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O140">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="P140">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O141">
         <v>3</v>
       </c>
       <c r="P141">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="Q141">
         <v>2.67</v>
@@ -23307,10 +23307,10 @@
         <v>1.93</v>
       </c>
       <c r="S141">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="T141">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="U141">
         <v>3.3</v>
@@ -23319,13 +23319,13 @@
         <v>1.26</v>
       </c>
       <c r="W141">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X141">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y141">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z141">
         <v>2.6</v>
@@ -23337,19 +23337,19 @@
         <v>1.57</v>
       </c>
       <c r="AC141">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AD141">
         <v>1.13</v>
       </c>
       <c r="AE141">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF141">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG141">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -24110,22 +24110,22 @@
         <v>2</v>
       </c>
       <c r="O146">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
       </c>
       <c r="R146">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T146">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U146">
         <v>2.25</v>
@@ -24134,25 +24134,25 @@
         <v>1.57</v>
       </c>
       <c r="W146">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z146">
         <v>4.25</v>
       </c>
       <c r="AA146">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB146">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC146">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AD146">
         <v>1.46</v>
@@ -24161,7 +24161,7 @@
         <v>1.16</v>
       </c>
       <c r="AF146">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG146">
         <v>2.3</v>
@@ -24180,7 +24180,7 @@
         <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25417,7 +25417,7 @@
         <v>4</v>
       </c>
       <c r="P154">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="Q154">
         <v>2.5</v>
@@ -25432,10 +25432,10 @@
         <v>4</v>
       </c>
       <c r="U154">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V154">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W154">
         <v>1.2</v>
@@ -25447,7 +25447,7 @@
         <v>1.13</v>
       </c>
       <c r="Z154">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AA154">
         <v>1.38</v>
@@ -25456,19 +25456,19 @@
         <v>2.64</v>
       </c>
       <c r="AC154">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD154">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE154">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AF154">
         <v>1.4</v>
       </c>
       <c r="AG154">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK154">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O155">
         <v>3.4</v>
       </c>
       <c r="P155">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q155">
         <v>3.24</v>
@@ -25595,7 +25595,7 @@
         <v>3.6</v>
       </c>
       <c r="U155">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="V155">
         <v>1.54</v>
@@ -25610,13 +25610,13 @@
         <v>1.18</v>
       </c>
       <c r="Z155">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA155">
         <v>1.7</v>
       </c>
       <c r="AB155">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC155">
         <v>2.75</v>
@@ -25631,7 +25631,7 @@
         <v>1.53</v>
       </c>
       <c r="AG155">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>2.25</v>
       </c>
       <c r="O157">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P157">
         <v>2.61</v>
@@ -25915,13 +25915,13 @@
         <v>2.19</v>
       </c>
       <c r="S157">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T157">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U157">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V157">
         <v>1.49</v>
@@ -25930,7 +25930,7 @@
         <v>1.11</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
         <v>1.19</v>
@@ -25957,7 +25957,7 @@
         <v>1.53</v>
       </c>
       <c r="AG157">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK157">
         <v>1.5</v>
@@ -28028,10 +28028,10 @@
         <v>2.05</v>
       </c>
       <c r="Q170">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="R170">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S170">
         <v>1.38</v>
@@ -28058,16 +28058,16 @@
         <v>3.08</v>
       </c>
       <c r="AA170">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB170">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC170">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD170">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE170">
         <v>1.05</v>
@@ -28092,7 +28092,7 @@
         <v>1.25</v>
       </c>
       <c r="AK170">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28351,10 +28351,10 @@
         <v>3.55</v>
       </c>
       <c r="P172">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="Q172">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R172">
         <v>2.2</v>
@@ -28375,7 +28375,7 @@
         <v>1.04</v>
       </c>
       <c r="X172">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y172">
         <v>1.3</v>
@@ -28384,7 +28384,7 @@
         <v>3.54</v>
       </c>
       <c r="AA172">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB172">
         <v>1.85</v>
@@ -28396,10 +28396,10 @@
         <v>1.3</v>
       </c>
       <c r="AE172">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF172">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG172">
         <v>1.85</v>
@@ -31611,7 +31611,7 @@
         <v>4</v>
       </c>
       <c r="P192">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="Q192">
         <v>2.42</v>
@@ -31626,19 +31626,19 @@
         <v>4.05</v>
       </c>
       <c r="U192">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V192">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="W192">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X192">
         <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z192">
         <v>6</v>
@@ -31647,7 +31647,7 @@
         <v>1.45</v>
       </c>
       <c r="AB192">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AC192">
         <v>2.17</v>
@@ -31656,13 +31656,13 @@
         <v>1.69</v>
       </c>
       <c r="AE192">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF192">
         <v>1.4</v>
       </c>
       <c r="AG192">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G195">
@@ -32103,55 +32103,55 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,34 +32257,34 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q196">
-        <v>1.98</v>
+        <v>3.12</v>
       </c>
       <c r="R196">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="S196">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T196">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U196">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V196">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W196">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X196">
         <v>1.01</v>
@@ -32293,28 +32293,28 @@
         <v>1.28</v>
       </c>
       <c r="Z196">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA196">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB196">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC196">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD196">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE196">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF196">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="AG196">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK196">
-        <v>2.8</v>
+        <v>1.43</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,25 +32420,25 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O197">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P197">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q197">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="R197">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S197">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T197">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U197">
         <v>2.97</v>
@@ -32450,19 +32450,19 @@
         <v>1.02</v>
       </c>
       <c r="X197">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y197">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z197">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA197">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AB197">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC197">
         <v>3.58</v>
@@ -32474,10 +32474,10 @@
         <v>1.03</v>
       </c>
       <c r="AF197">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG197">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK197">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O224">
         <v>3.35</v>
@@ -36830,10 +36830,10 @@
         <v>3.8</v>
       </c>
       <c r="Q224">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="R224">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S224">
         <v>1.4</v>
@@ -36860,10 +36860,10 @@
         <v>3.18</v>
       </c>
       <c r="AA224">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB224">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC224">
         <v>3.44</v>
@@ -36878,7 +36878,7 @@
         <v>1.8</v>
       </c>
       <c r="AG224">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>1.26</v>
       </c>
       <c r="AK224">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37310,52 +37310,52 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O227">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P227">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q227">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="R227">
         <v>2</v>
       </c>
       <c r="S227">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T227">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U227">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V227">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W227">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X227">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y227">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z227">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA227">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB227">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC227">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AD227">
         <v>1.17</v>
@@ -37364,10 +37364,10 @@
         <v>1.02</v>
       </c>
       <c r="AF227">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG227">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK227">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37799,16 +37799,16 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O230">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P230">
-        <v>5.39</v>
+        <v>5.3</v>
       </c>
       <c r="Q230">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R230">
         <v>2.38</v>
@@ -37820,13 +37820,13 @@
         <v>3.6</v>
       </c>
       <c r="U230">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V230">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W230">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X230">
         <v>1.03</v>
@@ -37838,10 +37838,10 @@
         <v>4.8</v>
       </c>
       <c r="AA230">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB230">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC230">
         <v>2.59</v>
@@ -37850,7 +37850,7 @@
         <v>1.51</v>
       </c>
       <c r="AE230">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF230">
         <v>1.62</v>
@@ -38940,34 +38940,34 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O237">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P237">
-        <v>3.45</v>
+        <v>2.67</v>
       </c>
       <c r="Q237">
         <v>3</v>
       </c>
       <c r="R237">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="S237">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T237">
         <v>2.62</v>
       </c>
       <c r="U237">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="V237">
         <v>1.28</v>
       </c>
       <c r="W237">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X237">
         <v>1.03</v>
@@ -38976,16 +38976,16 @@
         <v>1.36</v>
       </c>
       <c r="Z237">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AA237">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB237">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC237">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD237">
         <v>1.16</v>
@@ -38994,7 +38994,7 @@
         <v>1.01</v>
       </c>
       <c r="AF237">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG237">
         <v>1.81</v>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK237">
         <v>1.47</v>
@@ -39103,80 +39103,80 @@
         </is>
       </c>
       <c r="N238">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="O238">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P238">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Q238">
-        <v>5.23</v>
+        <v>5.87</v>
       </c>
       <c r="R238">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S238">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T238">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U238">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="V238">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W238">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X238">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
+        <v>1.24</v>
+      </c>
+      <c r="Z238">
+        <v>3.34</v>
+      </c>
+      <c r="AA238">
+        <v>1.87</v>
+      </c>
+      <c r="AB238">
+        <v>1.88</v>
+      </c>
+      <c r="AC238">
+        <v>3.04</v>
+      </c>
+      <c r="AD238">
+        <v>1.29</v>
+      </c>
+      <c r="AE238">
+        <v>1.07</v>
+      </c>
+      <c r="AF238">
+        <v>1.88</v>
+      </c>
+      <c r="AG238">
+        <v>1.82</v>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ238">
         <v>1.22</v>
       </c>
-      <c r="Z238">
-        <v>3.48</v>
-      </c>
-      <c r="AA238">
-        <v>1.84</v>
-      </c>
-      <c r="AB238">
-        <v>1.92</v>
-      </c>
-      <c r="AC238">
-        <v>2.97</v>
-      </c>
-      <c r="AD238">
-        <v>1.3</v>
-      </c>
-      <c r="AE238">
-        <v>1.08</v>
-      </c>
-      <c r="AF238">
-        <v>1.8</v>
-      </c>
-      <c r="AG238">
-        <v>1.88</v>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ238">
-        <v>2.14</v>
-      </c>
       <c r="AK238">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q239">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="R239">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="S239">
         <v>1.36</v>
       </c>
       <c r="T239">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U239">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V239">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W239">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X239">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z239">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA239">
+        <v>1.94</v>
+      </c>
+      <c r="AB239">
         <v>1.82</v>
       </c>
-      <c r="AB239">
-        <v>1.95</v>
-      </c>
       <c r="AC239">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD239">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE239">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF239">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG239">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK239">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39429,25 +39429,25 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O240">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P240">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q240">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="R240">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S240">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T240">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U240">
         <v>3</v>
@@ -39462,31 +39462,31 @@
         <v>1.03</v>
       </c>
       <c r="Y240">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z240">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA240">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB240">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC240">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD240">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE240">
         <v>1.04</v>
       </c>
       <c r="AF240">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG240">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK240">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39592,16 +39592,16 @@
         </is>
       </c>
       <c r="N241">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O241">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P241">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q241">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R241">
         <v>2.06</v>
@@ -39622,7 +39622,7 @@
         <v>1.05</v>
       </c>
       <c r="X241">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y241">
         <v>1.31</v>
@@ -39631,25 +39631,25 @@
         <v>3.12</v>
       </c>
       <c r="AA241">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB241">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC241">
         <v>3.5</v>
       </c>
       <c r="AD241">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE241">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF241">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG241">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK241">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39927,55 +39927,55 @@
         <v>0</v>
       </c>
       <c r="Q243">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R243">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S243">
+        <v>1.25</v>
+      </c>
+      <c r="T243">
+        <v>3.28</v>
+      </c>
+      <c r="U243">
+        <v>2.16</v>
+      </c>
+      <c r="V243">
+        <v>1.6</v>
+      </c>
+      <c r="W243">
+        <v>1.13</v>
+      </c>
+      <c r="X243">
+        <v>1.02</v>
+      </c>
+      <c r="Y243">
+        <v>1.12</v>
+      </c>
+      <c r="Z243">
+        <v>4.8</v>
+      </c>
+      <c r="AA243">
+        <v>1.44</v>
+      </c>
+      <c r="AB243">
+        <v>2.43</v>
+      </c>
+      <c r="AC243">
+        <v>2.2</v>
+      </c>
+      <c r="AD243">
+        <v>1.63</v>
+      </c>
+      <c r="AE243">
         <v>1.24</v>
       </c>
-      <c r="T243">
-        <v>3.34</v>
-      </c>
-      <c r="U243">
-        <v>2.1</v>
-      </c>
-      <c r="V243">
-        <v>1.64</v>
-      </c>
-      <c r="W243">
-        <v>1.15</v>
-      </c>
-      <c r="X243">
-        <v>1</v>
-      </c>
-      <c r="Y243">
-        <v>1.1</v>
-      </c>
-      <c r="Z243">
-        <v>5.1</v>
-      </c>
-      <c r="AA243">
-        <v>1.39</v>
-      </c>
-      <c r="AB243">
-        <v>2.62</v>
-      </c>
-      <c r="AC243">
-        <v>2</v>
-      </c>
-      <c r="AD243">
-        <v>1.71</v>
-      </c>
-      <c r="AE243">
-        <v>1.28</v>
-      </c>
       <c r="AF243">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AG243">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK243">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q244">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R244">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S244">
         <v>1.44</v>
       </c>
       <c r="T244">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U244">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V244">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W244">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X244">
+        <v>1.02</v>
+      </c>
+      <c r="Y244">
+        <v>1.32</v>
+      </c>
+      <c r="Z244">
+        <v>2.88</v>
+      </c>
+      <c r="AA244">
+        <v>2.09</v>
+      </c>
+      <c r="AB244">
+        <v>1.66</v>
+      </c>
+      <c r="AC244">
+        <v>3.58</v>
+      </c>
+      <c r="AD244">
+        <v>1.21</v>
+      </c>
+      <c r="AE244">
         <v>1.03</v>
       </c>
-      <c r="Y244">
-        <v>1.35</v>
-      </c>
-      <c r="Z244">
-        <v>2.74</v>
-      </c>
-      <c r="AA244">
-        <v>2.25</v>
-      </c>
-      <c r="AB244">
-        <v>1.61</v>
-      </c>
-      <c r="AC244">
-        <v>3.94</v>
-      </c>
-      <c r="AD244">
-        <v>1.17</v>
-      </c>
-      <c r="AE244">
-        <v>1.02</v>
-      </c>
       <c r="AF244">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG244">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.28</v>
       </c>
       <c r="AK244">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="O245">
+        <v>3.1</v>
+      </c>
+      <c r="P245">
         <v>3.25</v>
       </c>
-      <c r="P245">
-        <v>3.3</v>
-      </c>
       <c r="Q245">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R245">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S245">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T245">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="U245">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="V245">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W245">
+        <v>1.05</v>
+      </c>
+      <c r="X245">
         <v>1.02</v>
       </c>
-      <c r="X245">
-        <v>1.04</v>
-      </c>
       <c r="Y245">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z245">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="AA245">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AB245">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AC245">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AD245">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE245">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF245">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG245">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK245">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40570,28 +40570,28 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O247">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P247">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="Q247">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R247">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S247">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T247">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U247">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V247">
         <v>1.52</v>
@@ -40603,19 +40603,19 @@
         <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z247">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA247">
         <v>1.7</v>
       </c>
       <c r="AB247">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC247">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="AD247">
         <v>1.45</v>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK247">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,7 +40896,7 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O249">
         <v>3.2</v>
@@ -40908,7 +40908,7 @@
         <v>2.5</v>
       </c>
       <c r="R249">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S249">
         <v>1.4</v>
@@ -40926,7 +40926,7 @@
         <v>1.07</v>
       </c>
       <c r="X249">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y249">
         <v>1.32</v>
@@ -40935,16 +40935,16 @@
         <v>2.89</v>
       </c>
       <c r="AA249">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB249">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC249">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AD249">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE249">
         <v>1.04</v>
@@ -41711,10 +41711,10 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O254">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P254">
         <v>2.62</v>
@@ -41883,25 +41883,25 @@
         <v>0</v>
       </c>
       <c r="Q255">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="R255">
         <v>2.01</v>
       </c>
       <c r="S255">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T255">
+        <v>2.59</v>
+      </c>
+      <c r="U255">
         <v>2.88</v>
       </c>
-      <c r="U255">
-        <v>3.06</v>
-      </c>
       <c r="V255">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W255">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X255">
         <v>1.02</v>
@@ -41910,7 +41910,7 @@
         <v>1.31</v>
       </c>
       <c r="Z255">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="AA255">
         <v>2.02</v>
@@ -41919,19 +41919,19 @@
         <v>1.71</v>
       </c>
       <c r="AC255">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD255">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE255">
         <v>1.05</v>
       </c>
       <c r="AF255">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG255">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42037,25 +42037,25 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O256">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P256">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
       <c r="Q256">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="R256">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S256">
         <v>1.5</v>
       </c>
       <c r="T256">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="U256">
         <v>3.2</v>
@@ -42067,25 +42067,25 @@
         <v>1.04</v>
       </c>
       <c r="X256">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y256">
         <v>1.33</v>
       </c>
       <c r="Z256">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="AA256">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AB256">
         <v>1.66</v>
       </c>
       <c r="AC256">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="AD256">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE256">
         <v>1.02</v>
@@ -42200,52 +42200,52 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="O257">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P257">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q257">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R257">
         <v>2.25</v>
       </c>
       <c r="S257">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T257">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U257">
         <v>2.56</v>
       </c>
       <c r="V257">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W257">
         <v>1.06</v>
       </c>
       <c r="X257">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y257">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z257">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA257">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB257">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AC257">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD257">
         <v>1.36</v>
@@ -42254,10 +42254,10 @@
         <v>1.1</v>
       </c>
       <c r="AF257">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG257">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>1.25</v>
       </c>
       <c r="AK257">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42852,16 +42852,16 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O261">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P261">
         <v>4.2</v>
       </c>
       <c r="Q261">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R261">
         <v>2.06</v>
@@ -42891,19 +42891,19 @@
         <v>3.18</v>
       </c>
       <c r="AA261">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB261">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC261">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD261">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE261">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF261">
         <v>1.9</v>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK261">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O264">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P264">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -43356,7 +43356,7 @@
         <v>2.1</v>
       </c>
       <c r="S264">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T264">
         <v>2.74</v>
@@ -43374,7 +43374,7 @@
         <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z264">
         <v>3.2</v>
@@ -43507,7 +43507,7 @@
         <v>2</v>
       </c>
       <c r="O265">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P265">
         <v>3.2</v>
@@ -44645,19 +44645,19 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="O272">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="P272">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q272">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="R272">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S272">
         <v>1.4</v>
@@ -44666,10 +44666,10 @@
         <v>2.73</v>
       </c>
       <c r="U272">
-        <v>2.81</v>
+        <v>3.03</v>
       </c>
       <c r="V272">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W272">
         <v>1.04</v>
@@ -44678,19 +44678,19 @@
         <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z272">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA272">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB272">
         <v>1.8</v>
       </c>
       <c r="AC272">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AD272">
         <v>1.27</v>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK272">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44817,43 +44817,43 @@
         <v>2.15</v>
       </c>
       <c r="Q273">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="R273">
         <v>2.14</v>
       </c>
       <c r="S273">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T273">
         <v>3.23</v>
       </c>
       <c r="U273">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V273">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W273">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X273">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y273">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z273">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AA273">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AB273">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC273">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AD273">
         <v>1.33</v>
@@ -44865,7 +44865,7 @@
         <v>1.62</v>
       </c>
       <c r="AG273">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK273">
         <v>1.31</v>
@@ -45134,55 +45134,55 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O275">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P275">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q275">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R275">
         <v>2.1</v>
       </c>
       <c r="S275">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T275">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U275">
         <v>2.95</v>
       </c>
       <c r="V275">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W275">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X275">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z275">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="AA275">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AB275">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC275">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD275">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE275">
         <v>1.05</v>
@@ -45191,7 +45191,7 @@
         <v>1.77</v>
       </c>
       <c r="AG275">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK275">
         <v>1.37</v>
@@ -47090,22 +47090,22 @@
         </is>
       </c>
       <c r="N287">
-        <v>6.19</v>
+        <v>5</v>
       </c>
       <c r="O287">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="P287">
         <v>1.49</v>
       </c>
       <c r="Q287">
-        <v>5.5</v>
+        <v>5.97</v>
       </c>
       <c r="R287">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="S287">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T287">
         <v>2.99</v>
@@ -47114,34 +47114,34 @@
         <v>2.75</v>
       </c>
       <c r="V287">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W287">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X287">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z287">
         <v>3.58</v>
       </c>
       <c r="AA287">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB287">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC287">
         <v>3.1</v>
       </c>
       <c r="AD287">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE287">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF287">
         <v>1.85</v>
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O288">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P288">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q288">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R288">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="S288">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T288">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U288">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="V288">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W288">
         <v>1.01</v>
       </c>
       <c r="X288">
+        <v>1.03</v>
+      </c>
+      <c r="Y288">
+        <v>1.35</v>
+      </c>
+      <c r="Z288">
+        <v>2.74</v>
+      </c>
+      <c r="AA288">
+        <v>2.21</v>
+      </c>
+      <c r="AB288">
+        <v>1.59</v>
+      </c>
+      <c r="AC288">
+        <v>4.05</v>
+      </c>
+      <c r="AD288">
+        <v>1.16</v>
+      </c>
+      <c r="AE288">
         <v>1.01</v>
       </c>
-      <c r="Y288">
-        <v>1.33</v>
-      </c>
-      <c r="Z288">
-        <v>2.83</v>
-      </c>
-      <c r="AA288">
-        <v>2.14</v>
-      </c>
-      <c r="AB288">
-        <v>1.63</v>
-      </c>
-      <c r="AC288">
-        <v>3.9</v>
-      </c>
-      <c r="AD288">
-        <v>1.18</v>
-      </c>
-      <c r="AE288">
-        <v>1.02</v>
-      </c>
       <c r="AF288">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG288">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK288">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47905,25 +47905,25 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="O292">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P292">
         <v>2.8</v>
       </c>
       <c r="Q292">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R292">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S292">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T292">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U292">
         <v>2.96</v>
@@ -47932,31 +47932,31 @@
         <v>1.36</v>
       </c>
       <c r="W292">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X292">
         <v>1.02</v>
       </c>
       <c r="Y292">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z292">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AA292">
         <v>2</v>
       </c>
       <c r="AB292">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC292">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="AD292">
         <v>1.25</v>
       </c>
       <c r="AE292">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF292">
         <v>1.77</v>
@@ -48394,19 +48394,19 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O295">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="P295">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q295">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R295">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S295">
         <v>1.36</v>
@@ -48436,19 +48436,19 @@
         <v>2.1</v>
       </c>
       <c r="AB295">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC295">
         <v>3.68</v>
       </c>
       <c r="AD295">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE295">
         <v>1.03</v>
       </c>
       <c r="AF295">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG295">
         <v>1.86</v>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK295">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -50036,7 +50036,7 @@
         <v>1.87</v>
       </c>
       <c r="R305">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="S305">
         <v>1.3</v>
@@ -50045,13 +50045,13 @@
         <v>3.25</v>
       </c>
       <c r="U305">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V305">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W305">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X305">
         <v>1.02</v>
@@ -50060,10 +50060,10 @@
         <v>1.19</v>
       </c>
       <c r="Z305">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA305">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB305">
         <v>1.99</v>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK305">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="O307">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P307">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q307">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="R307">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="S307">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T307">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U307">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="V307">
         <v>1.3</v>
       </c>
       <c r="W307">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X307">
         <v>1.02</v>
       </c>
       <c r="Y307">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z307">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA307">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB307">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC307">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD307">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE307">
         <v>1.03</v>
       </c>
       <c r="AF307">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG307">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK307">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50513,31 +50513,31 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O308">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P308">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q308">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R308">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S308">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T308">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U308">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="V308">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W308">
         <v>1.02</v>
@@ -50546,28 +50546,28 @@
         <v>1.03</v>
       </c>
       <c r="Y308">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z308">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA308">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB308">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC308">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AD308">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE308">
         <v>1.03</v>
       </c>
       <c r="AF308">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG308">
         <v>1.85</v>
@@ -50586,7 +50586,7 @@
         <v>1.28</v>
       </c>
       <c r="AK308">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="O310">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P310">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q310">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R310">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S310">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T310">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U310">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="V310">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W310">
+        <v>1.02</v>
+      </c>
+      <c r="X310">
         <v>1.03</v>
       </c>
-      <c r="X310">
-        <v>1.01</v>
-      </c>
       <c r="Y310">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="Z310">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="AA310">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AB310">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC310">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AD310">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE310">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF310">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AG310">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK310">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,25 +51002,25 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O311">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P311">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q311">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R311">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S311">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T311">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U311">
         <v>3</v>
@@ -51032,10 +51032,10 @@
         <v>1.06</v>
       </c>
       <c r="X311">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z311">
         <v>2.92</v>
@@ -51044,10 +51044,10 @@
         <v>2.07</v>
       </c>
       <c r="AB311">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC311">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD311">
         <v>1.2</v>
@@ -51059,7 +51059,7 @@
         <v>1.91</v>
       </c>
       <c r="AG311">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK311">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51168,10 +51168,10 @@
         <v>2.37</v>
       </c>
       <c r="O312">
+        <v>2.8</v>
+      </c>
+      <c r="P312">
         <v>2.9</v>
-      </c>
-      <c r="P312">
-        <v>2.8</v>
       </c>
       <c r="Q312">
         <v>3.25</v>
@@ -51180,49 +51180,49 @@
         <v>1.91</v>
       </c>
       <c r="S312">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T312">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="U312">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V312">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W312">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X312">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y312">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z312">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AA312">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="AB312">
         <v>1.5</v>
       </c>
       <c r="AC312">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AD312">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE312">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF312">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AG312">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK312">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL312">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -647,43 +647,43 @@
         <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T2">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
         <v>1.09</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC2">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AD2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE2">
         <v>1.15</v>
@@ -692,7 +692,7 @@
         <v>1.48</v>
       </c>
       <c r="AG2">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1450,55 +1450,55 @@
         </is>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="P7">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
         <v>2.75</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.12</v>
@@ -1507,7 +1507,7 @@
         <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q8">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
         <v>2.75</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q9">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1797,7 +1797,7 @@
         <v>3.04</v>
       </c>
       <c r="U9">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="V9">
         <v>1.46</v>
@@ -1821,7 +1821,7 @@
         <v>1.97</v>
       </c>
       <c r="AC9">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AD9">
         <v>1.36</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O10">
         <v>3.5</v>
@@ -1954,10 +1954,10 @@
         <v>2.36</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
         <v>2.65</v>
@@ -1972,31 +1972,31 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
         <v>3.62</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG10">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
         <v>2.01</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>2.9</v>
+      </c>
+      <c r="O11">
         <v>3.25</v>
       </c>
-      <c r="O11">
-        <v>3.3</v>
-      </c>
       <c r="P11">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q11">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="AA11">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC11">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.54</v>
+        <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>3.09</v>
+        <v>2.66</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
         <v>2</v>
       </c>
       <c r="Q21">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S21">
         <v>1.4</v>
@@ -3765,13 +3765,13 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB21">
         <v>1.78</v>
@@ -3780,10 +3780,10 @@
         <v>3.44</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
         <v>1.8</v>
@@ -3805,7 +3805,7 @@
         <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q22">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3916,34 +3916,34 @@
         <v>2.81</v>
       </c>
       <c r="U22">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB22">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
         <v>1.08</v>
@@ -3952,7 +3952,7 @@
         <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R23">
         <v>1.91</v>
@@ -4076,37 +4076,37 @@
         <v>1.49</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U23">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
         <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z23">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA23">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB23">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC23">
-        <v>3.96</v>
+        <v>4.11</v>
       </c>
       <c r="AD23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE23">
         <v>1.03</v>
@@ -4115,7 +4115,7 @@
         <v>1.85</v>
       </c>
       <c r="AG23">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,55 +4221,55 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q24">
         <v>3</v>
       </c>
       <c r="R24">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U24">
         <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>3.83</v>
+        <v>3.74</v>
       </c>
       <c r="AA24">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC24">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD24">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
         <v>1.08</v>
@@ -4278,7 +4278,7 @@
         <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q25">
         <v>2.72</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S25">
         <v>1.41</v>
@@ -4405,22 +4405,22 @@
         <v>2.59</v>
       </c>
       <c r="U25">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
         <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AA25">
         <v>2.05</v>
@@ -4438,10 +4438,10 @@
         <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4553,31 +4553,31 @@
         <v>3.85</v>
       </c>
       <c r="P26">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q26">
         <v>2.1</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S26">
         <v>1.34</v>
       </c>
       <c r="T26">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U26">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.18</v>
@@ -4586,22 +4586,22 @@
         <v>3.9</v>
       </c>
       <c r="AA26">
+        <v>1.71</v>
+      </c>
+      <c r="AB26">
+        <v>2.07</v>
+      </c>
+      <c r="AC26">
+        <v>2.82</v>
+      </c>
+      <c r="AD26">
+        <v>1.35</v>
+      </c>
+      <c r="AE26">
+        <v>1.15</v>
+      </c>
+      <c r="AF26">
         <v>1.73</v>
-      </c>
-      <c r="AB26">
-        <v>2.05</v>
-      </c>
-      <c r="AC26">
-        <v>2.75</v>
-      </c>
-      <c r="AD26">
-        <v>1.42</v>
-      </c>
-      <c r="AE26">
-        <v>1.1</v>
-      </c>
-      <c r="AF26">
-        <v>1.7</v>
       </c>
       <c r="AG26">
         <v>1.97</v>
@@ -4722,22 +4722,22 @@
         <v>2.96</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S27">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U27">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X27">
         <v>1.04</v>
@@ -4746,13 +4746,13 @@
         <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AA27">
         <v>2.38</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
         <v>4.64</v>
@@ -4761,7 +4761,7 @@
         <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
         <v>2</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5238,25 +5238,25 @@
         <v>3.08</v>
       </c>
       <c r="AA30">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB30">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC30">
         <v>3.75</v>
       </c>
       <c r="AD30">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE30">
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG30">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
         <v>3.55</v>
@@ -5383,10 +5383,10 @@
         <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W31">
         <v>1.12</v>
@@ -5395,16 +5395,16 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA31">
         <v>1.64</v>
       </c>
       <c r="AB31">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC31">
         <v>2.39</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q32">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="R32">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
         <v>3</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -5561,16 +5561,16 @@
         <v>1.34</v>
       </c>
       <c r="Z32">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AA32">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB32">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC32">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="AD32">
         <v>1.23</v>
@@ -5579,7 +5579,7 @@
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG32">
         <v>1.75</v>
@@ -5598,7 +5598,7 @@
         <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,10 +5697,10 @@
         <v>4.35</v>
       </c>
       <c r="Q33">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="R33">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
         <v>1.34</v>
@@ -5727,10 +5727,10 @@
         <v>3.81</v>
       </c>
       <c r="AA33">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>3.1</v>
@@ -5742,10 +5742,10 @@
         <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7653,7 +7653,7 @@
         <v>4.5</v>
       </c>
       <c r="Q45">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R45">
         <v>2.24</v>
@@ -7665,10 +7665,10 @@
         <v>3.04</v>
       </c>
       <c r="U45">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V45">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7677,31 +7677,31 @@
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="AA45">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB45">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC45">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AD45">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE45">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8785,43 +8785,43 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
         <v>1.94</v>
       </c>
       <c r="Q52">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="R52">
         <v>2.23</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.16</v>
       </c>
       <c r="Z52">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
         <v>1.6</v>
@@ -8830,19 +8830,19 @@
         <v>2.15</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD52">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
         <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG52">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8951,13 +8951,13 @@
         <v>2.25</v>
       </c>
       <c r="O53">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="Q53">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8969,7 +8969,7 @@
         <v>3.1</v>
       </c>
       <c r="U53">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V53">
         <v>1.5</v>
@@ -8978,7 +8978,7 @@
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
         <v>1.16</v>
@@ -8987,10 +8987,10 @@
         <v>4.2</v>
       </c>
       <c r="AA53">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB53">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC53">
         <v>2.43</v>
@@ -9002,7 +9002,7 @@
         <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG53">
         <v>2.25</v>
@@ -9111,52 +9111,52 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O54">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="R54">
         <v>1.97</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T54">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U54">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="V54">
         <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z54">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AA54">
         <v>2.12</v>
       </c>
       <c r="AB54">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC54">
-        <v>3.73</v>
+        <v>3.52</v>
       </c>
       <c r="AD54">
         <v>1.27</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O57">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>4.2</v>
+        <v>4.58</v>
       </c>
       <c r="Q57">
         <v>2.29</v>
@@ -9636,13 +9636,13 @@
         <v>1.2</v>
       </c>
       <c r="Z57">
-        <v>4.14</v>
+        <v>3.92</v>
       </c>
       <c r="AA57">
         <v>1.75</v>
       </c>
       <c r="AB57">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AC57">
         <v>2.69</v>
@@ -10747,13 +10747,13 @@
         <v>3.65</v>
       </c>
       <c r="P64">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q64">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R64">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
         <v>1.24</v>
@@ -10762,7 +10762,7 @@
         <v>3.5</v>
       </c>
       <c r="U64">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V64">
         <v>1.61</v>
@@ -10774,22 +10774,22 @@
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z64">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB64">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AC64">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AD64">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AE64">
         <v>1.22</v>
@@ -10798,7 +10798,7 @@
         <v>1.44</v>
       </c>
       <c r="AG64">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10907,19 +10907,19 @@
         <v>1.91</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P65">
         <v>3.45</v>
       </c>
       <c r="Q65">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R65">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S65">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T65">
         <v>3.58</v>
@@ -10931,19 +10931,19 @@
         <v>1.66</v>
       </c>
       <c r="W65">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z65">
         <v>5.45</v>
       </c>
       <c r="AA65">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB65">
         <v>2.54</v>
@@ -10955,7 +10955,7 @@
         <v>1.69</v>
       </c>
       <c r="AE65">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF65">
         <v>1.44</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="R66">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
-        <v>2.94</v>
+        <v>3.33</v>
       </c>
       <c r="U66">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA66">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB66">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC66">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF66">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG66">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P67">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q67">
-        <v>4.6</v>
+        <v>4.88</v>
       </c>
       <c r="R67">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T67">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="U67">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V67">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA67">
         <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="AC67">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AD67">
+        <v>1.51</v>
+      </c>
+      <c r="AE67">
+        <v>1.16</v>
+      </c>
+      <c r="AF67">
         <v>1.6</v>
       </c>
-      <c r="AE67">
-        <v>1.21</v>
-      </c>
-      <c r="AF67">
-        <v>1.55</v>
-      </c>
       <c r="AG67">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="O69">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P69">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11731,7 +11731,7 @@
         <v>2.14</v>
       </c>
       <c r="R70">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="S70">
         <v>1.16</v>
@@ -11758,10 +11758,10 @@
         <v>6.74</v>
       </c>
       <c r="AA70">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AB70">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="AC70">
         <v>1.91</v>
@@ -11770,7 +11770,7 @@
         <v>1.91</v>
       </c>
       <c r="AE70">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF70">
         <v>1.4</v>
@@ -11792,7 +11792,7 @@
         <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,7 +11891,7 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="R71">
         <v>2.16</v>
@@ -11909,22 +11909,22 @@
         <v>1.53</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA71">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB71">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AC71">
         <v>2.55</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
+        <v>1.22</v>
+      </c>
+      <c r="AK71">
         <v>1.44</v>
-      </c>
-      <c r="AK71">
-        <v>1.43</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12214,7 +12214,7 @@
         <v>3.5</v>
       </c>
       <c r="P73">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q73">
         <v>2.95</v>
@@ -12223,13 +12223,13 @@
         <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U73">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V73">
         <v>1.53</v>
@@ -12253,7 +12253,7 @@
         <v>2.25</v>
       </c>
       <c r="AC73">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AD73">
         <v>1.51</v>
@@ -12262,10 +12262,10 @@
         <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12374,58 +12374,58 @@
         <v>2.15</v>
       </c>
       <c r="O74">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="Q74">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="R74">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S74">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T74">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U74">
         <v>2.16</v>
       </c>
       <c r="V74">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W74">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z74">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="AA74">
         <v>1.53</v>
       </c>
       <c r="AB74">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC74">
         <v>2.28</v>
       </c>
       <c r="AD74">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE74">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF74">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG74">
         <v>2.5</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK74">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12546,7 +12546,7 @@
         <v>1.86</v>
       </c>
       <c r="R75">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S75">
         <v>1.34</v>
@@ -12555,16 +12555,16 @@
         <v>2.95</v>
       </c>
       <c r="U75">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="V75">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W75">
         <v>1.06</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
         <v>1.19</v>
@@ -12576,10 +12576,10 @@
         <v>1.78</v>
       </c>
       <c r="AB75">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC75">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AD75">
         <v>1.35</v>
@@ -12591,7 +12591,7 @@
         <v>2.01</v>
       </c>
       <c r="AG75">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         <v>11</v>
       </c>
       <c r="O77">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="P77">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -12878,13 +12878,13 @@
         <v>1.2</v>
       </c>
       <c r="T77">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="U77">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V77">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W77">
         <v>1.21</v>
@@ -12896,16 +12896,16 @@
         <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA77">
         <v>1.32</v>
       </c>
       <c r="AB77">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="AC77">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD77">
         <v>1.95</v>
@@ -12914,10 +12914,10 @@
         <v>1.36</v>
       </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK77">
         <v>1.02</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="O83">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P83">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O89">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q89">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R89">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S89">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T89">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U89">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V89">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W89">
         <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y89">
         <v>1.32</v>
       </c>
       <c r="Z89">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA89">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB89">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC89">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AD89">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE89">
         <v>1.03</v>
       </c>
       <c r="AF89">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG89">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
         <v>1.49</v>
@@ -16120,28 +16120,28 @@
         </is>
       </c>
       <c r="N97">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P97">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q97">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="R97">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T97">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U97">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="V97">
         <v>1.48</v>
@@ -16150,7 +16150,7 @@
         <v>1.08</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
         <v>1.18</v>
@@ -16165,19 +16165,19 @@
         <v>2.18</v>
       </c>
       <c r="AC97">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AD97">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE97">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF97">
         <v>1.55</v>
       </c>
       <c r="AG97">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
         <v>1.3</v>
@@ -16455,55 +16455,55 @@
         <v>2.3</v>
       </c>
       <c r="Q99">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="R99">
         <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T99">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U99">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V99">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W99">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z99">
         <v>3.48</v>
       </c>
       <c r="AA99">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB99">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC99">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD99">
         <v>1.32</v>
       </c>
       <c r="AE99">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
         <v>1.7</v>
       </c>
       <c r="AG99">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK99">
         <v>1.36</v>
@@ -16612,13 +16612,13 @@
         <v>2.1</v>
       </c>
       <c r="O100">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P100">
         <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R100">
         <v>1.99</v>
@@ -16633,7 +16633,7 @@
         <v>3.05</v>
       </c>
       <c r="V100">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W100">
         <v>1.02</v>
@@ -16642,22 +16642,22 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z100">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA100">
         <v>2.02</v>
       </c>
       <c r="AB100">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC100">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="AD100">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE100">
         <v>1.03</v>
@@ -16666,7 +16666,7 @@
         <v>1.83</v>
       </c>
       <c r="AG100">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,61 +16772,61 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O101">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P101">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q101">
         <v>3.58</v>
       </c>
       <c r="R101">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S101">
+        <v>1.38</v>
+      </c>
+      <c r="T101">
+        <v>2.67</v>
+      </c>
+      <c r="U101">
+        <v>2.98</v>
+      </c>
+      <c r="V101">
         <v>1.35</v>
       </c>
-      <c r="T101">
-        <v>2.79</v>
-      </c>
-      <c r="U101">
-        <v>2.75</v>
-      </c>
-      <c r="V101">
-        <v>1.4</v>
-      </c>
       <c r="W101">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z101">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA101">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AB101">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC101">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD101">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE101">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF101">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG101">
         <v>2.08</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK101">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,31 +16935,31 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O102">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P102">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q102">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R102">
         <v>2</v>
       </c>
       <c r="S102">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T102">
         <v>2.69</v>
       </c>
       <c r="U102">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V102">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W102">
         <v>1.03</v>
@@ -16968,28 +16968,28 @@
         <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z102">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA102">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC102">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AD102">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE102">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG102">
         <v>2.05</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK102">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,10 +17107,10 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="R103">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S103">
         <v>1.4</v>
@@ -17119,7 +17119,7 @@
         <v>2.66</v>
       </c>
       <c r="U103">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="V103">
         <v>1.36</v>
@@ -17137,16 +17137,16 @@
         <v>3.14</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD103">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
         <v>1.06</v>
@@ -17155,7 +17155,7 @@
         <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK103">
         <v>1.43</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G108">
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S108">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="V108">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB108">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="AC108">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD108">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG108">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G109">
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="R109">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U109">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="V109">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA109">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB109">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="AC109">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD109">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE109">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18900,10 +18900,10 @@
         <v>4.45</v>
       </c>
       <c r="Q114">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="R114">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S114">
         <v>1.37</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="O115">
         <v>3.2</v>
@@ -19072,19 +19072,19 @@
         <v>1.35</v>
       </c>
       <c r="T115">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U115">
         <v>2.4</v>
       </c>
       <c r="V115">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W115">
         <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
         <v>1.17</v>
@@ -19093,7 +19093,7 @@
         <v>3.98</v>
       </c>
       <c r="AA115">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB115">
         <v>2.09</v>
@@ -19108,10 +19108,10 @@
         <v>1.14</v>
       </c>
       <c r="AF115">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG115">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -20684,34 +20684,34 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="O125">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P125">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q125">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="R125">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="S125">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T125">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="U125">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="V125">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W125">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X125">
         <v>1.03</v>
@@ -20723,7 +20723,7 @@
         <v>2.8</v>
       </c>
       <c r="AA125">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB125">
         <v>1.66</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK125">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O128">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P128">
         <v>2.8</v>
       </c>
       <c r="Q128">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="R128">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S128">
         <v>1.22</v>
@@ -21206,16 +21206,16 @@
         <v>1</v>
       </c>
       <c r="Y128">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z128">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA128">
         <v>1.37</v>
       </c>
       <c r="AB128">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AC128">
         <v>2</v>
@@ -21339,28 +21339,28 @@
         <v>3.3</v>
       </c>
       <c r="O129">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="P129">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Q129">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R129">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="S129">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W129">
         <v>1.15</v>
@@ -21375,10 +21375,10 @@
         <v>5.05</v>
       </c>
       <c r="AA129">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC129">
         <v>2.16</v>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AK129">
         <v>1.32</v>
@@ -21508,25 +21508,25 @@
         <v>2.17</v>
       </c>
       <c r="Q130">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R130">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S130">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T130">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="U130">
         <v>1.85</v>
       </c>
       <c r="V130">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="W130">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X130">
         <v>1.01</v>
@@ -21541,7 +21541,7 @@
         <v>1.25</v>
       </c>
       <c r="AB130">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AC130">
         <v>1.75</v>
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK130">
         <v>1.44</v>
@@ -21671,10 +21671,10 @@
         <v>4.95</v>
       </c>
       <c r="Q131">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R131">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="S131">
         <v>1.14</v>
@@ -21683,13 +21683,13 @@
         <v>5</v>
       </c>
       <c r="U131">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V131">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W131">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X131">
         <v>1.01</v>
@@ -21701,22 +21701,22 @@
         <v>6.95</v>
       </c>
       <c r="AA131">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB131">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC131">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD131">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AE131">
         <v>1.42</v>
       </c>
       <c r="AF131">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG131">
         <v>2.86</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK131">
         <v>2.49</v>
@@ -21825,22 +21825,22 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="O132">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P132">
         <v>3.65</v>
       </c>
       <c r="Q132">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R132">
         <v>2.55</v>
       </c>
       <c r="S132">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T132">
         <v>4.25</v>
@@ -21849,7 +21849,7 @@
         <v>1.91</v>
       </c>
       <c r="V132">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W132">
         <v>1.2</v>
@@ -21879,7 +21879,7 @@
         <v>1.37</v>
       </c>
       <c r="AF132">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG132">
         <v>2.94</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK132">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21994,7 +21994,7 @@
         <v>4</v>
       </c>
       <c r="P133">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q133">
         <v>3.2</v>
@@ -22006,7 +22006,7 @@
         <v>1.11</v>
       </c>
       <c r="T133">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="U133">
         <v>1.66</v>
@@ -22021,10 +22021,10 @@
         <v>1</v>
       </c>
       <c r="Y133">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z133">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA133">
         <v>1.16</v>
@@ -22036,7 +22036,7 @@
         <v>1.52</v>
       </c>
       <c r="AD133">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AE133">
         <v>1.65</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK133">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O134">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="P134">
-        <v>6.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q134">
+        <v>3.56</v>
+      </c>
+      <c r="R134">
+        <v>2.14</v>
+      </c>
+      <c r="S134">
+        <v>1.35</v>
+      </c>
+      <c r="T134">
+        <v>3</v>
+      </c>
+      <c r="U134">
+        <v>2.73</v>
+      </c>
+      <c r="V134">
+        <v>1.42</v>
+      </c>
+      <c r="W134">
+        <v>1.08</v>
+      </c>
+      <c r="X134">
+        <v>1.05</v>
+      </c>
+      <c r="Y134">
+        <v>1.24</v>
+      </c>
+      <c r="Z134">
+        <v>3.38</v>
+      </c>
+      <c r="AA134">
+        <v>1.83</v>
+      </c>
+      <c r="AB134">
         <v>1.95</v>
       </c>
-      <c r="R134">
-        <v>2.5</v>
-      </c>
-      <c r="S134">
-        <v>1.32</v>
-      </c>
-      <c r="T134">
+      <c r="AC134">
         <v>3.1</v>
       </c>
-      <c r="U134">
-        <v>2.25</v>
-      </c>
-      <c r="V134">
-        <v>1.51</v>
-      </c>
-      <c r="W134">
-        <v>1.11</v>
-      </c>
-      <c r="X134">
-        <v>1.02</v>
-      </c>
-      <c r="Y134">
-        <v>1.16</v>
-      </c>
-      <c r="Z134">
-        <v>4.1</v>
-      </c>
-      <c r="AA134">
-        <v>1.64</v>
-      </c>
-      <c r="AB134">
-        <v>2.25</v>
-      </c>
-      <c r="AC134">
-        <v>2.44</v>
-      </c>
       <c r="AD134">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE134">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG134">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK134">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="O135">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P135">
-        <v>2.42</v>
+        <v>6.75</v>
       </c>
       <c r="Q135">
-        <v>3.51</v>
+        <v>1.95</v>
       </c>
       <c r="R135">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="S135">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="U135">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="V135">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z135">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="AA135">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB135">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AC135">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AD135">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE135">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF135">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG135">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK135">
-        <v>1.4</v>
+        <v>2.47</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22640,10 +22640,10 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="O137">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P137">
         <v>2.6</v>
@@ -22658,25 +22658,25 @@
         <v>1.31</v>
       </c>
       <c r="T137">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U137">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V137">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W137">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X137">
         <v>1.05</v>
       </c>
       <c r="Y137">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z137">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AA137">
         <v>1.74</v>
@@ -22694,10 +22694,10 @@
         <v>1.09</v>
       </c>
       <c r="AF137">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG137">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O139">
         <v>3.1</v>
@@ -22975,19 +22975,19 @@
         <v>3</v>
       </c>
       <c r="Q139">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R139">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S139">
         <v>1.4</v>
       </c>
       <c r="T139">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U139">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="V139">
         <v>1.34</v>
@@ -22996,34 +22996,34 @@
         <v>1.02</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z139">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="AA139">
         <v>2.1</v>
       </c>
       <c r="AB139">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC139">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AD139">
         <v>1.21</v>
       </c>
       <c r="AE139">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
         <v>1.8</v>
       </c>
       <c r="AG139">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23458,13 +23458,13 @@
         <v>8.5</v>
       </c>
       <c r="O142">
-        <v>5.6</v>
+        <v>6.05</v>
       </c>
       <c r="P142">
         <v>1.31</v>
       </c>
       <c r="Q142">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R142">
         <v>2.8</v>
@@ -23476,10 +23476,10 @@
         <v>4.4</v>
       </c>
       <c r="U142">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V142">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W142">
         <v>1.2</v>
@@ -23488,7 +23488,7 @@
         <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z142">
         <v>7</v>
@@ -23500,19 +23500,19 @@
         <v>2.88</v>
       </c>
       <c r="AC142">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AD142">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE142">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF142">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG142">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.12</v>
+        <v>3.4</v>
       </c>
       <c r="AK142">
         <v>1.05</v>
@@ -23621,58 +23621,58 @@
         <v>1.65</v>
       </c>
       <c r="O143">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P143">
-        <v>4.28</v>
+        <v>3.9</v>
       </c>
       <c r="Q143">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R143">
         <v>2.5</v>
       </c>
       <c r="S143">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T143">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="U143">
         <v>2</v>
       </c>
       <c r="V143">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W143">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X143">
         <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z143">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA143">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB143">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AC143">
         <v>2.07</v>
       </c>
       <c r="AD143">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE143">
         <v>1.29</v>
       </c>
       <c r="AF143">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG143">
         <v>2.62</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK143">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23784,34 +23784,34 @@
         <v>2.8</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P144">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q144">
         <v>3.42</v>
       </c>
       <c r="R144">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S144">
         <v>1.26</v>
       </c>
       <c r="T144">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U144">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="V144">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W144">
         <v>1.13</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
         <v>1.14</v>
@@ -23820,10 +23820,10 @@
         <v>4.45</v>
       </c>
       <c r="AA144">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB144">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC144">
         <v>2.38</v>
@@ -23832,7 +23832,7 @@
         <v>1.5</v>
       </c>
       <c r="AE144">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF144">
         <v>1.48</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P145">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="Q145">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U145">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V145">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z145">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA145">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AB145">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AC145">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="AD145">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF145">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AG145">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK145">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24270,19 +24270,19 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="O147">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="P147">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q147">
         <v>3.91</v>
       </c>
       <c r="R147">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S147">
         <v>1.3</v>
@@ -24309,13 +24309,13 @@
         <v>3.78</v>
       </c>
       <c r="AA147">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB147">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC147">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD147">
         <v>1.42</v>
@@ -24433,34 +24433,34 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O148">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P148">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
       </c>
       <c r="R148">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S148">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T148">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U148">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V148">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W148">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X148">
         <v>1.03</v>
@@ -24469,28 +24469,28 @@
         <v>1.4</v>
       </c>
       <c r="Z148">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="AA148">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB148">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC148">
-        <v>4.14</v>
+        <v>3.62</v>
       </c>
       <c r="AD148">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE148">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF148">
         <v>2</v>
       </c>
       <c r="AG148">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK148">
         <v>2</v>
@@ -26389,25 +26389,25 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O160">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="P160">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Q160">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R160">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="S160">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T160">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="U160">
         <v>1.98</v>
@@ -26416,37 +26416,37 @@
         <v>1.77</v>
       </c>
       <c r="W160">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X160">
         <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z160">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="AA160">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB160">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AC160">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD160">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE160">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF160">
         <v>1.6</v>
       </c>
       <c r="AG160">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26561,16 +26561,16 @@
         <v>0</v>
       </c>
       <c r="Q161">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="R161">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S161">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T161">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="U161">
         <v>2.05</v>
@@ -26588,28 +26588,28 @@
         <v>1.06</v>
       </c>
       <c r="Z161">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AA161">
+        <v>1.35</v>
+      </c>
+      <c r="AB161">
+        <v>2.76</v>
+      </c>
+      <c r="AC161">
+        <v>2.02</v>
+      </c>
+      <c r="AD161">
+        <v>1.79</v>
+      </c>
+      <c r="AE161">
         <v>1.36</v>
-      </c>
-      <c r="AB161">
-        <v>2.72</v>
-      </c>
-      <c r="AC161">
-        <v>2.03</v>
-      </c>
-      <c r="AD161">
-        <v>1.78</v>
-      </c>
-      <c r="AE161">
-        <v>1.28</v>
       </c>
       <c r="AF161">
         <v>1.36</v>
       </c>
       <c r="AG161">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK161">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26911,31 +26911,31 @@
         <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z163">
         <v>4</v>
       </c>
       <c r="AA163">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB163">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC163">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD163">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE163">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF163">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG163">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -28185,49 +28185,49 @@
         <v>2.08</v>
       </c>
       <c r="O171">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P171">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q171">
         <v>2.56</v>
       </c>
       <c r="R171">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S171">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T171">
         <v>3.98</v>
       </c>
       <c r="U171">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V171">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W171">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X171">
         <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z171">
-        <v>6.4</v>
+        <v>6.21</v>
       </c>
       <c r="AA171">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB171">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AC171">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AD171">
         <v>1.82</v>
@@ -28508,28 +28508,28 @@
         </is>
       </c>
       <c r="N173">
-        <v>3.85</v>
+        <v>3.33</v>
       </c>
       <c r="O173">
-        <v>3.51</v>
+        <v>3.65</v>
       </c>
       <c r="P173">
         <v>1.85</v>
       </c>
       <c r="Q173">
-        <v>3.73</v>
+        <v>4.33</v>
       </c>
       <c r="R173">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S173">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T173">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="U173">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="V173">
         <v>1.5</v>
@@ -28541,31 +28541,31 @@
         <v>1.02</v>
       </c>
       <c r="Y173">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z173">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="AA173">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB173">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AC173">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD173">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE173">
         <v>1.15</v>
       </c>
       <c r="AF173">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG173">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O176">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="P176">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q176">
         <v>2.1</v>
@@ -29021,34 +29021,34 @@
         <v>2.6</v>
       </c>
       <c r="V176">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W176">
         <v>1.1</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y176">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z176">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AA176">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB176">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC176">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD176">
         <v>1.4</v>
       </c>
       <c r="AE176">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF176">
         <v>1.75</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29193,31 +29193,31 @@
         <v>0</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE177">
         <v>0</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29332,16 +29332,16 @@
         <v>0</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U178">
         <v>0</v>
@@ -29356,16 +29356,16 @@
         <v>0</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29377,10 +29377,10 @@
         <v>0</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O180">
         <v>3.1</v>
@@ -29658,49 +29658,49 @@
         <v>2.7</v>
       </c>
       <c r="Q180">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R180">
         <v>2.04</v>
       </c>
       <c r="S180">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T180">
         <v>2.9</v>
       </c>
       <c r="U180">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V180">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W180">
         <v>1.07</v>
       </c>
       <c r="X180">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y180">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z180">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA180">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AB180">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC180">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="AD180">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE180">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF180">
         <v>1.7</v>
@@ -29812,61 +29812,61 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="O181">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P181">
-        <v>4.45</v>
+        <v>6</v>
       </c>
       <c r="Q181">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="R181">
         <v>2.38</v>
       </c>
       <c r="S181">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T181">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U181">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="V181">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W181">
         <v>1.12</v>
       </c>
       <c r="X181">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y181">
         <v>1.2</v>
       </c>
       <c r="Z181">
-        <v>4.1</v>
+        <v>4.51</v>
       </c>
       <c r="AA181">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB181">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC181">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AD181">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE181">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF181">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG181">
         <v>2</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK181">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O184">
         <v>3.75</v>
       </c>
       <c r="P184">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q184">
         <v>2.23</v>
@@ -30322,40 +30322,40 @@
         <v>3.22</v>
       </c>
       <c r="U184">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V184">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W184">
         <v>1.11</v>
       </c>
       <c r="X184">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y184">
         <v>1.2</v>
       </c>
       <c r="Z184">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA184">
+        <v>1.65</v>
+      </c>
+      <c r="AB184">
+        <v>2.17</v>
+      </c>
+      <c r="AC184">
+        <v>2.52</v>
+      </c>
+      <c r="AD184">
+        <v>1.41</v>
+      </c>
+      <c r="AE184">
+        <v>1.18</v>
+      </c>
+      <c r="AF184">
         <v>1.62</v>
-      </c>
-      <c r="AB184">
-        <v>2.4</v>
-      </c>
-      <c r="AC184">
-        <v>2.46</v>
-      </c>
-      <c r="AD184">
-        <v>1.5</v>
-      </c>
-      <c r="AE184">
-        <v>1.2</v>
-      </c>
-      <c r="AF184">
-        <v>1.6</v>
       </c>
       <c r="AG184">
         <v>2.15</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="O188">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P188">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -30971,7 +30971,7 @@
         <v>1.32</v>
       </c>
       <c r="T188">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="U188">
         <v>2.6</v>
@@ -30986,16 +30986,16 @@
         <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z188">
-        <v>3.68</v>
+        <v>4.04</v>
       </c>
       <c r="AA188">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB188">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC188">
         <v>2.73</v>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AK188">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31771,61 +31771,61 @@
         <v>1.44</v>
       </c>
       <c r="O193">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P193">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q193">
+        <v>1.94</v>
+      </c>
+      <c r="R193">
+        <v>2.25</v>
+      </c>
+      <c r="S193">
+        <v>1.35</v>
+      </c>
+      <c r="T193">
+        <v>3.01</v>
+      </c>
+      <c r="U193">
+        <v>2.56</v>
+      </c>
+      <c r="V193">
+        <v>1.41</v>
+      </c>
+      <c r="W193">
+        <v>1.09</v>
+      </c>
+      <c r="X193">
+        <v>1.04</v>
+      </c>
+      <c r="Y193">
+        <v>1.21</v>
+      </c>
+      <c r="Z193">
+        <v>3.58</v>
+      </c>
+      <c r="AA193">
+        <v>1.77</v>
+      </c>
+      <c r="AB193">
+        <v>1.92</v>
+      </c>
+      <c r="AC193">
+        <v>2.92</v>
+      </c>
+      <c r="AD193">
+        <v>1.31</v>
+      </c>
+      <c r="AE193">
+        <v>1.08</v>
+      </c>
+      <c r="AF193">
         <v>1.91</v>
       </c>
-      <c r="R193">
-        <v>2.4</v>
-      </c>
-      <c r="S193">
-        <v>1.28</v>
-      </c>
-      <c r="T193">
-        <v>3.14</v>
-      </c>
-      <c r="U193">
-        <v>2.5</v>
-      </c>
-      <c r="V193">
-        <v>1.44</v>
-      </c>
-      <c r="W193">
-        <v>1.1</v>
-      </c>
-      <c r="X193">
-        <v>1.01</v>
-      </c>
-      <c r="Y193">
-        <v>1.2</v>
-      </c>
-      <c r="Z193">
-        <v>3.7</v>
-      </c>
-      <c r="AA193">
-        <v>1.72</v>
-      </c>
-      <c r="AB193">
-        <v>2.07</v>
-      </c>
-      <c r="AC193">
-        <v>2.65</v>
-      </c>
-      <c r="AD193">
-        <v>1.38</v>
-      </c>
-      <c r="AE193">
-        <v>1.1</v>
-      </c>
-      <c r="AF193">
-        <v>1.84</v>
-      </c>
       <c r="AG193">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK193">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31943,13 +31943,13 @@
         <v>1.86</v>
       </c>
       <c r="R194">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S194">
         <v>1.22</v>
       </c>
       <c r="T194">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U194">
         <v>2.23</v>
@@ -31961,7 +31961,7 @@
         <v>1.13</v>
       </c>
       <c r="X194">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
         <v>1.1</v>
@@ -31976,16 +31976,16 @@
         <v>2.46</v>
       </c>
       <c r="AC194">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AD194">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AE194">
         <v>1.22</v>
       </c>
       <c r="AF194">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG194">
         <v>2.1</v>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK194">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O213">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P213">
         <v>7</v>
       </c>
       <c r="Q213">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="R213">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="S213">
         <v>1.17</v>
       </c>
       <c r="T213">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U213">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="V213">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="W213">
         <v>1.2</v>
       </c>
       <c r="X213">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z213">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="AA213">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB213">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AC213">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AD213">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AE213">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF213">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG213">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK213">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -36006,10 +36006,10 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O219">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P219">
         <v>2.05</v>
@@ -36024,19 +36024,19 @@
         <v>1.33</v>
       </c>
       <c r="T219">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="U219">
         <v>2.75</v>
       </c>
       <c r="V219">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W219">
         <v>1.05</v>
       </c>
       <c r="X219">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y219">
         <v>1.25</v>
@@ -36045,7 +36045,7 @@
         <v>3.6</v>
       </c>
       <c r="AA219">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB219">
         <v>1.85</v>
@@ -36054,7 +36054,7 @@
         <v>3</v>
       </c>
       <c r="AD219">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE219">
         <v>1.09</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK219">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -37482,10 +37482,10 @@
         <v>1.25</v>
       </c>
       <c r="Q228">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="R228">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S228">
         <v>1.22</v>
@@ -37512,13 +37512,13 @@
         <v>5.06</v>
       </c>
       <c r="AA228">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB228">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC228">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AD228">
         <v>1.59</v>
@@ -41059,16 +41059,16 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O250">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P250">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="Q250">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="R250">
         <v>2.02</v>
@@ -41080,7 +41080,7 @@
         <v>2.39</v>
       </c>
       <c r="U250">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="V250">
         <v>1.25</v>
@@ -41089,34 +41089,34 @@
         <v>1.02</v>
       </c>
       <c r="X250">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y250">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z250">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AA250">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AB250">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC250">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AD250">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE250">
         <v>1.01</v>
       </c>
       <c r="AF250">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG250">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O251">
         <v>3.25</v>
       </c>
       <c r="P251">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q251">
         <v>2.82</v>
@@ -41246,7 +41246,7 @@
         <v>2.89</v>
       </c>
       <c r="V251">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W251">
         <v>1.08</v>
@@ -41255,31 +41255,31 @@
         <v>1.03</v>
       </c>
       <c r="Y251">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z251">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA251">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AB251">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC251">
         <v>3.05</v>
       </c>
       <c r="AD251">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE251">
         <v>1.07</v>
       </c>
       <c r="AF251">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG251">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="O254">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P254">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -42369,10 +42369,10 @@
         <v>3.4</v>
       </c>
       <c r="P258">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q258">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="R258">
         <v>2.13</v>
@@ -42381,7 +42381,7 @@
         <v>1.3</v>
       </c>
       <c r="T258">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U258">
         <v>2.59</v>
@@ -42396,31 +42396,31 @@
         <v>1.02</v>
       </c>
       <c r="Y258">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z258">
-        <v>3.58</v>
+        <v>3.83</v>
       </c>
       <c r="AA258">
         <v>1.78</v>
       </c>
       <c r="AB258">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC258">
         <v>2.88</v>
       </c>
       <c r="AD258">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE258">
         <v>1.1</v>
       </c>
       <c r="AF258">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG258">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q259">
         <v>1.67</v>
       </c>
       <c r="R259">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="S259">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T259">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="U259">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="V259">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="W259">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X259">
         <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z259">
-        <v>9.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA259">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AB259">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AC259">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AD259">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AE259">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF259">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AG259">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK259">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -43667,19 +43667,19 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="O266">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P266">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q266">
         <v>2.05</v>
       </c>
       <c r="R266">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="S266">
         <v>1.4</v>
@@ -43700,19 +43700,19 @@
         <v>1</v>
       </c>
       <c r="Y266">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z266">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA266">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB266">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC266">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AD266">
         <v>1.23</v>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK266">
         <v>2.38</v>
@@ -44156,7 +44156,7 @@
         </is>
       </c>
       <c r="N269">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="O269">
         <v>3.9</v>
@@ -44171,13 +44171,13 @@
         <v>2.24</v>
       </c>
       <c r="S269">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T269">
         <v>3.3</v>
       </c>
       <c r="U269">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V269">
         <v>1.47</v>
@@ -44198,7 +44198,7 @@
         <v>1.7</v>
       </c>
       <c r="AB269">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC269">
         <v>2.64</v>
@@ -44213,7 +44213,7 @@
         <v>1.68</v>
       </c>
       <c r="AG269">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK269">
         <v>1.18</v>
@@ -44319,19 +44319,19 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="O270">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P270">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q270">
         <v>3</v>
       </c>
       <c r="R270">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S270">
         <v>1.3</v>
@@ -44346,16 +44346,16 @@
         <v>1.46</v>
       </c>
       <c r="W270">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X270">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y270">
         <v>1.21</v>
       </c>
       <c r="Z270">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="AA270">
         <v>1.73</v>
@@ -44367,7 +44367,7 @@
         <v>2.8</v>
       </c>
       <c r="AD270">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE270">
         <v>1.11</v>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK270">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -45300,61 +45300,61 @@
         <v>1.75</v>
       </c>
       <c r="O276">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P276">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q276">
         <v>2.38</v>
       </c>
       <c r="R276">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S276">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T276">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="U276">
         <v>2.8</v>
       </c>
       <c r="V276">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W276">
         <v>1.08</v>
       </c>
       <c r="X276">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y276">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z276">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AA276">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB276">
         <v>1.85</v>
       </c>
       <c r="AC276">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD276">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE276">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF276">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG276">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK276">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45463,13 +45463,13 @@
         <v>2.02</v>
       </c>
       <c r="O277">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="Q277">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R277">
         <v>2.07</v>
@@ -45481,10 +45481,10 @@
         <v>2.7</v>
       </c>
       <c r="U277">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="V277">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W277">
         <v>1.06</v>
@@ -45964,10 +45964,10 @@
         <v>2.28</v>
       </c>
       <c r="S280">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T280">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U280">
         <v>2.25</v>
@@ -45994,19 +45994,19 @@
         <v>2.25</v>
       </c>
       <c r="AC280">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD280">
         <v>1.47</v>
       </c>
       <c r="AE280">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF280">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AG280">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>3.62</v>
       </c>
       <c r="R281">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S281">
         <v>1.3</v>
@@ -46145,7 +46145,7 @@
         <v>1.01</v>
       </c>
       <c r="Y281">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z281">
         <v>3.48</v>
@@ -46154,7 +46154,7 @@
         <v>1.81</v>
       </c>
       <c r="AB281">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AC281">
         <v>2.97</v>
@@ -46163,7 +46163,7 @@
         <v>1.3</v>
       </c>
       <c r="AE281">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF281">
         <v>1.64</v>
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AK281">
         <v>1.32</v>
@@ -46610,16 +46610,16 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U284">
         <v>0</v>
@@ -46634,31 +46634,31 @@
         <v>0</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE284">
         <v>0</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46930,61 +46930,61 @@
         <v>1.73</v>
       </c>
       <c r="O286">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="P286">
-        <v>3.8</v>
+        <v>4.28</v>
       </c>
       <c r="Q286">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R286">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S286">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T286">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="U286">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V286">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W286">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X286">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y286">
         <v>1.2</v>
       </c>
       <c r="Z286">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA286">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB286">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AC286">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD286">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE286">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF286">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG286">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK286">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,65 +47416,65 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O289">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="P289">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q289">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R289">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S289">
+        <v>1.69</v>
+      </c>
+      <c r="T289">
+        <v>2.1</v>
+      </c>
+      <c r="U289">
+        <v>4.15</v>
+      </c>
+      <c r="V289">
+        <v>1.16</v>
+      </c>
+      <c r="W289">
+        <v>1.02</v>
+      </c>
+      <c r="X289">
+        <v>1.17</v>
+      </c>
+      <c r="Y289">
+        <v>1.68</v>
+      </c>
+      <c r="Z289">
+        <v>2.14</v>
+      </c>
+      <c r="AA289">
+        <v>3.1</v>
+      </c>
+      <c r="AB289">
+        <v>1.33</v>
+      </c>
+      <c r="AC289">
+        <v>6.15</v>
+      </c>
+      <c r="AD289">
+        <v>1.1</v>
+      </c>
+      <c r="AE289">
+        <v>1.03</v>
+      </c>
+      <c r="AF289">
+        <v>2.3</v>
+      </c>
+      <c r="AG289">
         <v>1.53</v>
       </c>
-      <c r="T289">
-        <v>2.33</v>
-      </c>
-      <c r="U289">
-        <v>3.5</v>
-      </c>
-      <c r="V289">
-        <v>1.24</v>
-      </c>
-      <c r="W289">
-        <v>1.01</v>
-      </c>
-      <c r="X289">
-        <v>1.1</v>
-      </c>
-      <c r="Y289">
-        <v>1.5</v>
-      </c>
-      <c r="Z289">
-        <v>2.56</v>
-      </c>
-      <c r="AA289">
-        <v>2.5</v>
-      </c>
-      <c r="AB289">
-        <v>1.46</v>
-      </c>
-      <c r="AC289">
-        <v>5</v>
-      </c>
-      <c r="AD289">
-        <v>1.17</v>
-      </c>
-      <c r="AE289">
-        <v>1.05</v>
-      </c>
-      <c r="AF289">
-        <v>2</v>
-      </c>
-      <c r="AG289">
-        <v>1.73</v>
-      </c>
       <c r="AH289" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK289">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,55 +47579,55 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="O290">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P290">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="Q290">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="R290">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S290">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="T290">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U290">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="V290">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W290">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X290">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Y290">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="Z290">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AA290">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB290">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC290">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="AD290">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE290">
         <v>1.03</v>
@@ -47636,7 +47636,7 @@
         <v>2.3</v>
       </c>
       <c r="AG290">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK290">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="O291">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P291">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q291">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R291">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S291">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T291">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U291">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V291">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W291">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X291">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y291">
         <v>1.5</v>
       </c>
       <c r="Z291">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA291">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB291">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AC291">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD291">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE291">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF291">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG291">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK291">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -48240,16 +48240,16 @@
         <v>4.2</v>
       </c>
       <c r="Q294">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R294">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S294">
         <v>1.25</v>
       </c>
       <c r="T294">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U294">
         <v>2.4</v>
@@ -48264,16 +48264,16 @@
         <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z294">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA294">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB294">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AC294">
         <v>2.55</v>
@@ -48563,13 +48563,13 @@
         <v>3.5</v>
       </c>
       <c r="P296">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="Q296">
         <v>2.55</v>
       </c>
       <c r="R296">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S296">
         <v>1.38</v>
@@ -48581,7 +48581,7 @@
         <v>2.77</v>
       </c>
       <c r="V296">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W296">
         <v>1.05</v>
@@ -48593,22 +48593,22 @@
         <v>1.3</v>
       </c>
       <c r="Z296">
-        <v>3.24</v>
+        <v>3.59</v>
       </c>
       <c r="AA296">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB296">
         <v>1.85</v>
       </c>
       <c r="AC296">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AD296">
         <v>1.28</v>
       </c>
       <c r="AE296">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF296">
         <v>1.77</v>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK296">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48723,10 +48723,10 @@
         <v>6.2</v>
       </c>
       <c r="O297">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P297">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q297">
         <v>6</v>
@@ -48735,10 +48735,10 @@
         <v>2.35</v>
       </c>
       <c r="S297">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T297">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U297">
         <v>2.53</v>
@@ -48747,37 +48747,37 @@
         <v>1.46</v>
       </c>
       <c r="W297">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X297">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z297">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA297">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB297">
         <v>2.14</v>
       </c>
       <c r="AC297">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AD297">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE297">
         <v>1.1</v>
       </c>
       <c r="AF297">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG297">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>1.21</v>
       </c>
       <c r="AK297">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48883,52 +48883,52 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O298">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P298">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
       </c>
       <c r="R298">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S298">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T298">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U298">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="V298">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W298">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X298">
         <v>1.02</v>
       </c>
       <c r="Y298">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z298">
         <v>2.89</v>
       </c>
       <c r="AA298">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AB298">
         <v>1.75</v>
       </c>
       <c r="AC298">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AD298">
         <v>1.22</v>
@@ -49218,16 +49218,16 @@
         <v>1.65</v>
       </c>
       <c r="Q300">
-        <v>5.13</v>
+        <v>5.18</v>
       </c>
       <c r="R300">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S300">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T300">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U300">
         <v>2.1</v>
@@ -49245,7 +49245,7 @@
         <v>1.06</v>
       </c>
       <c r="Z300">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA300">
         <v>1.35</v>
@@ -49384,52 +49384,52 @@
         <v>1.53</v>
       </c>
       <c r="R301">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S301">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T301">
-        <v>3.08</v>
+        <v>3.94</v>
       </c>
       <c r="U301">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="V301">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="W301">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X301">
         <v>1.01</v>
       </c>
       <c r="Y301">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z301">
-        <v>5.47</v>
+        <v>7.2</v>
       </c>
       <c r="AA301">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB301">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="AC301">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD301">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AE301">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AF301">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="AG301">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>1.07</v>
       </c>
       <c r="AK301">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -50187,22 +50187,22 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="O306">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P306">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="Q306">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R306">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S306">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T306">
         <v>2.56</v>
@@ -50211,13 +50211,13 @@
         <v>3.3</v>
       </c>
       <c r="V306">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W306">
         <v>1.03</v>
       </c>
       <c r="X306">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y306">
         <v>1.41</v>
@@ -50226,19 +50226,19 @@
         <v>2.64</v>
       </c>
       <c r="AA306">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AB306">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC306">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD306">
         <v>1.16</v>
       </c>
       <c r="AE306">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF306">
         <v>2</v>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK306">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50676,19 +50676,19 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O309">
         <v>3.4</v>
       </c>
       <c r="P309">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q309">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="R309">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="S309">
         <v>1.28</v>
@@ -50700,7 +50700,7 @@
         <v>2.4</v>
       </c>
       <c r="V309">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W309">
         <v>1.12</v>
@@ -50727,7 +50727,7 @@
         <v>1.42</v>
       </c>
       <c r="AE309">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF309">
         <v>1.52</v>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK309">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -51328,10 +51328,10 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O313">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P313">
         <v>3.85</v>
@@ -51340,19 +51340,19 @@
         <v>2.38</v>
       </c>
       <c r="R313">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S313">
         <v>1.4</v>
       </c>
       <c r="T313">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="U313">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V313">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W313">
         <v>1.04</v>
@@ -51361,31 +51361,31 @@
         <v>1.02</v>
       </c>
       <c r="Y313">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z313">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="AA313">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AB313">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC313">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD313">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE313">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF313">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG313">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK313">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51491,19 +51491,19 @@
         </is>
       </c>
       <c r="N314">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O314">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P314">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q314">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R314">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S314">
         <v>1.28</v>
@@ -51512,37 +51512,37 @@
         <v>3.25</v>
       </c>
       <c r="U314">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V314">
         <v>1.57</v>
       </c>
       <c r="W314">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X314">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y314">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z314">
         <v>4.6</v>
       </c>
       <c r="AA314">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB314">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC314">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD314">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE314">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF314">
         <v>1.55</v>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.82</v>
+        <v>1.28</v>
       </c>
       <c r="AK314">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51989,13 +51989,13 @@
         <v>0</v>
       </c>
       <c r="Q317">
-        <v>5</v>
+        <v>5.52</v>
       </c>
       <c r="R317">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S317">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T317">
         <v>3.9</v>
@@ -52007,7 +52007,7 @@
         <v>1.63</v>
       </c>
       <c r="W317">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X317">
         <v>1.02</v>
@@ -52034,7 +52034,7 @@
         <v>1.22</v>
       </c>
       <c r="AF317">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AG317">
         <v>2.23</v>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>2.52</v>
+        <v>1.12</v>
       </c>
       <c r="AK317">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52155,7 +52155,7 @@
         <v>3.22</v>
       </c>
       <c r="R318">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S318">
         <v>1.22</v>
@@ -52167,7 +52167,7 @@
         <v>2.5</v>
       </c>
       <c r="V318">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W318">
         <v>1.06</v>
@@ -52176,7 +52176,7 @@
         <v>1</v>
       </c>
       <c r="Y318">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z318">
         <v>3.85</v>
@@ -52185,7 +52185,7 @@
         <v>1.67</v>
       </c>
       <c r="AB318">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AC318">
         <v>2.62</v>
@@ -52194,10 +52194,10 @@
         <v>1.38</v>
       </c>
       <c r="AE318">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF318">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG318">
         <v>1.95</v>
@@ -52478,55 +52478,55 @@
         <v>13.6</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA320">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB320">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52632,7 +52632,7 @@
         </is>
       </c>
       <c r="N321">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="O321">
         <v>3.5</v>
@@ -52641,7 +52641,7 @@
         <v>2.15</v>
       </c>
       <c r="Q321">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="R321">
         <v>2.08</v>
@@ -52653,7 +52653,7 @@
         <v>3</v>
       </c>
       <c r="U321">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="V321">
         <v>1.41</v>
@@ -52662,34 +52662,34 @@
         <v>1.06</v>
       </c>
       <c r="X321">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y321">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z321">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA321">
         <v>1.83</v>
       </c>
       <c r="AB321">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AC321">
         <v>2.99</v>
       </c>
       <c r="AD321">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE321">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF321">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG321">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
+        <v>1.29</v>
+      </c>
+      <c r="AK321">
         <v>1.3</v>
-      </c>
-      <c r="AK321">
-        <v>1.34</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O322">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P322">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52970,10 +52970,10 @@
         <v>9</v>
       </c>
       <c r="R323">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="S323">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T323">
         <v>3.15</v>
@@ -52982,7 +52982,7 @@
         <v>2.55</v>
       </c>
       <c r="V323">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W323">
         <v>1.06</v>
@@ -52997,7 +52997,7 @@
         <v>3.95</v>
       </c>
       <c r="AA323">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB323">
         <v>2.02</v>
@@ -53009,13 +53009,13 @@
         <v>1.38</v>
       </c>
       <c r="AE323">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF323">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG323">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK323">
         <v>1.04</v>
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O324">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P324">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53447,19 +53447,19 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O326">
         <v>3.8</v>
       </c>
       <c r="P326">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q326">
         <v>2.1</v>
       </c>
       <c r="R326">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S326">
         <v>1.3</v>
@@ -53468,37 +53468,37 @@
         <v>3.2</v>
       </c>
       <c r="U326">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V326">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W326">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X326">
         <v>1.04</v>
       </c>
       <c r="Y326">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z326">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA326">
         <v>1.69</v>
       </c>
       <c r="AB326">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AC326">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD326">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE326">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF326">
         <v>1.65</v>
@@ -53517,7 +53517,7 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK326">
         <v>2.1</v>
@@ -53619,7 +53619,7 @@
         <v>0</v>
       </c>
       <c r="Q327">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R327">
         <v>2.25</v>
@@ -53637,22 +53637,22 @@
         <v>1.47</v>
       </c>
       <c r="W327">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X327">
         <v>1.03</v>
       </c>
       <c r="Y327">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z327">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA327">
         <v>1.64</v>
       </c>
       <c r="AB327">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC327">
         <v>2.59</v>
@@ -53664,10 +53664,10 @@
         <v>1.11</v>
       </c>
       <c r="AF327">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG327">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AK327">
         <v>1.9</v>
@@ -53782,55 +53782,55 @@
         <v>4.11</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U328">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V328">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W328">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y328">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z328">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA328">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB328">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC328">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD328">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE328">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG328">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK328">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -54295,10 +54295,10 @@
         <v>1.04</v>
       </c>
       <c r="Y331">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z331">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA331">
         <v>1.7</v>
@@ -54316,10 +54316,10 @@
         <v>1.1</v>
       </c>
       <c r="AF331">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG331">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK331">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL331">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>3.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>2.23</v>
+        <v>4.2</v>
       </c>
       <c r="R10">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -1975,28 +1975,28 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>2.01</v>
+        <v>1.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>1.87</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
-        <v>4.2</v>
+        <v>2.23</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA12">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG12">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.27</v>
+        <v>2.01</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="P25">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="S25">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>3.07</v>
+        <v>2.53</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z25">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="AA25">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC25">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="R26">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U26">
-        <v>2.53</v>
+        <v>3.07</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA26">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G70">
@@ -11728,55 +11728,55 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>2.14</v>
+        <v>2.84</v>
       </c>
       <c r="R70">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="S70">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="U70">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="V70">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="W70">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="Z70">
-        <v>6.74</v>
+        <v>4.5</v>
       </c>
       <c r="AA70">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AB70">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC70">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AD70">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AE70">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G71">
@@ -11891,55 +11891,55 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>2.84</v>
+        <v>2.14</v>
       </c>
       <c r="R71">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T71">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="U71">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="V71">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="W71">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z71">
-        <v>4.5</v>
+        <v>6.74</v>
       </c>
       <c r="AA71">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AB71">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC71">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AD71">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG71">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12374,19 +12374,19 @@
         <v>2.15</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="Q74">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R74">
         <v>2.3</v>
       </c>
       <c r="S74">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
         <v>3.5</v>
@@ -12395,7 +12395,7 @@
         <v>2.16</v>
       </c>
       <c r="V74">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W74">
         <v>1.13</v>
@@ -12413,16 +12413,16 @@
         <v>1.53</v>
       </c>
       <c r="AB74">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC74">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD74">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF74">
         <v>1.43</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="O81">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="P81">
-        <v>3.45</v>
+        <v>6.95</v>
       </c>
       <c r="Q81">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="R81">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="T81">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="U81">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>3.05</v>
+        <v>3.53</v>
       </c>
       <c r="AA81">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AB81">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC81">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="AD81">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE81">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK81">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,65 +13675,65 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="O82">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="P82">
-        <v>6.95</v>
+        <v>3.45</v>
       </c>
       <c r="Q82">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="R82">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="S82">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T82">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="U82">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="V82">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W82">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z82">
-        <v>3.53</v>
+        <v>3.05</v>
       </c>
       <c r="AA82">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AB82">
+        <v>1.72</v>
+      </c>
+      <c r="AC82">
+        <v>3.42</v>
+      </c>
+      <c r="AD82">
+        <v>1.23</v>
+      </c>
+      <c r="AE82">
+        <v>1.05</v>
+      </c>
+      <c r="AF82">
+        <v>1.78</v>
+      </c>
+      <c r="AG82">
         <v>2</v>
       </c>
-      <c r="AC82">
-        <v>2.83</v>
-      </c>
-      <c r="AD82">
-        <v>1.33</v>
-      </c>
-      <c r="AE82">
-        <v>1.1</v>
-      </c>
-      <c r="AF82">
-        <v>1.93</v>
-      </c>
-      <c r="AG82">
-        <v>1.75</v>
-      </c>
       <c r="AH82" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK82">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O89">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="R89">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="U89">
+        <v>2.77</v>
+      </c>
+      <c r="V89">
+        <v>1.38</v>
+      </c>
+      <c r="W89">
+        <v>1.04</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="Y89">
+        <v>1.3</v>
+      </c>
+      <c r="Z89">
         <v>3.2</v>
       </c>
-      <c r="V89">
-        <v>1.34</v>
-      </c>
-      <c r="W89">
-        <v>1.05</v>
-      </c>
-      <c r="X89">
+      <c r="AA89">
+        <v>1.9</v>
+      </c>
+      <c r="AB89">
+        <v>1.87</v>
+      </c>
+      <c r="AC89">
+        <v>3.6</v>
+      </c>
+      <c r="AD89">
+        <v>1.24</v>
+      </c>
+      <c r="AE89">
         <v>1.07</v>
-      </c>
-      <c r="Y89">
-        <v>1.32</v>
-      </c>
-      <c r="Z89">
-        <v>2.88</v>
-      </c>
-      <c r="AA89">
-        <v>2.05</v>
-      </c>
-      <c r="AB89">
-        <v>1.68</v>
-      </c>
-      <c r="AC89">
-        <v>3.72</v>
-      </c>
-      <c r="AD89">
-        <v>1.2</v>
-      </c>
-      <c r="AE89">
-        <v>1.03</v>
       </c>
       <c r="AF89">
         <v>1.83</v>
       </c>
       <c r="AG89">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="O90">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>4.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q90">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="R90">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="S90">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T90">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="U90">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="V90">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y90">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z90">
-        <v>3.16</v>
+        <v>2.53</v>
       </c>
       <c r="AA90">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AB90">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AC90">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="AD90">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE90">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF90">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG90">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="O91">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>4.42</v>
       </c>
       <c r="Q91">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="R91">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S91">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T91">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U91">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="V91">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W91">
         <v>1.05</v>
@@ -15175,31 +15175,31 @@
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Z91">
+        <v>3.16</v>
+      </c>
+      <c r="AA91">
+        <v>2.12</v>
+      </c>
+      <c r="AB91">
+        <v>1.78</v>
+      </c>
+      <c r="AC91">
         <v>3.38</v>
       </c>
-      <c r="AA91">
-        <v>2</v>
-      </c>
-      <c r="AB91">
-        <v>1.8</v>
-      </c>
-      <c r="AC91">
-        <v>3.4</v>
-      </c>
       <c r="AD91">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AG91">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="O92">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P92">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="Q92">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="R92">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S92">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T92">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="U92">
-        <v>3.22</v>
+        <v>2.66</v>
       </c>
       <c r="V92">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Z92">
-        <v>2.85</v>
+        <v>3.38</v>
       </c>
       <c r="AA92">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB92">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC92">
-        <v>4.49</v>
+        <v>3.4</v>
       </c>
       <c r="AD92">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE92">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG92">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK92">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="O93">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P93">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="Q93">
-        <v>2.77</v>
+        <v>3.74</v>
       </c>
       <c r="R93">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="S93">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T93">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U93">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="V93">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W93">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X93">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z93">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="AA93">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AB93">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC93">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="AD93">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF93">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG93">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK93">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16455,49 +16455,49 @@
         <v>2.3</v>
       </c>
       <c r="Q99">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="R99">
         <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U99">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="V99">
         <v>1.43</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="AA99">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB99">
         <v>1.9</v>
       </c>
       <c r="AC99">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD99">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF99">
         <v>1.7</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AK99">
         <v>1.36</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G108">
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="R108">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="S108">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U108">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="V108">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X108">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA108">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB108">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="AC108">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD108">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE108">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF108">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG108">
-        <v>1.99</v>
+        <v>2.34</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G109">
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="R109">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="S109">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T109">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U109">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="V109">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W109">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z109">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA109">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB109">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="AC109">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD109">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE109">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF109">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG109">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -23461,7 +23461,7 @@
         <v>6.05</v>
       </c>
       <c r="P142">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Q142">
         <v>7</v>
@@ -23470,16 +23470,16 @@
         <v>2.8</v>
       </c>
       <c r="S142">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T142">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U142">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="V142">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="W142">
         <v>1.2</v>
@@ -23488,31 +23488,31 @@
         <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z142">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AA142">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB142">
         <v>2.88</v>
       </c>
       <c r="AC142">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AD142">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AE142">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF142">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG142">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23618,16 +23618,16 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O143">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P143">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q143">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R143">
         <v>2.5</v>
@@ -23642,7 +23642,7 @@
         <v>2</v>
       </c>
       <c r="V143">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W143">
         <v>1.16</v>
@@ -23651,31 +23651,31 @@
         <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z143">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA143">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB143">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AC143">
         <v>2.07</v>
       </c>
       <c r="AD143">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE143">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF143">
         <v>1.43</v>
       </c>
       <c r="AG143">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK143">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,37 +23781,37 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O144">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="P144">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q144">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="R144">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S144">
         <v>1.26</v>
       </c>
       <c r="T144">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U144">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V144">
         <v>1.56</v>
       </c>
       <c r="W144">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X144">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
         <v>1.14</v>
@@ -23820,10 +23820,10 @@
         <v>4.45</v>
       </c>
       <c r="AA144">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB144">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AC144">
         <v>2.38</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK144">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="O173">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="P173">
         <v>1.85</v>
       </c>
       <c r="Q173">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R173">
         <v>2.25</v>
       </c>
       <c r="S173">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T173">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="U173">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V173">
         <v>1.5</v>
       </c>
       <c r="W173">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X173">
         <v>1.02</v>
       </c>
       <c r="Y173">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z173">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="AA173">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB173">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC173">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD173">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE173">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF173">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG173">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK173">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O184">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P184">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q184">
         <v>2.23</v>
@@ -30319,16 +30319,16 @@
         <v>1.29</v>
       </c>
       <c r="T184">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U184">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="V184">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W184">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X184">
         <v>1.03</v>
@@ -30343,22 +30343,22 @@
         <v>1.65</v>
       </c>
       <c r="AB184">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC184">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD184">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE184">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF184">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG184">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O196">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P196">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="R196">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S196">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T196">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U196">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="V196">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W196">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y196">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z196">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA196">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB196">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC196">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD196">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE196">
         <v>1.03</v>
       </c>
       <c r="AF196">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG196">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK196">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q197">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="R197">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S197">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T197">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U197">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="V197">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W197">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X197">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z197">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA197">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB197">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC197">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD197">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE197">
         <v>1.03</v>
       </c>
       <c r="AF197">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG197">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK197">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G223">
@@ -41062,46 +41062,46 @@
         <v>2.18</v>
       </c>
       <c r="O250">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P250">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="Q250">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="R250">
         <v>2.02</v>
       </c>
       <c r="S250">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="T250">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="U250">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="V250">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W250">
         <v>1.02</v>
       </c>
       <c r="X250">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y250">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z250">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AA250">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AB250">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC250">
         <v>4.55</v>
@@ -41110,7 +41110,7 @@
         <v>1.15</v>
       </c>
       <c r="AE250">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF250">
         <v>2.04</v>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK250">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,16 +41222,16 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="O251">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="P251">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q251">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="R251">
         <v>2.1</v>
@@ -41255,31 +41255,31 @@
         <v>1.03</v>
       </c>
       <c r="Y251">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z251">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AA251">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AB251">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC251">
         <v>3.05</v>
       </c>
       <c r="AD251">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE251">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF251">
         <v>1.7</v>
       </c>
       <c r="AG251">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK251">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -46927,49 +46927,49 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O286">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="P286">
-        <v>4.28</v>
+        <v>4.46</v>
       </c>
       <c r="Q286">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R286">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S286">
         <v>1.3</v>
       </c>
       <c r="T286">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U286">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="V286">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W286">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X286">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y286">
         <v>1.2</v>
       </c>
       <c r="Z286">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA286">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB286">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC286">
         <v>2.66</v>
@@ -46978,13 +46978,13 @@
         <v>1.37</v>
       </c>
       <c r="AE286">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF286">
         <v>1.65</v>
       </c>
       <c r="AG286">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK286">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="O290">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P290">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q290">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R290">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S290">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T290">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U290">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V290">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W290">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X290">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y290">
         <v>1.5</v>
       </c>
       <c r="Z290">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA290">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB290">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AC290">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD290">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE290">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF290">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG290">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK290">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O291">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P291">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q291">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="R291">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S291">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T291">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U291">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V291">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W291">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X291">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y291">
         <v>1.5</v>
       </c>
       <c r="Z291">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA291">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AB291">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC291">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD291">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE291">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF291">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG291">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK291">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -48231,7 +48231,7 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O294">
         <v>4</v>
@@ -48240,22 +48240,22 @@
         <v>4.2</v>
       </c>
       <c r="Q294">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R294">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S294">
         <v>1.25</v>
       </c>
       <c r="T294">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U294">
         <v>2.4</v>
       </c>
       <c r="V294">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W294">
         <v>1.1</v>
@@ -48264,16 +48264,16 @@
         <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z294">
         <v>4.45</v>
       </c>
       <c r="AA294">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB294">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC294">
         <v>2.55</v>
@@ -48288,7 +48288,7 @@
         <v>1.59</v>
       </c>
       <c r="AG294">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK294">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>6.2</v>
+        <v>1.83</v>
       </c>
       <c r="O297">
-        <v>4.35</v>
+        <v>3.45</v>
       </c>
       <c r="P297">
-        <v>1.5</v>
+        <v>4.15</v>
       </c>
       <c r="Q297">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="R297">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="S297">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T297">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="U297">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="V297">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="W297">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X297">
         <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z297">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="AA297">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AB297">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AC297">
-        <v>2.71</v>
+        <v>3.95</v>
       </c>
       <c r="AD297">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE297">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF297">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG297">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK297">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="O298">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="P298">
-        <v>4.15</v>
+        <v>1.5</v>
       </c>
       <c r="Q298">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="R298">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="S298">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T298">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="U298">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="V298">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="W298">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X298">
         <v>1.02</v>
       </c>
       <c r="Y298">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z298">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="AA298">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AB298">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AC298">
-        <v>3.95</v>
+        <v>2.71</v>
       </c>
       <c r="AD298">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE298">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF298">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG298">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK298">
-        <v>1.96</v>
+        <v>1.12</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -50187,55 +50187,55 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="O306">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P306">
         <v>2.98</v>
       </c>
       <c r="Q306">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="R306">
         <v>1.91</v>
       </c>
       <c r="S306">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T306">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U306">
         <v>3.3</v>
       </c>
       <c r="V306">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W306">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X306">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y306">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z306">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AA306">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AB306">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC306">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD306">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE306">
         <v>1.01</v>
@@ -50244,7 +50244,7 @@
         <v>2</v>
       </c>
       <c r="AG306">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK306">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,80 +51002,80 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="O311">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P311">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q311">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="R311">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="S311">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="T311">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="U311">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="V311">
+        <v>1.25</v>
+      </c>
+      <c r="W311">
+        <v>1.01</v>
+      </c>
+      <c r="X311">
+        <v>1.07</v>
+      </c>
+      <c r="Y311">
+        <v>1.49</v>
+      </c>
+      <c r="Z311">
+        <v>2.52</v>
+      </c>
+      <c r="AA311">
+        <v>2.57</v>
+      </c>
+      <c r="AB311">
+        <v>1.5</v>
+      </c>
+      <c r="AC311">
+        <v>4.55</v>
+      </c>
+      <c r="AD311">
+        <v>1.13</v>
+      </c>
+      <c r="AE311">
+        <v>1.01</v>
+      </c>
+      <c r="AF311">
+        <v>2.01</v>
+      </c>
+      <c r="AG311">
+        <v>1.68</v>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ311">
         <v>1.33</v>
       </c>
-      <c r="W311">
-        <v>1.06</v>
-      </c>
-      <c r="X311">
-        <v>1.01</v>
-      </c>
-      <c r="Y311">
-        <v>1.35</v>
-      </c>
-      <c r="Z311">
-        <v>2.92</v>
-      </c>
-      <c r="AA311">
-        <v>2.07</v>
-      </c>
-      <c r="AB311">
-        <v>1.69</v>
-      </c>
-      <c r="AC311">
-        <v>3.72</v>
-      </c>
-      <c r="AD311">
-        <v>1.2</v>
-      </c>
-      <c r="AE311">
-        <v>1.03</v>
-      </c>
-      <c r="AF311">
-        <v>1.91</v>
-      </c>
-      <c r="AG311">
-        <v>1.75</v>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ311">
-        <v>1.24</v>
-      </c>
       <c r="AK311">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,64 +51165,64 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.37</v>
+        <v>1.74</v>
       </c>
       <c r="O312">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P312">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q312">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="R312">
+        <v>1.98</v>
+      </c>
+      <c r="S312">
+        <v>1.42</v>
+      </c>
+      <c r="T312">
+        <v>2.53</v>
+      </c>
+      <c r="U312">
+        <v>3</v>
+      </c>
+      <c r="V312">
+        <v>1.33</v>
+      </c>
+      <c r="W312">
+        <v>1.06</v>
+      </c>
+      <c r="X312">
+        <v>1.01</v>
+      </c>
+      <c r="Y312">
+        <v>1.35</v>
+      </c>
+      <c r="Z312">
+        <v>2.92</v>
+      </c>
+      <c r="AA312">
+        <v>2.07</v>
+      </c>
+      <c r="AB312">
+        <v>1.69</v>
+      </c>
+      <c r="AC312">
+        <v>3.72</v>
+      </c>
+      <c r="AD312">
+        <v>1.2</v>
+      </c>
+      <c r="AE312">
+        <v>1.03</v>
+      </c>
+      <c r="AF312">
         <v>1.91</v>
       </c>
-      <c r="S312">
-        <v>1.56</v>
-      </c>
-      <c r="T312">
-        <v>2.24</v>
-      </c>
-      <c r="U312">
-        <v>3.42</v>
-      </c>
-      <c r="V312">
-        <v>1.25</v>
-      </c>
-      <c r="W312">
-        <v>1.01</v>
-      </c>
-      <c r="X312">
-        <v>1.07</v>
-      </c>
-      <c r="Y312">
-        <v>1.49</v>
-      </c>
-      <c r="Z312">
-        <v>2.52</v>
-      </c>
-      <c r="AA312">
-        <v>2.57</v>
-      </c>
-      <c r="AB312">
-        <v>1.5</v>
-      </c>
-      <c r="AC312">
-        <v>4.55</v>
-      </c>
-      <c r="AD312">
-        <v>1.13</v>
-      </c>
-      <c r="AE312">
-        <v>1.01</v>
-      </c>
-      <c r="AF312">
-        <v>2.01</v>
-      </c>
       <c r="AG312">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK312">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AL312">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.9</v>
+      </c>
+      <c r="O10">
+        <v>3.25</v>
+      </c>
+      <c r="P10">
+        <v>2.15</v>
+      </c>
+      <c r="Q10">
         <v>3.4</v>
       </c>
-      <c r="O10">
-        <v>3.65</v>
-      </c>
-      <c r="P10">
-        <v>1.87</v>
-      </c>
-      <c r="Q10">
-        <v>4.2</v>
-      </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="S10">
+        <v>1.34</v>
+      </c>
+      <c r="T10">
+        <v>3.17</v>
+      </c>
+      <c r="U10">
+        <v>2.7</v>
+      </c>
+      <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.22</v>
+      </c>
+      <c r="Z10">
+        <v>3.54</v>
+      </c>
+      <c r="AA10">
+        <v>1.83</v>
+      </c>
+      <c r="AB10">
+        <v>2.01</v>
+      </c>
+      <c r="AC10">
+        <v>3.1</v>
+      </c>
+      <c r="AD10">
         <v>1.32</v>
       </c>
-      <c r="T10">
-        <v>3.27</v>
-      </c>
-      <c r="U10">
-        <v>2.61</v>
-      </c>
-      <c r="V10">
-        <v>1.47</v>
-      </c>
-      <c r="W10">
+      <c r="AE10">
         <v>1.08</v>
       </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>1.25</v>
-      </c>
-      <c r="Z10">
-        <v>4.1</v>
-      </c>
-      <c r="AA10">
-        <v>1.72</v>
-      </c>
-      <c r="AB10">
-        <v>2.07</v>
-      </c>
-      <c r="AC10">
-        <v>2.66</v>
-      </c>
-      <c r="AD10">
+      <c r="AF10">
+        <v>1.67</v>
+      </c>
+      <c r="AG10">
+        <v>2.1</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.3</v>
+      </c>
+      <c r="AK10">
         <v>1.35</v>
-      </c>
-      <c r="AE10">
-        <v>1.1</v>
-      </c>
-      <c r="AF10">
-        <v>1.62</v>
-      </c>
-      <c r="AG10">
-        <v>2.14</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.27</v>
-      </c>
-      <c r="AK10">
-        <v>1.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,52 +2102,52 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA11">
         <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AD11">
         <v>1.32</v>
@@ -2156,10 +2156,10 @@
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK11">
-        <v>1.35</v>
+        <v>2.01</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>3.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q12">
-        <v>2.23</v>
+        <v>4.2</v>
       </c>
       <c r="R12">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U12">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>2.01</v>
+        <v>1.27</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -13515,28 +13515,28 @@
         <v>1.38</v>
       </c>
       <c r="O81">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="P81">
         <v>6.95</v>
       </c>
       <c r="Q81">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R81">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S81">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T81">
         <v>2.92</v>
       </c>
       <c r="U81">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W81">
         <v>1.07</v>
@@ -13545,16 +13545,16 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB81">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC81">
         <v>2.83</v>
@@ -13566,7 +13566,7 @@
         <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG81">
         <v>1.75</v>
@@ -13585,7 +13585,7 @@
         <v>1.14</v>
       </c>
       <c r="AK81">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O82">
         <v>3.35</v>
       </c>
       <c r="P82">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="Q82">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="R82">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
         <v>1.41</v>
@@ -13696,7 +13696,7 @@
         <v>2.56</v>
       </c>
       <c r="U82">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="V82">
         <v>1.36</v>
@@ -13705,19 +13705,19 @@
         <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y82">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z82">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="AA82">
         <v>2.06</v>
       </c>
       <c r="AB82">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC82">
         <v>3.42</v>
@@ -13726,10 +13726,10 @@
         <v>1.23</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF82">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG82">
         <v>2</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK82">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="O91">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="Q91">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="R91">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S91">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T91">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U91">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="V91">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W91">
         <v>1.05</v>
@@ -15175,31 +15175,31 @@
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z91">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="AA91">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD91">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK91">
-        <v>1.99</v>
+        <v>1.51</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="O92">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P92">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="Q92">
-        <v>3.08</v>
+        <v>3.74</v>
       </c>
       <c r="R92">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S92">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T92">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="U92">
-        <v>2.66</v>
+        <v>3.22</v>
       </c>
       <c r="V92">
+        <v>1.3</v>
+      </c>
+      <c r="W92">
+        <v>1.03</v>
+      </c>
+      <c r="X92">
+        <v>1.05</v>
+      </c>
+      <c r="Y92">
+        <v>1.42</v>
+      </c>
+      <c r="Z92">
+        <v>2.85</v>
+      </c>
+      <c r="AA92">
+        <v>2.18</v>
+      </c>
+      <c r="AB92">
+        <v>1.59</v>
+      </c>
+      <c r="AC92">
+        <v>4.49</v>
+      </c>
+      <c r="AD92">
+        <v>1.2</v>
+      </c>
+      <c r="AE92">
+        <v>1.03</v>
+      </c>
+      <c r="AF92">
+        <v>1.85</v>
+      </c>
+      <c r="AG92">
+        <v>1.85</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.35</v>
+      </c>
+      <c r="AK92">
         <v>1.39</v>
-      </c>
-      <c r="W92">
-        <v>1.05</v>
-      </c>
-      <c r="X92">
-        <v>1.01</v>
-      </c>
-      <c r="Y92">
-        <v>1.24</v>
-      </c>
-      <c r="Z92">
-        <v>3.38</v>
-      </c>
-      <c r="AA92">
-        <v>2</v>
-      </c>
-      <c r="AB92">
-        <v>1.8</v>
-      </c>
-      <c r="AC92">
-        <v>3.4</v>
-      </c>
-      <c r="AD92">
-        <v>1.28</v>
-      </c>
-      <c r="AE92">
-        <v>1.06</v>
-      </c>
-      <c r="AF92">
-        <v>1.67</v>
-      </c>
-      <c r="AG92">
-        <v>2.08</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.31</v>
-      </c>
-      <c r="AK92">
-        <v>1.51</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.87</v>
+        <v>1.75</v>
       </c>
       <c r="O93">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="P93">
-        <v>2.53</v>
+        <v>4.42</v>
       </c>
       <c r="Q93">
-        <v>3.74</v>
+        <v>2.37</v>
       </c>
       <c r="R93">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="S93">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="U93">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="V93">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W93">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.35</v>
+      </c>
+      <c r="Z93">
+        <v>3.16</v>
+      </c>
+      <c r="AA93">
+        <v>2.12</v>
+      </c>
+      <c r="AB93">
+        <v>1.78</v>
+      </c>
+      <c r="AC93">
+        <v>3.38</v>
+      </c>
+      <c r="AD93">
+        <v>1.26</v>
+      </c>
+      <c r="AE93">
         <v>1.05</v>
       </c>
-      <c r="Y93">
-        <v>1.42</v>
-      </c>
-      <c r="Z93">
-        <v>2.85</v>
-      </c>
-      <c r="AA93">
-        <v>2.18</v>
-      </c>
-      <c r="AB93">
-        <v>1.59</v>
-      </c>
-      <c r="AC93">
-        <v>4.49</v>
-      </c>
-      <c r="AD93">
-        <v>1.2</v>
-      </c>
-      <c r="AE93">
-        <v>1.03</v>
-      </c>
       <c r="AF93">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG93">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK93">
-        <v>1.39</v>
+        <v>1.99</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G108">
@@ -17922,55 +17922,55 @@
         <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="S108">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="V108">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB108">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="AC108">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD108">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG108">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G109">
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="R109">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U109">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="V109">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA109">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB109">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="AC109">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD109">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
-        <v>1.99</v>
+        <v>2.34</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -22154,13 +22154,13 @@
         <v>2.9</v>
       </c>
       <c r="O134">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="P134">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q134">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="R134">
         <v>2.14</v>
@@ -22172,7 +22172,7 @@
         <v>3</v>
       </c>
       <c r="U134">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V134">
         <v>1.42</v>
@@ -22184,10 +22184,10 @@
         <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z134">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA134">
         <v>1.83</v>
@@ -22199,13 +22199,13 @@
         <v>3.1</v>
       </c>
       <c r="AD134">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE134">
         <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG134">
         <v>2.11</v>
@@ -22314,43 +22314,43 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O135">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P135">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
       <c r="Q135">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="R135">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S135">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T135">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U135">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="V135">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W135">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z135">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA135">
         <v>1.61</v>
@@ -22359,19 +22359,19 @@
         <v>2.3</v>
       </c>
       <c r="AC135">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD135">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE135">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF135">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG135">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK135">
-        <v>2.47</v>
+        <v>2.76</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O139">
         <v>3.1</v>
@@ -22975,55 +22975,55 @@
         <v>3</v>
       </c>
       <c r="Q139">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R139">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="S139">
         <v>1.4</v>
       </c>
       <c r="T139">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U139">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="V139">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z139">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="AA139">
         <v>2.1</v>
       </c>
       <c r="AB139">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC139">
         <v>3.78</v>
       </c>
       <c r="AD139">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE139">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF139">
         <v>1.8</v>
       </c>
       <c r="AG139">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q196">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S196">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T196">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U196">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="V196">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W196">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X196">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z196">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA196">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB196">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC196">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD196">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE196">
         <v>1.03</v>
       </c>
       <c r="AF196">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG196">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK196">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O197">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P197">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q197">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="R197">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S197">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T197">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U197">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="V197">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W197">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X197">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y197">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z197">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA197">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB197">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC197">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD197">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE197">
         <v>1.03</v>
       </c>
       <c r="AF197">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG197">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK197">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O289">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="P289">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q289">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R289">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S289">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="T289">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U289">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="V289">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X289">
+        <v>1.1</v>
+      </c>
+      <c r="Y289">
+        <v>1.5</v>
+      </c>
+      <c r="Z289">
+        <v>2.56</v>
+      </c>
+      <c r="AA289">
+        <v>2.5</v>
+      </c>
+      <c r="AB289">
+        <v>1.46</v>
+      </c>
+      <c r="AC289">
+        <v>5</v>
+      </c>
+      <c r="AD289">
         <v>1.17</v>
       </c>
-      <c r="Y289">
-        <v>1.68</v>
-      </c>
-      <c r="Z289">
-        <v>2.14</v>
-      </c>
-      <c r="AA289">
-        <v>3.1</v>
-      </c>
-      <c r="AB289">
-        <v>1.33</v>
-      </c>
-      <c r="AC289">
-        <v>6.15</v>
-      </c>
-      <c r="AD289">
-        <v>1.1</v>
-      </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF289">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG289">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK289">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,65 +47579,65 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O290">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="P290">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q290">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R290">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S290">
+        <v>1.69</v>
+      </c>
+      <c r="T290">
+        <v>2.1</v>
+      </c>
+      <c r="U290">
+        <v>4.15</v>
+      </c>
+      <c r="V290">
+        <v>1.16</v>
+      </c>
+      <c r="W290">
+        <v>1.02</v>
+      </c>
+      <c r="X290">
+        <v>1.17</v>
+      </c>
+      <c r="Y290">
+        <v>1.68</v>
+      </c>
+      <c r="Z290">
+        <v>2.14</v>
+      </c>
+      <c r="AA290">
+        <v>3.1</v>
+      </c>
+      <c r="AB290">
+        <v>1.33</v>
+      </c>
+      <c r="AC290">
+        <v>6.15</v>
+      </c>
+      <c r="AD290">
+        <v>1.1</v>
+      </c>
+      <c r="AE290">
+        <v>1.03</v>
+      </c>
+      <c r="AF290">
+        <v>2.3</v>
+      </c>
+      <c r="AG290">
         <v>1.53</v>
       </c>
-      <c r="T290">
-        <v>2.33</v>
-      </c>
-      <c r="U290">
-        <v>3.5</v>
-      </c>
-      <c r="V290">
-        <v>1.24</v>
-      </c>
-      <c r="W290">
-        <v>1.01</v>
-      </c>
-      <c r="X290">
-        <v>1.1</v>
-      </c>
-      <c r="Y290">
-        <v>1.5</v>
-      </c>
-      <c r="Z290">
-        <v>2.56</v>
-      </c>
-      <c r="AA290">
-        <v>2.5</v>
-      </c>
-      <c r="AB290">
-        <v>1.46</v>
-      </c>
-      <c r="AC290">
-        <v>5</v>
-      </c>
-      <c r="AD290">
-        <v>1.17</v>
-      </c>
-      <c r="AE290">
-        <v>1.05</v>
-      </c>
-      <c r="AF290">
-        <v>2</v>
-      </c>
-      <c r="AG290">
-        <v>1.73</v>
-      </c>
       <c r="AH290" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK290">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="O297">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="P297">
-        <v>4.15</v>
+        <v>1.5</v>
       </c>
       <c r="Q297">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="R297">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="S297">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T297">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="U297">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="V297">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="W297">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X297">
         <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z297">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="AA297">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AB297">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AC297">
-        <v>3.95</v>
+        <v>2.71</v>
       </c>
       <c r="AD297">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE297">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF297">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG297">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK297">
-        <v>1.96</v>
+        <v>1.12</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>6.2</v>
+        <v>1.83</v>
       </c>
       <c r="O298">
-        <v>4.35</v>
+        <v>3.45</v>
       </c>
       <c r="P298">
-        <v>1.5</v>
+        <v>4.15</v>
       </c>
       <c r="Q298">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="R298">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="S298">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T298">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="U298">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="V298">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="W298">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X298">
         <v>1.02</v>
       </c>
       <c r="Y298">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z298">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="AA298">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AB298">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AC298">
-        <v>2.71</v>
+        <v>3.95</v>
       </c>
       <c r="AD298">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE298">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF298">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG298">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK298">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.37</v>
+        <v>1.74</v>
       </c>
       <c r="O311">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P311">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q311">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="R311">
+        <v>1.98</v>
+      </c>
+      <c r="S311">
+        <v>1.42</v>
+      </c>
+      <c r="T311">
+        <v>2.53</v>
+      </c>
+      <c r="U311">
+        <v>3</v>
+      </c>
+      <c r="V311">
+        <v>1.33</v>
+      </c>
+      <c r="W311">
+        <v>1.06</v>
+      </c>
+      <c r="X311">
+        <v>1.01</v>
+      </c>
+      <c r="Y311">
+        <v>1.35</v>
+      </c>
+      <c r="Z311">
+        <v>2.92</v>
+      </c>
+      <c r="AA311">
+        <v>2.07</v>
+      </c>
+      <c r="AB311">
+        <v>1.69</v>
+      </c>
+      <c r="AC311">
+        <v>3.72</v>
+      </c>
+      <c r="AD311">
+        <v>1.2</v>
+      </c>
+      <c r="AE311">
+        <v>1.03</v>
+      </c>
+      <c r="AF311">
         <v>1.91</v>
       </c>
-      <c r="S311">
-        <v>1.56</v>
-      </c>
-      <c r="T311">
-        <v>2.24</v>
-      </c>
-      <c r="U311">
-        <v>3.42</v>
-      </c>
-      <c r="V311">
-        <v>1.25</v>
-      </c>
-      <c r="W311">
-        <v>1.01</v>
-      </c>
-      <c r="X311">
-        <v>1.07</v>
-      </c>
-      <c r="Y311">
-        <v>1.49</v>
-      </c>
-      <c r="Z311">
-        <v>2.52</v>
-      </c>
-      <c r="AA311">
-        <v>2.57</v>
-      </c>
-      <c r="AB311">
-        <v>1.5</v>
-      </c>
-      <c r="AC311">
-        <v>4.55</v>
-      </c>
-      <c r="AD311">
-        <v>1.13</v>
-      </c>
-      <c r="AE311">
-        <v>1.01</v>
-      </c>
-      <c r="AF311">
-        <v>2.01</v>
-      </c>
       <c r="AG311">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK311">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,80 +51165,80 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="O312">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P312">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q312">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="R312">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="S312">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="T312">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="U312">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="V312">
+        <v>1.25</v>
+      </c>
+      <c r="W312">
+        <v>1.01</v>
+      </c>
+      <c r="X312">
+        <v>1.07</v>
+      </c>
+      <c r="Y312">
+        <v>1.49</v>
+      </c>
+      <c r="Z312">
+        <v>2.52</v>
+      </c>
+      <c r="AA312">
+        <v>2.57</v>
+      </c>
+      <c r="AB312">
+        <v>1.5</v>
+      </c>
+      <c r="AC312">
+        <v>4.55</v>
+      </c>
+      <c r="AD312">
+        <v>1.13</v>
+      </c>
+      <c r="AE312">
+        <v>1.01</v>
+      </c>
+      <c r="AF312">
+        <v>2.01</v>
+      </c>
+      <c r="AG312">
+        <v>1.68</v>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ312">
         <v>1.33</v>
       </c>
-      <c r="W312">
-        <v>1.06</v>
-      </c>
-      <c r="X312">
-        <v>1.01</v>
-      </c>
-      <c r="Y312">
-        <v>1.35</v>
-      </c>
-      <c r="Z312">
-        <v>2.92</v>
-      </c>
-      <c r="AA312">
-        <v>2.07</v>
-      </c>
-      <c r="AB312">
-        <v>1.69</v>
-      </c>
-      <c r="AC312">
-        <v>3.72</v>
-      </c>
-      <c r="AD312">
-        <v>1.2</v>
-      </c>
-      <c r="AE312">
-        <v>1.03</v>
-      </c>
-      <c r="AF312">
-        <v>1.91</v>
-      </c>
-      <c r="AG312">
-        <v>1.75</v>
-      </c>
-      <c r="AH312" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ312">
-        <v>1.24</v>
-      </c>
       <c r="AK312">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -52970,13 +52970,13 @@
         <v>9</v>
       </c>
       <c r="R323">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S323">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T323">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U323">
         <v>2.55</v>
@@ -52988,7 +52988,7 @@
         <v>1.06</v>
       </c>
       <c r="X323">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y323">
         <v>1.2</v>
@@ -53006,16 +53006,16 @@
         <v>2.55</v>
       </c>
       <c r="AD323">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE323">
         <v>1.13</v>
       </c>
       <c r="AF323">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG323">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK323">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AL323">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -13527,25 +13527,25 @@
         <v>2.29</v>
       </c>
       <c r="S81">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U81">
         <v>2.74</v>
       </c>
       <c r="V81">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
         <v>3.5</v>
@@ -13554,7 +13554,7 @@
         <v>1.76</v>
       </c>
       <c r="AB81">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC81">
         <v>2.83</v>
@@ -13566,7 +13566,7 @@
         <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG81">
         <v>1.75</v>
@@ -13684,7 +13684,7 @@
         <v>3.65</v>
       </c>
       <c r="Q82">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R82">
         <v>2.1</v>
@@ -13696,7 +13696,7 @@
         <v>2.56</v>
       </c>
       <c r="U82">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V82">
         <v>1.36</v>
@@ -13717,7 +13717,7 @@
         <v>2.06</v>
       </c>
       <c r="AB82">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC82">
         <v>3.42</v>
@@ -13729,10 +13729,10 @@
         <v>1.04</v>
       </c>
       <c r="AF82">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK82">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,65 +22151,65 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.9</v>
+        <v>1.46</v>
       </c>
       <c r="O134">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="P134">
-        <v>2.48</v>
+        <v>5.95</v>
       </c>
       <c r="Q134">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="R134">
+        <v>2.6</v>
+      </c>
+      <c r="S134">
+        <v>1.25</v>
+      </c>
+      <c r="T134">
+        <v>3.6</v>
+      </c>
+      <c r="U134">
+        <v>2.2</v>
+      </c>
+      <c r="V134">
+        <v>1.54</v>
+      </c>
+      <c r="W134">
+        <v>1.1</v>
+      </c>
+      <c r="X134">
+        <v>1.02</v>
+      </c>
+      <c r="Y134">
+        <v>1.18</v>
+      </c>
+      <c r="Z134">
+        <v>4.82</v>
+      </c>
+      <c r="AA134">
+        <v>1.57</v>
+      </c>
+      <c r="AB134">
+        <v>2.37</v>
+      </c>
+      <c r="AC134">
+        <v>2.45</v>
+      </c>
+      <c r="AD134">
+        <v>1.53</v>
+      </c>
+      <c r="AE134">
+        <v>1.17</v>
+      </c>
+      <c r="AF134">
+        <v>1.73</v>
+      </c>
+      <c r="AG134">
         <v>2.06</v>
       </c>
-      <c r="S134">
-        <v>1.35</v>
-      </c>
-      <c r="T134">
-        <v>3</v>
-      </c>
-      <c r="U134">
-        <v>2.69</v>
-      </c>
-      <c r="V134">
-        <v>1.42</v>
-      </c>
-      <c r="W134">
-        <v>1.08</v>
-      </c>
-      <c r="X134">
-        <v>1</v>
-      </c>
-      <c r="Y134">
-        <v>1.28</v>
-      </c>
-      <c r="Z134">
-        <v>3.44</v>
-      </c>
-      <c r="AA134">
-        <v>1.9</v>
-      </c>
-      <c r="AB134">
-        <v>1.9</v>
-      </c>
-      <c r="AC134">
-        <v>3.1</v>
-      </c>
-      <c r="AD134">
-        <v>1.31</v>
-      </c>
-      <c r="AE134">
-        <v>1.12</v>
-      </c>
-      <c r="AF134">
-        <v>1.65</v>
-      </c>
-      <c r="AG134">
-        <v>2.11</v>
-      </c>
       <c r="AH134" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK134">
-        <v>1.4</v>
+        <v>2.56</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="O135">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="P135">
-        <v>5.95</v>
+        <v>2.48</v>
       </c>
       <c r="Q135">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="R135">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="S135">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T135">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U135">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="V135">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="W135">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y135">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z135">
-        <v>4.82</v>
+        <v>3.44</v>
       </c>
       <c r="AA135">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB135">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AC135">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD135">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE135">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG135">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>2.56</v>
+        <v>1.4</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,31 +47416,31 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="O289">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P289">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q289">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="R289">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="S289">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="T289">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="U289">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V289">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W289">
         <v>1.01</v>
@@ -47449,32 +47449,32 @@
         <v>1.07</v>
       </c>
       <c r="Y289">
+        <v>1.62</v>
+      </c>
+      <c r="Z289">
+        <v>2.21</v>
+      </c>
+      <c r="AA289">
+        <v>2.74</v>
+      </c>
+      <c r="AB289">
+        <v>1.42</v>
+      </c>
+      <c r="AC289">
+        <v>6</v>
+      </c>
+      <c r="AD289">
+        <v>1.11</v>
+      </c>
+      <c r="AE289">
+        <v>1.03</v>
+      </c>
+      <c r="AF289">
+        <v>2.3</v>
+      </c>
+      <c r="AG289">
         <v>1.5</v>
       </c>
-      <c r="Z289">
-        <v>2.51</v>
-      </c>
-      <c r="AA289">
-        <v>2.5</v>
-      </c>
-      <c r="AB289">
-        <v>1.47</v>
-      </c>
-      <c r="AC289">
-        <v>4.45</v>
-      </c>
-      <c r="AD289">
-        <v>1.14</v>
-      </c>
-      <c r="AE289">
-        <v>1.05</v>
-      </c>
-      <c r="AF289">
-        <v>2</v>
-      </c>
-      <c r="AG289">
-        <v>1.73</v>
-      </c>
       <c r="AH289" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK289">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,31 +47579,31 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="O290">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P290">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q290">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R290">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="S290">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="T290">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="U290">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="V290">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W290">
         <v>1.01</v>
@@ -47612,31 +47612,31 @@
         <v>1.07</v>
       </c>
       <c r="Y290">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z290">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="AA290">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB290">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC290">
-        <v>6</v>
+        <v>4.45</v>
       </c>
       <c r="AD290">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE290">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF290">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG290">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
+        <v>1.31</v>
+      </c>
+      <c r="AK290">
         <v>1.36</v>
-      </c>
-      <c r="AK290">
-        <v>1.7</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,65 +48557,65 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="O296">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="P296">
-        <v>4.36</v>
+        <v>1.5</v>
       </c>
       <c r="Q296">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="R296">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S296">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T296">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="U296">
-        <v>2.99</v>
+        <v>2.37</v>
       </c>
       <c r="V296">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W296">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X296">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y296">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z296">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="AA296">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AB296">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC296">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD296">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE296">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF296">
+        <v>1.82</v>
+      </c>
+      <c r="AG296">
         <v>1.9</v>
       </c>
-      <c r="AG296">
-        <v>1.8</v>
-      </c>
       <c r="AH296" t="inlineStr">
         <is>
           <t>[]</t>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK296">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>6.2</v>
+        <v>1.83</v>
       </c>
       <c r="O297">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="P297">
-        <v>1.5</v>
+        <v>4.36</v>
       </c>
       <c r="Q297">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="R297">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="S297">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T297">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="U297">
-        <v>2.37</v>
+        <v>2.99</v>
       </c>
       <c r="V297">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W297">
+        <v>1.07</v>
+      </c>
+      <c r="X297">
+        <v>1.02</v>
+      </c>
+      <c r="Y297">
+        <v>1.32</v>
+      </c>
+      <c r="Z297">
+        <v>2.89</v>
+      </c>
+      <c r="AA297">
+        <v>2.12</v>
+      </c>
+      <c r="AB297">
+        <v>1.72</v>
+      </c>
+      <c r="AC297">
+        <v>3.9</v>
+      </c>
+      <c r="AD297">
+        <v>1.22</v>
+      </c>
+      <c r="AE297">
         <v>1.08</v>
       </c>
-      <c r="X297">
-        <v>1.03</v>
-      </c>
-      <c r="Y297">
-        <v>1.2</v>
-      </c>
-      <c r="Z297">
-        <v>4</v>
-      </c>
-      <c r="AA297">
-        <v>1.74</v>
-      </c>
-      <c r="AB297">
-        <v>2.02</v>
-      </c>
-      <c r="AC297">
-        <v>2.75</v>
-      </c>
-      <c r="AD297">
-        <v>1.4</v>
-      </c>
-      <c r="AE297">
-        <v>1.1</v>
-      </c>
       <c r="AF297">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG297">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK297">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="AL297">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.55</v>
+      </c>
+      <c r="O25">
+        <v>3.8</v>
+      </c>
+      <c r="P25">
+        <v>4.75</v>
+      </c>
+      <c r="Q25">
+        <v>2.1</v>
+      </c>
+      <c r="R25">
+        <v>2.26</v>
+      </c>
+      <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>3.08</v>
+      </c>
+      <c r="U25">
+        <v>2.53</v>
+      </c>
+      <c r="V25">
+        <v>1.43</v>
+      </c>
+      <c r="W25">
+        <v>1.06</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.18</v>
+      </c>
+      <c r="Z25">
+        <v>3.9</v>
+      </c>
+      <c r="AA25">
+        <v>1.71</v>
+      </c>
+      <c r="AB25">
         <v>2.07</v>
       </c>
-      <c r="O25">
-        <v>3.25</v>
-      </c>
-      <c r="P25">
-        <v>3.4</v>
-      </c>
-      <c r="Q25">
-        <v>2.62</v>
-      </c>
-      <c r="R25">
-        <v>2</v>
-      </c>
-      <c r="S25">
-        <v>1.44</v>
-      </c>
-      <c r="T25">
-        <v>2.75</v>
-      </c>
-      <c r="U25">
-        <v>2.91</v>
-      </c>
-      <c r="V25">
+      <c r="AC25">
+        <v>2.9</v>
+      </c>
+      <c r="AD25">
         <v>1.36</v>
       </c>
-      <c r="W25">
-        <v>1.07</v>
-      </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>1.3</v>
-      </c>
-      <c r="Z25">
-        <v>3.1</v>
-      </c>
-      <c r="AA25">
-        <v>2.05</v>
-      </c>
-      <c r="AB25">
-        <v>1.75</v>
-      </c>
-      <c r="AC25">
-        <v>3.5</v>
-      </c>
-      <c r="AD25">
-        <v>1.25</v>
-      </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="R26">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="O81">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P81">
-        <v>6.95</v>
+        <v>4</v>
       </c>
       <c r="Q81">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="R81">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T81">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="U81">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V81">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z81">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="AA81">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AB81">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC81">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="AD81">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE81">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF81">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG81">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK81">
-        <v>2.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="O82">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="P82">
-        <v>3.65</v>
+        <v>6.95</v>
       </c>
       <c r="Q82">
-        <v>2.63</v>
+        <v>1.89</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S82">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T82">
-        <v>2.56</v>
+        <v>3.11</v>
       </c>
       <c r="U82">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="AA82">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AB82">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AC82">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="AD82">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE82">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG82">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK82">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q102">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R102">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
         <v>1.4</v>
       </c>
       <c r="T102">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U102">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z102">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AA102">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC102">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD102">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE102">
         <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG102">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK102">
         <v>1.43</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S103">
         <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U103">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="V103">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z103">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="AA103">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD103">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
         <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK103">
         <v>1.43</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
-        <v>6.2</v>
+        <v>1.83</v>
       </c>
       <c r="O296">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="P296">
-        <v>1.5</v>
+        <v>4.36</v>
       </c>
       <c r="Q296">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="R296">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="S296">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T296">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="U296">
-        <v>2.37</v>
+        <v>2.99</v>
       </c>
       <c r="V296">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W296">
+        <v>1.07</v>
+      </c>
+      <c r="X296">
+        <v>1.02</v>
+      </c>
+      <c r="Y296">
+        <v>1.32</v>
+      </c>
+      <c r="Z296">
+        <v>2.89</v>
+      </c>
+      <c r="AA296">
+        <v>2.12</v>
+      </c>
+      <c r="AB296">
+        <v>1.72</v>
+      </c>
+      <c r="AC296">
+        <v>3.9</v>
+      </c>
+      <c r="AD296">
+        <v>1.22</v>
+      </c>
+      <c r="AE296">
         <v>1.08</v>
       </c>
-      <c r="X296">
-        <v>1.03</v>
-      </c>
-      <c r="Y296">
-        <v>1.2</v>
-      </c>
-      <c r="Z296">
-        <v>4</v>
-      </c>
-      <c r="AA296">
-        <v>1.74</v>
-      </c>
-      <c r="AB296">
-        <v>2.02</v>
-      </c>
-      <c r="AC296">
-        <v>2.75</v>
-      </c>
-      <c r="AD296">
-        <v>1.4</v>
-      </c>
-      <c r="AE296">
-        <v>1.1</v>
-      </c>
       <c r="AF296">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG296">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK296">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,65 +48720,65 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="O297">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="P297">
-        <v>4.36</v>
+        <v>1.5</v>
       </c>
       <c r="Q297">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="R297">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S297">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T297">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="U297">
-        <v>2.99</v>
+        <v>2.37</v>
       </c>
       <c r="V297">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W297">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X297">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y297">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z297">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="AA297">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AB297">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC297">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD297">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE297">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF297">
+        <v>1.82</v>
+      </c>
+      <c r="AG297">
         <v>1.9</v>
       </c>
-      <c r="AG297">
-        <v>1.8</v>
-      </c>
       <c r="AH297" t="inlineStr">
         <is>
           <t>[]</t>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK297">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="AL297">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.98</v>
+      </c>
+      <c r="O10">
         <v>3.4</v>
       </c>
-      <c r="O10">
-        <v>3.5</v>
-      </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
+        <v>2.78</v>
+      </c>
+      <c r="U10">
+        <v>2.7</v>
+      </c>
+      <c r="V10">
+        <v>1.42</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.22</v>
+      </c>
+      <c r="Z10">
+        <v>3.8</v>
+      </c>
+      <c r="AA10">
+        <v>1.87</v>
+      </c>
+      <c r="AB10">
+        <v>1.76</v>
+      </c>
+      <c r="AC10">
         <v>3.1</v>
       </c>
-      <c r="U10">
-        <v>2.45</v>
-      </c>
-      <c r="V10">
-        <v>1.48</v>
-      </c>
-      <c r="W10">
-        <v>1.06</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.25</v>
-      </c>
-      <c r="Z10">
-        <v>3.9</v>
-      </c>
-      <c r="AA10">
-        <v>1.8</v>
-      </c>
-      <c r="AB10">
-        <v>2.07</v>
-      </c>
-      <c r="AC10">
-        <v>3.05</v>
-      </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AK10">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA11">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         <v>1.91</v>
       </c>
       <c r="S19">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U19">
         <v>3.5</v>
@@ -3439,19 +3439,19 @@
         <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z19">
         <v>2.52</v>
       </c>
       <c r="AA19">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB19">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC19">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD19">
         <v>1.12</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AG19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="O25">
+        <v>3.8</v>
+      </c>
+      <c r="P25">
+        <v>4.4</v>
+      </c>
+      <c r="Q25">
+        <v>2.11</v>
+      </c>
+      <c r="R25">
+        <v>2.24</v>
+      </c>
+      <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
         <v>3.2</v>
       </c>
-      <c r="P25">
-        <v>3.4</v>
-      </c>
-      <c r="Q25">
-        <v>2.75</v>
-      </c>
-      <c r="R25">
-        <v>2</v>
-      </c>
-      <c r="S25">
-        <v>1.44</v>
-      </c>
-      <c r="T25">
-        <v>2.75</v>
-      </c>
       <c r="U25">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z25">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA25">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC25">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG25">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="S26">
+        <v>1.44</v>
+      </c>
+      <c r="T26">
+        <v>2.75</v>
+      </c>
+      <c r="U26">
+        <v>2.91</v>
+      </c>
+      <c r="V26">
+        <v>1.36</v>
+      </c>
+      <c r="W26">
+        <v>1.07</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
         <v>1.3</v>
       </c>
-      <c r="T26">
-        <v>3.2</v>
-      </c>
-      <c r="U26">
-        <v>2.53</v>
-      </c>
-      <c r="V26">
-        <v>1.43</v>
-      </c>
-      <c r="W26">
-        <v>1.06</v>
-      </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>1.18</v>
-      </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="R29">
         <v>1.91</v>
@@ -5093,7 +5093,7 @@
         <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="O60">
-        <v>4.55</v>
+        <v>3.14</v>
       </c>
       <c r="P60">
-        <v>7.05</v>
+        <v>3.61</v>
       </c>
       <c r="Q60">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="R60">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="T60">
-        <v>3.75</v>
+        <v>2.47</v>
       </c>
       <c r="U60">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="V60">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="W60">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z60">
-        <v>4.6</v>
+        <v>2.83</v>
       </c>
       <c r="AA60">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB60">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="AC60">
-        <v>2.25</v>
+        <v>3.76</v>
       </c>
       <c r="AD60">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="AE60">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG60">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK60">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="O61">
-        <v>3.14</v>
+        <v>4.55</v>
       </c>
       <c r="P61">
-        <v>3.61</v>
+        <v>7.05</v>
       </c>
       <c r="Q61">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="R61">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="S61">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="U61">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="V61">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="W61">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>2.83</v>
+        <v>4.6</v>
       </c>
       <c r="AA61">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB61">
-        <v>1.63</v>
+        <v>2.41</v>
       </c>
       <c r="AC61">
-        <v>3.76</v>
+        <v>2.25</v>
       </c>
       <c r="AD61">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AE61">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG61">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>5.75</v>
       </c>
       <c r="Q78">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R78">
         <v>2.7</v>
@@ -13047,7 +13047,7 @@
         <v>2</v>
       </c>
       <c r="V78">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W78">
         <v>1.18</v>
@@ -13056,10 +13056,10 @@
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>5.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA78">
         <v>1.42</v>
@@ -13068,7 +13068,7 @@
         <v>2.76</v>
       </c>
       <c r="AC78">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AD78">
         <v>1.73</v>
@@ -14170,7 +14170,7 @@
         <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="Q85">
         <v>2.8</v>
@@ -14179,10 +14179,10 @@
         <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T85">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="U85">
         <v>2.75</v>
@@ -14218,7 +14218,7 @@
         <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
         <v>2.01</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O89">
         <v>3.2</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q89">
         <v>2.85</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S89">
         <v>1.33</v>
@@ -14837,13 +14837,13 @@
         <v>3.1</v>
       </c>
       <c r="U89">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V89">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
         <v>1.05</v>
@@ -14861,16 +14861,16 @@
         <v>1.87</v>
       </c>
       <c r="AC89">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD89">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE89">
         <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG89">
         <v>2</v>
@@ -16120,16 +16120,16 @@
         </is>
       </c>
       <c r="N97">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O97">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="P97">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q97">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="R97">
         <v>2.25</v>
@@ -16141,7 +16141,7 @@
         <v>3.28</v>
       </c>
       <c r="U97">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V97">
         <v>1.49</v>
@@ -16467,7 +16467,7 @@
         <v>3.1</v>
       </c>
       <c r="U99">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V99">
         <v>1.4</v>
@@ -16491,7 +16491,7 @@
         <v>2.01</v>
       </c>
       <c r="AC99">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AD99">
         <v>1.34</v>
@@ -18568,10 +18568,10 @@
         <v>2.75</v>
       </c>
       <c r="O112">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="P112">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="Q112">
         <v>3.38</v>
@@ -18586,7 +18586,7 @@
         <v>2.9</v>
       </c>
       <c r="U112">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
         <v>1.43</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK112">
         <v>1.48</v>
@@ -18737,7 +18737,7 @@
         <v>3</v>
       </c>
       <c r="Q113">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R113">
         <v>2.04</v>
@@ -18746,10 +18746,10 @@
         <v>1.47</v>
       </c>
       <c r="T113">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="U113">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="V113">
         <v>1.3</v>
@@ -18761,10 +18761,10 @@
         <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z113">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AA113">
         <v>2.3</v>
@@ -18776,7 +18776,7 @@
         <v>4.33</v>
       </c>
       <c r="AD113">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE113">
         <v>1.01</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB116">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19389,10 +19389,10 @@
         <v>0</v>
       </c>
       <c r="Q117">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R117">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="S117">
         <v>1.07</v>
@@ -19413,10 +19413,10 @@
         <v>1</v>
       </c>
       <c r="Y117">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Z117">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA117">
         <v>1.14</v>
@@ -19425,10 +19425,10 @@
         <v>5.25</v>
       </c>
       <c r="AC117">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AD117">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AE117">
         <v>1.83</v>
@@ -19555,19 +19555,19 @@
         <v>3.1</v>
       </c>
       <c r="R118">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T118">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U118">
         <v>2.4</v>
       </c>
       <c r="V118">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W118">
         <v>1.09</v>
@@ -19579,10 +19579,10 @@
         <v>1.22</v>
       </c>
       <c r="Z118">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="AA118">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB118">
         <v>2.1</v>
@@ -19597,7 +19597,7 @@
         <v>1.16</v>
       </c>
       <c r="AF118">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG118">
         <v>2.3</v>
@@ -22486,7 +22486,7 @@
         <v>2.6</v>
       </c>
       <c r="Q136">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="R136">
         <v>2.2</v>
@@ -22498,10 +22498,10 @@
         <v>3.1</v>
       </c>
       <c r="U136">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V136">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
         <v>1.06</v>
@@ -22510,7 +22510,7 @@
         <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z136">
         <v>3.92</v>
@@ -22522,7 +22522,7 @@
         <v>2.01</v>
       </c>
       <c r="AC136">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD136">
         <v>1.39</v>
@@ -22534,7 +22534,7 @@
         <v>1.62</v>
       </c>
       <c r="AG136">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22972,7 +22972,7 @@
         <v>3.6</v>
       </c>
       <c r="P139">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23183,10 +23183,10 @@
         <v>1.02</v>
       </c>
       <c r="AF140">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG140">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>1.34</v>
       </c>
       <c r="AK140">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23298,7 +23298,7 @@
         <v>5.75</v>
       </c>
       <c r="P141">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Q141">
         <v>7</v>
@@ -23310,7 +23310,7 @@
         <v>1.2</v>
       </c>
       <c r="T141">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="U141">
         <v>1.93</v>
@@ -23328,7 +23328,7 @@
         <v>1.11</v>
       </c>
       <c r="Z141">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="AA141">
         <v>1.4</v>
@@ -23340,16 +23340,16 @@
         <v>1.93</v>
       </c>
       <c r="AD141">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AE141">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF141">
         <v>1.67</v>
       </c>
       <c r="AG141">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AK141">
         <v>1.07</v>
@@ -24279,7 +24279,7 @@
         <v>3.93</v>
       </c>
       <c r="Q147">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R147">
         <v>2.16</v>
@@ -24288,7 +24288,7 @@
         <v>1.45</v>
       </c>
       <c r="T147">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="U147">
         <v>2.9</v>
@@ -24327,7 +24327,7 @@
         <v>2</v>
       </c>
       <c r="AG147">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>1.17</v>
       </c>
       <c r="AK147">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25746,7 +25746,7 @@
         <v>2.61</v>
       </c>
       <c r="Q156">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R156">
         <v>2.37</v>
@@ -25755,10 +25755,10 @@
         <v>1.29</v>
       </c>
       <c r="T156">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U156">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="V156">
         <v>1.49</v>
@@ -25788,13 +25788,13 @@
         <v>1.41</v>
       </c>
       <c r="AE156">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF156">
         <v>1.53</v>
       </c>
       <c r="AG156">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -26247,10 +26247,10 @@
         <v>4.33</v>
       </c>
       <c r="U159">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V159">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W159">
         <v>1.22</v>
@@ -26283,7 +26283,7 @@
         <v>1.6</v>
       </c>
       <c r="AG159">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -28348,10 +28348,10 @@
         <v>3.85</v>
       </c>
       <c r="O172">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="P172">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q172">
         <v>4</v>
@@ -28384,10 +28384,10 @@
         <v>3.68</v>
       </c>
       <c r="AA172">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB172">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC172">
         <v>2.85</v>
@@ -28870,7 +28870,7 @@
         <v>1.25</v>
       </c>
       <c r="Z175">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA175">
         <v>1.74</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK175">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="O176">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P176">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="Q176">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="R176">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S176">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T176">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U176">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V176">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y176">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z176">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA176">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB176">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AC176">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD176">
+        <v>1.15</v>
+      </c>
+      <c r="AE176">
+        <v>1.02</v>
+      </c>
+      <c r="AF176">
+        <v>1.97</v>
+      </c>
+      <c r="AG176">
+        <v>1.72</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
+        <v>1.27</v>
+      </c>
+      <c r="AK176">
         <v>1.23</v>
-      </c>
-      <c r="AE176">
-        <v>1.04</v>
-      </c>
-      <c r="AF176">
-        <v>1.85</v>
-      </c>
-      <c r="AG176">
-        <v>1.82</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.25</v>
-      </c>
-      <c r="AK176">
-        <v>1.71</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="O177">
+        <v>3.15</v>
+      </c>
+      <c r="P177">
+        <v>3.6</v>
+      </c>
+      <c r="Q177">
+        <v>2.5</v>
+      </c>
+      <c r="R177">
+        <v>2.1</v>
+      </c>
+      <c r="S177">
+        <v>1.36</v>
+      </c>
+      <c r="T177">
+        <v>2.88</v>
+      </c>
+      <c r="U177">
+        <v>3</v>
+      </c>
+      <c r="V177">
+        <v>1.33</v>
+      </c>
+      <c r="W177">
+        <v>1.06</v>
+      </c>
+      <c r="X177">
+        <v>1.03</v>
+      </c>
+      <c r="Y177">
+        <v>1.3</v>
+      </c>
+      <c r="Z177">
         <v>2.95</v>
       </c>
-      <c r="P177">
-        <v>2.19</v>
-      </c>
-      <c r="Q177">
-        <v>3.85</v>
-      </c>
-      <c r="R177">
+      <c r="AA177">
         <v>2</v>
       </c>
-      <c r="S177">
-        <v>1.44</v>
-      </c>
-      <c r="T177">
-        <v>2.63</v>
-      </c>
-      <c r="U177">
-        <v>3.25</v>
-      </c>
-      <c r="V177">
-        <v>1.29</v>
-      </c>
-      <c r="W177">
+      <c r="AB177">
+        <v>1.66</v>
+      </c>
+      <c r="AC177">
+        <v>3.45</v>
+      </c>
+      <c r="AD177">
+        <v>1.23</v>
+      </c>
+      <c r="AE177">
         <v>1.04</v>
       </c>
-      <c r="X177">
-        <v>1.05</v>
-      </c>
-      <c r="Y177">
-        <v>1.4</v>
-      </c>
-      <c r="Z177">
-        <v>2.55</v>
-      </c>
-      <c r="AA177">
-        <v>2.25</v>
-      </c>
-      <c r="AB177">
-        <v>1.52</v>
-      </c>
-      <c r="AC177">
-        <v>4.2</v>
-      </c>
-      <c r="AD177">
-        <v>1.15</v>
-      </c>
-      <c r="AE177">
-        <v>1.02</v>
-      </c>
       <c r="AF177">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG177">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29658,7 +29658,7 @@
         <v>5.8</v>
       </c>
       <c r="Q180">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R180">
         <v>2.38</v>
@@ -29667,7 +29667,7 @@
         <v>1.28</v>
       </c>
       <c r="T180">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U180">
         <v>2.36</v>
@@ -29694,7 +29694,7 @@
         <v>2.24</v>
       </c>
       <c r="AC180">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD180">
         <v>1.5</v>
@@ -29703,7 +29703,7 @@
         <v>1.13</v>
       </c>
       <c r="AF180">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG180">
         <v>2</v>
@@ -30144,7 +30144,7 @@
         <v>4.25</v>
       </c>
       <c r="P183">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q183">
         <v>2</v>
@@ -30174,13 +30174,13 @@
         <v>1.18</v>
       </c>
       <c r="Z183">
-        <v>5.63</v>
+        <v>4.85</v>
       </c>
       <c r="AA183">
         <v>1.49</v>
       </c>
       <c r="AB183">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC183">
         <v>2.24</v>
@@ -30192,7 +30192,7 @@
         <v>1.17</v>
       </c>
       <c r="AF183">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG183">
         <v>2.31</v>
@@ -31448,7 +31448,7 @@
         <v>4</v>
       </c>
       <c r="P191">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="Q191">
         <v>2.4</v>
@@ -31460,10 +31460,10 @@
         <v>1.22</v>
       </c>
       <c r="T191">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U191">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V191">
         <v>1.67</v>
@@ -31496,7 +31496,7 @@
         <v>1.25</v>
       </c>
       <c r="AF191">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG191">
         <v>2.7</v>
@@ -36495,25 +36495,25 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O222">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P222">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q222">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="R222">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S222">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T222">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U222">
         <v>3.04</v>
@@ -36525,7 +36525,7 @@
         <v>1.05</v>
       </c>
       <c r="X222">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y222">
         <v>1.34</v>
@@ -36534,19 +36534,19 @@
         <v>2.78</v>
       </c>
       <c r="AA222">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB222">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC222">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD222">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE222">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF222">
         <v>1.82</v>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AK222">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -38792,43 +38792,43 @@
         <v>2</v>
       </c>
       <c r="S236">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T236">
         <v>2.65</v>
       </c>
       <c r="U236">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="V236">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W236">
         <v>1.05</v>
       </c>
       <c r="X236">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y236">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z236">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA236">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AB236">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC236">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD236">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE236">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF236">
         <v>1.85</v>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK236">
         <v>1.43</v>
@@ -39441,7 +39441,7 @@
         <v>2.64</v>
       </c>
       <c r="R240">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S240">
         <v>1.36</v>
@@ -39468,10 +39468,10 @@
         <v>2.92</v>
       </c>
       <c r="AA240">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB240">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC240">
         <v>3.5</v>
@@ -39927,10 +39927,10 @@
         <v>3.35</v>
       </c>
       <c r="Q243">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="R243">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S243">
         <v>1.43</v>
@@ -39960,7 +39960,7 @@
         <v>2.1</v>
       </c>
       <c r="AB243">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC243">
         <v>3.58</v>
@@ -40090,10 +40090,10 @@
         <v>3.25</v>
       </c>
       <c r="Q244">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R244">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S244">
         <v>1.35</v>
@@ -40111,7 +40111,7 @@
         <v>1.04</v>
       </c>
       <c r="X244">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y244">
         <v>1.34</v>
@@ -40154,7 +40154,7 @@
         <v>1.28</v>
       </c>
       <c r="AK244">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40431,10 +40431,10 @@
         <v>2.43</v>
       </c>
       <c r="V246">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W246">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X246">
         <v>1.03</v>
@@ -40443,19 +40443,19 @@
         <v>1.2</v>
       </c>
       <c r="Z246">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA246">
         <v>1.66</v>
       </c>
       <c r="AB246">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC246">
         <v>2.56</v>
       </c>
       <c r="AD246">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE246">
         <v>1.19</v>
@@ -40464,7 +40464,7 @@
         <v>1.67</v>
       </c>
       <c r="AG246">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>4.75</v>
       </c>
       <c r="AD249">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE249">
         <v>1.01</v>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="O250">
         <v>3.24</v>
@@ -41089,7 +41089,7 @@
         <v>1.08</v>
       </c>
       <c r="X250">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y250">
         <v>1.3</v>
@@ -41551,7 +41551,7 @@
         <v>2.39</v>
       </c>
       <c r="O253">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="P253">
         <v>2.73</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB253">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41723,13 +41723,13 @@
         <v>3.89</v>
       </c>
       <c r="R254">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S254">
         <v>1.4</v>
       </c>
       <c r="T254">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U254">
         <v>3.05</v>
@@ -41741,19 +41741,19 @@
         <v>1.06</v>
       </c>
       <c r="X254">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y254">
         <v>1.3</v>
       </c>
       <c r="Z254">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AA254">
         <v>2.02</v>
       </c>
       <c r="AB254">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AC254">
         <v>3.42</v>
@@ -43670,7 +43670,7 @@
         <v>1.53</v>
       </c>
       <c r="O266">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="P266">
         <v>6.5</v>
@@ -43706,16 +43706,16 @@
         <v>3.45</v>
       </c>
       <c r="AA266">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB266">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC266">
         <v>3.45</v>
       </c>
       <c r="AD266">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE266">
         <v>1.1</v>
@@ -44226,7 +44226,7 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK269">
         <v>1.18</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="O278">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="P278">
-        <v>3.9</v>
+        <v>5.05</v>
       </c>
       <c r="Q278">
         <v>2.5</v>
@@ -45638,49 +45638,49 @@
         <v>1.91</v>
       </c>
       <c r="S278">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T278">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U278">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="V278">
         <v>1.18</v>
       </c>
       <c r="W278">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X278">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y278">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Z278">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AA278">
         <v>2.7</v>
       </c>
       <c r="AB278">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AC278">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="AD278">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AE278">
         <v>1.03</v>
       </c>
       <c r="AF278">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AG278">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>1.2</v>
       </c>
       <c r="AK278">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45792,7 +45792,7 @@
         <v>2.8</v>
       </c>
       <c r="P279">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK286">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47262,10 +47262,10 @@
         <v>3.65</v>
       </c>
       <c r="Q288">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R288">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S288">
         <v>1.45</v>
@@ -47298,10 +47298,10 @@
         <v>1.61</v>
       </c>
       <c r="AC288">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD288">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE288">
         <v>1.01</v>
@@ -47310,7 +47310,7 @@
         <v>1.95</v>
       </c>
       <c r="AG288">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O289">
         <v>2.62</v>
@@ -47431,31 +47431,31 @@
         <v>1.91</v>
       </c>
       <c r="S289">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T289">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U289">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V289">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W289">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y289">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z289">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AA289">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AB289">
         <v>1.42</v>
@@ -47473,7 +47473,7 @@
         <v>2.3</v>
       </c>
       <c r="AG289">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK289">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47588,13 +47588,13 @@
         <v>2.5</v>
       </c>
       <c r="Q290">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R290">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S290">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="T290">
         <v>2.31</v>
@@ -47603,7 +47603,7 @@
         <v>3.5</v>
       </c>
       <c r="V290">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W290">
         <v>1.01</v>
@@ -47612,31 +47612,31 @@
         <v>1.07</v>
       </c>
       <c r="Y290">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z290">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AA290">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB290">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AC290">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AD290">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE290">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF290">
         <v>2</v>
       </c>
       <c r="AG290">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK290">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -48095,7 +48095,7 @@
         <v>1.55</v>
       </c>
       <c r="W293">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X293">
         <v>1.04</v>
@@ -48107,7 +48107,7 @@
         <v>4.9</v>
       </c>
       <c r="AA293">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB293">
         <v>2.33</v>
@@ -48119,7 +48119,7 @@
         <v>1.47</v>
       </c>
       <c r="AE293">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF293">
         <v>1.59</v>
@@ -48138,7 +48138,7 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK293">
         <v>2.05</v>
@@ -48231,16 +48231,16 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O294">
         <v>3.28</v>
       </c>
       <c r="P294">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="Q294">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="R294">
         <v>2.14</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O296">
-        <v>3.23</v>
+        <v>4.35</v>
       </c>
       <c r="P296">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="Q296">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="R296">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="S296">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T296">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U296">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V296">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="W296">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X296">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y296">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z296">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="AA296">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AB296">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AC296">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="AD296">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AE296">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF296">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG296">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK296">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O297">
-        <v>4.35</v>
+        <v>3.23</v>
       </c>
       <c r="P297">
-        <v>1.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q297">
-        <v>6</v>
+        <v>2.45</v>
       </c>
       <c r="R297">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="S297">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T297">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U297">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V297">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="W297">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X297">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z297">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="AA297">
+        <v>2.12</v>
+      </c>
+      <c r="AB297">
         <v>1.74</v>
       </c>
-      <c r="AB297">
-        <v>2.01</v>
-      </c>
       <c r="AC297">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD297">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AE297">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF297">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG297">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK297">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="O299">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P299">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q299">
         <v>5</v>
@@ -49097,7 +49097,7 @@
         <v>1.75</v>
       </c>
       <c r="AE299">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF299">
         <v>1.46</v>
@@ -49375,28 +49375,28 @@
         <v>2.2</v>
       </c>
       <c r="O301">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P301">
         <v>3.3</v>
       </c>
       <c r="Q301">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R301">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="S301">
         <v>1.6</v>
       </c>
       <c r="T301">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U301">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="V301">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W301">
         <v>1.03</v>
@@ -49417,19 +49417,19 @@
         <v>1.36</v>
       </c>
       <c r="AC301">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AD301">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE301">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF301">
         <v>2.4</v>
       </c>
       <c r="AG301">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK301">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49544,16 +49544,16 @@
         <v>3.9</v>
       </c>
       <c r="Q302">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="R302">
         <v>1.95</v>
       </c>
       <c r="S302">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T302">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U302">
         <v>3.5</v>
@@ -49568,7 +49568,7 @@
         <v>1.11</v>
       </c>
       <c r="Y302">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z302">
         <v>2.55</v>
@@ -49577,7 +49577,7 @@
         <v>2.38</v>
       </c>
       <c r="AB302">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AC302">
         <v>5</v>
@@ -49589,10 +49589,10 @@
         <v>1</v>
       </c>
       <c r="AF302">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG302">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK302">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49707,55 +49707,55 @@
         <v>4.1</v>
       </c>
       <c r="Q303">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="R303">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="S303">
         <v>1.57</v>
       </c>
       <c r="T303">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="U303">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V303">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W303">
         <v>1.03</v>
       </c>
       <c r="X303">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Y303">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z303">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AA303">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB303">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AC303">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD303">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE303">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF303">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AG303">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49867,58 +49867,58 @@
         <v>3.3</v>
       </c>
       <c r="P304">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q304">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R304">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="S304">
         <v>1.56</v>
       </c>
       <c r="T304">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="U304">
         <v>3.5</v>
       </c>
       <c r="V304">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W304">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X304">
         <v>1.11</v>
       </c>
       <c r="Y304">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z304">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AA304">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AB304">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AC304">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD304">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE304">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF304">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG304">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>1.14</v>
       </c>
       <c r="AK304">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50042,7 +50042,7 @@
         <v>1.33</v>
       </c>
       <c r="T305">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U305">
         <v>2.45</v>
@@ -50078,7 +50078,7 @@
         <v>1.15</v>
       </c>
       <c r="AF305">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG305">
         <v>1.91</v>
@@ -50097,7 +50097,7 @@
         <v>1.12</v>
       </c>
       <c r="AK305">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -51328,49 +51328,49 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O313">
         <v>3.4</v>
       </c>
       <c r="P313">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q313">
         <v>2.38</v>
       </c>
       <c r="R313">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S313">
         <v>1.4</v>
       </c>
       <c r="T313">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="U313">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="V313">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W313">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X313">
         <v>1.03</v>
       </c>
       <c r="Y313">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z313">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AA313">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AB313">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC313">
         <v>3.8</v>
@@ -51382,10 +51382,10 @@
         <v>1.05</v>
       </c>
       <c r="AF313">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG313">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK313">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51657,7 +51657,7 @@
         <v>2.5</v>
       </c>
       <c r="O315">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P315">
         <v>3.4</v>
@@ -51820,31 +51820,31 @@
         <v>2.7</v>
       </c>
       <c r="O316">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P316">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q316">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R316">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S316">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T316">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U316">
         <v>3.75</v>
       </c>
       <c r="V316">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W316">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X316">
         <v>1.08</v>
@@ -51859,7 +51859,7 @@
         <v>2.55</v>
       </c>
       <c r="AB316">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC316">
         <v>5.93</v>
@@ -51871,7 +51871,7 @@
         <v>1.03</v>
       </c>
       <c r="AF316">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG316">
         <v>1.57</v>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK316">
         <v>1.36</v>
@@ -52306,13 +52306,13 @@
         </is>
       </c>
       <c r="N319">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O319">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P319">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q319">
         <v>0</v>
@@ -52487,7 +52487,7 @@
         <v>1.17</v>
       </c>
       <c r="T320">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U320">
         <v>1.99</v>
@@ -52505,7 +52505,7 @@
         <v>1.06</v>
       </c>
       <c r="Z320">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA320">
         <v>1.32</v>
@@ -52523,10 +52523,10 @@
         <v>1.33</v>
       </c>
       <c r="AF320">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG320">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -53785,13 +53785,13 @@
         <v>2.25</v>
       </c>
       <c r="R328">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S328">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T328">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U328">
         <v>2.25</v>
@@ -53809,28 +53809,28 @@
         <v>1.13</v>
       </c>
       <c r="Z328">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA328">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB328">
         <v>2.3</v>
       </c>
       <c r="AC328">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD328">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE328">
         <v>1.15</v>
       </c>
       <c r="AF328">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG328">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>1.15</v>
       </c>
       <c r="AK328">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="O330">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="P330">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="Q330">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.98</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>2.17</v>
+        <v>4.26</v>
       </c>
       <c r="Q10">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>3.19</v>
       </c>
       <c r="U10">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
+        <v>1.2</v>
+      </c>
+      <c r="Z10">
+        <v>3.88</v>
+      </c>
+      <c r="AA10">
+        <v>1.81</v>
+      </c>
+      <c r="AB10">
+        <v>2.04</v>
+      </c>
+      <c r="AC10">
+        <v>3</v>
+      </c>
+      <c r="AD10">
+        <v>1.38</v>
+      </c>
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
+        <v>1.69</v>
+      </c>
+      <c r="AG10">
+        <v>2.05</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.22</v>
       </c>
-      <c r="Z10">
-        <v>3.8</v>
-      </c>
-      <c r="AA10">
-        <v>1.87</v>
-      </c>
-      <c r="AB10">
-        <v>1.76</v>
-      </c>
-      <c r="AC10">
-        <v>3.1</v>
-      </c>
-      <c r="AD10">
-        <v>1.27</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
-      <c r="AF10">
-        <v>1.67</v>
-      </c>
-      <c r="AG10">
-        <v>2.1</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.64</v>
-      </c>
       <c r="AK10">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>2.98</v>
+      </c>
+      <c r="O11">
         <v>3.4</v>
       </c>
-      <c r="O11">
-        <v>3.5</v>
-      </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
+        <v>2.78</v>
+      </c>
+      <c r="U11">
+        <v>2.7</v>
+      </c>
+      <c r="V11">
+        <v>1.42</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.22</v>
+      </c>
+      <c r="Z11">
+        <v>3.8</v>
+      </c>
+      <c r="AA11">
+        <v>1.87</v>
+      </c>
+      <c r="AB11">
+        <v>1.76</v>
+      </c>
+      <c r="AC11">
         <v>3.1</v>
       </c>
-      <c r="U11">
-        <v>2.45</v>
-      </c>
-      <c r="V11">
-        <v>1.48</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.25</v>
-      </c>
-      <c r="Z11">
-        <v>3.9</v>
-      </c>
-      <c r="AA11">
-        <v>1.8</v>
-      </c>
-      <c r="AB11">
-        <v>2.07</v>
-      </c>
-      <c r="AC11">
-        <v>3.05</v>
-      </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AK11">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
         <v>3.5</v>
       </c>
       <c r="P12">
-        <v>4.26</v>
+        <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="R12">
         <v>2.19</v>
@@ -2283,46 +2283,46 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD12">
         <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="O81">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="P81">
-        <v>4</v>
+        <v>6.96</v>
       </c>
       <c r="Q81">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="S81">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U81">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="AB81">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC81">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="AD81">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AE81">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AK81">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="O82">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="P82">
-        <v>6.96</v>
+        <v>4</v>
       </c>
       <c r="Q82">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="R82">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U82">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V82">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W82">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z82">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA82">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AB82">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC82">
-        <v>3.03</v>
+        <v>3.34</v>
       </c>
       <c r="AD82">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE82">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF82">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
+        <v>2</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>1.25</v>
+      </c>
+      <c r="AK82">
         <v>1.75</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.04</v>
-      </c>
-      <c r="AK82">
-        <v>2.88</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R102">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S102">
         <v>1.4</v>
       </c>
       <c r="T102">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U102">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="V102">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
+        <v>1.04</v>
+      </c>
+      <c r="X102">
+        <v>1.04</v>
+      </c>
+      <c r="Y102">
+        <v>1.35</v>
+      </c>
+      <c r="Z102">
+        <v>3.27</v>
+      </c>
+      <c r="AA102">
+        <v>2.07</v>
+      </c>
+      <c r="AB102">
+        <v>1.79</v>
+      </c>
+      <c r="AC102">
+        <v>3.28</v>
+      </c>
+      <c r="AD102">
+        <v>1.25</v>
+      </c>
+      <c r="AE102">
         <v>1.06</v>
       </c>
-      <c r="X102">
-        <v>1</v>
-      </c>
-      <c r="Y102">
-        <v>1.24</v>
-      </c>
-      <c r="Z102">
-        <v>3.55</v>
-      </c>
-      <c r="AA102">
-        <v>1.9</v>
-      </c>
-      <c r="AB102">
-        <v>1.84</v>
-      </c>
-      <c r="AC102">
-        <v>3.08</v>
-      </c>
-      <c r="AD102">
-        <v>1.28</v>
-      </c>
-      <c r="AE102">
-        <v>1.08</v>
-      </c>
       <c r="AF102">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK102">
         <v>1.43</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q103">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R103">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
         <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U103">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V103">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z103">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="AA103">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB103">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AC103">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD103">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF103">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AG103">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK103">
         <v>1.43</v>
@@ -22803,19 +22803,19 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="O138">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P138">
+        <v>3.1</v>
+      </c>
+      <c r="Q138">
         <v>3</v>
       </c>
-      <c r="Q138">
-        <v>2.9</v>
-      </c>
       <c r="R138">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S138">
         <v>1.4</v>
@@ -22836,10 +22836,10 @@
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z138">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA138">
         <v>2.1</v>
@@ -22860,7 +22860,7 @@
         <v>1.8</v>
       </c>
       <c r="AG138">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>1.36</v>
       </c>
       <c r="AK138">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -28674,22 +28674,22 @@
         <v>1.44</v>
       </c>
       <c r="O174">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P174">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q174">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R174">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="S174">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T174">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U174">
         <v>2.42</v>
@@ -28701,34 +28701,34 @@
         <v>1.11</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
         <v>1.16</v>
       </c>
       <c r="Z174">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA174">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB174">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC174">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD174">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE174">
         <v>1.13</v>
       </c>
       <c r="AF174">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG174">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK174">
         <v>1.98</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="O176">
+        <v>3.15</v>
+      </c>
+      <c r="P176">
+        <v>3.6</v>
+      </c>
+      <c r="Q176">
+        <v>2.5</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>1.36</v>
+      </c>
+      <c r="T176">
+        <v>2.88</v>
+      </c>
+      <c r="U176">
+        <v>3</v>
+      </c>
+      <c r="V176">
+        <v>1.33</v>
+      </c>
+      <c r="W176">
+        <v>1.06</v>
+      </c>
+      <c r="X176">
+        <v>1.03</v>
+      </c>
+      <c r="Y176">
+        <v>1.3</v>
+      </c>
+      <c r="Z176">
         <v>2.95</v>
       </c>
-      <c r="P176">
-        <v>2.19</v>
-      </c>
-      <c r="Q176">
-        <v>3.85</v>
-      </c>
-      <c r="R176">
+      <c r="AA176">
         <v>2</v>
       </c>
-      <c r="S176">
-        <v>1.44</v>
-      </c>
-      <c r="T176">
-        <v>2.63</v>
-      </c>
-      <c r="U176">
-        <v>3.25</v>
-      </c>
-      <c r="V176">
-        <v>1.29</v>
-      </c>
-      <c r="W176">
+      <c r="AB176">
+        <v>1.66</v>
+      </c>
+      <c r="AC176">
+        <v>3.45</v>
+      </c>
+      <c r="AD176">
+        <v>1.23</v>
+      </c>
+      <c r="AE176">
         <v>1.04</v>
       </c>
-      <c r="X176">
-        <v>1.05</v>
-      </c>
-      <c r="Y176">
-        <v>1.4</v>
-      </c>
-      <c r="Z176">
-        <v>2.55</v>
-      </c>
-      <c r="AA176">
-        <v>2.25</v>
-      </c>
-      <c r="AB176">
-        <v>1.52</v>
-      </c>
-      <c r="AC176">
-        <v>4.2</v>
-      </c>
-      <c r="AD176">
-        <v>1.15</v>
-      </c>
-      <c r="AE176">
-        <v>1.02</v>
-      </c>
       <c r="AF176">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG176">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK176">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,80 +29160,80 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="O177">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P177">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="Q177">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="R177">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S177">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T177">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U177">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V177">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W177">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X177">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y177">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z177">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA177">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB177">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AC177">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD177">
+        <v>1.15</v>
+      </c>
+      <c r="AE177">
+        <v>1.02</v>
+      </c>
+      <c r="AF177">
+        <v>1.97</v>
+      </c>
+      <c r="AG177">
+        <v>1.72</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ177">
+        <v>1.27</v>
+      </c>
+      <c r="AK177">
         <v>1.23</v>
-      </c>
-      <c r="AE177">
-        <v>1.04</v>
-      </c>
-      <c r="AF177">
-        <v>1.85</v>
-      </c>
-      <c r="AG177">
-        <v>1.82</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ177">
-        <v>1.25</v>
-      </c>
-      <c r="AK177">
-        <v>1.71</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="O319">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="P319">
+        <v>1.93</v>
+      </c>
+      <c r="Q319">
+        <v>3.8</v>
+      </c>
+      <c r="R319">
+        <v>2.1</v>
+      </c>
+      <c r="S319">
+        <v>1.39</v>
+      </c>
+      <c r="T319">
+        <v>2.75</v>
+      </c>
+      <c r="U319">
+        <v>2.85</v>
+      </c>
+      <c r="V319">
+        <v>1.36</v>
+      </c>
+      <c r="W319">
+        <v>1.05</v>
+      </c>
+      <c r="X319">
+        <v>1.02</v>
+      </c>
+      <c r="Y319">
+        <v>1.33</v>
+      </c>
+      <c r="Z319">
+        <v>3.01</v>
+      </c>
+      <c r="AA319">
         <v>2.05</v>
       </c>
-      <c r="Q319">
-        <v>0</v>
-      </c>
-      <c r="R319">
-        <v>0</v>
-      </c>
-      <c r="S319">
-        <v>0</v>
-      </c>
-      <c r="T319">
-        <v>0</v>
-      </c>
-      <c r="U319">
-        <v>0</v>
-      </c>
-      <c r="V319">
-        <v>0</v>
-      </c>
-      <c r="W319">
-        <v>0</v>
-      </c>
-      <c r="X319">
-        <v>0</v>
-      </c>
-      <c r="Y319">
-        <v>0</v>
-      </c>
-      <c r="Z319">
-        <v>0</v>
-      </c>
-      <c r="AA319">
-        <v>0</v>
-      </c>
       <c r="AB319">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC319">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD319">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE319">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF319">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG319">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK319">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52970,10 +52970,10 @@
         <v>9</v>
       </c>
       <c r="R323">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="S323">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T323">
         <v>3.15</v>
@@ -52982,10 +52982,10 @@
         <v>2.55</v>
       </c>
       <c r="V323">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W323">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X323">
         <v>1.01</v>
@@ -52994,10 +52994,10 @@
         <v>1.2</v>
       </c>
       <c r="Z323">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA323">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB323">
         <v>2.1</v>
@@ -53006,10 +53006,10 @@
         <v>2.55</v>
       </c>
       <c r="AD323">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE323">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF323">
         <v>1.75</v>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK323">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="O329">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="P329">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X329">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC329">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AD329">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="O330">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P330">
-        <v>5.35</v>
+        <v>4.05</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R330">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S330">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T330">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U330">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V330">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W330">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X330">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y330">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z330">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA330">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB330">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC330">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD330">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE330">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG330">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK330">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL330">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O79">
         <v>3.1</v>
@@ -13219,7 +13219,7 @@
         <v>1.06</v>
       </c>
       <c r="Y79">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
         <v>3</v>
@@ -13237,13 +13237,13 @@
         <v>1.25</v>
       </c>
       <c r="AE79">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF79">
         <v>1.8</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK79">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="O81">
-        <v>4.35</v>
+        <v>3.03</v>
       </c>
       <c r="P81">
-        <v>6.96</v>
+        <v>4.2</v>
       </c>
       <c r="Q81">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="R81">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="S81">
+        <v>1.36</v>
+      </c>
+      <c r="T81">
+        <v>2.87</v>
+      </c>
+      <c r="U81">
+        <v>2.88</v>
+      </c>
+      <c r="V81">
+        <v>1.33</v>
+      </c>
+      <c r="W81">
+        <v>1.08</v>
+      </c>
+      <c r="X81">
+        <v>1.04</v>
+      </c>
+      <c r="Y81">
         <v>1.3</v>
       </c>
-      <c r="T81">
-        <v>3.2</v>
-      </c>
-      <c r="U81">
-        <v>2.5</v>
-      </c>
-      <c r="V81">
-        <v>1.41</v>
-      </c>
-      <c r="W81">
-        <v>1.07</v>
-      </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.22</v>
-      </c>
       <c r="Z81">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA81">
+        <v>2</v>
+      </c>
+      <c r="AB81">
+        <v>1.72</v>
+      </c>
+      <c r="AC81">
+        <v>3.6</v>
+      </c>
+      <c r="AD81">
+        <v>1.25</v>
+      </c>
+      <c r="AE81">
+        <v>1.06</v>
+      </c>
+      <c r="AF81">
+        <v>1.83</v>
+      </c>
+      <c r="AG81">
+        <v>1.83</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.25</v>
+      </c>
+      <c r="AK81">
         <v>1.76</v>
-      </c>
-      <c r="AB81">
-        <v>2.05</v>
-      </c>
-      <c r="AC81">
-        <v>3.03</v>
-      </c>
-      <c r="AD81">
-        <v>1.35</v>
-      </c>
-      <c r="AE81">
-        <v>1.1</v>
-      </c>
-      <c r="AF81">
-        <v>1.93</v>
-      </c>
-      <c r="AG81">
-        <v>1.75</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.04</v>
-      </c>
-      <c r="AK81">
-        <v>2.88</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="Q82">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T82">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="U82">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z82">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA82">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AB82">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC82">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AD82">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK82">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q102">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R102">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
         <v>1.4</v>
       </c>
       <c r="T102">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U102">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z102">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="AA102">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AC102">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD102">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE102">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AG102">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK102">
         <v>1.43</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S103">
         <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U103">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="V103">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
+        <v>1.04</v>
+      </c>
+      <c r="X103">
+        <v>1.04</v>
+      </c>
+      <c r="Y103">
+        <v>1.35</v>
+      </c>
+      <c r="Z103">
+        <v>3.27</v>
+      </c>
+      <c r="AA103">
+        <v>2.07</v>
+      </c>
+      <c r="AB103">
+        <v>1.79</v>
+      </c>
+      <c r="AC103">
+        <v>3.28</v>
+      </c>
+      <c r="AD103">
+        <v>1.25</v>
+      </c>
+      <c r="AE103">
         <v>1.06</v>
       </c>
-      <c r="X103">
-        <v>1</v>
-      </c>
-      <c r="Y103">
-        <v>1.24</v>
-      </c>
-      <c r="Z103">
-        <v>3.55</v>
-      </c>
-      <c r="AA103">
-        <v>1.9</v>
-      </c>
-      <c r="AB103">
-        <v>1.84</v>
-      </c>
-      <c r="AC103">
-        <v>3.08</v>
-      </c>
-      <c r="AD103">
-        <v>1.28</v>
-      </c>
-      <c r="AE103">
-        <v>1.08</v>
-      </c>
       <c r="AF103">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK103">
         <v>1.43</v>
@@ -18248,10 +18248,10 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R110">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S110">
         <v>1.48</v>
@@ -18260,13 +18260,13 @@
         <v>2.56</v>
       </c>
       <c r="U110">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="V110">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
         <v>1.04</v>
@@ -18296,7 +18296,7 @@
         <v>1.88</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK110">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,34 +18402,34 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O111">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P111">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="Q111">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="R111">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S111">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T111">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U111">
         <v>3.5</v>
       </c>
       <c r="V111">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W111">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
         <v>1.03</v>
@@ -18441,10 +18441,10 @@
         <v>2.49</v>
       </c>
       <c r="AA111">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB111">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC111">
         <v>4.75</v>
@@ -18456,10 +18456,10 @@
         <v>1.01</v>
       </c>
       <c r="AF111">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG111">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19869,34 +19869,34 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="O120">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P120">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="Q120">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R120">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T120">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U120">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V120">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W120">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
         <v>1.04</v>
@@ -19917,7 +19917,7 @@
         <v>2.67</v>
       </c>
       <c r="AD120">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE120">
         <v>1.11</v>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK120">
         <v>1.7</v>
@@ -28677,25 +28677,25 @@
         <v>4.25</v>
       </c>
       <c r="P174">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q174">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R174">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S174">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T174">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U174">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="V174">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W174">
         <v>1.11</v>
@@ -28707,25 +28707,25 @@
         <v>1.16</v>
       </c>
       <c r="Z174">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA174">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB174">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC174">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD174">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE174">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF174">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG174">
         <v>2</v>
@@ -28744,7 +28744,7 @@
         <v>1.14</v>
       </c>
       <c r="AK174">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29501,10 +29501,10 @@
         <v>2.04</v>
       </c>
       <c r="S179">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T179">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U179">
         <v>2.65</v>
@@ -29516,7 +29516,7 @@
         <v>1.07</v>
       </c>
       <c r="X179">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y179">
         <v>1.27</v>
@@ -29537,13 +29537,13 @@
         <v>1.26</v>
       </c>
       <c r="AE179">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF179">
         <v>1.7</v>
       </c>
       <c r="AG179">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -38943,10 +38943,10 @@
         <v>4.85</v>
       </c>
       <c r="O237">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P237">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q237">
         <v>5.69</v>
@@ -38967,10 +38967,10 @@
         <v>1.4</v>
       </c>
       <c r="W237">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X237">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y237">
         <v>1.24</v>
@@ -38979,16 +38979,16 @@
         <v>3.34</v>
       </c>
       <c r="AA237">
+        <v>1.88</v>
+      </c>
+      <c r="AB237">
         <v>1.9</v>
       </c>
-      <c r="AB237">
-        <v>1.88</v>
-      </c>
       <c r="AC237">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD237">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE237">
         <v>1.07</v>
@@ -38997,7 +38997,7 @@
         <v>1.85</v>
       </c>
       <c r="AG237">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.22</v>
       </c>
       <c r="AK237">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,7 +39103,7 @@
         </is>
       </c>
       <c r="N238">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="O238">
         <v>3.35</v>
@@ -39118,16 +39118,16 @@
         <v>2.2</v>
       </c>
       <c r="S238">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T238">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="U238">
         <v>2.77</v>
       </c>
       <c r="V238">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W238">
         <v>1.08</v>
@@ -39145,7 +39145,7 @@
         <v>1.95</v>
       </c>
       <c r="AB238">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC238">
         <v>3.14</v>
@@ -39160,7 +39160,7 @@
         <v>1.82</v>
       </c>
       <c r="AG238">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>1.27</v>
       </c>
       <c r="AK238">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O239">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P239">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="Q239">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="R239">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S239">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T239">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="U239">
         <v>3</v>
       </c>
       <c r="V239">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W239">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X239">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y239">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z239">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA239">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB239">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC239">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD239">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE239">
         <v>1.04</v>
       </c>
       <c r="AF239">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG239">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>1.22</v>
       </c>
       <c r="AK239">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="O243">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P243">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q243">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="R243">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S243">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T243">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U243">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="V243">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W243">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X243">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y243">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z243">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA243">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB243">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC243">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AD243">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE243">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF243">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG243">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK243">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="O244">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P244">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q244">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="R244">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S244">
+        <v>1.43</v>
+      </c>
+      <c r="T244">
+        <v>2.65</v>
+      </c>
+      <c r="U244">
+        <v>3.02</v>
+      </c>
+      <c r="V244">
         <v>1.35</v>
       </c>
-      <c r="T244">
+      <c r="W244">
+        <v>1.07</v>
+      </c>
+      <c r="X244">
+        <v>1.02</v>
+      </c>
+      <c r="Y244">
+        <v>1.32</v>
+      </c>
+      <c r="Z244">
         <v>2.88</v>
       </c>
-      <c r="U244">
-        <v>2.7</v>
-      </c>
-      <c r="V244">
-        <v>1.4</v>
-      </c>
-      <c r="W244">
-        <v>1.04</v>
-      </c>
-      <c r="X244">
+      <c r="AA244">
+        <v>2.1</v>
+      </c>
+      <c r="AB244">
+        <v>1.67</v>
+      </c>
+      <c r="AC244">
+        <v>3.58</v>
+      </c>
+      <c r="AD244">
+        <v>1.21</v>
+      </c>
+      <c r="AE244">
         <v>1.03</v>
       </c>
-      <c r="Y244">
-        <v>1.34</v>
-      </c>
-      <c r="Z244">
-        <v>3.08</v>
-      </c>
-      <c r="AA244">
-        <v>1.95</v>
-      </c>
-      <c r="AB244">
-        <v>1.8</v>
-      </c>
-      <c r="AC244">
-        <v>3.2</v>
-      </c>
-      <c r="AD244">
-        <v>1.26</v>
-      </c>
-      <c r="AE244">
-        <v>1.06</v>
-      </c>
       <c r="AF244">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG244">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK244">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O263">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P263">
+        <v>3.75</v>
+      </c>
+      <c r="Q263">
+        <v>2.5</v>
+      </c>
+      <c r="R263">
+        <v>2.2</v>
+      </c>
+      <c r="S263">
+        <v>1.4</v>
+      </c>
+      <c r="T263">
+        <v>2.47</v>
+      </c>
+      <c r="U263">
+        <v>3.02</v>
+      </c>
+      <c r="V263">
+        <v>1.31</v>
+      </c>
+      <c r="W263">
+        <v>1.07</v>
+      </c>
+      <c r="X263">
+        <v>1.04</v>
+      </c>
+      <c r="Y263">
+        <v>1.33</v>
+      </c>
+      <c r="Z263">
         <v>2.83</v>
       </c>
-      <c r="Q263">
-        <v>2.48</v>
-      </c>
-      <c r="R263">
+      <c r="AA263">
         <v>2.09</v>
       </c>
-      <c r="S263">
-        <v>1.36</v>
-      </c>
-      <c r="T263">
-        <v>3.03</v>
-      </c>
-      <c r="U263">
-        <v>2.66</v>
-      </c>
-      <c r="V263">
-        <v>1.39</v>
-      </c>
-      <c r="W263">
-        <v>1.06</v>
-      </c>
-      <c r="X263">
-        <v>1.01</v>
-      </c>
-      <c r="Y263">
-        <v>1.25</v>
-      </c>
-      <c r="Z263">
-        <v>3.05</v>
-      </c>
-      <c r="AA263">
-        <v>1.9</v>
-      </c>
       <c r="AB263">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC263">
-        <v>3.04</v>
+        <v>3.78</v>
       </c>
       <c r="AD263">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE263">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF263">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AG263">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK263">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,80 +43504,80 @@
         </is>
       </c>
       <c r="N265">
+        <v>2.15</v>
+      </c>
+      <c r="O265">
+        <v>3.1</v>
+      </c>
+      <c r="P265">
+        <v>2.83</v>
+      </c>
+      <c r="Q265">
+        <v>2.48</v>
+      </c>
+      <c r="R265">
+        <v>2.09</v>
+      </c>
+      <c r="S265">
+        <v>1.36</v>
+      </c>
+      <c r="T265">
+        <v>3.03</v>
+      </c>
+      <c r="U265">
+        <v>2.66</v>
+      </c>
+      <c r="V265">
+        <v>1.39</v>
+      </c>
+      <c r="W265">
+        <v>1.06</v>
+      </c>
+      <c r="X265">
+        <v>1.01</v>
+      </c>
+      <c r="Y265">
+        <v>1.25</v>
+      </c>
+      <c r="Z265">
+        <v>3.05</v>
+      </c>
+      <c r="AA265">
+        <v>1.9</v>
+      </c>
+      <c r="AB265">
         <v>1.85</v>
       </c>
-      <c r="O265">
-        <v>3.25</v>
-      </c>
-      <c r="P265">
-        <v>3.75</v>
-      </c>
-      <c r="Q265">
-        <v>2.5</v>
-      </c>
-      <c r="R265">
-        <v>2.2</v>
-      </c>
-      <c r="S265">
-        <v>1.4</v>
-      </c>
-      <c r="T265">
-        <v>2.47</v>
-      </c>
-      <c r="U265">
-        <v>3.02</v>
-      </c>
-      <c r="V265">
-        <v>1.31</v>
-      </c>
-      <c r="W265">
-        <v>1.07</v>
-      </c>
-      <c r="X265">
-        <v>1.04</v>
-      </c>
-      <c r="Y265">
+      <c r="AC265">
+        <v>3.04</v>
+      </c>
+      <c r="AD265">
+        <v>1.29</v>
+      </c>
+      <c r="AE265">
+        <v>1.08</v>
+      </c>
+      <c r="AF265">
+        <v>1.68</v>
+      </c>
+      <c r="AG265">
+        <v>2.04</v>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ265">
         <v>1.33</v>
       </c>
-      <c r="Z265">
-        <v>2.83</v>
-      </c>
-      <c r="AA265">
-        <v>2.09</v>
-      </c>
-      <c r="AB265">
-        <v>1.66</v>
-      </c>
-      <c r="AC265">
-        <v>3.78</v>
-      </c>
-      <c r="AD265">
-        <v>1.21</v>
-      </c>
-      <c r="AE265">
-        <v>1.04</v>
-      </c>
-      <c r="AF265">
-        <v>1.95</v>
-      </c>
-      <c r="AG265">
-        <v>1.77</v>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ265">
-        <v>1.22</v>
-      </c>
       <c r="AK265">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -45140,10 +45140,10 @@
         <v>3.1</v>
       </c>
       <c r="P275">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Q275">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R275">
         <v>2.1</v>
@@ -45152,7 +45152,7 @@
         <v>1.4</v>
       </c>
       <c r="T275">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U275">
         <v>2.95</v>
@@ -45164,7 +45164,7 @@
         <v>1.04</v>
       </c>
       <c r="X275">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
         <v>1.31</v>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK275">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45300,10 +45300,10 @@
         <v>1.75</v>
       </c>
       <c r="O276">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P276">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q276">
         <v>2.3</v>
@@ -45348,10 +45348,10 @@
         <v>1.33</v>
       </c>
       <c r="AE276">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF276">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG276">
         <v>1.92</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O278">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P278">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="Q278">
         <v>2.5</v>
@@ -45638,25 +45638,25 @@
         <v>1.91</v>
       </c>
       <c r="S278">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T278">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U278">
         <v>3.75</v>
       </c>
       <c r="V278">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W278">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X278">
         <v>1.07</v>
       </c>
       <c r="Y278">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="Z278">
         <v>2.45</v>
@@ -45668,13 +45668,13 @@
         <v>1.46</v>
       </c>
       <c r="AC278">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="AD278">
         <v>1.12</v>
       </c>
       <c r="AE278">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF278">
         <v>2.4</v>
@@ -45792,7 +45792,7 @@
         <v>2.8</v>
       </c>
       <c r="P279">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>2.97</v>
       </c>
       <c r="AD281">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE281">
         <v>1.06</v>
@@ -47416,7 +47416,7 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="O289">
         <v>2.62</v>
@@ -47446,16 +47446,16 @@
         <v>1.03</v>
       </c>
       <c r="X289">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y289">
         <v>1.57</v>
       </c>
       <c r="Z289">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AA289">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AB289">
         <v>1.42</v>
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK289">
         <v>1.75</v>
@@ -47588,10 +47588,10 @@
         <v>2.5</v>
       </c>
       <c r="Q290">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R290">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S290">
         <v>1.54</v>
@@ -47618,16 +47618,16 @@
         <v>2.5</v>
       </c>
       <c r="AA290">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AB290">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC290">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD290">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE290">
         <v>1</v>
@@ -49375,28 +49375,28 @@
         <v>2.2</v>
       </c>
       <c r="O301">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="P301">
         <v>3.3</v>
       </c>
       <c r="Q301">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R301">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S301">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T301">
         <v>2.2</v>
       </c>
       <c r="U301">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="V301">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W301">
         <v>1.03</v>
@@ -49417,19 +49417,19 @@
         <v>1.36</v>
       </c>
       <c r="AC301">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="AD301">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE301">
         <v>1.02</v>
       </c>
       <c r="AF301">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG301">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK301">
         <v>1.57</v>
@@ -49544,7 +49544,7 @@
         <v>3.9</v>
       </c>
       <c r="Q302">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R302">
         <v>1.95</v>
@@ -49553,7 +49553,7 @@
         <v>1.55</v>
       </c>
       <c r="T302">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="U302">
         <v>3.5</v>
@@ -49589,10 +49589,10 @@
         <v>1</v>
       </c>
       <c r="AF302">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG302">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK302">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49707,10 +49707,10 @@
         <v>4.1</v>
       </c>
       <c r="Q303">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R303">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S303">
         <v>1.57</v>
@@ -49743,7 +49743,7 @@
         <v>1.3</v>
       </c>
       <c r="AC303">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD303">
         <v>1.05</v>
@@ -49752,10 +49752,10 @@
         <v>1.02</v>
       </c>
       <c r="AF303">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AG303">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49864,10 +49864,10 @@
         <v>2.3</v>
       </c>
       <c r="O304">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="P304">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q304">
         <v>2.26</v>
@@ -49876,10 +49876,10 @@
         <v>1.84</v>
       </c>
       <c r="S304">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T304">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U304">
         <v>3.5</v>
@@ -49897,7 +49897,7 @@
         <v>1.53</v>
       </c>
       <c r="Z304">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AA304">
         <v>2.63</v>
@@ -49906,7 +49906,7 @@
         <v>1.47</v>
       </c>
       <c r="AC304">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD304">
         <v>1.15</v>
@@ -49915,10 +49915,10 @@
         <v>1</v>
       </c>
       <c r="AF304">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AG304">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>1.14</v>
       </c>
       <c r="AK304">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50842,49 +50842,49 @@
         <v>1.5</v>
       </c>
       <c r="O310">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P310">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q310">
         <v>2.1</v>
       </c>
       <c r="R310">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S310">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T310">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="U310">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V310">
         <v>1.3</v>
       </c>
       <c r="W310">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X310">
         <v>1.03</v>
       </c>
       <c r="Y310">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z310">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AA310">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AB310">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC310">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AD310">
         <v>1.17</v>
@@ -50893,10 +50893,10 @@
         <v>1.02</v>
       </c>
       <c r="AF310">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AG310">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AK310">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,28 +51002,28 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O311">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P311">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="Q311">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R311">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S311">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T311">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U311">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V311">
         <v>1.33</v>
@@ -51032,34 +51032,34 @@
         <v>1.06</v>
       </c>
       <c r="X311">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y311">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z311">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA311">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB311">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC311">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD311">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE311">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF311">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG311">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK311">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51165,34 +51165,34 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O312">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P312">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="Q312">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R312">
         <v>1.94</v>
       </c>
       <c r="S312">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T312">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="U312">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="V312">
         <v>1.25</v>
       </c>
       <c r="W312">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X312">
         <v>1.07</v>
@@ -51204,7 +51204,7 @@
         <v>2.44</v>
       </c>
       <c r="AA312">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="AB312">
         <v>1.5</v>
@@ -51222,7 +51222,7 @@
         <v>2</v>
       </c>
       <c r="AG312">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>1.57</v>
       </c>
       <c r="W314">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X314">
         <v>1.01</v>
@@ -51530,13 +51530,13 @@
         <v>5.05</v>
       </c>
       <c r="AA314">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB314">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC314">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="AD314">
         <v>1.47</v>
@@ -51564,7 +51564,7 @@
         <v>1.8</v>
       </c>
       <c r="AK314">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51657,10 +51657,10 @@
         <v>2.5</v>
       </c>
       <c r="O315">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P315">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O316">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="P316">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q316">
         <v>3.4</v>
@@ -51832,16 +51832,16 @@
         <v>1.95</v>
       </c>
       <c r="S316">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T316">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="U316">
         <v>3.75</v>
       </c>
       <c r="V316">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W316">
         <v>1.04</v>
@@ -51859,7 +51859,7 @@
         <v>2.55</v>
       </c>
       <c r="AB316">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC316">
         <v>5.93</v>
@@ -51874,7 +51874,7 @@
         <v>2.2</v>
       </c>
       <c r="AG316">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK316">
         <v>1.36</v>
@@ -52001,10 +52001,10 @@
         <v>3.9</v>
       </c>
       <c r="U317">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V317">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W317">
         <v>1.11</v>
@@ -52031,13 +52031,13 @@
         <v>1.61</v>
       </c>
       <c r="AE317">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF317">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AG317">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52152,25 +52152,25 @@
         <v>0</v>
       </c>
       <c r="Q318">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R318">
         <v>2.28</v>
       </c>
       <c r="S318">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T318">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U318">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="V318">
         <v>1.47</v>
       </c>
       <c r="W318">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X318">
         <v>1</v>
@@ -52185,7 +52185,7 @@
         <v>1.67</v>
       </c>
       <c r="AB318">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC318">
         <v>2.62</v>
@@ -52200,7 +52200,7 @@
         <v>1.55</v>
       </c>
       <c r="AG318">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AK318">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -53447,7 +53447,7 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O326">
         <v>3.75</v>
@@ -53462,19 +53462,19 @@
         <v>2.35</v>
       </c>
       <c r="S326">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T326">
         <v>3.05</v>
       </c>
       <c r="U326">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V326">
         <v>1.47</v>
       </c>
       <c r="W326">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X326">
         <v>1.04</v>
@@ -53501,10 +53501,10 @@
         <v>1.15</v>
       </c>
       <c r="AF326">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG326">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK326">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53655,7 +53655,7 @@
         <v>2.02</v>
       </c>
       <c r="AC327">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AD327">
         <v>1.4</v>
@@ -54304,7 +54304,7 @@
         <v>1.7</v>
       </c>
       <c r="AB331">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC331">
         <v>2.74</v>
@@ -54316,10 +54316,10 @@
         <v>1.1</v>
       </c>
       <c r="AF331">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG331">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -656,13 +656,13 @@
         <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
         <v>1.53</v>
       </c>
       <c r="W2">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,7 +671,7 @@
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="AA2">
         <v>1.6</v>
@@ -680,13 +680,13 @@
         <v>2.3</v>
       </c>
       <c r="AC2">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD2">
         <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF2">
         <v>1.48</v>
@@ -1456,7 +1456,7 @@
         <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
         <v>3.54</v>
@@ -1468,19 +1468,19 @@
         <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="U7">
         <v>2.75</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.22</v>
@@ -1504,10 +1504,10 @@
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2.43</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
         <v>1.39</v>
@@ -1658,16 +1658,16 @@
         <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
         <v>1.85</v>
@@ -1686,7 +1686,7 @@
         <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1803,7 +1803,7 @@
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1833,7 +1833,7 @@
         <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
         <v>2.17</v>
@@ -1957,7 +1957,7 @@
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1975,13 +1975,13 @@
         <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="AA10">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
         <v>3</v>
@@ -1990,7 +1990,7 @@
         <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
         <v>1.69</v>
@@ -2105,7 +2105,7 @@
         <v>3.05</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
         <v>2.13</v>
@@ -2123,10 +2123,10 @@
         <v>2.77</v>
       </c>
       <c r="U11">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2147,7 +2147,7 @@
         <v>1.76</v>
       </c>
       <c r="AC11">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD11">
         <v>1.27</v>
@@ -2175,7 +2175,7 @@
         <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="O12">
         <v>3.53</v>
@@ -2283,7 +2283,7 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="U12">
         <v>2.45</v>
@@ -2301,7 +2301,7 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.85</v>
+        <v>4.16</v>
       </c>
       <c r="AA12">
         <v>1.8</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q21">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R21">
         <v>2.1</v>
@@ -3750,7 +3750,7 @@
         <v>1.41</v>
       </c>
       <c r="T21">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="U21">
         <v>2.88</v>
@@ -3771,10 +3771,10 @@
         <v>3.25</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
         <v>3.44</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="Q22">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3925,7 +3925,7 @@
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.24</v>
@@ -3937,7 +3937,7 @@
         <v>1.86</v>
       </c>
       <c r="AB22">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC22">
         <v>2.94</v>
@@ -4061,13 +4061,13 @@
         <v>2.3</v>
       </c>
       <c r="O23">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R23">
         <v>1.91</v>
@@ -4091,7 +4091,7 @@
         <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z23">
         <v>2.8</v>
@@ -4109,7 +4109,7 @@
         <v>1.18</v>
       </c>
       <c r="AE23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
         <v>1.85</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O24">
         <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -4242,7 +4242,7 @@
         <v>2.91</v>
       </c>
       <c r="U24">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4278,7 +4278,7 @@
         <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O25">
         <v>3.8</v>
       </c>
       <c r="P25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R25">
         <v>2.26</v>
@@ -4402,16 +4402,16 @@
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4423,10 +4423,10 @@
         <v>3.9</v>
       </c>
       <c r="AA25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB25">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC25">
         <v>2.74</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,46 +4547,46 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
         <v>2.97</v>
       </c>
       <c r="P26">
-        <v>2.93</v>
+        <v>3.23</v>
       </c>
       <c r="Q26">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S26">
         <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U26">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
         <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
         <v>1.75</v>
@@ -4731,10 +4731,10 @@
         <v>2.36</v>
       </c>
       <c r="U27">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
         <v>1</v>
@@ -4746,16 +4746,16 @@
         <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AA27">
         <v>2.4</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="AD27">
         <v>1.15</v>
@@ -4764,10 +4764,10 @@
         <v>1</v>
       </c>
       <c r="AF27">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>2.38</v>
       </c>
       <c r="R30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S30">
         <v>1.34</v>
@@ -5220,7 +5220,7 @@
         <v>2.85</v>
       </c>
       <c r="U30">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V30">
         <v>1.36</v>
@@ -5232,19 +5232,19 @@
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA30">
         <v>2.13</v>
       </c>
       <c r="AB30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC30">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="AD30">
         <v>1.22</v>
@@ -5253,7 +5253,7 @@
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG30">
         <v>1.83</v>
@@ -5365,7 +5365,7 @@
         <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
         <v>3.45</v>
@@ -5407,7 +5407,7 @@
         <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD31">
         <v>1.43</v>
@@ -5419,7 +5419,7 @@
         <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5528,10 +5528,10 @@
         <v>1.65</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
         <v>2.21</v>
@@ -5540,7 +5540,7 @@
         <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T32">
         <v>2.56</v>
@@ -5549,19 +5549,19 @@
         <v>3</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
         <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z32">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AA32">
         <v>2.1</v>
@@ -5691,46 +5691,46 @@
         <v>1.69</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="Q33">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S33">
         <v>1.35</v>
       </c>
       <c r="T33">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U33">
         <v>2.43</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC33">
         <v>3.1</v>
@@ -5742,10 +5742,10 @@
         <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>1.66</v>
       </c>
       <c r="O45">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P45">
         <v>4.8</v>
@@ -7659,10 +7659,10 @@
         <v>2.3</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
         <v>2.6</v>
@@ -7671,7 +7671,7 @@
         <v>1.44</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
         <v>1.02</v>
@@ -7686,13 +7686,13 @@
         <v>1.72</v>
       </c>
       <c r="AB45">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC45">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AD45">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE45">
         <v>1.11</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>2.09</v>
       </c>
       <c r="AB54">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC54">
         <v>3.44</v>
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
       <c r="Q57">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R57">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
         <v>1.36</v>
       </c>
       <c r="T57">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U57">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
         <v>1.46</v>
@@ -9633,19 +9633,19 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
-        <v>4.06</v>
+        <v>4.01</v>
       </c>
       <c r="AA57">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB57">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC57">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AD57">
         <v>1.41</v>
@@ -9654,10 +9654,10 @@
         <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG57">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10110,31 +10110,31 @@
         <v>2.6</v>
       </c>
       <c r="U60">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="V60">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
         <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z60">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA60">
         <v>2.2</v>
       </c>
       <c r="AB60">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC60">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AD60">
         <v>1.19</v>
@@ -10143,10 +10143,10 @@
         <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG60">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>6.15</v>
       </c>
       <c r="Q61">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R61">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S61">
         <v>1.22</v>
@@ -10273,7 +10273,7 @@
         <v>3.75</v>
       </c>
       <c r="U61">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="V61">
         <v>1.6</v>
@@ -10297,10 +10297,10 @@
         <v>2.38</v>
       </c>
       <c r="AC61">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD61">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE61">
         <v>1.19</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10614,16 +10614,16 @@
         <v>1.17</v>
       </c>
       <c r="Z63">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="AA63">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB63">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="AC63">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD63">
         <v>1.56</v>
@@ -10632,7 +10632,7 @@
         <v>1.2</v>
       </c>
       <c r="AF63">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG63">
         <v>2.4</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O64">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P64">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q64">
         <v>3</v>
       </c>
       <c r="R64">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="S64">
         <v>1.23</v>
       </c>
       <c r="T64">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U64">
         <v>2.1</v>
@@ -10768,13 +10768,13 @@
         <v>1.65</v>
       </c>
       <c r="W64">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z64">
         <v>5.35</v>
@@ -10789,7 +10789,7 @@
         <v>2.19</v>
       </c>
       <c r="AD64">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE64">
         <v>1.22</v>
@@ -10922,7 +10922,7 @@
         <v>1.24</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
         <v>2.1</v>
@@ -10931,7 +10931,7 @@
         <v>1.65</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
         <v>3.5</v>
@@ -11079,19 +11079,19 @@
         <v>2.8</v>
       </c>
       <c r="R66">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
         <v>3.1</v>
       </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
         <v>1.11</v>
@@ -11103,7 +11103,7 @@
         <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="AA66">
         <v>1.77</v>
@@ -11112,13 +11112,13 @@
         <v>2.05</v>
       </c>
       <c r="AC66">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AD66">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
         <v>1.57</v>
@@ -11140,7 +11140,7 @@
         <v>1.36</v>
       </c>
       <c r="AK66">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11245,49 +11245,49 @@
         <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U67">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V67">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC67">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AD67">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE67">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG67">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11399,10 +11399,10 @@
         <v>3.75</v>
       </c>
       <c r="P68">
-        <v>5.4</v>
+        <v>4.89</v>
       </c>
       <c r="Q68">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R68">
         <v>2.17</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12555,13 +12555,13 @@
         <v>3.21</v>
       </c>
       <c r="U75">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V75">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12570,22 +12570,22 @@
         <v>1.17</v>
       </c>
       <c r="Z75">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="AA75">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB75">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC75">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD75">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
         <v>1.93</v>
@@ -12607,7 +12607,7 @@
         <v>1.18</v>
       </c>
       <c r="AK75">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="O76">
         <v>3.15</v>
@@ -13240,7 +13240,7 @@
         <v>1.04</v>
       </c>
       <c r="AF79">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG79">
         <v>1.87</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK79">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13524,13 +13524,13 @@
         <v>2.63</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S81">
         <v>1.36</v>
       </c>
       <c r="T81">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="U81">
         <v>2.88</v>
@@ -13554,10 +13554,10 @@
         <v>2</v>
       </c>
       <c r="AB81">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC81">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD81">
         <v>1.25</v>
@@ -13566,10 +13566,10 @@
         <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG81">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK81">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>7.3</v>
       </c>
       <c r="Q82">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R82">
         <v>2.31</v>
@@ -13708,16 +13708,16 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA82">
         <v>1.75</v>
       </c>
       <c r="AB82">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC82">
         <v>2.81</v>
@@ -13729,10 +13729,10 @@
         <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O83">
         <v>2.95</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,16 +17750,16 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q107">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R107">
         <v>2.18</v>
@@ -17786,22 +17786,22 @@
         <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA107">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB107">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC107">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD107">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE107">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF107">
         <v>1.53</v>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK107">
         <v>1.91</v>
@@ -18565,65 +18565,65 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P112">
         <v>4.4</v>
       </c>
       <c r="Q112">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R112">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S112">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U112">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z112">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="AA112">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB112">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC112">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE112">
         <v>1.06</v>
       </c>
       <c r="AF112">
+        <v>1.86</v>
+      </c>
+      <c r="AG112">
         <v>1.84</v>
       </c>
-      <c r="AG112">
-        <v>1.86</v>
-      </c>
       <c r="AH112" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
         <v>2.11</v>
@@ -19054,34 +19054,34 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="Q115">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R115">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="S115">
         <v>1.07</v>
       </c>
       <c r="T115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U115">
         <v>1.5</v>
       </c>
       <c r="V115">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="W115">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -19090,7 +19090,7 @@
         <v>1.04</v>
       </c>
       <c r="Z115">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA115">
         <v>1.14</v>
@@ -19111,7 +19111,7 @@
         <v>2</v>
       </c>
       <c r="AG115">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.01</v>
       </c>
       <c r="AK115">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O118">
         <v>3.3</v>
       </c>
       <c r="P118">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -19564,13 +19564,13 @@
         <v>3.25</v>
       </c>
       <c r="U118">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V118">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X118">
         <v>1.04</v>
@@ -19588,16 +19588,16 @@
         <v>2.15</v>
       </c>
       <c r="AC118">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AD118">
         <v>1.45</v>
       </c>
       <c r="AE118">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF118">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG118">
         <v>2.25</v>
@@ -19616,7 +19616,7 @@
         <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20856,7 +20856,7 @@
         <v>3.01</v>
       </c>
       <c r="Q126">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="R126">
         <v>2.35</v>
@@ -20871,16 +20871,16 @@
         <v>2</v>
       </c>
       <c r="V126">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W126">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X126">
         <v>1</v>
       </c>
       <c r="Y126">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z126">
         <v>5.75</v>
@@ -20895,16 +20895,16 @@
         <v>2</v>
       </c>
       <c r="AD126">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE126">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF126">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG126">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="O134">
         <v>3.3</v>
@@ -22160,10 +22160,10 @@
         <v>2.6</v>
       </c>
       <c r="Q134">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R134">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S134">
         <v>1.32</v>
@@ -22172,13 +22172,13 @@
         <v>3</v>
       </c>
       <c r="U134">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V134">
         <v>1.46</v>
       </c>
       <c r="W134">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X134">
         <v>1.05</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q136">
         <v>2.7</v>
@@ -22498,10 +22498,10 @@
         <v>2.83</v>
       </c>
       <c r="U136">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V136">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W136">
         <v>1.05</v>
@@ -22534,7 +22534,7 @@
         <v>1.77</v>
       </c>
       <c r="AG136">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK136">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22996,7 +22996,7 @@
         <v>1.04</v>
       </c>
       <c r="X139">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y139">
         <v>1.47</v>
@@ -23023,7 +23023,7 @@
         <v>2.13</v>
       </c>
       <c r="AG139">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O143">
         <v>3.25</v>
@@ -23633,10 +23633,10 @@
         <v>2.05</v>
       </c>
       <c r="S143">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T143">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U143">
         <v>3.05</v>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK143">
         <v>1.84</v>
@@ -23781,25 +23781,25 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O144">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
       </c>
       <c r="R144">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S144">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T144">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U144">
         <v>2.25</v>
@@ -23808,7 +23808,7 @@
         <v>1.57</v>
       </c>
       <c r="W144">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X144">
         <v>1.02</v>
@@ -23823,13 +23823,13 @@
         <v>1.6</v>
       </c>
       <c r="AB144">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="AC144">
         <v>2.6</v>
       </c>
       <c r="AD144">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE144">
         <v>1.16</v>
@@ -26552,16 +26552,16 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O161">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P161">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q161">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R161">
         <v>2.5</v>
@@ -26579,16 +26579,16 @@
         <v>1.5</v>
       </c>
       <c r="W161">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X161">
         <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z161">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA161">
         <v>1.5</v>
@@ -26603,7 +26603,7 @@
         <v>1.44</v>
       </c>
       <c r="AE161">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF161">
         <v>1.62</v>
@@ -26622,7 +26622,7 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK161">
         <v>3.1</v>
@@ -30627,22 +30627,22 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O186">
         <v>3.36</v>
       </c>
       <c r="P186">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q186">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R186">
         <v>2.12</v>
       </c>
       <c r="S186">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T186">
         <v>3.26</v>
@@ -30700,7 +30700,7 @@
         <v>1.57</v>
       </c>
       <c r="AK186">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O209">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P209">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -40244,34 +40244,34 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="O245">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P245">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="Q245">
         <v>2</v>
       </c>
       <c r="R245">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="S245">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T245">
         <v>3.3</v>
       </c>
       <c r="U245">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V245">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W245">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X245">
         <v>1.03</v>
@@ -40280,7 +40280,7 @@
         <v>1.2</v>
       </c>
       <c r="Z245">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="AA245">
         <v>1.66</v>
@@ -40289,13 +40289,13 @@
         <v>2.15</v>
       </c>
       <c r="AC245">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AD245">
         <v>1.52</v>
       </c>
       <c r="AE245">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF245">
         <v>1.67</v>
@@ -42040,58 +42040,58 @@
         <v>1.91</v>
       </c>
       <c r="O256">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P256">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q256">
         <v>2.38</v>
       </c>
       <c r="R256">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S256">
         <v>1.33</v>
       </c>
       <c r="T256">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="U256">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="V256">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W256">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X256">
         <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z256">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA256">
         <v>1.8</v>
       </c>
       <c r="AB256">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC256">
         <v>2.95</v>
       </c>
       <c r="AD256">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE256">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF256">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG256">
         <v>2.05</v>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK256">
         <v>1.85</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="O263">
         <v>3.3</v>
       </c>
       <c r="P263">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="Q263">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="R263">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="S263">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T263">
-        <v>2.78</v>
+        <v>3.11</v>
       </c>
       <c r="U263">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V263">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W263">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X263">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y263">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z263">
-        <v>3.2</v>
+        <v>3.69</v>
       </c>
       <c r="AA263">
         <v>1.85</v>
       </c>
       <c r="AB263">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC263">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AD263">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE263">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF263">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG263">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK263">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O264">
         <v>3.3</v>
       </c>
       <c r="P264">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="Q264">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="R264">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="S264">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T264">
-        <v>3.11</v>
+        <v>2.78</v>
       </c>
       <c r="U264">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V264">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W264">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X264">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z264">
-        <v>3.69</v>
+        <v>3.2</v>
       </c>
       <c r="AA264">
         <v>1.85</v>
       </c>
       <c r="AB264">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC264">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD264">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE264">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF264">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG264">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK264">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O269">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P269">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q269">
         <v>3</v>
@@ -44645,16 +44645,16 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O272">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P272">
         <v>2.15</v>
       </c>
       <c r="Q272">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="R272">
         <v>2.12</v>
@@ -44663,16 +44663,16 @@
         <v>1.32</v>
       </c>
       <c r="T272">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U272">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V272">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W272">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X272">
         <v>1.03</v>
@@ -44681,28 +44681,28 @@
         <v>1.23</v>
       </c>
       <c r="Z272">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA272">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB272">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC272">
         <v>2.95</v>
       </c>
       <c r="AD272">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE272">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF272">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AG272">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AK272">
         <v>1.31</v>
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O274">
         <v>3.1</v>
@@ -44980,13 +44980,13 @@
         <v>2.35</v>
       </c>
       <c r="Q274">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R274">
         <v>2.1</v>
       </c>
       <c r="S274">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T274">
         <v>2.75</v>
@@ -44998,7 +44998,7 @@
         <v>1.34</v>
       </c>
       <c r="W274">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X274">
         <v>1.03</v>
@@ -45007,16 +45007,16 @@
         <v>1.31</v>
       </c>
       <c r="Z274">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AA274">
         <v>2.05</v>
       </c>
       <c r="AB274">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC274">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD274">
         <v>1.27</v>
@@ -45028,7 +45028,7 @@
         <v>1.77</v>
       </c>
       <c r="AG274">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45300,10 +45300,10 @@
         <v>2</v>
       </c>
       <c r="O276">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P276">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="Q276">
         <v>2.66</v>
@@ -45330,10 +45330,10 @@
         <v>1.02</v>
       </c>
       <c r="Y276">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z276">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="AA276">
         <v>2.01</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,80 +47253,80 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="O288">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P288">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q288">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="R288">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="S288">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T288">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U288">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V288">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W288">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X288">
         <v>1.07</v>
       </c>
       <c r="Y288">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z288">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AA288">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AB288">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC288">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD288">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE288">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF288">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG288">
+        <v>1.58</v>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ288">
+        <v>1.36</v>
+      </c>
+      <c r="AK288">
         <v>1.69</v>
-      </c>
-      <c r="AH288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ288">
-        <v>1.4</v>
-      </c>
-      <c r="AK288">
-        <v>1.36</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="O289">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P289">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q289">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R289">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S289">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="T289">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U289">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V289">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W289">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X289">
         <v>1.07</v>
       </c>
       <c r="Y289">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z289">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AA289">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB289">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC289">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD289">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF289">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG289">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
+        <v>1.4</v>
+      </c>
+      <c r="AK289">
         <v>1.36</v>
-      </c>
-      <c r="AK289">
-        <v>1.69</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O305">
         <v>4.05</v>
       </c>
       <c r="P305">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q305">
         <v>1.86</v>
@@ -50060,25 +50060,25 @@
         <v>1.19</v>
       </c>
       <c r="Z305">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="AA305">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB305">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC305">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD305">
         <v>1.36</v>
       </c>
       <c r="AE305">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF305">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG305">
         <v>1.91</v>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK305">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AL305">
         <v>0</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q9">
-        <v>3.76</v>
+        <v>2.33</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="U9">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
         <v>1.44</v>
@@ -1809,31 +1809,31 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="AA9">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB9">
+        <v>2</v>
+      </c>
+      <c r="AC9">
+        <v>3</v>
+      </c>
+      <c r="AD9">
+        <v>1.39</v>
+      </c>
+      <c r="AE9">
+        <v>1.09</v>
+      </c>
+      <c r="AF9">
+        <v>1.69</v>
+      </c>
+      <c r="AG9">
         <v>2.05</v>
-      </c>
-      <c r="AC9">
-        <v>2.88</v>
-      </c>
-      <c r="AD9">
-        <v>1.4</v>
-      </c>
-      <c r="AE9">
-        <v>1.12</v>
-      </c>
-      <c r="AF9">
-        <v>1.6</v>
-      </c>
-      <c r="AG9">
-        <v>2.19</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="O10">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="Q10">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.8</v>
+        <v>4.24</v>
       </c>
       <c r="AA10">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
         <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AK10">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P11">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB11">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="AC11">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
+        <v>1.67</v>
+      </c>
+      <c r="AG11">
+        <v>2.1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.65</v>
       </c>
-      <c r="AG11">
-        <v>2.15</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.83</v>
-      </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>2.33</v>
+        <v>3.76</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2467,10 +2467,10 @@
         <v>2.66</v>
       </c>
       <c r="AA13">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
         <v>4.25</v>
@@ -2485,7 +2485,7 @@
         <v>1.95</v>
       </c>
       <c r="AG13">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
         <v>1.63</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O35">
         <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q35">
         <v>2.79</v>
@@ -6029,7 +6029,7 @@
         <v>2.04</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T35">
         <v>2.56</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
         <v>1.57</v>
@@ -6186,7 +6186,7 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="R36">
         <v>2.25</v>
@@ -6201,7 +6201,7 @@
         <v>2.56</v>
       </c>
       <c r="V36">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
         <v>1.09</v>
@@ -6219,7 +6219,7 @@
         <v>1.76</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC36">
         <v>2.88</v>
@@ -6234,7 +6234,7 @@
         <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,52 +6503,52 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="O38">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q38">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R38">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="S38">
         <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U38">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V38">
         <v>1.64</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
         <v>5.5</v>
       </c>
       <c r="AA38">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC38">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AD38">
         <v>1.65</v>
@@ -6557,10 +6557,10 @@
         <v>1.23</v>
       </c>
       <c r="AF38">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>4.2</v>
       </c>
       <c r="Q46">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
         <v>1.28</v>
@@ -7846,7 +7846,7 @@
         <v>3.72</v>
       </c>
       <c r="AA46">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB46">
         <v>1.97</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -9117,10 +9117,10 @@
         <v>3.2</v>
       </c>
       <c r="P54">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="R54">
         <v>1.98</v>
@@ -9144,25 +9144,25 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z54">
-        <v>3.35</v>
+        <v>2.91</v>
       </c>
       <c r="AA54">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB54">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC54">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AD54">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE54">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF54">
         <v>1.77</v>
@@ -9184,7 +9184,7 @@
         <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P56">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O64">
         <v>3.65</v>
@@ -10753,7 +10753,7 @@
         <v>3</v>
       </c>
       <c r="R64">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="S64">
         <v>1.22</v>
@@ -10774,7 +10774,7 @@
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z64">
         <v>5.35</v>
@@ -10789,10 +10789,10 @@
         <v>2.2</v>
       </c>
       <c r="AD64">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE64">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF64">
         <v>1.44</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q65">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S65">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="U65">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V65">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="W65">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>5.6</v>
+        <v>3.92</v>
       </c>
       <c r="AA65">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AB65">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC65">
-        <v>2.07</v>
+        <v>2.58</v>
       </c>
       <c r="AD65">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AE65">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q66">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R66">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="U66">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="V66">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X66">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>3.92</v>
+        <v>5.6</v>
       </c>
       <c r="AA66">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AB66">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AC66">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="AD66">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF66">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12383,7 +12383,7 @@
         <v>2.57</v>
       </c>
       <c r="R74">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S74">
         <v>1.2</v>
@@ -12398,7 +12398,7 @@
         <v>1.65</v>
       </c>
       <c r="W74">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12413,10 +12413,10 @@
         <v>1.44</v>
       </c>
       <c r="AB74">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AC74">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="AD74">
         <v>1.84</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12697,25 +12697,25 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O76">
         <v>3.15</v>
       </c>
       <c r="P76">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="Q76">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="R76">
         <v>1.93</v>
       </c>
       <c r="S76">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T76">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U76">
         <v>3.2</v>
@@ -12727,7 +12727,7 @@
         <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
         <v>1.4</v>
@@ -12745,10 +12745,10 @@
         <v>3.78</v>
       </c>
       <c r="AD76">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF76">
         <v>2</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="O81">
-        <v>4.3</v>
+        <v>3.03</v>
       </c>
       <c r="P81">
-        <v>7.2</v>
+        <v>3.88</v>
       </c>
       <c r="Q81">
-        <v>1.89</v>
+        <v>2.63</v>
       </c>
       <c r="R81">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="S81">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="T81">
-        <v>3.18</v>
+        <v>2.57</v>
       </c>
       <c r="U81">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V81">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z81">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA81">
+        <v>2</v>
+      </c>
+      <c r="AB81">
+        <v>1.73</v>
+      </c>
+      <c r="AC81">
+        <v>3.34</v>
+      </c>
+      <c r="AD81">
+        <v>1.25</v>
+      </c>
+      <c r="AE81">
+        <v>1.05</v>
+      </c>
+      <c r="AF81">
+        <v>1.81</v>
+      </c>
+      <c r="AG81">
+        <v>1.86</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.26</v>
+      </c>
+      <c r="AK81">
         <v>1.75</v>
-      </c>
-      <c r="AB81">
-        <v>1.94</v>
-      </c>
-      <c r="AC81">
-        <v>2.81</v>
-      </c>
-      <c r="AD81">
-        <v>1.37</v>
-      </c>
-      <c r="AE81">
-        <v>1.1</v>
-      </c>
-      <c r="AF81">
-        <v>1.96</v>
-      </c>
-      <c r="AG81">
-        <v>1.75</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.03</v>
-      </c>
-      <c r="AK81">
-        <v>2.8</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.87</v>
+        <v>1.37</v>
       </c>
       <c r="O82">
-        <v>3.03</v>
+        <v>4.3</v>
       </c>
       <c r="P82">
-        <v>3.88</v>
+        <v>7.2</v>
       </c>
       <c r="Q82">
-        <v>2.63</v>
+        <v>1.89</v>
       </c>
       <c r="R82">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="S82">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="T82">
-        <v>2.57</v>
+        <v>3.18</v>
       </c>
       <c r="U82">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W82">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA82">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB82">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AC82">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AD82">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AG82">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AK82">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14828,13 +14828,13 @@
         <v>2.85</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S89">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U89">
         <v>2.69</v>
@@ -14843,7 +14843,7 @@
         <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -14861,7 +14861,7 @@
         <v>1.87</v>
       </c>
       <c r="AC89">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD89">
         <v>1.3</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK89">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P94">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -15646,10 +15646,10 @@
         <v>1.87</v>
       </c>
       <c r="S94">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U94">
         <v>3</v>
@@ -15704,7 +15704,7 @@
         <v>1.35</v>
       </c>
       <c r="AK94">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,10 +15803,10 @@
         <v>1.85</v>
       </c>
       <c r="Q95">
-        <v>4.88</v>
+        <v>4.33</v>
       </c>
       <c r="R95">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S95">
         <v>1.41</v>
@@ -15836,7 +15836,7 @@
         <v>1.98</v>
       </c>
       <c r="AB95">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC95">
         <v>3.7</v>
@@ -15848,7 +15848,7 @@
         <v>1.05</v>
       </c>
       <c r="AF95">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG95">
         <v>1.85</v>
@@ -16301,7 +16301,7 @@
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="U98">
         <v>2.75</v>
@@ -17267,7 +17267,7 @@
         <v>3.2</v>
       </c>
       <c r="P104">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="Q104">
         <v>2.36</v>
@@ -17276,19 +17276,19 @@
         <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U104">
         <v>3.2</v>
       </c>
       <c r="V104">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W104">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X104">
         <v>1.06</v>
@@ -17309,13 +17309,13 @@
         <v>3.82</v>
       </c>
       <c r="AD104">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE104">
         <v>1.03</v>
       </c>
       <c r="AF104">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG104">
         <v>1.7</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P105">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q105">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="R105">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S105">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T105">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U105">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="V105">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
+        <v>1.22</v>
+      </c>
+      <c r="Z105">
+        <v>3.7</v>
+      </c>
+      <c r="AA105">
+        <v>1.79</v>
+      </c>
+      <c r="AB105">
+        <v>1.92</v>
+      </c>
+      <c r="AC105">
+        <v>3</v>
+      </c>
+      <c r="AD105">
+        <v>1.37</v>
+      </c>
+      <c r="AE105">
+        <v>1.08</v>
+      </c>
+      <c r="AF105">
+        <v>1.74</v>
+      </c>
+      <c r="AG105">
+        <v>2</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.2</v>
       </c>
-      <c r="Z105">
-        <v>3.8</v>
-      </c>
-      <c r="AA105">
-        <v>1.73</v>
-      </c>
-      <c r="AB105">
-        <v>2</v>
-      </c>
-      <c r="AC105">
-        <v>2.92</v>
-      </c>
-      <c r="AD105">
-        <v>1.33</v>
-      </c>
-      <c r="AE105">
-        <v>1.1</v>
-      </c>
-      <c r="AF105">
-        <v>1.7</v>
-      </c>
-      <c r="AG105">
-        <v>2.05</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.21</v>
-      </c>
       <c r="AK105">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O106">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
+        <v>1.8</v>
+      </c>
+      <c r="Q106">
+        <v>3.95</v>
+      </c>
+      <c r="R106">
+        <v>2.18</v>
+      </c>
+      <c r="S106">
+        <v>1.31</v>
+      </c>
+      <c r="T106">
+        <v>3.02</v>
+      </c>
+      <c r="U106">
+        <v>2.56</v>
+      </c>
+      <c r="V106">
+        <v>1.42</v>
+      </c>
+      <c r="W106">
+        <v>1.09</v>
+      </c>
+      <c r="X106">
+        <v>1.04</v>
+      </c>
+      <c r="Y106">
+        <v>1.2</v>
+      </c>
+      <c r="Z106">
+        <v>3.8</v>
+      </c>
+      <c r="AA106">
         <v>1.73</v>
       </c>
-      <c r="Q106">
-        <v>4.4</v>
-      </c>
-      <c r="R106">
-        <v>2.25</v>
-      </c>
-      <c r="S106">
-        <v>1.35</v>
-      </c>
-      <c r="T106">
-        <v>3</v>
-      </c>
-      <c r="U106">
-        <v>2.65</v>
-      </c>
-      <c r="V106">
-        <v>1.44</v>
-      </c>
-      <c r="W106">
-        <v>1.08</v>
-      </c>
-      <c r="X106">
-        <v>1.02</v>
-      </c>
-      <c r="Y106">
-        <v>1.22</v>
-      </c>
-      <c r="Z106">
-        <v>3.7</v>
-      </c>
-      <c r="AA106">
-        <v>1.79</v>
-      </c>
       <c r="AB106">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC106">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD106">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG106">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK106">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.5</v>
+        <v>2.74</v>
       </c>
       <c r="O132">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="P132">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q132">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="R132">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="S132">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T132">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U132">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="V132">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="W132">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y132">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z132">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA132">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB132">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="AC132">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="AD132">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AE132">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF132">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG132">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK132">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="O133">
+        <v>4.4</v>
+      </c>
+      <c r="P133">
+        <v>5.25</v>
+      </c>
+      <c r="Q133">
+        <v>1.91</v>
+      </c>
+      <c r="R133">
+        <v>2.5</v>
+      </c>
+      <c r="S133">
+        <v>1.28</v>
+      </c>
+      <c r="T133">
         <v>3.3</v>
       </c>
-      <c r="P133">
-        <v>2.39</v>
-      </c>
-      <c r="Q133">
-        <v>3.42</v>
-      </c>
-      <c r="R133">
-        <v>2.32</v>
-      </c>
-      <c r="S133">
-        <v>1.35</v>
-      </c>
-      <c r="T133">
-        <v>3</v>
-      </c>
       <c r="U133">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V133">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z133">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="AA133">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB133">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="AC133">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="AD133">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AE133">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF133">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG133">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK133">
-        <v>1.4</v>
+        <v>2.53</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22640,16 +22640,16 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O137">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P137">
         <v>2.9</v>
       </c>
       <c r="Q137">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R137">
         <v>1.97</v>
@@ -22670,13 +22670,13 @@
         <v>1.04</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z137">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="AA137">
         <v>2.1</v>
@@ -22685,19 +22685,19 @@
         <v>1.7</v>
       </c>
       <c r="AC137">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AD137">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE137">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF137">
         <v>1.8</v>
       </c>
       <c r="AG137">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>1.36</v>
       </c>
       <c r="AK137">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O139">
         <v>3</v>
       </c>
       <c r="P139">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -23020,7 +23020,7 @@
         <v>1.02</v>
       </c>
       <c r="AF139">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG139">
         <v>1.65</v>
@@ -23132,28 +23132,28 @@
         <v>8.5</v>
       </c>
       <c r="O140">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P140">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q140">
         <v>7</v>
       </c>
       <c r="R140">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="S140">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T140">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="U140">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V140">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W140">
         <v>1.21</v>
@@ -23162,10 +23162,10 @@
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z140">
-        <v>6.25</v>
+        <v>6.55</v>
       </c>
       <c r="AA140">
         <v>1.4</v>
@@ -23174,10 +23174,10 @@
         <v>2.88</v>
       </c>
       <c r="AC140">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AD140">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE140">
         <v>1.34</v>
@@ -23186,7 +23186,7 @@
         <v>1.67</v>
       </c>
       <c r="AG140">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="AK140">
         <v>1.07</v>
@@ -23301,7 +23301,7 @@
         <v>4.1</v>
       </c>
       <c r="Q141">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="R141">
         <v>2.5</v>
@@ -23310,7 +23310,7 @@
         <v>1.22</v>
       </c>
       <c r="T141">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U141">
         <v>1.99</v>
@@ -23319,10 +23319,10 @@
         <v>1.83</v>
       </c>
       <c r="W141">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X141">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y141">
         <v>1.1</v>
@@ -23365,7 +23365,7 @@
         <v>1.17</v>
       </c>
       <c r="AK141">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23458,13 +23458,13 @@
         <v>2.55</v>
       </c>
       <c r="O142">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="P142">
         <v>2.44</v>
       </c>
       <c r="Q142">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="R142">
         <v>2.26</v>
@@ -23476,19 +23476,19 @@
         <v>3.6</v>
       </c>
       <c r="U142">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V142">
         <v>1.6</v>
       </c>
       <c r="W142">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X142">
         <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z142">
         <v>4.8</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>4.07</v>
+        <v>3.75</v>
       </c>
       <c r="O162">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P162">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -28185,13 +28185,13 @@
         <v>3.85</v>
       </c>
       <c r="O171">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P171">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q171">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R171">
         <v>2.3</v>
@@ -28200,10 +28200,10 @@
         <v>1.33</v>
       </c>
       <c r="T171">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U171">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V171">
         <v>1.5</v>
@@ -28227,7 +28227,7 @@
         <v>2.25</v>
       </c>
       <c r="AC171">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="AD171">
         <v>1.44</v>
@@ -28236,7 +28236,7 @@
         <v>1.13</v>
       </c>
       <c r="AF171">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG171">
         <v>2.3</v>
@@ -28514,7 +28514,7 @@
         <v>4.3</v>
       </c>
       <c r="P173">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q173">
         <v>1.91</v>
@@ -28523,10 +28523,10 @@
         <v>2.34</v>
       </c>
       <c r="S173">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T173">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U173">
         <v>2.36</v>
@@ -28547,13 +28547,13 @@
         <v>4.4</v>
       </c>
       <c r="AA173">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB173">
         <v>2.25</v>
       </c>
       <c r="AC173">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD173">
         <v>1.44</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK173">
         <v>2.5</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,80 +28834,80 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.14</v>
+        <v>2.65</v>
       </c>
       <c r="O175">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P175">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q175">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S175">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T175">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U175">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V175">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W175">
+        <v>1.04</v>
+      </c>
+      <c r="X175">
         <v>1.06</v>
       </c>
-      <c r="X175">
-        <v>1.05</v>
-      </c>
       <c r="Y175">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z175">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="AA175">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB175">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AC175">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD175">
+        <v>1.14</v>
+      </c>
+      <c r="AE175">
+        <v>1.01</v>
+      </c>
+      <c r="AF175">
+        <v>1.97</v>
+      </c>
+      <c r="AG175">
+        <v>1.73</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
+        <v>1.27</v>
+      </c>
+      <c r="AK175">
         <v>1.23</v>
-      </c>
-      <c r="AE175">
-        <v>1.02</v>
-      </c>
-      <c r="AF175">
-        <v>1.85</v>
-      </c>
-      <c r="AG175">
-        <v>1.82</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>1.26</v>
-      </c>
-      <c r="AK175">
-        <v>1.71</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O176">
+        <v>3.1</v>
+      </c>
+      <c r="P176">
         <v>3</v>
       </c>
-      <c r="P176">
+      <c r="Q176">
         <v>2.5</v>
       </c>
-      <c r="Q176">
-        <v>3.1</v>
-      </c>
       <c r="R176">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T176">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U176">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V176">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W176">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
         <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z176">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="AA176">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="AB176">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AC176">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AD176">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AE176">
         <v>1.02</v>
       </c>
       <c r="AF176">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG176">
+        <v>1.82</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
+        <v>1.25</v>
+      </c>
+      <c r="AK176">
         <v>1.71</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.27</v>
-      </c>
-      <c r="AK176">
-        <v>1.23</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O179">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P179">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q179">
         <v>1.95</v>
@@ -29522,13 +29522,13 @@
         <v>1.2</v>
       </c>
       <c r="Z179">
-        <v>4.54</v>
+        <v>4.59</v>
       </c>
       <c r="AA179">
         <v>1.6</v>
       </c>
       <c r="AB179">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC179">
         <v>2.46</v>
@@ -29537,7 +29537,7 @@
         <v>1.51</v>
       </c>
       <c r="AE179">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF179">
         <v>1.75</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK179">
         <v>2.9</v>
@@ -29978,10 +29978,10 @@
         <v>1.62</v>
       </c>
       <c r="O182">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P182">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="Q182">
         <v>2</v>
@@ -29990,13 +29990,13 @@
         <v>2.6</v>
       </c>
       <c r="S182">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T182">
         <v>3.8</v>
       </c>
       <c r="U182">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V182">
         <v>1.6</v>
@@ -30017,19 +30017,19 @@
         <v>1.5</v>
       </c>
       <c r="AB182">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC182">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AD182">
         <v>1.59</v>
       </c>
       <c r="AE182">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF182">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG182">
         <v>2.4</v>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK182">
         <v>2.3</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="O193">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P193">
-        <v>2.83</v>
+        <v>5.53</v>
       </c>
       <c r="Q193">
+        <v>2.1</v>
+      </c>
+      <c r="R193">
+        <v>1.99</v>
+      </c>
+      <c r="S193">
+        <v>1.4</v>
+      </c>
+      <c r="T193">
+        <v>2.5</v>
+      </c>
+      <c r="U193">
         <v>3</v>
       </c>
-      <c r="R193">
-        <v>2.1</v>
-      </c>
-      <c r="S193">
+      <c r="V193">
+        <v>1.3</v>
+      </c>
+      <c r="W193">
+        <v>1.05</v>
+      </c>
+      <c r="X193">
+        <v>1.05</v>
+      </c>
+      <c r="Y193">
         <v>1.36</v>
       </c>
-      <c r="T193">
-        <v>2.63</v>
-      </c>
-      <c r="U193">
-        <v>2.88</v>
-      </c>
-      <c r="V193">
-        <v>1.33</v>
-      </c>
-      <c r="W193">
+      <c r="Z193">
+        <v>2.69</v>
+      </c>
+      <c r="AA193">
+        <v>2.21</v>
+      </c>
+      <c r="AB193">
+        <v>1.6</v>
+      </c>
+      <c r="AC193">
+        <v>4.4</v>
+      </c>
+      <c r="AD193">
+        <v>1.18</v>
+      </c>
+      <c r="AE193">
         <v>1.02</v>
       </c>
-      <c r="X193">
-        <v>1</v>
-      </c>
-      <c r="Y193">
-        <v>1.33</v>
-      </c>
-      <c r="Z193">
-        <v>3.08</v>
-      </c>
-      <c r="AA193">
-        <v>1.97</v>
-      </c>
-      <c r="AB193">
-        <v>1.73</v>
-      </c>
-      <c r="AC193">
-        <v>3.42</v>
-      </c>
-      <c r="AD193">
-        <v>1.23</v>
-      </c>
-      <c r="AE193">
-        <v>1.04</v>
-      </c>
       <c r="AF193">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG193">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK193">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G194">
@@ -31934,61 +31934,61 @@
         <v>2.3</v>
       </c>
       <c r="O194">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P194">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q194">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R194">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S194">
         <v>1.36</v>
       </c>
       <c r="T194">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U194">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V194">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W194">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X194">
         <v>1</v>
       </c>
       <c r="Y194">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z194">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA194">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB194">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AC194">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD194">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE194">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF194">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG194">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK194">
         <v>1.5</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,80 +32094,80 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="O195">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P195">
-        <v>5.53</v>
+        <v>2.69</v>
       </c>
       <c r="Q195">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="R195">
         <v>1.99</v>
       </c>
       <c r="S195">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T195">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="U195">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="V195">
+        <v>1.4</v>
+      </c>
+      <c r="W195">
+        <v>1.08</v>
+      </c>
+      <c r="X195">
+        <v>1</v>
+      </c>
+      <c r="Y195">
+        <v>1.31</v>
+      </c>
+      <c r="Z195">
+        <v>3.24</v>
+      </c>
+      <c r="AA195">
+        <v>1.95</v>
+      </c>
+      <c r="AB195">
+        <v>1.85</v>
+      </c>
+      <c r="AC195">
+        <v>3.28</v>
+      </c>
+      <c r="AD195">
+        <v>1.25</v>
+      </c>
+      <c r="AE195">
+        <v>1.05</v>
+      </c>
+      <c r="AF195">
+        <v>1.71</v>
+      </c>
+      <c r="AG195">
+        <v>1.95</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ195">
         <v>1.3</v>
       </c>
-      <c r="W195">
-        <v>1.05</v>
-      </c>
-      <c r="X195">
-        <v>1.03</v>
-      </c>
-      <c r="Y195">
-        <v>1.36</v>
-      </c>
-      <c r="Z195">
-        <v>2.69</v>
-      </c>
-      <c r="AA195">
-        <v>2.21</v>
-      </c>
-      <c r="AB195">
-        <v>1.65</v>
-      </c>
-      <c r="AC195">
-        <v>4</v>
-      </c>
-      <c r="AD195">
-        <v>1.18</v>
-      </c>
-      <c r="AE195">
-        <v>1.04</v>
-      </c>
-      <c r="AF195">
-        <v>2.2</v>
-      </c>
-      <c r="AG195">
-        <v>1.54</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ195">
-        <v>1.2</v>
-      </c>
       <c r="AK195">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="O206">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="P206">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q206">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="R206">
         <v>2.11</v>
       </c>
       <c r="S206">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T206">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U206">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="V206">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W206">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X206">
         <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z206">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA206">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AB206">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AC206">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD206">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE206">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF206">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG206">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK206">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O207">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P207">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q207">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R207">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S207">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T207">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="U207">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="V207">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="W207">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X207">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z207">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA207">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AB207">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AC207">
-        <v>3.34</v>
+        <v>2.59</v>
       </c>
       <c r="AD207">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AE207">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF207">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG207">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK207">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,31 +34213,31 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="O208">
         <v>3.15</v>
       </c>
       <c r="P208">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="Q208">
-        <v>4.01</v>
+        <v>2.62</v>
       </c>
       <c r="R208">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S208">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T208">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U208">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V208">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W208">
         <v>1.07</v>
@@ -34246,31 +34246,31 @@
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z208">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA208">
+        <v>1.81</v>
+      </c>
+      <c r="AB208">
         <v>1.88</v>
       </c>
-      <c r="AB208">
-        <v>1.81</v>
-      </c>
       <c r="AC208">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD208">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE208">
         <v>1.07</v>
       </c>
       <c r="AF208">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG208">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK208">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="O209">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P209">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="Q209">
-        <v>2.26</v>
+        <v>4.01</v>
       </c>
       <c r="R209">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S209">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T209">
+        <v>2.88</v>
+      </c>
+      <c r="U209">
+        <v>2.6</v>
+      </c>
+      <c r="V209">
+        <v>1.4</v>
+      </c>
+      <c r="W209">
+        <v>1.07</v>
+      </c>
+      <c r="X209">
+        <v>1.01</v>
+      </c>
+      <c r="Y209">
+        <v>1.26</v>
+      </c>
+      <c r="Z209">
+        <v>3.2</v>
+      </c>
+      <c r="AA209">
+        <v>1.88</v>
+      </c>
+      <c r="AB209">
+        <v>1.81</v>
+      </c>
+      <c r="AC209">
         <v>3.14</v>
       </c>
-      <c r="U209">
-        <v>2.41</v>
-      </c>
-      <c r="V209">
-        <v>1.46</v>
-      </c>
-      <c r="W209">
-        <v>1.1</v>
-      </c>
-      <c r="X209">
-        <v>1.03</v>
-      </c>
-      <c r="Y209">
-        <v>1.17</v>
-      </c>
-      <c r="Z209">
-        <v>3.98</v>
-      </c>
-      <c r="AA209">
-        <v>1.69</v>
-      </c>
-      <c r="AB209">
-        <v>2.12</v>
-      </c>
-      <c r="AC209">
-        <v>2.59</v>
-      </c>
       <c r="AD209">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AE209">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF209">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AG209">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK209">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -36658,10 +36658,10 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O223">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P223">
         <v>3.3</v>
@@ -36670,52 +36670,52 @@
         <v>2.86</v>
       </c>
       <c r="R223">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="S223">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T223">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="U223">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="V223">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W223">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X223">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y223">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z223">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AA223">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AB223">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AC223">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AD223">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE223">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF223">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG223">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.28</v>
       </c>
       <c r="AK223">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36824,28 +36824,28 @@
         <v>2.48</v>
       </c>
       <c r="O224">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P224">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q224">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="R224">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S224">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T224">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U224">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="V224">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W224">
         <v>1.02</v>
@@ -36854,19 +36854,19 @@
         <v>1.04</v>
       </c>
       <c r="Y224">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z224">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AA224">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AB224">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AC224">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AD224">
         <v>1.12</v>
@@ -36875,10 +36875,10 @@
         <v>1.01</v>
       </c>
       <c r="AF224">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AG224">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK224">
         <v>1.43</v>
@@ -36990,10 +36990,10 @@
         <v>3.1</v>
       </c>
       <c r="P225">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q225">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="R225">
         <v>2</v>
@@ -37002,10 +37002,10 @@
         <v>1.44</v>
       </c>
       <c r="T225">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="U225">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V225">
         <v>1.27</v>
@@ -37041,7 +37041,7 @@
         <v>2</v>
       </c>
       <c r="AG225">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37147,10 +37147,10 @@
         </is>
       </c>
       <c r="N226">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O226">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P226">
         <v>1.25</v>
@@ -37162,7 +37162,7 @@
         <v>2.5</v>
       </c>
       <c r="S226">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T226">
         <v>3.4</v>
@@ -37174,7 +37174,7 @@
         <v>1.59</v>
       </c>
       <c r="W226">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X226">
         <v>1.02</v>
@@ -37183,13 +37183,13 @@
         <v>1.16</v>
       </c>
       <c r="Z226">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="AA226">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB226">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AC226">
         <v>2.3</v>
@@ -37198,13 +37198,13 @@
         <v>1.59</v>
       </c>
       <c r="AE226">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF226">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG226">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -40256,10 +40256,10 @@
         <v>2.03</v>
       </c>
       <c r="R245">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="S245">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T245">
         <v>3.3</v>
@@ -40268,7 +40268,7 @@
         <v>2.3</v>
       </c>
       <c r="V245">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W245">
         <v>1.12</v>
@@ -40280,7 +40280,7 @@
         <v>1.2</v>
       </c>
       <c r="Z245">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="AA245">
         <v>1.66</v>
@@ -40301,7 +40301,7 @@
         <v>1.67</v>
       </c>
       <c r="AG245">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK245">
         <v>2.43</v>
@@ -40733,16 +40733,16 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O248">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P248">
         <v>2.63</v>
       </c>
       <c r="Q248">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R248">
         <v>2.1</v>
@@ -40778,7 +40778,7 @@
         <v>1.9</v>
       </c>
       <c r="AC248">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="AD248">
         <v>1.3</v>
@@ -40787,7 +40787,7 @@
         <v>1.07</v>
       </c>
       <c r="AF248">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG248">
         <v>2.05</v>
@@ -40905,16 +40905,16 @@
         <v>3.2</v>
       </c>
       <c r="Q249">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="R249">
         <v>2.03</v>
       </c>
       <c r="S249">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="T249">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="U249">
         <v>3.75</v>
@@ -40932,19 +40932,19 @@
         <v>1.46</v>
       </c>
       <c r="Z249">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AA249">
         <v>2.5</v>
       </c>
       <c r="AB249">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC249">
         <v>5</v>
       </c>
       <c r="AD249">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE249">
         <v>1.01</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O250">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P250">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41240,7 +41240,7 @@
         <v>1.36</v>
       </c>
       <c r="T251">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U251">
         <v>2.71</v>
@@ -41252,7 +41252,7 @@
         <v>1.06</v>
       </c>
       <c r="X251">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y251">
         <v>1.26</v>
@@ -41264,7 +41264,7 @@
         <v>1.85</v>
       </c>
       <c r="AB251">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC251">
         <v>3.14</v>
@@ -41292,7 +41292,7 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK251">
         <v>1.3</v>
@@ -42698,10 +42698,10 @@
         <v>0</v>
       </c>
       <c r="Q260">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="R260">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S260">
         <v>1.33</v>
@@ -42734,10 +42734,10 @@
         <v>1.81</v>
       </c>
       <c r="AC260">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD260">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE260">
         <v>1.07</v>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AK260">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O261">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P261">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -46450,7 +46450,7 @@
         <v>1.74</v>
       </c>
       <c r="R283">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S283">
         <v>1.4</v>
@@ -46489,7 +46489,7 @@
         <v>1.22</v>
       </c>
       <c r="AE283">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF283">
         <v>2.25</v>
@@ -46508,7 +46508,7 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AK283">
         <v>3.3</v>
@@ -46604,16 +46604,16 @@
         <v>1.93</v>
       </c>
       <c r="O284">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P284">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q284">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R284">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S284">
         <v>1.25</v>
@@ -46625,7 +46625,7 @@
         <v>2.2</v>
       </c>
       <c r="V284">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W284">
         <v>1.13</v>
@@ -46643,13 +46643,13 @@
         <v>1.6</v>
       </c>
       <c r="AB284">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AC284">
         <v>2.36</v>
       </c>
       <c r="AD284">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE284">
         <v>1.17</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O285">
         <v>4</v>
@@ -46773,7 +46773,7 @@
         <v>4</v>
       </c>
       <c r="Q285">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R285">
         <v>2.5</v>
@@ -46782,13 +46782,13 @@
         <v>1.35</v>
       </c>
       <c r="T285">
-        <v>3.44</v>
+        <v>2.87</v>
       </c>
       <c r="U285">
         <v>2.3</v>
       </c>
       <c r="V285">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W285">
         <v>1.15</v>
@@ -46797,31 +46797,31 @@
         <v>1.02</v>
       </c>
       <c r="Y285">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z285">
-        <v>5.03</v>
+        <v>4.8</v>
       </c>
       <c r="AA285">
         <v>1.57</v>
       </c>
       <c r="AB285">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="AC285">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="AD285">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE285">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF285">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG285">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK285">
         <v>2.1</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
+        <v>1.96</v>
+      </c>
+      <c r="O288">
         <v>2.62</v>
       </c>
-      <c r="O288">
-        <v>2.9</v>
-      </c>
       <c r="P288">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q288">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="R288">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S288">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T288">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U288">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V288">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W288">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X288">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y288">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z288">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AA288">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AB288">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC288">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD288">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE288">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF288">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG288">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK288">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="O289">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="P289">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q289">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R289">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S289">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T289">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U289">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V289">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W289">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X289">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y289">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z289">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AA289">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB289">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC289">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD289">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE289">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF289">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG289">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK289">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47745,61 +47745,61 @@
         <v>1.11</v>
       </c>
       <c r="O291">
-        <v>7.3</v>
+        <v>7.55</v>
       </c>
       <c r="P291">
         <v>12</v>
       </c>
       <c r="Q291">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="R291">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="S291">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T291">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U291">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V291">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W291">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X291">
         <v>0</v>
       </c>
       <c r="Y291">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z291">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA291">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB291">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AC291">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AD291">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE291">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF291">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG291">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.01</v>
       </c>
       <c r="AK291">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>2.25</v>
       </c>
       <c r="V292">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W292">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X292">
         <v>1.04</v>
@@ -47962,7 +47962,7 @@
         <v>1.59</v>
       </c>
       <c r="AG292">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -48240,16 +48240,16 @@
         <v>4.7</v>
       </c>
       <c r="Q294">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="R294">
         <v>2.08</v>
       </c>
       <c r="S294">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T294">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U294">
         <v>3.1</v>
@@ -48270,13 +48270,13 @@
         <v>2.59</v>
       </c>
       <c r="AA294">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB294">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC294">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AD294">
         <v>1.16</v>
@@ -48288,7 +48288,7 @@
         <v>2</v>
       </c>
       <c r="AG294">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>1.26</v>
       </c>
       <c r="AK294">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
-        <v>6.55</v>
+        <v>1.84</v>
       </c>
       <c r="O296">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P296">
-        <v>1.45</v>
+        <v>3.58</v>
       </c>
       <c r="Q296">
-        <v>6.2</v>
+        <v>2.41</v>
       </c>
       <c r="R296">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="S296">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T296">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U296">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="V296">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W296">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X296">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y296">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z296">
+        <v>2.99</v>
+      </c>
+      <c r="AA296">
+        <v>2.08</v>
+      </c>
+      <c r="AB296">
+        <v>1.7</v>
+      </c>
+      <c r="AC296">
         <v>3.85</v>
       </c>
-      <c r="AA296">
-        <v>1.78</v>
-      </c>
-      <c r="AB296">
-        <v>2.1</v>
-      </c>
-      <c r="AC296">
-        <v>2.7</v>
-      </c>
       <c r="AD296">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE296">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF296">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG296">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK296">
-        <v>1.07</v>
+        <v>1.85</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.84</v>
+        <v>6.55</v>
       </c>
       <c r="O297">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P297">
-        <v>3.58</v>
+        <v>1.45</v>
       </c>
       <c r="Q297">
-        <v>2.41</v>
+        <v>6.2</v>
       </c>
       <c r="R297">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="S297">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T297">
+        <v>3.2</v>
+      </c>
+      <c r="U297">
+        <v>2.57</v>
+      </c>
+      <c r="V297">
+        <v>1.44</v>
+      </c>
+      <c r="W297">
+        <v>1.1</v>
+      </c>
+      <c r="X297">
+        <v>1.03</v>
+      </c>
+      <c r="Y297">
+        <v>1.25</v>
+      </c>
+      <c r="Z297">
+        <v>3.85</v>
+      </c>
+      <c r="AA297">
+        <v>1.78</v>
+      </c>
+      <c r="AB297">
+        <v>2.1</v>
+      </c>
+      <c r="AC297">
         <v>2.7</v>
       </c>
-      <c r="U297">
-        <v>3</v>
-      </c>
-      <c r="V297">
-        <v>1.34</v>
-      </c>
-      <c r="W297">
-        <v>1.04</v>
-      </c>
-      <c r="X297">
-        <v>1.04</v>
-      </c>
-      <c r="Y297">
-        <v>1.34</v>
-      </c>
-      <c r="Z297">
-        <v>2.99</v>
-      </c>
-      <c r="AA297">
-        <v>2.08</v>
-      </c>
-      <c r="AB297">
-        <v>1.7</v>
-      </c>
-      <c r="AC297">
-        <v>3.85</v>
-      </c>
       <c r="AD297">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE297">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF297">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG297">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK297">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48898,13 +48898,13 @@
         <v>1.78</v>
       </c>
       <c r="S298">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T298">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="U298">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="V298">
         <v>1.25</v>
@@ -48916,31 +48916,31 @@
         <v>1.07</v>
       </c>
       <c r="Y298">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Z298">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AA298">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AB298">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC298">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD298">
         <v>1.12</v>
       </c>
       <c r="AE298">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF298">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG298">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AK298">
         <v>1.3</v>
@@ -49055,22 +49055,22 @@
         <v>1.5</v>
       </c>
       <c r="Q299">
-        <v>5.13</v>
+        <v>5.07</v>
       </c>
       <c r="R299">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S299">
         <v>1.18</v>
       </c>
       <c r="T299">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="U299">
         <v>2.1</v>
       </c>
       <c r="V299">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="W299">
         <v>1.22</v>
@@ -49079,7 +49079,7 @@
         <v>1.01</v>
       </c>
       <c r="Y299">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z299">
         <v>7</v>
@@ -49088,7 +49088,7 @@
         <v>1.36</v>
       </c>
       <c r="AB299">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC299">
         <v>1.92</v>
@@ -49100,7 +49100,7 @@
         <v>1.3</v>
       </c>
       <c r="AF299">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG299">
         <v>2.5</v>
@@ -50042,13 +50042,13 @@
         <v>1.33</v>
       </c>
       <c r="T305">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U305">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V305">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W305">
         <v>1.07</v>
@@ -50060,7 +50060,7 @@
         <v>1.19</v>
       </c>
       <c r="Z305">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="AA305">
         <v>1.72</v>
@@ -50075,7 +50075,7 @@
         <v>1.36</v>
       </c>
       <c r="AE305">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF305">
         <v>1.79</v>
@@ -50193,7 +50193,7 @@
         <v>3.15</v>
       </c>
       <c r="P306">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q306">
         <v>2.8</v>
@@ -50235,7 +50235,7 @@
         <v>4.8</v>
       </c>
       <c r="AD306">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE306">
         <v>1.01</v>
@@ -50244,7 +50244,7 @@
         <v>2</v>
       </c>
       <c r="AG306">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>1.33</v>
       </c>
       <c r="AK306">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O307">
         <v>3.1</v>
       </c>
       <c r="P307">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q307">
-        <v>3.18</v>
+        <v>2.54</v>
       </c>
       <c r="R307">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S307">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T307">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U307">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="V307">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W307">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X307">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y307">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z307">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AA307">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB307">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC307">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD307">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE307">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF307">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG307">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK307">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O308">
         <v>3.1</v>
       </c>
       <c r="P308">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q308">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="R308">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="S308">
         <v>1.44</v>
       </c>
       <c r="T308">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U308">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V308">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W308">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X308">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y308">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z308">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AA308">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB308">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC308">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AD308">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE308">
         <v>1.03</v>
       </c>
       <c r="AF308">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG308">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK308">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O309">
         <v>3.4</v>
       </c>
       <c r="P309">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q309">
         <v>2.9</v>
@@ -50706,7 +50706,7 @@
         <v>1.12</v>
       </c>
       <c r="X309">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y309">
         <v>1.2</v>
@@ -50730,10 +50730,10 @@
         <v>1.16</v>
       </c>
       <c r="AF309">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG309">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK309">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -52656,7 +52656,7 @@
         <v>3.2</v>
       </c>
       <c r="V321">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W321">
         <v>1.04</v>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK321">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52795,19 +52795,19 @@
         </is>
       </c>
       <c r="N322">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="O322">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P322">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Q322">
         <v>9</v>
       </c>
       <c r="R322">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="S322">
         <v>1.3</v>
@@ -52819,10 +52819,10 @@
         <v>2.55</v>
       </c>
       <c r="V322">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W322">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X322">
         <v>1.01</v>
@@ -52834,7 +52834,7 @@
         <v>4.15</v>
       </c>
       <c r="AA322">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB322">
         <v>2.1</v>
@@ -52849,7 +52849,7 @@
         <v>1.13</v>
       </c>
       <c r="AF322">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AG322">
         <v>1.75</v>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK322">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O323">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="P323">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="Q323">
         <v>1.53</v>
@@ -52979,10 +52979,10 @@
         <v>4.4</v>
       </c>
       <c r="U323">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V323">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W323">
         <v>1.22</v>
@@ -52994,25 +52994,25 @@
         <v>1.06</v>
       </c>
       <c r="Z323">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA323">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB323">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC323">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD323">
         <v>1.85</v>
       </c>
       <c r="AE323">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF323">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG323">
         <v>1.95</v>
@@ -53139,16 +53139,16 @@
         <v>1.25</v>
       </c>
       <c r="T324">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U324">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V324">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W324">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X324">
         <v>1.02</v>
@@ -53166,13 +53166,13 @@
         <v>2.12</v>
       </c>
       <c r="AC324">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AD324">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE324">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF324">
         <v>1.53</v>
@@ -53779,13 +53779,13 @@
         <v>4.05</v>
       </c>
       <c r="P328">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="Q328">
         <v>2.02</v>
       </c>
       <c r="R328">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S328">
         <v>1.26</v>
@@ -53803,13 +53803,13 @@
         <v>1.12</v>
       </c>
       <c r="X328">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y328">
         <v>1.13</v>
       </c>
       <c r="Z328">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA328">
         <v>1.6</v>
@@ -53843,7 +53843,7 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK328">
         <v>2.33</v>

--- a/jogos_2026-09-06.xlsx
+++ b/jogos_2026-09-06.xlsx
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.46</v>
+        <v>6.6</v>
       </c>
       <c r="O58">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="P58">
-        <v>5.65</v>
+        <v>1.31</v>
       </c>
       <c r="Q58">
-        <v>1.99</v>
+        <v>6.9</v>
       </c>
       <c r="R58">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S58">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="V58">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AA58">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB58">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AC58">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="AD58">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK58">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,61 +9926,61 @@
         </is>
       </c>
       <c r="N59">
-        <v>7.7</v>
+        <v>1.47</v>
       </c>
       <c r="O59">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="P59">
-        <v>1.3</v>
+        <v>5.09</v>
       </c>
       <c r="Q59">
-        <v>6.9</v>
+        <v>1.99</v>
       </c>
       <c r="R59">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T59">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U59">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="V59">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="W59">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AA59">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AB59">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="AC59">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="AD59">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AE59">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
         <v>1.95</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK59">
-        <v>1.02</v>
+        <v>2.39</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R65">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="U65">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>3.92</v>
+        <v>5.6</v>
       </c>
       <c r="AA65">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AB65">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AC65">
-        <v>2.58</v>
+        <v>2.07</v>
       </c>
       <c r="AD65">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF65">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q66">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="U66">
+        <v>2.59</v>
+      </c>
+      <c r="V66">
+        <v>1.49</v>
+      </c>
+      <c r="W66">
+        <v>1.08</v>
+      </c>
+      <c r="X66">
+        <v>1.05</v>
+      </c>
+      <c r="Y66">
+        <v>1.18</v>
+      </c>
+      <c r="Z66">
+        <v>3.92</v>
+      </c>
+      <c r="AA66">
+        <v>1.77</v>
+      </c>
+      <c r="AB66">
         <v>2.05</v>
       </c>
-      <c r="V66">
-        <v>1.7</v>
-      </c>
-      <c r="W66">
-        <v>1.2</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.1</v>
-      </c>
-      <c r="Z66">
-        <v>5.6</v>
-      </c>
-      <c r="AA66">
-        <v>1.42</v>
-      </c>
-      <c r="AB66">
-        <v>2.63</v>
-      </c>
       <c r="AC66">
-        <v>2.07</v>
+        <v>2.58</v>
       </c>
       <c r="AD66">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AE66">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG66">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -14001,28 +14001,28 @@
         </is>
       </c>
       <c r="N84">
+        <v>1.18</v>
+      </c>
+      <c r="O84">
+        <v>7.5</v>
+      </c>
+      <c r="P84">
+        <v>17</v>
+      </c>
+      <c r="Q84">
+        <v>1.52</v>
+      </c>
+      <c r="R84">
+        <v>2.71</v>
+      </c>
+      <c r="S84">
         <v>1.17</v>
       </c>
-      <c r="O84">
-        <v>6.6</v>
-      </c>
-      <c r="P84">
-        <v>13</v>
-      </c>
-      <c r="Q84">
-        <v>1.55</v>
-      </c>
-      <c r="R84">
-        <v>2.69</v>
-      </c>
-      <c r="S84">
-        <v>1.18</v>
-      </c>
       <c r="T84">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="U84">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V84">
         <v>1.6</v>
@@ -14037,22 +14037,22 @@
         <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="AA84">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB84">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AC84">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD84">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE84">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF84">
         <v>1.98</v>
@@ -14834,7 +14834,7 @@
         <v>1.33</v>
       </c>
       <c r="T89">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U89">
         <v>2.69</v>
@@ -14849,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="Y89">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z89">
         <v>3.4</v>
@@ -14861,7 +14861,7 @@
         <v>1.87</v>
       </c>
       <c r="AC89">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD89">
         <v>1.3</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O101">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P101">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R101">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S101">
         <v>1.4</v>
       </c>
       <c r="T101">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U101">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V101">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z101">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="AA101">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AB101">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC101">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD101">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF101">
         <v>1.75</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.32</v>
       </c>
       <c r="AK101">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O102">
+        <v>3.16</v>
+      </c>
+      <c r="P102">
+        <v>2.39</v>
+      </c>
+      <c r="Q102">
         <v>3.1</v>
       </c>
-      <c r="P102">
-        <v>2.4</v>
-      </c>
-      <c r="Q102">
-        <v>3.38</v>
-      </c>
       <c r="R102">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
         <v>1.4</v>
       </c>
       <c r="T102">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U102">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="AA102">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB102">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AC102">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AD102">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE102">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
         <v>1.75</v>
       </c>
       <c r="AG102">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.32</v>
       </c>
       <c r="AK102">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O105">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P105">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Q105">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="R105">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S105">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T105">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U105">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z105">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA105">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB105">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC105">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD105">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK105">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O106">
         <v>3.6</v>
       </c>
       <c r="P106">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Q106">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="R106">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U106">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W106">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA106">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB106">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC106">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD106">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE106">
         <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="O115">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="P115">
         <v>22.55</v>
@@ -19072,16 +19072,16 @@
         <v>1.07</v>
       </c>
       <c r="T115">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U115">
         <v>1.5</v>
       </c>
       <c r="V115">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="W115">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -19090,7 +19090,7 @@
         <v>1.04</v>
       </c>
       <c r="Z115">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AA115">
         <v>1.14</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O123">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="Q123">
         <v>3</v>
@@ -20415,7 +20415,7 @@
         <v>1.86</v>
       </c>
       <c r="AG123">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O134">
         <v>3.3</v>
@@ -28508,10 +28508,10 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O173">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P173">
         <v>5</v>
@@ -28520,7 +28520,7 @@
         <v>1.91</v>
       </c>
       <c r="R173">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S173">
         <v>1.29</v>
@@ -28550,7 +28550,7 @@
         <v>1.61</v>
       </c>
       <c r="AB173">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC173">
         <v>2.6</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O175">
+        <v>3.1</v>
+      </c>
+      <c r="P175">
         <v>3</v>
       </c>
-      <c r="P175">
-        <v>2.4</v>
-      </c>
       <c r="Q175">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="R175">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S175">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T175">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U175">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V175">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W175">
+        <v>1.06</v>
+      </c>
+      <c r="X175">
         <v>1.04</v>
       </c>
-      <c r="X175">
-        <v>1.06</v>
-      </c>
       <c r="Y175">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z175">
-        <v>2.13</v>
+        <v>2.95</v>
       </c>
       <c r="AA175">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB175">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AC175">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD175">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE175">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF175">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG175">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="O176">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P176">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Q176">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R176">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S176">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T176">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U176">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V176">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W176">
+        <v>1.04</v>
+      </c>
+      <c r="X176">
         <v>1.06</v>
       </c>
-      <c r="X176">
-        <v>1.04</v>
-      </c>
       <c r="Y176">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z176">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="AA176">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB176">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AC176">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD176">
+        <v>1.14</v>
+      </c>
+      <c r="AE176">
+        <v>1.01</v>
+      </c>
+      <c r="AF176">
+        <v>1.97</v>
+      </c>
+      <c r="AG176">
+        <v>1.73</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
+        <v>1.27</v>
+      </c>
+      <c r="AK176">
         <v>1.23</v>
-      </c>
-      <c r="AE176">
-        <v>1.02</v>
-      </c>
-      <c r="AF176">
-        <v>1.85</v>
-      </c>
-      <c r="AG176">
-        <v>1.82</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.25</v>
-      </c>
-      <c r="AK176">
-        <v>1.71</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29338,10 +29338,10 @@
         <v>2.04</v>
       </c>
       <c r="S178">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T178">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U178">
         <v>2.7</v>
@@ -29377,10 +29377,10 @@
         <v>1.07</v>
       </c>
       <c r="AF178">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG178">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -30011,28 +30011,28 @@
         <v>1.18</v>
       </c>
       <c r="Z182">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AA182">
         <v>1.5</v>
       </c>
       <c r="AB182">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="AC182">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AD182">
         <v>1.59</v>
       </c>
       <c r="AE182">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF182">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG182">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.08</v>
+        <v>1.18</v>
       </c>
       <c r="O183">
-        <v>2.85</v>
+        <v>5.8</v>
       </c>
       <c r="P183">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q183">
-        <v>3.08</v>
+        <v>1.78</v>
       </c>
       <c r="R183">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="S183">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="T183">
-        <v>2.19</v>
+        <v>2.67</v>
       </c>
       <c r="U183">
-        <v>3.96</v>
+        <v>2.92</v>
       </c>
       <c r="V183">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W183">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X183">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="Z183">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="AA183">
-        <v>2.77</v>
+        <v>1.88</v>
       </c>
       <c r="AB183">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AC183">
-        <v>5.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD183">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AE183">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF183">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="AG183">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK183">
-        <v>1.71</v>
+        <v>4.61</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="O184">
-        <v>5.8</v>
+        <v>2.85</v>
       </c>
       <c r="P184">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q184">
-        <v>1.78</v>
+        <v>3.08</v>
       </c>
       <c r="R184">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="S184">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="T184">
-        <v>2.67</v>
+        <v>2.19</v>
       </c>
       <c r="U184">
-        <v>2.92</v>
+        <v>3.96</v>
       </c>
       <c r="V184">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W184">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X184">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y184">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="Z184">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="AA184">
-        <v>1.88</v>
+        <v>2.77</v>
       </c>
       <c r="AB184">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="AC184">
-        <v>2.92</v>
+        <v>5.83</v>
       </c>
       <c r="AD184">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AE184">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF184">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="AG184">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK184">
-        <v>4.61</v>
+        <v>1.71</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,80 +31768,80 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="O193">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P193">
-        <v>5.53</v>
+        <v>2.69</v>
       </c>
       <c r="Q193">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="R193">
         <v>1.99</v>
       </c>
       <c r="S193">
+        <v>1.36</v>
+      </c>
+      <c r="T193">
+        <v>2.63</v>
+      </c>
+      <c r="U193">
+        <v>2.7</v>
+      </c>
+      <c r="V193">
         <v>1.4</v>
       </c>
-      <c r="T193">
-        <v>2.5</v>
-      </c>
-      <c r="U193">
-        <v>3</v>
-      </c>
-      <c r="V193">
+      <c r="W193">
+        <v>1.08</v>
+      </c>
+      <c r="X193">
+        <v>1</v>
+      </c>
+      <c r="Y193">
+        <v>1.31</v>
+      </c>
+      <c r="Z193">
+        <v>3.24</v>
+      </c>
+      <c r="AA193">
+        <v>1.95</v>
+      </c>
+      <c r="AB193">
+        <v>1.85</v>
+      </c>
+      <c r="AC193">
+        <v>3.28</v>
+      </c>
+      <c r="AD193">
+        <v>1.25</v>
+      </c>
+      <c r="AE193">
+        <v>1.05</v>
+      </c>
+      <c r="AF193">
+        <v>1.71</v>
+      </c>
+      <c r="AG193">
+        <v>1.95</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ193">
         <v>1.3</v>
       </c>
-      <c r="W193">
-        <v>1.05</v>
-      </c>
-      <c r="X193">
-        <v>1.05</v>
-      </c>
-      <c r="Y193">
-        <v>1.36</v>
-      </c>
-      <c r="Z193">
-        <v>2.69</v>
-      </c>
-      <c r="AA193">
-        <v>2.21</v>
-      </c>
-      <c r="AB193">
-        <v>1.6</v>
-      </c>
-      <c r="AC193">
-        <v>4.4</v>
-      </c>
-      <c r="AD193">
-        <v>1.18</v>
-      </c>
-      <c r="AE193">
-        <v>1.02</v>
-      </c>
-      <c r="AF193">
-        <v>2.2</v>
-      </c>
-      <c r="AG193">
-        <v>1.55</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ193">
-        <v>1.2</v>
-      </c>
       <c r="AK193">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="O195">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P195">
-        <v>2.69</v>
+        <v>5.53</v>
       </c>
       <c r="Q195">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="R195">
         <v>1.99</v>
       </c>
       <c r="S195">
+        <v>1.4</v>
+      </c>
+      <c r="T195">
+        <v>2.5</v>
+      </c>
+      <c r="U195">
+        <v>3</v>
+      </c>
+      <c r="V195">
+        <v>1.3</v>
+      </c>
+      <c r="W195">
+        <v>1.05</v>
+      </c>
+      <c r="X195">
+        <v>1.05</v>
+      </c>
+      <c r="Y195">
         <v>1.36</v>
       </c>
-      <c r="T195">
-        <v>2.63</v>
-      </c>
-      <c r="U195">
-        <v>2.7</v>
-      </c>
-      <c r="V195">
-        <v>1.4</v>
-      </c>
-      <c r="W195">
-        <v>1.08</v>
-      </c>
-      <c r="X195">
-        <v>1</v>
-      </c>
-      <c r="Y195">
-        <v>1.31</v>
-      </c>
       <c r="Z195">
-        <v>3.24</v>
+        <v>2.69</v>
       </c>
       <c r="AA195">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AB195">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC195">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="AD195">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE195">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF195">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AG195">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK195">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,31 +34213,31 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.09</v>
+        <v>3.3</v>
       </c>
       <c r="O208">
         <v>3.15</v>
       </c>
       <c r="P208">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="Q208">
-        <v>2.62</v>
+        <v>4.01</v>
       </c>
       <c r="R208">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S208">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T208">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="U208">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V208">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W208">
         <v>1.07</v>
@@ -34246,31 +34246,31 @@
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z208">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA208">
+        <v>1.88</v>
+      </c>
+      <c r="AB208">
         <v>1.81</v>
       </c>
-      <c r="AB208">
-        <v>1.88</v>
-      </c>
       <c r="AC208">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AD208">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE208">
         <v>1.07</v>
       </c>
       <c r="AF208">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AG208">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK208">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,31 +34376,31 @@
         </is>
       </c>
       <c r="N209">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="O209">
         <v>3.15</v>
       </c>
       <c r="P209">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="Q209">
-        <v>4.01</v>
+        <v>2.62</v>
       </c>
       <c r="R209">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S209">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T209">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U209">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V209">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W209">
         <v>1.07</v>
@@ -34409,31 +34409,31 @@
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z209">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA209">
+        <v>1.81</v>
+      </c>
+      <c r="AB209">
         <v>1.88</v>
       </c>
-      <c r="AB209">
-        <v>1.81</v>
-      </c>
       <c r="AC209">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD209">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE209">
         <v>1.07</v>
       </c>
       <c r="AF209">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG209">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK209">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -44180,7 +44180,7 @@
         <v>2.4</v>
       </c>
       <c r="V269">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W269">
         <v>1.11</v>
@@ -45137,16 +45137,16 @@
         <v>1.75</v>
       </c>
       <c r="O275">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P275">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q275">
         <v>2.3</v>
       </c>
       <c r="R275">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S275">
         <v>1.38</v>
@@ -45155,10 +45155,10 @@
         <v>2.85</v>
       </c>
       <c r="U275">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="V275">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W275">
         <v>1.08</v>
@@ -45170,7 +45170,7 @@
         <v>1.24</v>
       </c>
       <c r="Z275">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="AA275">
         <v>1.9</v>
@@ -45188,10 +45188,10 @@
         <v>1.07</v>
       </c>
       <c r="AF275">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG275">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>2.87</v>
       </c>
       <c r="P277">
-        <v>4.2</v>
+        <v>4.48</v>
       </c>
       <c r="Q277">
         <v>2.5</v>
@@ -45511,7 +45511,7 @@
         <v>1.12</v>
       </c>
       <c r="AE277">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF277">
         <v>2.25</v>
@@ -45949,10 +45949,10 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="O280">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="P280">
         <v>2.2</v>
@@ -45964,28 +45964,28 @@
         <v>2.12</v>
       </c>
       <c r="S280">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T280">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U280">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="V280">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W280">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X280">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y280">
         <v>1.2</v>
       </c>
       <c r="Z280">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA280">
         <v>1.81</v>
@@ -46006,7 +46006,7 @@
         <v>1.64</v>
       </c>
       <c r="AG280">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AK280">
         <v>1.36</v>
@@ -46764,16 +46764,16 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="O285">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P285">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="Q285">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R285">
         <v>2.5</v>
@@ -46809,7 +46809,7 @@
         <v>2.27</v>
       </c>
       <c r="AC285">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AD285">
         <v>1.55</v>
@@ -46821,7 +46821,7 @@
         <v>1.57</v>
       </c>
       <c r="AG285">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK285">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="O288">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="P288">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q288">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R288">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S288">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T288">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U288">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V288">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W288">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X288">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y288">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z288">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AA288">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB288">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC288">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD288">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE288">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF288">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG288">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK288">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
+        <v>1.98</v>
+      </c>
+      <c r="O289">
         <v>2.62</v>
       </c>
-      <c r="O289">
-        <v>2.9</v>
-      </c>
       <c r="P289">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q289">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="R289">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S289">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T289">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U289">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V289">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W289">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
         <v>1.07</v>
       </c>
       <c r="Y289">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z289">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AA289">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB289">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC289">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD289">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE289">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF289">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG289">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK289">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -48400,7 +48400,7 @@
         <v>3.4</v>
       </c>
       <c r="P295">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q295">
         <v>2.55</v>
@@ -48467,7 +48467,7 @@
         <v>1.25</v>
       </c>
       <c r="AK295">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O296">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P296">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="Q296">
         <v>2.41</v>
@@ -48614,7 +48614,7 @@
         <v>1.91</v>
       </c>
       <c r="AG296">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>4.6</v>
       </c>
       <c r="O299">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P299">
         <v>1.5</v>
@@ -49082,13 +49082,13 @@
         <v>1.06</v>
       </c>
       <c r="Z299">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="AA299">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB299">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AC299">
         <v>1.92</v>
@@ -49103,7 +49103,7 @@
         <v>1.44</v>
       </c>
       <c r="AG299">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49375,7 +49375,7 @@
         <v>2.2</v>
       </c>
       <c r="O301">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="P301">
         <v>3.4</v>
@@ -49414,7 +49414,7 @@
         <v>3.1</v>
       </c>
       <c r="AB301">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC301">
         <v>6.4</v>
@@ -49535,16 +49535,16 @@
         </is>
       </c>
       <c r="N302">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O302">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P302">
         <v>3.4</v>
       </c>
       <c r="Q302">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="R302">
         <v>1.95</v>
@@ -49605,7 +49605,7 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK302">
         <v>1.66</v>
@@ -49707,7 +49707,7 @@
         <v>4.1</v>
       </c>
       <c r="Q303">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="R303">
         <v>1.85</v>
@@ -49719,7 +49719,7 @@
         <v>2.14</v>
       </c>
       <c r="U303">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V303">
         <v>1.15</v>
@@ -49731,10 +49731,10 @@
         <v>1.09</v>
       </c>
       <c r="Y303">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Z303">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AA303">
         <v>3.4</v>
@@ -49743,7 +49743,7 @@
         <v>1.3</v>
       </c>
       <c r="AC303">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="AD303">
         <v>1.05</v>
@@ -49752,7 +49752,7 @@
         <v>1.03</v>
       </c>
       <c r="AF303">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG303">
         <v>1.5</v>
@@ -49867,7 +49867,7 @@
         <v>3.25</v>
       </c>
       <c r="P304">
-        <v>5</v>
+        <v>5.59</v>
       </c>
       <c r="Q304">
         <v>2.26</v>
@@ -49879,7 +49879,7 @@
         <v>1.57</v>
       </c>
       <c r="T304">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="U304">
         <v>3.5</v>
@@ -49934,7 +49934,7 @@
         <v>1.14</v>
       </c>
       <c r="AK304">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -51494,10 +51494,10 @@
         <v>3.9</v>
       </c>
       <c r="O314">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P314">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="Q314">
         <v>3.75</v>
@@ -51518,7 +51518,7 @@
         <v>1.57</v>
       </c>
       <c r="W314">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X314">
         <v>1.01</v>
@@ -51527,22 +51527,22 @@
         <v>1.11</v>
       </c>
       <c r="Z314">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA314">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB314">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC314">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD314">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE314">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF314">
         <v>1.55</v>
@@ -51564,7 +51564,7 @@
         <v>1.98</v>
       </c>
       <c r="AK314">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O316">
         <v>2.85</v>
       </c>
       <c r="P316">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q316">
         <v>3.75</v>
@@ -51862,7 +51862,7 @@
         <v>1.36</v>
       </c>
       <c r="AC316">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="AD316">
         <v>1.08</v>
@@ -51980,16 +51980,16 @@
         </is>
       </c>
       <c r="N317">
-        <v>4.98</v>
+        <v>5.65</v>
       </c>
       <c r="O317">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P317">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Q317">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R317">
         <v>2.55</v>
@@ -52001,10 +52001,10 @@
         <v>3.9</v>
       </c>
       <c r="U317">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V317">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W317">
         <v>1.17</v>
@@ -52028,16 +52028,16 @@
         <v>2.1</v>
       </c>
       <c r="AD317">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AE317">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF317">
         <v>1.56</v>
       </c>
       <c r="AG317">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.06</v>
+        <v>2.52</v>
       </c>
       <c r="AK317">
         <v>1.13</v>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O318">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="P318">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q318">
         <v>2.8</v>
@@ -52158,49 +52158,49 @@
         <v>2.28</v>
       </c>
       <c r="S318">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T318">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U318">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="V318">
         <v>1.5</v>
       </c>
       <c r="W318">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X318">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y318">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z318">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AA318">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB318">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AC318">
         <v>2.59</v>
       </c>
       <c r="AD318">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE318">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF318">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG318">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AK318">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52312,7 +52312,7 @@
         <v>3.3</v>
       </c>
       <c r="P319">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q319">
         <v>4</v>
@@ -52321,7 +52321,7 @@
         <v>2.05</v>
       </c>
       <c r="S319">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T319">
         <v>2.7</v>
@@ -52339,31 +52339,31 @@
         <v>1.02</v>
       </c>
       <c r="Y319">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z319">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA319">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AB319">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC319">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="AD319">
         <v>1.23</v>
       </c>
       <c r="AE319">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF319">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AG319">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK319">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52469,7 +52469,7 @@
         </is>
       </c>
       <c r="N320">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="O320">
         <v>3.4</v>
@@ -52493,7 +52493,7 @@
         <v>2.65</v>
       </c>
       <c r="V320">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W320">
         <v>1.1</v>
@@ -52508,10 +52508,10 @@
         <v>3.3</v>
       </c>
       <c r="AA320">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB320">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC320">
         <v>3.25</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="O323">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P323">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="Q323">
         <v>1.53</v>
@@ -52979,7 +52979,7 @@
         <v>4.4</v>
       </c>
       <c r="U323">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V323">
         <v>1.73</v>
@@ -52994,28 +52994,28 @@
         <v>1.06</v>
       </c>
       <c r="Z323">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA323">
         <v>1.32</v>
       </c>
       <c r="AB323">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AC323">
         <v>1.85</v>
       </c>
       <c r="AD323">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE323">
         <v>1.33</v>
       </c>
       <c r="AF323">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG323">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O324">
         <v>3.6</v>
       </c>
       <c r="P324">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q324">
         <v>2.75</v>
@@ -53172,7 +53172,7 @@
         <v>1.39</v>
       </c>
       <c r="AE324">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF324">
         <v>1.53</v>
@@ -53287,13 +53287,13 @@
         <v>1.85</v>
       </c>
       <c r="O325">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="P325">
         <v>7.75</v>
       </c>
       <c r="Q325">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R325">
         <v>2.3</v>
@@ -53308,10 +53308,10 @@
         <v>2.87</v>
       </c>
       <c r="V325">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W325">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X325">
         <v>1.01</v>
@@ -53320,13 +53320,13 @@
         <v>1.25</v>
       </c>
       <c r="Z325">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="AA325">
+        <v>1.95</v>
+      </c>
+      <c r="AB325">
         <v>1.93</v>
-      </c>
-      <c r="AB325">
-        <v>1.85</v>
       </c>
       <c r="AC325">
         <v>3.12</v>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK325">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53450,16 +53450,16 @@
         <v>1.53</v>
       </c>
       <c r="O326">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P326">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q326">
         <v>2.1</v>
       </c>
       <c r="R326">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S326">
         <v>1.33</v>
@@ -53483,7 +53483,7 @@
         <v>1.22</v>
       </c>
       <c r="Z326">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AA326">
         <v>1.69</v>
@@ -53498,7 +53498,7 @@
         <v>1.42</v>
       </c>
       <c r="AE326">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF326">
         <v>1.7</v>
@@ -53610,19 +53610,19 @@
         </is>
       </c>
       <c r="N327">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="O327">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P327">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="Q327">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="R327">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S327">
         <v>1.29</v>
@@ -53634,7 +53634,7 @@
         <v>2.4</v>
       </c>
       <c r="V327">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W327">
         <v>1.11</v>
@@ -53646,28 +53646,28 @@
         <v>1.15</v>
       </c>
       <c r="Z327">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA327">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB327">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AC327">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD327">
         <v>1.4</v>
       </c>
       <c r="AE327">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF327">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG327">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53779,58 +53779,58 @@
         <v>4.05</v>
       </c>
       <c r="P328">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="Q328">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="R328">
         <v>2.4</v>
       </c>
       <c r="S328">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T328">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U328">
         <v>2.25</v>
       </c>
       <c r="V328">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W328">
         <v>1.12</v>
       </c>
       <c r="X328">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y328">
         <v>1.13</v>
       </c>
       <c r="Z328">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA328">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB328">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC328">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AD328">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE328">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF328">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG328">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>1.15</v>
       </c>
       <c r="AK328">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O329">
-        <v>3.03</v>
+        <v>3.6</v>
       </c>
       <c r="P329">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="Q329">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="R329">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S329">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T329">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U329">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="V329">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W329">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X329">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y329">
         <v>1.29</v>
       </c>
       <c r="Z329">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AA329">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB329">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC329">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="AD329">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE329">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF329">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG329">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK329">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G330">
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="O330">
+        <v>3.15</v>
+      </c>
+      <c r="P330">
         <v>3.4</v>
       </c>
-      <c r="P330">
-        <v>4.3</v>
-      </c>
       <c r="Q330">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="R330">
         <v>2.05</v>
       </c>
       <c r="S330">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T330">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U330">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="V330">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W330">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X330">
         <v>1.03</v>
       </c>
       <c r="Y330">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z330">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AA330">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB330">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC330">
-        <v>2.8</v>
+        <v>3.96</v>
       </c>
       <c r="AD330">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE330">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF330">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AG330">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK330">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54271,7 +54271,7 @@
         <v>0</v>
       </c>
       <c r="Q331">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R331">
         <v>2.25</v>
@@ -54283,13 +54283,13 @@
         <v>3.3</v>
       </c>
       <c r="U331">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V331">
         <v>1.45</v>
       </c>
       <c r="W331">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X331">
         <v>1.04</v>
@@ -54298,28 +54298,28 @@
         <v>1.19</v>
       </c>
       <c r="Z331">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AA331">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB331">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC331">
         <v>2.83</v>
       </c>
       <c r="AD331">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE331">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF331">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG331">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>
